--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F2C853-700D-47A2-8917-18E83836A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BC743B-7E84-465C-B11B-461790A89559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B95" s="2">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="F233" s="3"/>
     </row>
-    <row r="234" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B234" s="2">
         <f t="shared" si="3"/>
         <v>230</v>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F292" s="3"/>
     </row>
-    <row r="293" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B293" s="2">
         <f t="shared" si="4"/>
         <v>289</v>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="F514" s="3"/>
     </row>
-    <row r="515" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="515" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B515" s="2">
         <f t="shared" si="7"/>
         <v>511</v>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="F516" s="3"/>
     </row>
-    <row r="517" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="517" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B517" s="2">
         <f t="shared" si="7"/>
         <v>513</v>
@@ -12437,10 +12437,8 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="AL KHAN BAKERS (NESPAK)"/>
-        <filter val="Gourmet (Pak Arab)"/>
-        <filter val="ORGANICS (PAK HEIGHTS BUILDING)"/>
-        <filter val="PAK MADINA SUPER STORE (BEGAM KOT)"/>
+        <filter val="CROWN SUPER MARKET"/>
+        <filter val="EURO STORE CROWN BEHRIA TOWN"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BC743B-7E84-465C-B11B-461790A89559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7698ED03-3F02-4212-902B-24593C04FCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B82" s="2">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="F129" s="3"/>
     </row>
-    <row r="130" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B130" s="2">
         <f t="shared" si="1"/>
         <v>126</v>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="F176" s="3"/>
     </row>
-    <row r="177" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B177" s="2">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="F229" s="3"/>
     </row>
-    <row r="230" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B230" s="2">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="F233" s="3"/>
     </row>
-    <row r="234" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B234" s="2">
         <f t="shared" si="3"/>
         <v>230</v>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="F444" s="3"/>
     </row>
-    <row r="445" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B445" s="2">
         <f t="shared" si="6"/>
         <v>441</v>
@@ -12437,8 +12437,12 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="CROWN SUPER MARKET"/>
-        <filter val="EURO STORE CROWN BEHRIA TOWN"/>
+        <filter val="Al Fatah (Lake City)"/>
+        <filter val="BASHIR SONS PHARMACY (LAKE CITY)"/>
+        <filter val="BUNDU KHAN LAKE CITY"/>
+        <filter val="CLINIX SUPERMARKET (LAKE CITY)"/>
+        <filter val="Jalal Sons (Lake City) 01"/>
+        <filter val="Lake City Management Pvt Ltd"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7698ED03-3F02-4212-902B-24593C04FCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9E15DF-828A-41BA-8F53-5E324092521B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B82" s="2">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="F129" s="3"/>
     </row>
-    <row r="130" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B130" s="2">
         <f t="shared" si="1"/>
         <v>126</v>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="F176" s="3"/>
     </row>
-    <row r="177" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B177" s="2">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="F229" s="3"/>
     </row>
-    <row r="230" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B230" s="2">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="F407" s="3"/>
     </row>
-    <row r="408" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B408" s="2">
         <f t="shared" si="6"/>
         <v>404</v>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="F408" s="3"/>
     </row>
-    <row r="409" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B409" s="2">
         <f t="shared" si="6"/>
         <v>405</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="F409" s="3"/>
     </row>
-    <row r="410" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B410" s="2">
         <f t="shared" si="6"/>
         <v>406</v>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="F410" s="3"/>
     </row>
-    <row r="411" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B411" s="2">
         <f t="shared" si="6"/>
         <v>407</v>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F411" s="3"/>
     </row>
-    <row r="412" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B412" s="2">
         <f t="shared" si="6"/>
         <v>408</v>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="F412" s="3"/>
     </row>
-    <row r="413" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B413" s="2">
         <f t="shared" si="6"/>
         <v>409</v>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="F413" s="3"/>
     </row>
-    <row r="414" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B414" s="2">
         <f t="shared" si="6"/>
         <v>410</v>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="F414" s="3"/>
     </row>
-    <row r="415" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B415" s="2">
         <f t="shared" si="6"/>
         <v>411</v>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B416" s="2">
         <f t="shared" si="6"/>
         <v>412</v>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="F416" s="3"/>
     </row>
-    <row r="417" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B417" s="2">
         <f t="shared" si="6"/>
         <v>413</v>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="F417" s="3"/>
     </row>
-    <row r="418" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B418" s="2">
         <f t="shared" si="6"/>
         <v>414</v>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B419" s="2">
         <f t="shared" si="6"/>
         <v>415</v>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="F419" s="3"/>
     </row>
-    <row r="420" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B420" s="2">
         <f t="shared" si="6"/>
         <v>416</v>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="F420" s="3"/>
     </row>
-    <row r="421" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B421" s="2">
         <f t="shared" si="6"/>
         <v>417</v>
@@ -9535,7 +9535,7 @@
       </c>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B422" s="2">
         <f t="shared" si="6"/>
         <v>418</v>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B423" s="2">
         <f t="shared" si="6"/>
         <v>419</v>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="F423" s="3"/>
     </row>
-    <row r="424" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B424" s="2">
         <f t="shared" si="6"/>
         <v>420</v>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="F424" s="3"/>
     </row>
-    <row r="425" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B425" s="2">
         <f t="shared" si="6"/>
         <v>421</v>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="F425" s="3"/>
     </row>
-    <row r="426" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B426" s="2">
         <f t="shared" si="6"/>
         <v>422</v>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B428" s="2">
         <f t="shared" si="6"/>
         <v>424</v>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B429" s="2">
         <f t="shared" si="6"/>
         <v>425</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B430" s="2">
         <f t="shared" si="6"/>
         <v>426</v>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B431" s="2">
         <f t="shared" si="6"/>
         <v>427</v>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="F431" s="3"/>
     </row>
-    <row r="432" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B432" s="2">
         <f t="shared" si="6"/>
         <v>428</v>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B433" s="2">
         <f t="shared" si="6"/>
         <v>429</v>
@@ -9727,7 +9727,7 @@
       </c>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B434" s="2">
         <f t="shared" si="6"/>
         <v>430</v>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="F434" s="3"/>
     </row>
-    <row r="435" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B435" s="2">
         <f t="shared" si="6"/>
         <v>431</v>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B436" s="2">
         <f t="shared" si="6"/>
         <v>432</v>
@@ -9775,7 +9775,7 @@
       </c>
       <c r="F436" s="3"/>
     </row>
-    <row r="437" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B437" s="2">
         <f t="shared" si="6"/>
         <v>433</v>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B438" s="2">
         <f t="shared" si="6"/>
         <v>434</v>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B439" s="2">
         <f t="shared" si="6"/>
         <v>435</v>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B440" s="2">
         <f t="shared" si="6"/>
         <v>436</v>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B441" s="2">
         <f t="shared" si="6"/>
         <v>437</v>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="F441" s="3"/>
     </row>
-    <row r="442" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B442" s="2">
         <f t="shared" si="6"/>
         <v>438</v>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="F444" s="3"/>
     </row>
-    <row r="445" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B445" s="2">
         <f t="shared" si="6"/>
         <v>441</v>
@@ -12437,12 +12437,41 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Al Fatah (Lake City)"/>
-        <filter val="BASHIR SONS PHARMACY (LAKE CITY)"/>
-        <filter val="BUNDU KHAN LAKE CITY"/>
-        <filter val="CLINIX SUPERMARKET (LAKE CITY)"/>
+        <filter val="JALAL SONS  (COLLEGE ROAD) 02"/>
+        <filter val="Jalal sons  (Izmair Town) 01"/>
+        <filter val="Jalal sons (Askari 10 F sector ) 01"/>
+        <filter val="JALAL SONS (ASKARI 11 B BLOCK) 02"/>
+        <filter val="JALAL SONS (AYUBIA) 02"/>
+        <filter val="JALAL SONS (Bahira Orchard) 01"/>
+        <filter val="Jalal Sons (Bahria Town)  01"/>
+        <filter val="JALAL SONS (C BLOCK MODEL TOWN) 02"/>
+        <filter val="JALAL SONS (DHA C BLOCK,PHASE 6) 02"/>
+        <filter val="JALAL SONS (DHA PH IV) 02"/>
+        <filter val="JALAL SONS (DHA PH V) 02"/>
+        <filter val="JALAL SONS (DHA Y BLOCK) 02"/>
+        <filter val="JALAL SONS (EME) 02"/>
+        <filter val="JALAL SONS (FAISAL TOWN) 02"/>
+        <filter val="Jalal Sons (H Block) 01"/>
+        <filter val="JALAL SONS (HUSSAIN CHOWK GULBERG III) 02"/>
+        <filter val="JALAL SONS (IQBAL TOWN) 02"/>
+        <filter val="Jalal Sons (J.T Shadewal) 01"/>
+        <filter val="JALAL SONS (JOHER TOWN) 02"/>
         <filter val="Jalal Sons (Lake City) 01"/>
-        <filter val="Lake City Management Pvt Ltd"/>
+        <filter val="Jalal sons (Main Market) 01"/>
+        <filter val="JALAL SONS (MODEL TOWN LINK ROAD) 02"/>
+        <filter val="Jalal Sons (PAF Market) 01 main Market"/>
+        <filter val="JALAL SONS (PARAGON CITY) 02"/>
+        <filter val="JALAL SONS (PH VI) 02"/>
+        <filter val="JALAL SONS (PHASE 8 EX PARK VIEW) 02"/>
+        <filter val="JALAL SONS (REVAZ GARDEN) 02"/>
+        <filter val="JALAL SONS (SHADMAN) 02"/>
+        <filter val="JALAL SONS (SHAUKAT KHANUM) 02"/>
+        <filter val="JALAL SONS (STATE LIFE) 02"/>
+        <filter val="JALAL SONS (TALWAR CHOWK) 02"/>
+        <filter val="JALAL SONS (VALENCIA TOWN) 02"/>
+        <filter val="JALAL SONS (WAPDA TOWN) 02"/>
+        <filter val="JALAL SONS (XX) 02"/>
+        <filter val="Jalal Sons Askari X (01)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9E15DF-828A-41BA-8F53-5E324092521B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC1644D-C2D8-4000-A929-5E2A8F5E1ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="F407" s="3"/>
     </row>
-    <row r="408" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B408" s="2">
         <f t="shared" si="6"/>
         <v>404</v>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="F408" s="3"/>
     </row>
-    <row r="409" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B409" s="2">
         <f t="shared" si="6"/>
         <v>405</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="F409" s="3"/>
     </row>
-    <row r="410" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B410" s="2">
         <f t="shared" si="6"/>
         <v>406</v>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="F410" s="3"/>
     </row>
-    <row r="411" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B411" s="2">
         <f t="shared" si="6"/>
         <v>407</v>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F411" s="3"/>
     </row>
-    <row r="412" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B412" s="2">
         <f t="shared" si="6"/>
         <v>408</v>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="F412" s="3"/>
     </row>
-    <row r="413" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B413" s="2">
         <f t="shared" si="6"/>
         <v>409</v>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="F413" s="3"/>
     </row>
-    <row r="414" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B414" s="2">
         <f t="shared" si="6"/>
         <v>410</v>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="F414" s="3"/>
     </row>
-    <row r="415" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B415" s="2">
         <f t="shared" si="6"/>
         <v>411</v>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B416" s="2">
         <f t="shared" si="6"/>
         <v>412</v>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="F416" s="3"/>
     </row>
-    <row r="417" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B417" s="2">
         <f t="shared" si="6"/>
         <v>413</v>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="F417" s="3"/>
     </row>
-    <row r="418" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B418" s="2">
         <f t="shared" si="6"/>
         <v>414</v>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B419" s="2">
         <f t="shared" si="6"/>
         <v>415</v>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="F419" s="3"/>
     </row>
-    <row r="420" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B420" s="2">
         <f t="shared" si="6"/>
         <v>416</v>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="F420" s="3"/>
     </row>
-    <row r="421" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B421" s="2">
         <f t="shared" si="6"/>
         <v>417</v>
@@ -9535,7 +9535,7 @@
       </c>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B422" s="2">
         <f t="shared" si="6"/>
         <v>418</v>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B423" s="2">
         <f t="shared" si="6"/>
         <v>419</v>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="F423" s="3"/>
     </row>
-    <row r="424" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B424" s="2">
         <f t="shared" si="6"/>
         <v>420</v>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="F424" s="3"/>
     </row>
-    <row r="425" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B425" s="2">
         <f t="shared" si="6"/>
         <v>421</v>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="F425" s="3"/>
     </row>
-    <row r="426" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B426" s="2">
         <f t="shared" si="6"/>
         <v>422</v>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B428" s="2">
         <f t="shared" si="6"/>
         <v>424</v>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B429" s="2">
         <f t="shared" si="6"/>
         <v>425</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B430" s="2">
         <f t="shared" si="6"/>
         <v>426</v>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B431" s="2">
         <f t="shared" si="6"/>
         <v>427</v>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="F431" s="3"/>
     </row>
-    <row r="432" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B432" s="2">
         <f t="shared" si="6"/>
         <v>428</v>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B433" s="2">
         <f t="shared" si="6"/>
         <v>429</v>
@@ -9727,7 +9727,7 @@
       </c>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B434" s="2">
         <f t="shared" si="6"/>
         <v>430</v>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="F434" s="3"/>
     </row>
-    <row r="435" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B435" s="2">
         <f t="shared" si="6"/>
         <v>431</v>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B436" s="2">
         <f t="shared" si="6"/>
         <v>432</v>
@@ -9775,7 +9775,7 @@
       </c>
       <c r="F436" s="3"/>
     </row>
-    <row r="437" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B437" s="2">
         <f t="shared" si="6"/>
         <v>433</v>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B438" s="2">
         <f t="shared" si="6"/>
         <v>434</v>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B439" s="2">
         <f t="shared" si="6"/>
         <v>435</v>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B440" s="2">
         <f t="shared" si="6"/>
         <v>436</v>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B441" s="2">
         <f t="shared" si="6"/>
         <v>437</v>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="F441" s="3"/>
     </row>
-    <row r="442" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B442" s="2">
         <f t="shared" si="6"/>
         <v>438</v>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="F595" s="3"/>
     </row>
-    <row r="596" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B596" s="2">
         <f t="shared" si="9"/>
         <v>592</v>
@@ -12437,41 +12437,7 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="JALAL SONS  (COLLEGE ROAD) 02"/>
-        <filter val="Jalal sons  (Izmair Town) 01"/>
-        <filter val="Jalal sons (Askari 10 F sector ) 01"/>
-        <filter val="JALAL SONS (ASKARI 11 B BLOCK) 02"/>
-        <filter val="JALAL SONS (AYUBIA) 02"/>
-        <filter val="JALAL SONS (Bahira Orchard) 01"/>
-        <filter val="Jalal Sons (Bahria Town)  01"/>
-        <filter val="JALAL SONS (C BLOCK MODEL TOWN) 02"/>
-        <filter val="JALAL SONS (DHA C BLOCK,PHASE 6) 02"/>
-        <filter val="JALAL SONS (DHA PH IV) 02"/>
-        <filter val="JALAL SONS (DHA PH V) 02"/>
-        <filter val="JALAL SONS (DHA Y BLOCK) 02"/>
-        <filter val="JALAL SONS (EME) 02"/>
-        <filter val="JALAL SONS (FAISAL TOWN) 02"/>
-        <filter val="Jalal Sons (H Block) 01"/>
-        <filter val="JALAL SONS (HUSSAIN CHOWK GULBERG III) 02"/>
-        <filter val="JALAL SONS (IQBAL TOWN) 02"/>
-        <filter val="Jalal Sons (J.T Shadewal) 01"/>
-        <filter val="JALAL SONS (JOHER TOWN) 02"/>
-        <filter val="Jalal Sons (Lake City) 01"/>
-        <filter val="Jalal sons (Main Market) 01"/>
-        <filter val="JALAL SONS (MODEL TOWN LINK ROAD) 02"/>
-        <filter val="Jalal Sons (PAF Market) 01 main Market"/>
-        <filter val="JALAL SONS (PARAGON CITY) 02"/>
-        <filter val="JALAL SONS (PH VI) 02"/>
-        <filter val="JALAL SONS (PHASE 8 EX PARK VIEW) 02"/>
-        <filter val="JALAL SONS (REVAZ GARDEN) 02"/>
-        <filter val="JALAL SONS (SHADMAN) 02"/>
-        <filter val="JALAL SONS (SHAUKAT KHANUM) 02"/>
-        <filter val="JALAL SONS (STATE LIFE) 02"/>
-        <filter val="JALAL SONS (TALWAR CHOWK) 02"/>
-        <filter val="JALAL SONS (VALENCIA TOWN) 02"/>
-        <filter val="JALAL SONS (WAPDA TOWN) 02"/>
-        <filter val="JALAL SONS (XX) 02"/>
-        <filter val="Jalal Sons Askari X (01)"/>
+        <filter val="VIP GENERAL STORE ZARAR SHAHEED ROAD"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC1644D-C2D8-4000-A929-5E2A8F5E1ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7065D3D2-5288-4AF9-8B81-F022C6D17155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="F313" s="3"/>
     </row>
-    <row r="314" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B314" s="2">
         <f t="shared" si="4"/>
         <v>310</v>
@@ -11519,7 +11519,7 @@
       </c>
       <c r="F545" s="3"/>
     </row>
-    <row r="546" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B546" s="2">
         <f t="shared" si="8"/>
         <v>542</v>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="F595" s="3"/>
     </row>
-    <row r="596" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="596" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B596" s="2">
         <f t="shared" si="9"/>
         <v>592</v>
@@ -12394,7 +12394,7 @@
     <row r="601" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C601" s="4"/>
     </row>
-    <row r="602" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B602" s="2">
         <v>509</v>
       </c>
@@ -12437,7 +12437,9 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="VIP GENERAL STORE ZARAR SHAHEED ROAD"/>
+        <filter val="Gourmet -Daram Pure"/>
+        <filter val="Nabeel Traders  SD Ramgher Mughalpura"/>
+        <filter val="RAMZAN CANTEEN RAILWAY STATION"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7065D3D2-5288-4AF9-8B81-F022C6D17155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1AC417-4819-475F-A10B-30C89D9C9E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="F313" s="3"/>
     </row>
-    <row r="314" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B314" s="2">
         <f t="shared" si="4"/>
         <v>310</v>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="F383" s="3"/>
     </row>
-    <row r="384" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B384" s="2">
         <f t="shared" si="5"/>
         <v>380</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="F537" s="3"/>
     </row>
-    <row r="538" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B538" s="2">
         <f t="shared" si="8"/>
         <v>534</v>
@@ -11407,7 +11407,7 @@
       </c>
       <c r="F538" s="3"/>
     </row>
-    <row r="539" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B539" s="2">
         <f t="shared" si="8"/>
         <v>535</v>
@@ -11423,7 +11423,7 @@
       </c>
       <c r="F539" s="3"/>
     </row>
-    <row r="540" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B540" s="2">
         <f t="shared" si="8"/>
         <v>536</v>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="F540" s="3"/>
     </row>
-    <row r="541" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B541" s="2">
         <f t="shared" si="8"/>
         <v>537</v>
@@ -11455,7 +11455,7 @@
       </c>
       <c r="F541" s="3"/>
     </row>
-    <row r="542" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B542" s="2">
         <f t="shared" si="8"/>
         <v>538</v>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="F542" s="3"/>
     </row>
-    <row r="543" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B543" s="2">
         <f t="shared" si="8"/>
         <v>539</v>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="F543" s="3"/>
     </row>
-    <row r="544" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B544" s="2">
         <f t="shared" si="8"/>
         <v>540</v>
@@ -11519,7 +11519,7 @@
       </c>
       <c r="F545" s="3"/>
     </row>
-    <row r="546" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="546" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B546" s="2">
         <f t="shared" si="8"/>
         <v>542</v>
@@ -12394,7 +12394,7 @@
     <row r="601" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C601" s="4"/>
     </row>
-    <row r="602" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="602" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B602" s="2">
         <v>509</v>
       </c>
@@ -12437,9 +12437,14 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Gourmet -Daram Pure"/>
-        <filter val="Nabeel Traders  SD Ramgher Mughalpura"/>
-        <filter val="RAMZAN CANTEEN RAILWAY STATION"/>
+        <filter val="GRAIN MART WAPDA TOWN"/>
+        <filter val="Rainbow ( DHA Rahbar )"/>
+        <filter val="Rainbow Bahria Town"/>
+        <filter val="RAINBOW CASH &amp; CARRY (MAIN BARKI ROAD)"/>
+        <filter val="Rainbow Cash And Carry (Shahdra)"/>
+        <filter val="Rainbow cash n carry - EME"/>
+        <filter val="Rainbow cash n carry - WT"/>
+        <filter val="Rainbow Faisal Town"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1AC417-4819-475F-A10B-30C89D9C9E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFBD1F2-0390-4D68-BCD6-A59B7617A9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="F383" s="3"/>
     </row>
-    <row r="384" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B384" s="2">
         <f t="shared" si="5"/>
         <v>380</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="F537" s="3"/>
     </row>
-    <row r="538" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="538" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B538" s="2">
         <f t="shared" si="8"/>
         <v>534</v>
@@ -11407,7 +11407,7 @@
       </c>
       <c r="F538" s="3"/>
     </row>
-    <row r="539" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="539" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B539" s="2">
         <f t="shared" si="8"/>
         <v>535</v>
@@ -11423,7 +11423,7 @@
       </c>
       <c r="F539" s="3"/>
     </row>
-    <row r="540" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="540" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B540" s="2">
         <f t="shared" si="8"/>
         <v>536</v>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="F540" s="3"/>
     </row>
-    <row r="541" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="541" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B541" s="2">
         <f t="shared" si="8"/>
         <v>537</v>
@@ -11455,7 +11455,7 @@
       </c>
       <c r="F541" s="3"/>
     </row>
-    <row r="542" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="542" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B542" s="2">
         <f t="shared" si="8"/>
         <v>538</v>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="F542" s="3"/>
     </row>
-    <row r="543" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="543" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B543" s="2">
         <f t="shared" si="8"/>
         <v>539</v>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="F543" s="3"/>
     </row>
-    <row r="544" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="544" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B544" s="2">
         <f t="shared" si="8"/>
         <v>540</v>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="F595" s="3"/>
     </row>
-    <row r="596" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B596" s="2">
         <f t="shared" si="9"/>
         <v>592</v>
@@ -12437,14 +12437,7 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="GRAIN MART WAPDA TOWN"/>
-        <filter val="Rainbow ( DHA Rahbar )"/>
-        <filter val="Rainbow Bahria Town"/>
-        <filter val="RAINBOW CASH &amp; CARRY (MAIN BARKI ROAD)"/>
-        <filter val="Rainbow Cash And Carry (Shahdra)"/>
-        <filter val="Rainbow cash n carry - EME"/>
-        <filter val="Rainbow cash n carry - WT"/>
-        <filter val="Rainbow Faisal Town"/>
+        <filter val="VIP GENERAL STORE ZARAR SHAHEED ROAD"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFBD1F2-0390-4D68-BCD6-A59B7617A9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BCC6C9-23A2-4830-8A99-FAC21EF4C4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B34" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B40" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B52" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B77" s="2">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="F109" s="3"/>
     </row>
-    <row r="110" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B110" s="2">
         <f t="shared" si="1"/>
         <v>106</v>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="F120" s="3"/>
     </row>
-    <row r="121" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B121" s="2">
         <f t="shared" si="1"/>
         <v>117</v>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="F130" s="3"/>
     </row>
-    <row r="131" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B131" s="2">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="F132" s="3"/>
     </row>
-    <row r="133" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B133" s="2">
         <f t="shared" si="1"/>
         <v>129</v>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="F163" s="3"/>
     </row>
-    <row r="164" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B164" s="2">
         <f t="shared" si="2"/>
         <v>160</v>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="F168" s="3"/>
     </row>
-    <row r="169" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B169" s="2">
         <f t="shared" si="2"/>
         <v>165</v>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="F178" s="3"/>
     </row>
-    <row r="179" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B179" s="2">
         <f t="shared" si="2"/>
         <v>175</v>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="F184" s="3"/>
     </row>
-    <row r="185" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B185" s="2">
         <f t="shared" si="2"/>
         <v>181</v>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="F190" s="3"/>
     </row>
-    <row r="191" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B191" s="2">
         <f t="shared" si="2"/>
         <v>187</v>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="F207" s="3"/>
     </row>
-    <row r="208" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B208" s="2">
         <f t="shared" si="3"/>
         <v>204</v>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="F216" s="3"/>
     </row>
-    <row r="217" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B217" s="2">
         <f t="shared" si="3"/>
         <v>213</v>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="F227" s="3"/>
     </row>
-    <row r="228" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B228" s="2">
         <f t="shared" si="3"/>
         <v>224</v>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="F230" s="3"/>
     </row>
-    <row r="231" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B231" s="2">
         <f t="shared" si="3"/>
         <v>227</v>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="F231" s="3"/>
     </row>
-    <row r="232" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B232" s="2">
         <f t="shared" si="3"/>
         <v>228</v>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="F232" s="3"/>
     </row>
-    <row r="233" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B233" s="2">
         <f t="shared" si="3"/>
         <v>229</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="F303" s="3"/>
     </row>
-    <row r="304" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B304" s="2">
         <f t="shared" si="4"/>
         <v>300</v>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="F326" s="3"/>
     </row>
-    <row r="327" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B327" s="2">
         <f t="shared" si="4"/>
         <v>323</v>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="F327" s="3"/>
     </row>
-    <row r="328" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B328" s="2">
         <f t="shared" si="4"/>
         <v>324</v>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="F332" s="3"/>
     </row>
-    <row r="333" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B333" s="2">
         <f t="shared" si="5"/>
         <v>329</v>
@@ -8287,7 +8287,7 @@
       </c>
       <c r="F343" s="3"/>
     </row>
-    <row r="344" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B344" s="2">
         <f t="shared" si="5"/>
         <v>340</v>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="F344" s="3"/>
     </row>
-    <row r="345" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B345" s="2">
         <f t="shared" si="5"/>
         <v>341</v>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="F345" s="3"/>
     </row>
-    <row r="346" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B346" s="2">
         <f t="shared" si="5"/>
         <v>342</v>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="F361" s="3"/>
     </row>
-    <row r="362" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B362" s="2">
         <f t="shared" si="5"/>
         <v>358</v>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="F375" s="3"/>
     </row>
-    <row r="376" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B376" s="2">
         <f t="shared" si="5"/>
         <v>372</v>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="F376" s="3"/>
     </row>
-    <row r="377" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B377" s="2">
         <f t="shared" si="5"/>
         <v>373</v>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="F381" s="3"/>
     </row>
-    <row r="382" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B382" s="2">
         <f t="shared" si="5"/>
         <v>378</v>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="F395" s="3"/>
     </row>
-    <row r="396" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B396" s="2">
         <f t="shared" si="6"/>
         <v>392</v>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="F444" s="3"/>
     </row>
-    <row r="445" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B445" s="2">
         <f t="shared" si="6"/>
         <v>441</v>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="F446" s="3"/>
     </row>
-    <row r="447" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B447" s="2">
         <f t="shared" si="6"/>
         <v>443</v>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="F450" s="3"/>
     </row>
-    <row r="451" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B451" s="2">
         <f t="shared" si="6"/>
         <v>447</v>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="F467" s="3"/>
     </row>
-    <row r="468" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B468" s="2">
         <f t="shared" si="7"/>
         <v>464</v>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="F484" s="3"/>
     </row>
-    <row r="485" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B485" s="2">
         <f t="shared" si="7"/>
         <v>481</v>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="F504" s="3"/>
     </row>
-    <row r="505" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B505" s="2">
         <f t="shared" si="7"/>
         <v>501</v>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="F505" s="3"/>
     </row>
-    <row r="506" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B506" s="2">
         <f t="shared" si="7"/>
         <v>502</v>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="F511" s="3"/>
     </row>
-    <row r="512" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B512" s="2">
         <f t="shared" si="7"/>
         <v>508</v>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="F516" s="3"/>
     </row>
-    <row r="517" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B517" s="2">
         <f t="shared" si="7"/>
         <v>513</v>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="F528" s="3"/>
     </row>
-    <row r="529" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B529" s="2">
         <f t="shared" si="8"/>
         <v>525</v>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="F555" s="3"/>
     </row>
-    <row r="556" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B556" s="2">
         <f t="shared" si="8"/>
         <v>552</v>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="F595" s="3"/>
     </row>
-    <row r="596" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="596" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B596" s="2">
         <f t="shared" si="9"/>
         <v>592</v>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="E599" s="5"/>
     </row>
-    <row r="600" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B600" s="6">
         <v>596</v>
       </c>
@@ -12394,7 +12394,7 @@
     <row r="601" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C601" s="4"/>
     </row>
-    <row r="602" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B602" s="2">
         <v>509</v>
       </c>
@@ -12437,7 +12437,54 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="VIP GENERAL STORE ZARAR SHAHEED ROAD"/>
+        <filter val="Ajmair Foods (Maulana Shaukat Ali Road LHR)"/>
+        <filter val="Ajmair Foods (Samanabad)"/>
+        <filter val="Ajmair Foods (Sham Nagar)"/>
+        <filter val="Ajmair Foods (Swami Nagar)"/>
+        <filter val="AJMAIR FOODS CANAL CITY"/>
+        <filter val="Ajmair Foods Pvt LTD Nadrabad"/>
+        <filter val="Al Buraq Departmental Store (Samnabad)"/>
+        <filter val="AL-Saad Super Mart  (GT Road Manawan)"/>
+        <filter val="BASHIR SONS (NAWAB TOWN)"/>
+        <filter val="BASHIR SONS PHARMACY (NAKHUDA CHOWK)"/>
+        <filter val="BASHIR SONS PHARMACY (RACHNA BLOCK)"/>
+        <filter val="BUNDU KHAN (SAMNABAD)"/>
+        <filter val="BUNDU KHAN (YATEEM KHANA)"/>
+        <filter val="BUNDU KHAN NASEER ABAD"/>
+        <filter val="BUNDU KHAN YOUHANABAD"/>
+        <filter val="Butt Sweet (Yuhannabad)"/>
+        <filter val="CHINAR MART (PHASE-5)"/>
+        <filter val="CLINIX PHARMACY (MAIN SAWAMI NAGAR ROAD)"/>
+        <filter val="CLINIX SUPERMARKET (CHOWK NAKHUDA)"/>
+        <filter val="CLINIX SUPERMARKET (MANAWAN)"/>
+        <filter val="CLINIX SUPERMARKET (SAMANABAD)"/>
+        <filter val="CLINIX SUPERMARKET (SHAM NAGAR)"/>
+        <filter val="GOURMET BAKERS (MANAWWAN)"/>
+        <filter val="Gourmet Ismail Nagar"/>
+        <filter val="Gourmet Jinnah Rd"/>
+        <filter val="Gourmet -Karishn nagar"/>
+        <filter val="Gourmet -Nadeem Sheed Rd"/>
+        <filter val="Gourmet Nadrabad"/>
+        <filter val="Gourmet Naseerabad"/>
+        <filter val="Gourmet -Samanabad"/>
+        <filter val="Gourmet -Yateem Khana"/>
+        <filter val="Gourmet Yohannabad"/>
+        <filter val="Gourmet-Canal View"/>
+        <filter val="HAJVERY FOODS (OG BAKERS KRISHAN NAGAR)"/>
+        <filter val="Lake City Management Pvt Ltd"/>
+        <filter val="LARAIB BAKERS &amp; SWEETS (YATEEM kHANA)"/>
+        <filter val="LARAIB BAKERS SWEETS (YOUHANABAD)"/>
+        <filter val="M/S AL- JANNAT ENTERPRISES"/>
+        <filter val="Madina Store (GhaziAbad)"/>
+        <filter val="Malmo Bakery Samnabad"/>
+        <filter val="Nabeel Traders  SD Ramgher Mughalpura"/>
+        <filter val="Naqshbandi Store"/>
+        <filter val="NEAMAT KHANA STORES (PRIVATE) LIMITED"/>
+        <filter val="Omega Mart (Youhanabad)"/>
+        <filter val="PAK MADINA SUPER STORE (BEGAM KOT)"/>
+        <filter val="PUNJAB CASH &amp; CARRY (MANAWAN)"/>
+        <filter val="Risen / Manawa _CB TRADERS"/>
+        <filter val="SANA CASH AND CARRY IQBAL AVENUE CANAL ROAD"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BCC6C9-23A2-4830-8A99-FAC21EF4C4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2A13F7-C68C-4AB2-AAD1-5D009D6A78A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B34" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B40" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B52" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B77" s="2">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="F109" s="3"/>
     </row>
-    <row r="110" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B110" s="2">
         <f t="shared" si="1"/>
         <v>106</v>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="F120" s="3"/>
     </row>
-    <row r="121" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B121" s="2">
         <f t="shared" si="1"/>
         <v>117</v>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="F130" s="3"/>
     </row>
-    <row r="131" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B131" s="2">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="F132" s="3"/>
     </row>
-    <row r="133" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B133" s="2">
         <f t="shared" si="1"/>
         <v>129</v>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="F163" s="3"/>
     </row>
-    <row r="164" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B164" s="2">
         <f t="shared" si="2"/>
         <v>160</v>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="F168" s="3"/>
     </row>
-    <row r="169" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B169" s="2">
         <f t="shared" si="2"/>
         <v>165</v>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="F178" s="3"/>
     </row>
-    <row r="179" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B179" s="2">
         <f t="shared" si="2"/>
         <v>175</v>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="F184" s="3"/>
     </row>
-    <row r="185" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B185" s="2">
         <f t="shared" si="2"/>
         <v>181</v>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="F190" s="3"/>
     </row>
-    <row r="191" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B191" s="2">
         <f t="shared" si="2"/>
         <v>187</v>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="F207" s="3"/>
     </row>
-    <row r="208" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B208" s="2">
         <f t="shared" si="3"/>
         <v>204</v>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="F216" s="3"/>
     </row>
-    <row r="217" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B217" s="2">
         <f t="shared" si="3"/>
         <v>213</v>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="F227" s="3"/>
     </row>
-    <row r="228" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B228" s="2">
         <f t="shared" si="3"/>
         <v>224</v>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="F230" s="3"/>
     </row>
-    <row r="231" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B231" s="2">
         <f t="shared" si="3"/>
         <v>227</v>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="F231" s="3"/>
     </row>
-    <row r="232" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B232" s="2">
         <f t="shared" si="3"/>
         <v>228</v>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="F232" s="3"/>
     </row>
-    <row r="233" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B233" s="2">
         <f t="shared" si="3"/>
         <v>229</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="F303" s="3"/>
     </row>
-    <row r="304" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B304" s="2">
         <f t="shared" si="4"/>
         <v>300</v>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="F326" s="3"/>
     </row>
-    <row r="327" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B327" s="2">
         <f t="shared" si="4"/>
         <v>323</v>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="F327" s="3"/>
     </row>
-    <row r="328" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B328" s="2">
         <f t="shared" si="4"/>
         <v>324</v>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="F332" s="3"/>
     </row>
-    <row r="333" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B333" s="2">
         <f t="shared" si="5"/>
         <v>329</v>
@@ -8287,7 +8287,7 @@
       </c>
       <c r="F343" s="3"/>
     </row>
-    <row r="344" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B344" s="2">
         <f t="shared" si="5"/>
         <v>340</v>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="F344" s="3"/>
     </row>
-    <row r="345" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B345" s="2">
         <f t="shared" si="5"/>
         <v>341</v>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="F345" s="3"/>
     </row>
-    <row r="346" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B346" s="2">
         <f t="shared" si="5"/>
         <v>342</v>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="F361" s="3"/>
     </row>
-    <row r="362" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B362" s="2">
         <f t="shared" si="5"/>
         <v>358</v>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="F375" s="3"/>
     </row>
-    <row r="376" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B376" s="2">
         <f t="shared" si="5"/>
         <v>372</v>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="F376" s="3"/>
     </row>
-    <row r="377" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="377" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B377" s="2">
         <f t="shared" si="5"/>
         <v>373</v>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="F381" s="3"/>
     </row>
-    <row r="382" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="382" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B382" s="2">
         <f t="shared" si="5"/>
         <v>378</v>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="F395" s="3"/>
     </row>
-    <row r="396" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B396" s="2">
         <f t="shared" si="6"/>
         <v>392</v>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="F444" s="3"/>
     </row>
-    <row r="445" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B445" s="2">
         <f t="shared" si="6"/>
         <v>441</v>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="F446" s="3"/>
     </row>
-    <row r="447" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="447" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B447" s="2">
         <f t="shared" si="6"/>
         <v>443</v>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="F450" s="3"/>
     </row>
-    <row r="451" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="451" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B451" s="2">
         <f t="shared" si="6"/>
         <v>447</v>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="F467" s="3"/>
     </row>
-    <row r="468" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="468" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B468" s="2">
         <f t="shared" si="7"/>
         <v>464</v>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="F484" s="3"/>
     </row>
-    <row r="485" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="485" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B485" s="2">
         <f t="shared" si="7"/>
         <v>481</v>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="F504" s="3"/>
     </row>
-    <row r="505" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="505" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B505" s="2">
         <f t="shared" si="7"/>
         <v>501</v>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="F505" s="3"/>
     </row>
-    <row r="506" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="506" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B506" s="2">
         <f t="shared" si="7"/>
         <v>502</v>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="F509" s="3"/>
     </row>
-    <row r="510" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B510" s="2">
         <f t="shared" si="7"/>
         <v>506</v>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="F511" s="3"/>
     </row>
-    <row r="512" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="512" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B512" s="2">
         <f t="shared" si="7"/>
         <v>508</v>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="F516" s="3"/>
     </row>
-    <row r="517" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="517" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B517" s="2">
         <f t="shared" si="7"/>
         <v>513</v>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="F528" s="3"/>
     </row>
-    <row r="529" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="529" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B529" s="2">
         <f t="shared" si="8"/>
         <v>525</v>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="F555" s="3"/>
     </row>
-    <row r="556" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="556" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B556" s="2">
         <f t="shared" si="8"/>
         <v>552</v>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F587" s="3"/>
     </row>
-    <row r="588" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B588" s="2">
         <f t="shared" si="9"/>
         <v>584</v>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="E599" s="5"/>
     </row>
-    <row r="600" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="600" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B600" s="6">
         <v>596</v>
       </c>
@@ -12394,7 +12394,7 @@
     <row r="601" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C601" s="4"/>
     </row>
-    <row r="602" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="602" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B602" s="2">
         <v>509</v>
       </c>
@@ -12437,54 +12437,9 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Ajmair Foods (Maulana Shaukat Ali Road LHR)"/>
-        <filter val="Ajmair Foods (Samanabad)"/>
-        <filter val="Ajmair Foods (Sham Nagar)"/>
-        <filter val="Ajmair Foods (Swami Nagar)"/>
-        <filter val="AJMAIR FOODS CANAL CITY"/>
-        <filter val="Ajmair Foods Pvt LTD Nadrabad"/>
-        <filter val="Al Buraq Departmental Store (Samnabad)"/>
-        <filter val="AL-Saad Super Mart  (GT Road Manawan)"/>
-        <filter val="BASHIR SONS (NAWAB TOWN)"/>
-        <filter val="BASHIR SONS PHARMACY (NAKHUDA CHOWK)"/>
-        <filter val="BASHIR SONS PHARMACY (RACHNA BLOCK)"/>
-        <filter val="BUNDU KHAN (SAMNABAD)"/>
-        <filter val="BUNDU KHAN (YATEEM KHANA)"/>
-        <filter val="BUNDU KHAN NASEER ABAD"/>
-        <filter val="BUNDU KHAN YOUHANABAD"/>
-        <filter val="Butt Sweet (Yuhannabad)"/>
-        <filter val="CHINAR MART (PHASE-5)"/>
-        <filter val="CLINIX PHARMACY (MAIN SAWAMI NAGAR ROAD)"/>
-        <filter val="CLINIX SUPERMARKET (CHOWK NAKHUDA)"/>
-        <filter val="CLINIX SUPERMARKET (MANAWAN)"/>
-        <filter val="CLINIX SUPERMARKET (SAMANABAD)"/>
-        <filter val="CLINIX SUPERMARKET (SHAM NAGAR)"/>
-        <filter val="GOURMET BAKERS (MANAWWAN)"/>
-        <filter val="Gourmet Ismail Nagar"/>
-        <filter val="Gourmet Jinnah Rd"/>
-        <filter val="Gourmet -Karishn nagar"/>
-        <filter val="Gourmet -Nadeem Sheed Rd"/>
-        <filter val="Gourmet Nadrabad"/>
-        <filter val="Gourmet Naseerabad"/>
-        <filter val="Gourmet -Samanabad"/>
-        <filter val="Gourmet -Yateem Khana"/>
-        <filter val="Gourmet Yohannabad"/>
-        <filter val="Gourmet-Canal View"/>
-        <filter val="HAJVERY FOODS (OG BAKERS KRISHAN NAGAR)"/>
-        <filter val="Lake City Management Pvt Ltd"/>
-        <filter val="LARAIB BAKERS &amp; SWEETS (YATEEM kHANA)"/>
-        <filter val="LARAIB BAKERS SWEETS (YOUHANABAD)"/>
-        <filter val="M/S AL- JANNAT ENTERPRISES"/>
-        <filter val="Madina Store (GhaziAbad)"/>
-        <filter val="Malmo Bakery Samnabad"/>
-        <filter val="Nabeel Traders  SD Ramgher Mughalpura"/>
-        <filter val="Naqshbandi Store"/>
-        <filter val="NEAMAT KHANA STORES (PRIVATE) LIMITED"/>
-        <filter val="Omega Mart (Youhanabad)"/>
-        <filter val="PAK MADINA SUPER STORE (BEGAM KOT)"/>
-        <filter val="PUNJAB CASH &amp; CARRY (MANAWAN)"/>
-        <filter val="Risen / Manawa _CB TRADERS"/>
-        <filter val="SANA CASH AND CARRY IQBAL AVENUE CANAL ROAD"/>
+        <filter val="Numan Store"/>
+        <filter val="Risen / Gajjumata _FR TRADERS"/>
+        <filter val="UMAIMA SUPER STORE IMPERIAL GARDEN"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2A13F7-C68C-4AB2-AAD1-5D009D6A78A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE3E8891-640E-48C3-8730-4669B1E1697E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B82" s="2">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B84" s="2">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="F129" s="3"/>
     </row>
-    <row r="130" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B130" s="2">
         <f t="shared" si="1"/>
         <v>126</v>
@@ -5295,7 +5295,7 @@
       </c>
       <c r="F156" s="3"/>
     </row>
-    <row r="157" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B157" s="2">
         <f t="shared" si="2"/>
         <v>153</v>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="F176" s="3"/>
     </row>
-    <row r="177" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B177" s="2">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="F208" s="3"/>
     </row>
-    <row r="209" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B209" s="2">
         <f t="shared" si="3"/>
         <v>205</v>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="F209" s="3"/>
     </row>
-    <row r="210" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B210" s="2">
         <f t="shared" si="3"/>
         <v>206</v>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="F229" s="3"/>
     </row>
-    <row r="230" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B230" s="2">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="F405" s="3"/>
     </row>
-    <row r="406" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B406" s="2">
         <f t="shared" si="6"/>
         <v>402</v>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B431" s="2">
         <f t="shared" si="6"/>
         <v>427</v>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="F444" s="3"/>
     </row>
-    <row r="445" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B445" s="2">
         <f t="shared" si="6"/>
         <v>441</v>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="F509" s="3"/>
     </row>
-    <row r="510" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="510" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B510" s="2">
         <f t="shared" si="7"/>
         <v>506</v>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F587" s="3"/>
     </row>
-    <row r="588" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="588" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B588" s="2">
         <f t="shared" si="9"/>
         <v>584</v>
@@ -12437,9 +12437,19 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Numan Store"/>
-        <filter val="Risen / Gajjumata _FR TRADERS"/>
-        <filter val="UMAIMA SUPER STORE IMPERIAL GARDEN"/>
+        <filter val="AJMAIR FOODS CANAL CITY"/>
+        <filter val="Al Fatah (Lake City)"/>
+        <filter val="Al Fatah (Paragon City)"/>
+        <filter val="BASHIR SONS PHARMACY (LAKE CITY)"/>
+        <filter val="BUNDU KHAN (PARAGON CITY)"/>
+        <filter val="BUNDU KHAN LAKE CITY"/>
+        <filter val="CITY GENERAL STORE BEGUM KOT"/>
+        <filter val="CITY MART JURY PULL"/>
+        <filter val="CLINIX SUPERMARKET (LAKE CITY)"/>
+        <filter val="IDEAL MART EDEN CITY PH 8"/>
+        <filter val="Jalal Sons (Lake City) 01"/>
+        <filter val="JALAL SONS (PARAGON CITY) 02"/>
+        <filter val="Lake City Management Pvt Ltd"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE3E8891-640E-48C3-8730-4669B1E1697E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D079B6E7-FCB2-4698-834C-E16A1961BF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B82" s="2">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B84" s="2">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="F129" s="3"/>
     </row>
-    <row r="130" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B130" s="2">
         <f t="shared" si="1"/>
         <v>126</v>
@@ -5295,7 +5295,7 @@
       </c>
       <c r="F156" s="3"/>
     </row>
-    <row r="157" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B157" s="2">
         <f t="shared" si="2"/>
         <v>153</v>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="F176" s="3"/>
     </row>
-    <row r="177" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B177" s="2">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="F208" s="3"/>
     </row>
-    <row r="209" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B209" s="2">
         <f t="shared" si="3"/>
         <v>205</v>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="F209" s="3"/>
     </row>
-    <row r="210" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B210" s="2">
         <f t="shared" si="3"/>
         <v>206</v>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="F229" s="3"/>
     </row>
-    <row r="230" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B230" s="2">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="F241" s="3"/>
     </row>
-    <row r="242" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B242" s="2">
         <f t="shared" si="3"/>
         <v>238</v>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="F242" s="3"/>
     </row>
-    <row r="243" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B243" s="2">
         <f t="shared" si="3"/>
         <v>239</v>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="F405" s="3"/>
     </row>
-    <row r="406" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B406" s="2">
         <f t="shared" si="6"/>
         <v>402</v>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B431" s="2">
         <f t="shared" si="6"/>
         <v>427</v>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="F444" s="3"/>
     </row>
-    <row r="445" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B445" s="2">
         <f t="shared" si="6"/>
         <v>441</v>
@@ -12437,19 +12437,8 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="AJMAIR FOODS CANAL CITY"/>
-        <filter val="Al Fatah (Lake City)"/>
-        <filter val="Al Fatah (Paragon City)"/>
-        <filter val="BASHIR SONS PHARMACY (LAKE CITY)"/>
-        <filter val="BUNDU KHAN (PARAGON CITY)"/>
-        <filter val="BUNDU KHAN LAKE CITY"/>
-        <filter val="CITY GENERAL STORE BEGUM KOT"/>
-        <filter val="CITY MART JURY PULL"/>
-        <filter val="CLINIX SUPERMARKET (LAKE CITY)"/>
-        <filter val="IDEAL MART EDEN CITY PH 8"/>
-        <filter val="Jalal Sons (Lake City) 01"/>
-        <filter val="JALAL SONS (PARAGON CITY) 02"/>
-        <filter val="Lake City Management Pvt Ltd"/>
+        <filter val="Decent Dept Store (Wahdat)"/>
+        <filter val="Decent Store (Johar Town)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D079B6E7-FCB2-4698-834C-E16A1961BF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F34CC5-BAA4-4173-A10E-4038016BC194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="807">
   <si>
     <t>Sr#</t>
   </si>
@@ -2199,9 +2199,6 @@
     <t>Risen / TN Traders (Raiwind Road )</t>
   </si>
   <si>
-    <t>9402653</t>
-  </si>
-  <si>
     <t>SAFIA MANZOOR (LIAQAT CHOWK)</t>
   </si>
   <si>
@@ -2446,6 +2443,12 @@
   </si>
   <si>
     <t>2759936-5</t>
+  </si>
+  <si>
+    <t>9402653-2</t>
+  </si>
+  <si>
+    <t>327787628948-9</t>
   </si>
 </sst>
 </file>
@@ -2516,7 +2519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2538,6 +2541,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2845,10 +2851,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
     </row>
     <row r="4" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -4469,7 +4475,7 @@
         <v>101</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>90</v>
@@ -6655,7 +6661,7 @@
       </c>
       <c r="F241" s="3"/>
     </row>
-    <row r="242" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B242" s="2">
         <f t="shared" si="3"/>
         <v>238</v>
@@ -6671,7 +6677,7 @@
       </c>
       <c r="F242" s="3"/>
     </row>
-    <row r="243" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B243" s="2">
         <f t="shared" si="3"/>
         <v>239</v>
@@ -9669,7 +9675,7 @@
         <v>426</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D430" s="2" t="s">
         <v>524</v>
@@ -11343,7 +11349,7 @@
       </c>
       <c r="F534" s="3"/>
     </row>
-    <row r="535" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B535" s="2">
         <f t="shared" si="8"/>
         <v>531</v>
@@ -11640,10 +11646,10 @@
         <v>722</v>
       </c>
       <c r="D553" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="E553" s="1" t="s">
-        <v>5</v>
+        <v>805</v>
+      </c>
+      <c r="E553" s="13" t="s">
+        <v>806</v>
       </c>
       <c r="F553" s="3"/>
     </row>
@@ -11653,10 +11659,10 @@
         <v>550</v>
       </c>
       <c r="C554" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D554" s="2" t="s">
         <v>724</v>
-      </c>
-      <c r="D554" s="2" t="s">
-        <v>725</v>
       </c>
       <c r="E554" s="1" t="s">
         <v>5</v>
@@ -11669,10 +11675,10 @@
         <v>551</v>
       </c>
       <c r="C555" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="D555" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="D555" s="2" t="s">
-        <v>727</v>
       </c>
       <c r="E555" s="1" t="s">
         <v>5</v>
@@ -11685,10 +11691,10 @@
         <v>552</v>
       </c>
       <c r="C556" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="D556" s="2" t="s">
         <v>728</v>
-      </c>
-      <c r="D556" s="2" t="s">
-        <v>729</v>
       </c>
       <c r="E556" s="1" t="s">
         <v>5</v>
@@ -11701,10 +11707,10 @@
         <v>553</v>
       </c>
       <c r="C557" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="D557" s="2" t="s">
         <v>730</v>
-      </c>
-      <c r="D557" s="2" t="s">
-        <v>731</v>
       </c>
       <c r="E557" s="1" t="s">
         <v>5</v>
@@ -11717,10 +11723,10 @@
         <v>554</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E558" s="1" t="s">
         <v>5</v>
@@ -11733,10 +11739,10 @@
         <v>555</v>
       </c>
       <c r="C559" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>5</v>
@@ -11749,7 +11755,7 @@
         <v>556</v>
       </c>
       <c r="C560" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D560" s="2" t="s">
         <v>161</v>
@@ -11765,10 +11771,10 @@
         <v>557</v>
       </c>
       <c r="C561" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="D561" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="D561" s="2" t="s">
-        <v>736</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>5</v>
@@ -11781,10 +11787,10 @@
         <v>558</v>
       </c>
       <c r="C562" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="D562" s="2" t="s">
         <v>737</v>
-      </c>
-      <c r="D562" s="2" t="s">
-        <v>738</v>
       </c>
       <c r="E562" s="1" t="s">
         <v>5</v>
@@ -11797,10 +11803,10 @@
         <v>559</v>
       </c>
       <c r="C563" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="D563" s="2" t="s">
         <v>739</v>
-      </c>
-      <c r="D563" s="2" t="s">
-        <v>740</v>
       </c>
       <c r="E563" s="1" t="s">
         <v>5</v>
@@ -11813,10 +11819,10 @@
         <v>560</v>
       </c>
       <c r="C564" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E564" s="1" t="s">
         <v>5</v>
@@ -11829,10 +11835,10 @@
         <v>561</v>
       </c>
       <c r="C565" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E565" s="1" t="s">
         <v>5</v>
@@ -11845,10 +11851,10 @@
         <v>562</v>
       </c>
       <c r="C566" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E566" s="1" t="s">
         <v>5</v>
@@ -11861,10 +11867,10 @@
         <v>563</v>
       </c>
       <c r="C567" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E567" s="1" t="s">
         <v>5</v>
@@ -11877,10 +11883,10 @@
         <v>564</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D568" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E568" s="1" t="s">
         <v>5</v>
@@ -11893,10 +11899,10 @@
         <v>565</v>
       </c>
       <c r="C569" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D569" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E569" s="1" t="s">
         <v>5</v>
@@ -11909,10 +11915,10 @@
         <v>566</v>
       </c>
       <c r="C570" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D570" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E570" s="1" t="s">
         <v>5</v>
@@ -11925,10 +11931,10 @@
         <v>567</v>
       </c>
       <c r="C571" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D571" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E571" s="1" t="s">
         <v>5</v>
@@ -11941,10 +11947,10 @@
         <v>568</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E572" s="1" t="s">
         <v>5</v>
@@ -11957,10 +11963,10 @@
         <v>569</v>
       </c>
       <c r="C573" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E573" s="1" t="s">
         <v>5</v>
@@ -11973,10 +11979,10 @@
         <v>570</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E574" s="1" t="s">
         <v>5</v>
@@ -11989,10 +11995,10 @@
         <v>571</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E575" s="1" t="s">
         <v>5</v>
@@ -12005,10 +12011,10 @@
         <v>572</v>
       </c>
       <c r="C576" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E576" s="1" t="s">
         <v>5</v>
@@ -12021,10 +12027,10 @@
         <v>573</v>
       </c>
       <c r="C577" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="D577" s="2" t="s">
         <v>754</v>
-      </c>
-      <c r="D577" s="2" t="s">
-        <v>755</v>
       </c>
       <c r="E577" s="2" t="s">
         <v>5</v>
@@ -12037,10 +12043,10 @@
         <v>574</v>
       </c>
       <c r="C578" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D578" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="D578" s="2" t="s">
-        <v>757</v>
       </c>
       <c r="E578" s="1" t="s">
         <v>5</v>
@@ -12053,10 +12059,10 @@
         <v>575</v>
       </c>
       <c r="C579" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="D579" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="D579" s="2" t="s">
-        <v>759</v>
       </c>
       <c r="E579" s="1" t="s">
         <v>5</v>
@@ -12069,10 +12075,10 @@
         <v>576</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E580" s="1" t="s">
         <v>5</v>
@@ -12085,10 +12091,10 @@
         <v>577</v>
       </c>
       <c r="C581" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="D581" s="2" t="s">
         <v>761</v>
-      </c>
-      <c r="D581" s="2" t="s">
-        <v>762</v>
       </c>
       <c r="E581" s="1" t="s">
         <v>5</v>
@@ -12101,10 +12107,10 @@
         <v>578</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D582" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E582" s="7">
         <v>3520268948847</v>
@@ -12117,10 +12123,10 @@
         <v>579</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D583" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E583" s="1" t="s">
         <v>5</v>
@@ -12133,10 +12139,10 @@
         <v>580</v>
       </c>
       <c r="C584" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="D584" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="D584" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="E584" s="1" t="s">
         <v>5</v>
@@ -12149,10 +12155,10 @@
         <v>581</v>
       </c>
       <c r="C585" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="D585" s="2" t="s">
         <v>767</v>
-      </c>
-      <c r="D585" s="2" t="s">
-        <v>768</v>
       </c>
       <c r="E585" s="1" t="s">
         <v>5</v>
@@ -12165,10 +12171,10 @@
         <v>582</v>
       </c>
       <c r="C586" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D586" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E586" s="1" t="s">
         <v>5</v>
@@ -12181,10 +12187,10 @@
         <v>583</v>
       </c>
       <c r="C587" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="D587" s="2" t="s">
         <v>770</v>
-      </c>
-      <c r="D587" s="2" t="s">
-        <v>771</v>
       </c>
       <c r="E587" s="1" t="s">
         <v>5</v>
@@ -12197,10 +12203,10 @@
         <v>584</v>
       </c>
       <c r="C588" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="D588" s="2" t="s">
         <v>772</v>
-      </c>
-      <c r="D588" s="2" t="s">
-        <v>773</v>
       </c>
       <c r="E588" s="1" t="s">
         <v>5</v>
@@ -12213,10 +12219,10 @@
         <v>585</v>
       </c>
       <c r="C589" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="D589" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="D589" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="E589" s="1" t="s">
         <v>5</v>
@@ -12229,10 +12235,10 @@
         <v>586</v>
       </c>
       <c r="C590" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="D590" s="2" t="s">
         <v>776</v>
-      </c>
-      <c r="D590" s="2" t="s">
-        <v>777</v>
       </c>
       <c r="E590" s="1" t="s">
         <v>5</v>
@@ -12245,10 +12251,10 @@
         <v>587</v>
       </c>
       <c r="C591" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="D591" s="2" t="s">
         <v>778</v>
-      </c>
-      <c r="D591" s="2" t="s">
-        <v>779</v>
       </c>
       <c r="E591" s="1" t="s">
         <v>5</v>
@@ -12261,10 +12267,10 @@
         <v>588</v>
       </c>
       <c r="C592" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="D592" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="D592" s="2" t="s">
-        <v>781</v>
       </c>
       <c r="E592" s="1" t="s">
         <v>5</v>
@@ -12277,10 +12283,10 @@
         <v>589</v>
       </c>
       <c r="C593" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="D593" s="2" t="s">
         <v>782</v>
-      </c>
-      <c r="D593" s="2" t="s">
-        <v>783</v>
       </c>
       <c r="E593" s="1" t="s">
         <v>5</v>
@@ -12293,10 +12299,10 @@
         <v>590</v>
       </c>
       <c r="C594" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="D594" s="2" t="s">
         <v>784</v>
-      </c>
-      <c r="D594" s="2" t="s">
-        <v>785</v>
       </c>
       <c r="E594" s="1" t="s">
         <v>5</v>
@@ -12309,10 +12315,10 @@
         <v>591</v>
       </c>
       <c r="C595" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="D595" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="D595" s="2" t="s">
-        <v>787</v>
       </c>
       <c r="E595" s="1" t="s">
         <v>5</v>
@@ -12325,10 +12331,10 @@
         <v>592</v>
       </c>
       <c r="C596" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="D596" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="D596" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="E596" s="1" t="s">
         <v>5</v>
@@ -12341,10 +12347,10 @@
         <v>593</v>
       </c>
       <c r="C597" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="D597" s="2" t="s">
         <v>790</v>
-      </c>
-      <c r="D597" s="2" t="s">
-        <v>791</v>
       </c>
       <c r="E597" s="1" t="s">
         <v>5</v>
@@ -12357,10 +12363,10 @@
         <v>594</v>
       </c>
       <c r="C598" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="D598" s="2" t="s">
         <v>792</v>
-      </c>
-      <c r="D598" s="2" t="s">
-        <v>793</v>
       </c>
       <c r="E598" s="1" t="s">
         <v>5</v>
@@ -12372,10 +12378,10 @@
         <v>595</v>
       </c>
       <c r="C599" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="D599" s="2" t="s">
         <v>794</v>
-      </c>
-      <c r="D599" s="2" t="s">
-        <v>795</v>
       </c>
       <c r="E599" s="5"/>
     </row>
@@ -12384,10 +12390,10 @@
         <v>596</v>
       </c>
       <c r="C600" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="D600" s="6" t="s">
         <v>796</v>
-      </c>
-      <c r="D600" s="6" t="s">
-        <v>797</v>
       </c>
       <c r="E600" s="5"/>
     </row>
@@ -12399,10 +12405,10 @@
         <v>509</v>
       </c>
       <c r="C602" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D602" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="603" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
@@ -12410,10 +12416,10 @@
         <v>334</v>
       </c>
       <c r="C603" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="D603" t="s">
         <v>802</v>
-      </c>
-      <c r="D603" t="s">
-        <v>803</v>
       </c>
       <c r="E603" s="11">
         <v>3277876171384</v>
@@ -12424,10 +12430,10 @@
         <v>263</v>
       </c>
       <c r="C604" s="10" t="s">
+        <v>803</v>
+      </c>
+      <c r="D604" s="12" t="s">
         <v>804</v>
-      </c>
-      <c r="D604" s="12" t="s">
-        <v>805</v>
       </c>
       <c r="E604" s="11">
         <v>3520210170957</v>
@@ -12437,8 +12443,7 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Decent Dept Store (Wahdat)"/>
-        <filter val="Decent Store (Johar Town)"/>
+        <filter val="Raheem Store Iqbal Town"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F34CC5-BAA4-4173-A10E-4038016BC194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB8E337-FA04-4F2B-8ECD-C3C33BBFAF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1953,9 +1953,6 @@
     <t>1510459-1</t>
   </si>
   <si>
-    <t>NEAMAT KHANA STORES (PRIVATE) LIMITED</t>
-  </si>
-  <si>
     <t>5562800-8</t>
   </si>
   <si>
@@ -2449,6 +2446,9 @@
   </si>
   <si>
     <t>327787628948-9</t>
+  </si>
+  <si>
+    <t>NEMAT KHANA STORES (PRIVATE) LIMITED</t>
   </si>
 </sst>
 </file>
@@ -4475,7 +4475,7 @@
         <v>101</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>90</v>
@@ -9675,7 +9675,7 @@
         <v>426</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D430" s="2" t="s">
         <v>524</v>
@@ -10885,16 +10885,16 @@
       </c>
       <c r="F505" s="3"/>
     </row>
-    <row r="506" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B506" s="2">
         <f t="shared" si="7"/>
         <v>502</v>
       </c>
       <c r="C506" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="D506" s="2" t="s">
         <v>641</v>
-      </c>
-      <c r="D506" s="2" t="s">
-        <v>642</v>
       </c>
       <c r="E506" s="1" t="s">
         <v>5</v>
@@ -10907,10 +10907,10 @@
         <v>503</v>
       </c>
       <c r="C507" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="D507" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="D507" s="2" t="s">
-        <v>644</v>
       </c>
       <c r="E507" s="1" t="s">
         <v>5</v>
@@ -10923,10 +10923,10 @@
         <v>504</v>
       </c>
       <c r="C508" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="D508" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="D508" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="E508" s="1" t="s">
         <v>5</v>
@@ -10939,10 +10939,10 @@
         <v>505</v>
       </c>
       <c r="C509" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="D509" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="D509" s="2" t="s">
-        <v>648</v>
       </c>
       <c r="E509" s="1" t="s">
         <v>5</v>
@@ -10955,10 +10955,10 @@
         <v>506</v>
       </c>
       <c r="C510" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="D510" s="2" t="s">
         <v>649</v>
-      </c>
-      <c r="D510" s="2" t="s">
-        <v>650</v>
       </c>
       <c r="E510" s="1" t="s">
         <v>5</v>
@@ -10971,7 +10971,7 @@
         <v>507</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D511" s="2" t="s">
         <v>497</v>
@@ -10987,10 +10987,10 @@
         <v>508</v>
       </c>
       <c r="C512" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="D512" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="D512" s="2" t="s">
-        <v>653</v>
       </c>
       <c r="E512" s="1" t="s">
         <v>5</v>
@@ -11003,10 +11003,10 @@
         <v>509</v>
       </c>
       <c r="C513" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D513" s="2" t="s">
         <v>654</v>
-      </c>
-      <c r="D513" s="2" t="s">
-        <v>655</v>
       </c>
       <c r="E513" s="1" t="s">
         <v>5</v>
@@ -11019,10 +11019,10 @@
         <v>510</v>
       </c>
       <c r="C514" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="D514" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="D514" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="E514" s="1" t="s">
         <v>5</v>
@@ -11035,10 +11035,10 @@
         <v>511</v>
       </c>
       <c r="C515" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="D515" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="D515" s="2" t="s">
-        <v>659</v>
       </c>
       <c r="E515" s="1" t="s">
         <v>5</v>
@@ -11051,13 +11051,13 @@
         <v>512</v>
       </c>
       <c r="C516" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="D516" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E516" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="D516" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E516" s="2" t="s">
-        <v>661</v>
       </c>
       <c r="F516" s="3"/>
     </row>
@@ -11067,10 +11067,10 @@
         <v>513</v>
       </c>
       <c r="C517" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="D517" s="2" t="s">
         <v>662</v>
-      </c>
-      <c r="D517" s="2" t="s">
-        <v>663</v>
       </c>
       <c r="E517" s="1" t="s">
         <v>5</v>
@@ -11083,10 +11083,10 @@
         <v>514</v>
       </c>
       <c r="C518" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="D518" s="2" t="s">
         <v>664</v>
-      </c>
-      <c r="D518" s="2" t="s">
-        <v>665</v>
       </c>
       <c r="E518" s="1" t="s">
         <v>5</v>
@@ -11099,10 +11099,10 @@
         <v>515</v>
       </c>
       <c r="C519" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="D519" s="2" t="s">
         <v>666</v>
-      </c>
-      <c r="D519" s="2" t="s">
-        <v>667</v>
       </c>
       <c r="E519" s="1" t="s">
         <v>5</v>
@@ -11115,10 +11115,10 @@
         <v>516</v>
       </c>
       <c r="C520" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="D520" s="2" t="s">
         <v>668</v>
-      </c>
-      <c r="D520" s="2" t="s">
-        <v>669</v>
       </c>
       <c r="E520" s="1" t="s">
         <v>5</v>
@@ -11131,10 +11131,10 @@
         <v>517</v>
       </c>
       <c r="C521" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="D521" s="2" t="s">
         <v>670</v>
-      </c>
-      <c r="D521" s="2" t="s">
-        <v>671</v>
       </c>
       <c r="E521" s="1" t="s">
         <v>5</v>
@@ -11147,7 +11147,7 @@
         <v>518</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D522" s="2" t="s">
         <v>5</v>
@@ -11163,10 +11163,10 @@
         <v>519</v>
       </c>
       <c r="C523" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="D523" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="D523" s="2" t="s">
-        <v>674</v>
       </c>
       <c r="E523" s="1" t="s">
         <v>5</v>
@@ -11179,10 +11179,10 @@
         <v>520</v>
       </c>
       <c r="C524" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="D524" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="D524" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="E524" s="1" t="s">
         <v>5</v>
@@ -11195,10 +11195,10 @@
         <v>521</v>
       </c>
       <c r="C525" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="D525" s="2" t="s">
         <v>677</v>
-      </c>
-      <c r="D525" s="2" t="s">
-        <v>678</v>
       </c>
       <c r="E525" s="1" t="s">
         <v>5</v>
@@ -11211,10 +11211,10 @@
         <v>522</v>
       </c>
       <c r="C526" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="D526" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="D526" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="E526" s="1" t="s">
         <v>5</v>
@@ -11227,10 +11227,10 @@
         <v>523</v>
       </c>
       <c r="C527" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="D527" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="D527" s="2" t="s">
-        <v>682</v>
       </c>
       <c r="E527" s="1" t="s">
         <v>5</v>
@@ -11243,10 +11243,10 @@
         <v>524</v>
       </c>
       <c r="C528" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="D528" s="2" t="s">
         <v>683</v>
-      </c>
-      <c r="D528" s="2" t="s">
-        <v>684</v>
       </c>
       <c r="E528" s="1" t="s">
         <v>5</v>
@@ -11259,10 +11259,10 @@
         <v>525</v>
       </c>
       <c r="C529" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>5</v>
@@ -11275,7 +11275,7 @@
         <v>526</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D530" s="2" t="s">
         <v>5</v>
@@ -11291,10 +11291,10 @@
         <v>527</v>
       </c>
       <c r="C531" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="D531" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="D531" s="2" t="s">
-        <v>688</v>
       </c>
       <c r="E531" s="1" t="s">
         <v>5</v>
@@ -11307,10 +11307,10 @@
         <v>528</v>
       </c>
       <c r="C532" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="D532" s="2" t="s">
         <v>689</v>
-      </c>
-      <c r="D532" s="2" t="s">
-        <v>690</v>
       </c>
       <c r="E532" s="1" t="s">
         <v>5</v>
@@ -11323,10 +11323,10 @@
         <v>529</v>
       </c>
       <c r="C533" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="D533" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="D533" s="2" t="s">
-        <v>692</v>
       </c>
       <c r="E533" s="1" t="s">
         <v>5</v>
@@ -11339,26 +11339,26 @@
         <v>530</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D534" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E534" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F534" s="3"/>
     </row>
-    <row r="535" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="535" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B535" s="2">
         <f t="shared" si="8"/>
         <v>531</v>
       </c>
       <c r="C535" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="D535" s="2" t="s">
         <v>694</v>
-      </c>
-      <c r="D535" s="2" t="s">
-        <v>695</v>
       </c>
       <c r="E535" s="1" t="s">
         <v>5</v>
@@ -11371,10 +11371,10 @@
         <v>532</v>
       </c>
       <c r="C536" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="D536" s="2" t="s">
         <v>696</v>
-      </c>
-      <c r="D536" s="2" t="s">
-        <v>697</v>
       </c>
       <c r="E536" s="1" t="s">
         <v>5</v>
@@ -11387,10 +11387,10 @@
         <v>533</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D537" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E537" s="1" t="s">
         <v>5</v>
@@ -11403,10 +11403,10 @@
         <v>534</v>
       </c>
       <c r="C538" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="D538" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="D538" s="2" t="s">
-        <v>700</v>
       </c>
       <c r="E538" s="1" t="s">
         <v>5</v>
@@ -11419,10 +11419,10 @@
         <v>535</v>
       </c>
       <c r="C539" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E539" s="1" t="s">
         <v>5</v>
@@ -11435,10 +11435,10 @@
         <v>536</v>
       </c>
       <c r="C540" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D540" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E540" s="1" t="s">
         <v>5</v>
@@ -11451,10 +11451,10 @@
         <v>537</v>
       </c>
       <c r="C541" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D541" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E541" s="1" t="s">
         <v>5</v>
@@ -11467,10 +11467,10 @@
         <v>538</v>
       </c>
       <c r="C542" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D542" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E542" s="1" t="s">
         <v>5</v>
@@ -11483,10 +11483,10 @@
         <v>539</v>
       </c>
       <c r="C543" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D543" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E543" s="1" t="s">
         <v>5</v>
@@ -11499,10 +11499,10 @@
         <v>540</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D544" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E544" s="1" t="s">
         <v>5</v>
@@ -11515,10 +11515,10 @@
         <v>541</v>
       </c>
       <c r="C545" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="D545" s="2" t="s">
         <v>707</v>
-      </c>
-      <c r="D545" s="2" t="s">
-        <v>708</v>
       </c>
       <c r="E545" s="1" t="s">
         <v>5</v>
@@ -11531,13 +11531,13 @@
         <v>542</v>
       </c>
       <c r="C546" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="D546" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E546" s="2" t="s">
         <v>709</v>
-      </c>
-      <c r="D546" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E546" s="2" t="s">
-        <v>710</v>
       </c>
       <c r="F546" s="3"/>
     </row>
@@ -11547,13 +11547,13 @@
         <v>543</v>
       </c>
       <c r="C547" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="D547" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E547" s="2" t="s">
         <v>711</v>
-      </c>
-      <c r="D547" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E547" s="2" t="s">
-        <v>712</v>
       </c>
       <c r="F547" s="3"/>
     </row>
@@ -11563,10 +11563,10 @@
         <v>544</v>
       </c>
       <c r="C548" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="D548" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="D548" s="2" t="s">
-        <v>714</v>
       </c>
       <c r="E548" s="1" t="s">
         <v>5</v>
@@ -11579,10 +11579,10 @@
         <v>545</v>
       </c>
       <c r="C549" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="D549" s="2" t="s">
         <v>715</v>
-      </c>
-      <c r="D549" s="2" t="s">
-        <v>716</v>
       </c>
       <c r="E549" s="1" t="s">
         <v>5</v>
@@ -11595,10 +11595,10 @@
         <v>546</v>
       </c>
       <c r="C550" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="D550" s="2" t="s">
         <v>717</v>
-      </c>
-      <c r="D550" s="2" t="s">
-        <v>718</v>
       </c>
       <c r="E550" s="1" t="s">
         <v>5</v>
@@ -11611,7 +11611,7 @@
         <v>547</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D551" s="2" t="s">
         <v>587</v>
@@ -11627,10 +11627,10 @@
         <v>548</v>
       </c>
       <c r="C552" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="D552" s="2" t="s">
         <v>720</v>
-      </c>
-      <c r="D552" s="2" t="s">
-        <v>721</v>
       </c>
       <c r="E552" s="1" t="s">
         <v>5</v>
@@ -11643,13 +11643,13 @@
         <v>549</v>
       </c>
       <c r="C553" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D553" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="E553" s="13" t="s">
         <v>805</v>
-      </c>
-      <c r="E553" s="13" t="s">
-        <v>806</v>
       </c>
       <c r="F553" s="3"/>
     </row>
@@ -11659,10 +11659,10 @@
         <v>550</v>
       </c>
       <c r="C554" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="D554" s="2" t="s">
         <v>723</v>
-      </c>
-      <c r="D554" s="2" t="s">
-        <v>724</v>
       </c>
       <c r="E554" s="1" t="s">
         <v>5</v>
@@ -11675,10 +11675,10 @@
         <v>551</v>
       </c>
       <c r="C555" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="D555" s="2" t="s">
         <v>725</v>
-      </c>
-      <c r="D555" s="2" t="s">
-        <v>726</v>
       </c>
       <c r="E555" s="1" t="s">
         <v>5</v>
@@ -11691,10 +11691,10 @@
         <v>552</v>
       </c>
       <c r="C556" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="D556" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="D556" s="2" t="s">
-        <v>728</v>
       </c>
       <c r="E556" s="1" t="s">
         <v>5</v>
@@ -11707,10 +11707,10 @@
         <v>553</v>
       </c>
       <c r="C557" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="D557" s="2" t="s">
         <v>729</v>
-      </c>
-      <c r="D557" s="2" t="s">
-        <v>730</v>
       </c>
       <c r="E557" s="1" t="s">
         <v>5</v>
@@ -11723,10 +11723,10 @@
         <v>554</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E558" s="1" t="s">
         <v>5</v>
@@ -11739,10 +11739,10 @@
         <v>555</v>
       </c>
       <c r="C559" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>5</v>
@@ -11755,7 +11755,7 @@
         <v>556</v>
       </c>
       <c r="C560" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D560" s="2" t="s">
         <v>161</v>
@@ -11771,10 +11771,10 @@
         <v>557</v>
       </c>
       <c r="C561" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="D561" s="2" t="s">
         <v>734</v>
-      </c>
-      <c r="D561" s="2" t="s">
-        <v>735</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>5</v>
@@ -11787,10 +11787,10 @@
         <v>558</v>
       </c>
       <c r="C562" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="D562" s="2" t="s">
         <v>736</v>
-      </c>
-      <c r="D562" s="2" t="s">
-        <v>737</v>
       </c>
       <c r="E562" s="1" t="s">
         <v>5</v>
@@ -11803,10 +11803,10 @@
         <v>559</v>
       </c>
       <c r="C563" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="D563" s="2" t="s">
         <v>738</v>
-      </c>
-      <c r="D563" s="2" t="s">
-        <v>739</v>
       </c>
       <c r="E563" s="1" t="s">
         <v>5</v>
@@ -11819,10 +11819,10 @@
         <v>560</v>
       </c>
       <c r="C564" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E564" s="1" t="s">
         <v>5</v>
@@ -11835,10 +11835,10 @@
         <v>561</v>
       </c>
       <c r="C565" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E565" s="1" t="s">
         <v>5</v>
@@ -11851,10 +11851,10 @@
         <v>562</v>
       </c>
       <c r="C566" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E566" s="1" t="s">
         <v>5</v>
@@ -11867,10 +11867,10 @@
         <v>563</v>
       </c>
       <c r="C567" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E567" s="1" t="s">
         <v>5</v>
@@ -11883,10 +11883,10 @@
         <v>564</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D568" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E568" s="1" t="s">
         <v>5</v>
@@ -11899,10 +11899,10 @@
         <v>565</v>
       </c>
       <c r="C569" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D569" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E569" s="1" t="s">
         <v>5</v>
@@ -11915,10 +11915,10 @@
         <v>566</v>
       </c>
       <c r="C570" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D570" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E570" s="1" t="s">
         <v>5</v>
@@ -11931,10 +11931,10 @@
         <v>567</v>
       </c>
       <c r="C571" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D571" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E571" s="1" t="s">
         <v>5</v>
@@ -11947,10 +11947,10 @@
         <v>568</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E572" s="1" t="s">
         <v>5</v>
@@ -11963,10 +11963,10 @@
         <v>569</v>
       </c>
       <c r="C573" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E573" s="1" t="s">
         <v>5</v>
@@ -11979,10 +11979,10 @@
         <v>570</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E574" s="1" t="s">
         <v>5</v>
@@ -11995,10 +11995,10 @@
         <v>571</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E575" s="1" t="s">
         <v>5</v>
@@ -12011,10 +12011,10 @@
         <v>572</v>
       </c>
       <c r="C576" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E576" s="1" t="s">
         <v>5</v>
@@ -12027,10 +12027,10 @@
         <v>573</v>
       </c>
       <c r="C577" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="D577" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="D577" s="2" t="s">
-        <v>754</v>
       </c>
       <c r="E577" s="2" t="s">
         <v>5</v>
@@ -12043,10 +12043,10 @@
         <v>574</v>
       </c>
       <c r="C578" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="D578" s="2" t="s">
         <v>755</v>
-      </c>
-      <c r="D578" s="2" t="s">
-        <v>756</v>
       </c>
       <c r="E578" s="1" t="s">
         <v>5</v>
@@ -12059,10 +12059,10 @@
         <v>575</v>
       </c>
       <c r="C579" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="D579" s="2" t="s">
         <v>757</v>
-      </c>
-      <c r="D579" s="2" t="s">
-        <v>758</v>
       </c>
       <c r="E579" s="1" t="s">
         <v>5</v>
@@ -12075,10 +12075,10 @@
         <v>576</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E580" s="1" t="s">
         <v>5</v>
@@ -12091,10 +12091,10 @@
         <v>577</v>
       </c>
       <c r="C581" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="D581" s="2" t="s">
         <v>760</v>
-      </c>
-      <c r="D581" s="2" t="s">
-        <v>761</v>
       </c>
       <c r="E581" s="1" t="s">
         <v>5</v>
@@ -12107,10 +12107,10 @@
         <v>578</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D582" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E582" s="7">
         <v>3520268948847</v>
@@ -12123,10 +12123,10 @@
         <v>579</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D583" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E583" s="1" t="s">
         <v>5</v>
@@ -12139,10 +12139,10 @@
         <v>580</v>
       </c>
       <c r="C584" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="D584" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="D584" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="E584" s="1" t="s">
         <v>5</v>
@@ -12155,10 +12155,10 @@
         <v>581</v>
       </c>
       <c r="C585" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="D585" s="2" t="s">
         <v>766</v>
-      </c>
-      <c r="D585" s="2" t="s">
-        <v>767</v>
       </c>
       <c r="E585" s="1" t="s">
         <v>5</v>
@@ -12171,10 +12171,10 @@
         <v>582</v>
       </c>
       <c r="C586" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D586" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E586" s="1" t="s">
         <v>5</v>
@@ -12187,10 +12187,10 @@
         <v>583</v>
       </c>
       <c r="C587" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="D587" s="2" t="s">
         <v>769</v>
-      </c>
-      <c r="D587" s="2" t="s">
-        <v>770</v>
       </c>
       <c r="E587" s="1" t="s">
         <v>5</v>
@@ -12203,10 +12203,10 @@
         <v>584</v>
       </c>
       <c r="C588" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="D588" s="2" t="s">
         <v>771</v>
-      </c>
-      <c r="D588" s="2" t="s">
-        <v>772</v>
       </c>
       <c r="E588" s="1" t="s">
         <v>5</v>
@@ -12219,10 +12219,10 @@
         <v>585</v>
       </c>
       <c r="C589" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="D589" s="2" t="s">
         <v>773</v>
-      </c>
-      <c r="D589" s="2" t="s">
-        <v>774</v>
       </c>
       <c r="E589" s="1" t="s">
         <v>5</v>
@@ -12235,10 +12235,10 @@
         <v>586</v>
       </c>
       <c r="C590" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="D590" s="2" t="s">
         <v>775</v>
-      </c>
-      <c r="D590" s="2" t="s">
-        <v>776</v>
       </c>
       <c r="E590" s="1" t="s">
         <v>5</v>
@@ -12251,10 +12251,10 @@
         <v>587</v>
       </c>
       <c r="C591" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="D591" s="2" t="s">
         <v>777</v>
-      </c>
-      <c r="D591" s="2" t="s">
-        <v>778</v>
       </c>
       <c r="E591" s="1" t="s">
         <v>5</v>
@@ -12267,10 +12267,10 @@
         <v>588</v>
       </c>
       <c r="C592" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="D592" s="2" t="s">
         <v>779</v>
-      </c>
-      <c r="D592" s="2" t="s">
-        <v>780</v>
       </c>
       <c r="E592" s="1" t="s">
         <v>5</v>
@@ -12283,10 +12283,10 @@
         <v>589</v>
       </c>
       <c r="C593" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="D593" s="2" t="s">
         <v>781</v>
-      </c>
-      <c r="D593" s="2" t="s">
-        <v>782</v>
       </c>
       <c r="E593" s="1" t="s">
         <v>5</v>
@@ -12299,10 +12299,10 @@
         <v>590</v>
       </c>
       <c r="C594" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="D594" s="2" t="s">
         <v>783</v>
-      </c>
-      <c r="D594" s="2" t="s">
-        <v>784</v>
       </c>
       <c r="E594" s="1" t="s">
         <v>5</v>
@@ -12315,10 +12315,10 @@
         <v>591</v>
       </c>
       <c r="C595" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="D595" s="2" t="s">
         <v>785</v>
-      </c>
-      <c r="D595" s="2" t="s">
-        <v>786</v>
       </c>
       <c r="E595" s="1" t="s">
         <v>5</v>
@@ -12331,10 +12331,10 @@
         <v>592</v>
       </c>
       <c r="C596" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="D596" s="2" t="s">
         <v>787</v>
-      </c>
-      <c r="D596" s="2" t="s">
-        <v>788</v>
       </c>
       <c r="E596" s="1" t="s">
         <v>5</v>
@@ -12347,10 +12347,10 @@
         <v>593</v>
       </c>
       <c r="C597" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="D597" s="2" t="s">
         <v>789</v>
-      </c>
-      <c r="D597" s="2" t="s">
-        <v>790</v>
       </c>
       <c r="E597" s="1" t="s">
         <v>5</v>
@@ -12363,10 +12363,10 @@
         <v>594</v>
       </c>
       <c r="C598" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="D598" s="2" t="s">
         <v>791</v>
-      </c>
-      <c r="D598" s="2" t="s">
-        <v>792</v>
       </c>
       <c r="E598" s="1" t="s">
         <v>5</v>
@@ -12378,10 +12378,10 @@
         <v>595</v>
       </c>
       <c r="C599" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="D599" s="2" t="s">
         <v>793</v>
-      </c>
-      <c r="D599" s="2" t="s">
-        <v>794</v>
       </c>
       <c r="E599" s="5"/>
     </row>
@@ -12390,10 +12390,10 @@
         <v>596</v>
       </c>
       <c r="C600" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="D600" s="6" t="s">
         <v>795</v>
-      </c>
-      <c r="D600" s="6" t="s">
-        <v>796</v>
       </c>
       <c r="E600" s="5"/>
     </row>
@@ -12405,10 +12405,10 @@
         <v>509</v>
       </c>
       <c r="C602" s="4" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D602" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="603" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
@@ -12416,10 +12416,10 @@
         <v>334</v>
       </c>
       <c r="C603" s="10" t="s">
+        <v>800</v>
+      </c>
+      <c r="D603" t="s">
         <v>801</v>
-      </c>
-      <c r="D603" t="s">
-        <v>802</v>
       </c>
       <c r="E603" s="11">
         <v>3277876171384</v>
@@ -12430,10 +12430,10 @@
         <v>263</v>
       </c>
       <c r="C604" s="10" t="s">
+        <v>802</v>
+      </c>
+      <c r="D604" s="12" t="s">
         <v>803</v>
-      </c>
-      <c r="D604" s="12" t="s">
-        <v>804</v>
       </c>
       <c r="E604" s="11">
         <v>3520210170957</v>
@@ -12441,9 +12441,61 @@
     </row>
   </sheetData>
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="502"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="Raheem Store Iqbal Town"/>
+        <filter val="Ajmair Foods (Maulana Shaukat Ali Road LHR)"/>
+        <filter val="Ajmair Foods (Samanabad)"/>
+        <filter val="Ajmair Foods (Sham Nagar)"/>
+        <filter val="Ajmair Foods (Swami Nagar)"/>
+        <filter val="AJMAIR FOODS CANAL CITY"/>
+        <filter val="Ajmair Foods Pvt LTD Nadrabad"/>
+        <filter val="Al Buraq Departmental Store (Samnabad)"/>
+        <filter val="AL-Saad Super Mart  (GT Road Manawan)"/>
+        <filter val="BASHIR SONS (NAWAB TOWN)"/>
+        <filter val="BASHIR SONS PHARMACY (NAKHUDA CHOWK)"/>
+        <filter val="BASHIR SONS PHARMACY (RACHNA BLOCK)"/>
+        <filter val="BUNDU KHAN (SAMNABAD)"/>
+        <filter val="BUNDU KHAN (YATEEM KHANA)"/>
+        <filter val="BUNDU KHAN NASEER ABAD"/>
+        <filter val="BUNDU KHAN YOUHANABAD"/>
+        <filter val="Butt Sweet (Yuhannabad)"/>
+        <filter val="CHINAR MART (PHASE-5)"/>
+        <filter val="CLINIX PHARMACY (MAIN SAWAMI NAGAR ROAD)"/>
+        <filter val="CLINIX SUPERMARKET (CHOWK NAKHUDA)"/>
+        <filter val="CLINIX SUPERMARKET (MANAWAN)"/>
+        <filter val="CLINIX SUPERMARKET (SAMANABAD)"/>
+        <filter val="CLINIX SUPERMARKET (SHAM NAGAR)"/>
+        <filter val="GOURMET BAKERS (MANAWWAN)"/>
+        <filter val="Gourmet Ismail Nagar"/>
+        <filter val="Gourmet Jinnah Rd"/>
+        <filter val="Gourmet -Karishn nagar"/>
+        <filter val="Gourmet -Nadeem Sheed Rd"/>
+        <filter val="Gourmet Nadrabad"/>
+        <filter val="Gourmet Naseerabad"/>
+        <filter val="Gourmet -Samanabad"/>
+        <filter val="Gourmet -Yateem Khana"/>
+        <filter val="Gourmet Yohannabad"/>
+        <filter val="Gourmet-Canal View"/>
+        <filter val="HAJVERY FOODS (OG BAKERS KRISHAN NAGAR)"/>
+        <filter val="Lake City Management Pvt Ltd"/>
+        <filter val="LARAIB BAKERS &amp; SWEETS (YATEEM kHANA)"/>
+        <filter val="LARAIB BAKERS SWEETS (YOUHANABAD)"/>
+        <filter val="M/S AL- JANNAT ENTERPRISES"/>
+        <filter val="Madina Store (GhaziAbad)"/>
+        <filter val="Malmo Bakery Samnabad"/>
+        <filter val="Nabeel Traders  SD Ramgher Mughalpura"/>
+        <filter val="Naqshbandi Store"/>
+        <filter val="NEAMAT KHANA STORES (PRIVATE) LIMITED"/>
+        <filter val="Omega Mart (Youhanabad)"/>
+        <filter val="PAK MADINA SUPER STORE (BEGAM KOT)"/>
+        <filter val="PUNJAB CASH &amp; CARRY (MANAWAN)"/>
+        <filter val="Risen / Manawa _CB TRADERS"/>
+        <filter val="SANA CASH AND CARRY IQBAL AVENUE CANAL ROAD"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB8E337-FA04-4F2B-8ECD-C3C33BBFAF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E135435-D30A-4A9F-BC58-B6EC269E4015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="F407" s="3"/>
     </row>
-    <row r="408" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B408" s="2">
         <f t="shared" si="6"/>
         <v>404</v>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="F408" s="3"/>
     </row>
-    <row r="409" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B409" s="2">
         <f t="shared" si="6"/>
         <v>405</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="F409" s="3"/>
     </row>
-    <row r="410" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B410" s="2">
         <f t="shared" si="6"/>
         <v>406</v>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="F410" s="3"/>
     </row>
-    <row r="411" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B411" s="2">
         <f t="shared" si="6"/>
         <v>407</v>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F411" s="3"/>
     </row>
-    <row r="412" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B412" s="2">
         <f t="shared" si="6"/>
         <v>408</v>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="F412" s="3"/>
     </row>
-    <row r="413" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B413" s="2">
         <f t="shared" si="6"/>
         <v>409</v>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="F413" s="3"/>
     </row>
-    <row r="414" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B414" s="2">
         <f t="shared" si="6"/>
         <v>410</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="F414" s="3"/>
     </row>
-    <row r="415" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B415" s="2">
         <f t="shared" si="6"/>
         <v>411</v>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B416" s="2">
         <f t="shared" si="6"/>
         <v>412</v>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="F416" s="3"/>
     </row>
-    <row r="417" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B417" s="2">
         <f t="shared" si="6"/>
         <v>413</v>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="F417" s="3"/>
     </row>
-    <row r="418" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B418" s="2">
         <f t="shared" si="6"/>
         <v>414</v>
@@ -9493,7 +9493,7 @@
       </c>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B419" s="2">
         <f t="shared" si="6"/>
         <v>415</v>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="F419" s="3"/>
     </row>
-    <row r="420" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B420" s="2">
         <f t="shared" si="6"/>
         <v>416</v>
@@ -9525,7 +9525,7 @@
       </c>
       <c r="F420" s="3"/>
     </row>
-    <row r="421" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B421" s="2">
         <f t="shared" si="6"/>
         <v>417</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B422" s="2">
         <f t="shared" si="6"/>
         <v>418</v>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B423" s="2">
         <f t="shared" si="6"/>
         <v>419</v>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="F423" s="3"/>
     </row>
-    <row r="424" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B424" s="2">
         <f t="shared" si="6"/>
         <v>420</v>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="F424" s="3"/>
     </row>
-    <row r="425" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B425" s="2">
         <f t="shared" si="6"/>
         <v>421</v>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="F425" s="3"/>
     </row>
-    <row r="426" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B426" s="2">
         <f t="shared" si="6"/>
         <v>422</v>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B428" s="2">
         <f t="shared" si="6"/>
         <v>424</v>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B429" s="2">
         <f t="shared" si="6"/>
         <v>425</v>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B430" s="2">
         <f t="shared" si="6"/>
         <v>426</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B431" s="2">
         <f t="shared" si="6"/>
         <v>427</v>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="F431" s="3"/>
     </row>
-    <row r="432" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B432" s="2">
         <f t="shared" si="6"/>
         <v>428</v>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B433" s="2">
         <f t="shared" si="6"/>
         <v>429</v>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B434" s="2">
         <f t="shared" si="6"/>
         <v>430</v>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="F434" s="3"/>
     </row>
-    <row r="435" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B435" s="2">
         <f t="shared" si="6"/>
         <v>431</v>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B436" s="2">
         <f t="shared" si="6"/>
         <v>432</v>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="F436" s="3"/>
     </row>
-    <row r="437" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B437" s="2">
         <f t="shared" si="6"/>
         <v>433</v>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B438" s="2">
         <f t="shared" si="6"/>
         <v>434</v>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B439" s="2">
         <f t="shared" si="6"/>
         <v>435</v>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B440" s="2">
         <f t="shared" si="6"/>
         <v>436</v>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B441" s="2">
         <f t="shared" si="6"/>
         <v>437</v>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="F441" s="3"/>
     </row>
-    <row r="442" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B442" s="2">
         <f t="shared" si="6"/>
         <v>438</v>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="F505" s="3"/>
     </row>
-    <row r="506" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="506" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B506" s="2">
         <f t="shared" si="7"/>
         <v>502</v>
@@ -12441,61 +12441,43 @@
     </row>
   </sheetData>
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="502"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="Ajmair Foods (Maulana Shaukat Ali Road LHR)"/>
-        <filter val="Ajmair Foods (Samanabad)"/>
-        <filter val="Ajmair Foods (Sham Nagar)"/>
-        <filter val="Ajmair Foods (Swami Nagar)"/>
-        <filter val="AJMAIR FOODS CANAL CITY"/>
-        <filter val="Ajmair Foods Pvt LTD Nadrabad"/>
-        <filter val="Al Buraq Departmental Store (Samnabad)"/>
-        <filter val="AL-Saad Super Mart  (GT Road Manawan)"/>
-        <filter val="BASHIR SONS (NAWAB TOWN)"/>
-        <filter val="BASHIR SONS PHARMACY (NAKHUDA CHOWK)"/>
-        <filter val="BASHIR SONS PHARMACY (RACHNA BLOCK)"/>
-        <filter val="BUNDU KHAN (SAMNABAD)"/>
-        <filter val="BUNDU KHAN (YATEEM KHANA)"/>
-        <filter val="BUNDU KHAN NASEER ABAD"/>
-        <filter val="BUNDU KHAN YOUHANABAD"/>
-        <filter val="Butt Sweet (Yuhannabad)"/>
-        <filter val="CHINAR MART (PHASE-5)"/>
-        <filter val="CLINIX PHARMACY (MAIN SAWAMI NAGAR ROAD)"/>
-        <filter val="CLINIX SUPERMARKET (CHOWK NAKHUDA)"/>
-        <filter val="CLINIX SUPERMARKET (MANAWAN)"/>
-        <filter val="CLINIX SUPERMARKET (SAMANABAD)"/>
-        <filter val="CLINIX SUPERMARKET (SHAM NAGAR)"/>
-        <filter val="GOURMET BAKERS (MANAWWAN)"/>
-        <filter val="Gourmet Ismail Nagar"/>
-        <filter val="Gourmet Jinnah Rd"/>
-        <filter val="Gourmet -Karishn nagar"/>
-        <filter val="Gourmet -Nadeem Sheed Rd"/>
-        <filter val="Gourmet Nadrabad"/>
-        <filter val="Gourmet Naseerabad"/>
-        <filter val="Gourmet -Samanabad"/>
-        <filter val="Gourmet -Yateem Khana"/>
-        <filter val="Gourmet Yohannabad"/>
-        <filter val="Gourmet-Canal View"/>
-        <filter val="HAJVERY FOODS (OG BAKERS KRISHAN NAGAR)"/>
-        <filter val="Lake City Management Pvt Ltd"/>
-        <filter val="LARAIB BAKERS &amp; SWEETS (YATEEM kHANA)"/>
-        <filter val="LARAIB BAKERS SWEETS (YOUHANABAD)"/>
-        <filter val="M/S AL- JANNAT ENTERPRISES"/>
-        <filter val="Madina Store (GhaziAbad)"/>
-        <filter val="Malmo Bakery Samnabad"/>
-        <filter val="Nabeel Traders  SD Ramgher Mughalpura"/>
-        <filter val="Naqshbandi Store"/>
-        <filter val="NEAMAT KHANA STORES (PRIVATE) LIMITED"/>
-        <filter val="Omega Mart (Youhanabad)"/>
-        <filter val="PAK MADINA SUPER STORE (BEGAM KOT)"/>
-        <filter val="PUNJAB CASH &amp; CARRY (MANAWAN)"/>
-        <filter val="Risen / Manawa _CB TRADERS"/>
-        <filter val="SANA CASH AND CARRY IQBAL AVENUE CANAL ROAD"/>
+        <filter val="JALAL SONS  (COLLEGE ROAD) 02"/>
+        <filter val="Jalal sons  (Izmair Town) 01"/>
+        <filter val="Jalal sons (Askari 10 F sector ) 01"/>
+        <filter val="JALAL SONS (ASKARI 11 B BLOCK) 02"/>
+        <filter val="JALAL SONS (AYUBIA) 02"/>
+        <filter val="JALAL SONS (Bahira Orchard) 01"/>
+        <filter val="Jalal Sons (Bahria Town)  01"/>
+        <filter val="JALAL SONS (C BLOCK MODEL TOWN) 02"/>
+        <filter val="JALAL SONS (DHA C BLOCK,PHASE 6) 02"/>
+        <filter val="JALAL SONS (DHA PH IV) 02"/>
+        <filter val="JALAL SONS (DHA PH V) 02"/>
+        <filter val="JALAL SONS (DHA Y BLOCK) 02"/>
+        <filter val="JALAL SONS (EME) 02"/>
+        <filter val="JALAL SONS (FAISAL TOWN) 02"/>
+        <filter val="Jalal Sons (H Block) 01"/>
+        <filter val="JALAL SONS (HUSSAIN CHOWK GULBERG III) 02"/>
+        <filter val="JALAL SONS (IQBAL TOWN) 02"/>
+        <filter val="Jalal Sons (J.T Shadewal) 01"/>
+        <filter val="JALAL SONS (JOHER TOWN) 02"/>
+        <filter val="Jalal Sons (Lake City) 01"/>
+        <filter val="Jalal sons (Main Market) 01"/>
+        <filter val="JALAL SONS (MODEL TOWN LINK ROAD) 02"/>
+        <filter val="Jalal Sons (PAF Market) 01 main Market"/>
+        <filter val="JALAL SONS (PARAGON CITY) 02"/>
+        <filter val="JALAL SONS (PH VI) 02"/>
+        <filter val="JALAL SONS (PHASE 8 EX PARK VIEW) 02"/>
+        <filter val="JALAL SONS (REVAZ GARDEN) 02"/>
+        <filter val="JALAL SONS (SHADMAN) 02"/>
+        <filter val="JALAL SONS (SHAUKAT KHANUM) 02"/>
+        <filter val="JALAL SONS (STATE LIFE) 02"/>
+        <filter val="JALAL SONS (TALWAR CHOWK) 02"/>
+        <filter val="JALAL SONS (VALENCIA TOWN) 02"/>
+        <filter val="JALAL SONS (WAPDA TOWN) 02"/>
+        <filter val="JALAL SONS (XX) 02"/>
+        <filter val="Jalal Sons Askari X (01)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E135435-D30A-4A9F-BC58-B6EC269E4015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70484CE0-6121-4156-B20B-7CBC2A71CBF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70484CE0-6121-4156-B20B-7CBC2A71CBF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BE8089-ABEE-424F-935C-06E38FD354DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="F407" s="3"/>
     </row>
-    <row r="408" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B408" s="2">
         <f t="shared" si="6"/>
         <v>404</v>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="F408" s="3"/>
     </row>
-    <row r="409" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B409" s="2">
         <f t="shared" si="6"/>
         <v>405</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="F409" s="3"/>
     </row>
-    <row r="410" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B410" s="2">
         <f t="shared" si="6"/>
         <v>406</v>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="F410" s="3"/>
     </row>
-    <row r="411" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B411" s="2">
         <f t="shared" si="6"/>
         <v>407</v>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F411" s="3"/>
     </row>
-    <row r="412" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B412" s="2">
         <f t="shared" si="6"/>
         <v>408</v>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="F412" s="3"/>
     </row>
-    <row r="413" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B413" s="2">
         <f t="shared" si="6"/>
         <v>409</v>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="F413" s="3"/>
     </row>
-    <row r="414" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B414" s="2">
         <f t="shared" si="6"/>
         <v>410</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="F414" s="3"/>
     </row>
-    <row r="415" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B415" s="2">
         <f t="shared" si="6"/>
         <v>411</v>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B416" s="2">
         <f t="shared" si="6"/>
         <v>412</v>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="F416" s="3"/>
     </row>
-    <row r="417" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B417" s="2">
         <f t="shared" si="6"/>
         <v>413</v>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="F417" s="3"/>
     </row>
-    <row r="418" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B418" s="2">
         <f t="shared" si="6"/>
         <v>414</v>
@@ -9493,7 +9493,7 @@
       </c>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B419" s="2">
         <f t="shared" si="6"/>
         <v>415</v>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="F419" s="3"/>
     </row>
-    <row r="420" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B420" s="2">
         <f t="shared" si="6"/>
         <v>416</v>
@@ -9525,7 +9525,7 @@
       </c>
       <c r="F420" s="3"/>
     </row>
-    <row r="421" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B421" s="2">
         <f t="shared" si="6"/>
         <v>417</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B422" s="2">
         <f t="shared" si="6"/>
         <v>418</v>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B423" s="2">
         <f t="shared" si="6"/>
         <v>419</v>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="F423" s="3"/>
     </row>
-    <row r="424" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B424" s="2">
         <f t="shared" si="6"/>
         <v>420</v>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="F424" s="3"/>
     </row>
-    <row r="425" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B425" s="2">
         <f t="shared" si="6"/>
         <v>421</v>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="F425" s="3"/>
     </row>
-    <row r="426" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B426" s="2">
         <f t="shared" si="6"/>
         <v>422</v>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B428" s="2">
         <f t="shared" si="6"/>
         <v>424</v>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B429" s="2">
         <f t="shared" si="6"/>
         <v>425</v>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B430" s="2">
         <f t="shared" si="6"/>
         <v>426</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B431" s="2">
         <f t="shared" si="6"/>
         <v>427</v>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="F431" s="3"/>
     </row>
-    <row r="432" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B432" s="2">
         <f t="shared" si="6"/>
         <v>428</v>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B433" s="2">
         <f t="shared" si="6"/>
         <v>429</v>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B434" s="2">
         <f t="shared" si="6"/>
         <v>430</v>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="F434" s="3"/>
     </row>
-    <row r="435" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B435" s="2">
         <f t="shared" si="6"/>
         <v>431</v>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B436" s="2">
         <f t="shared" si="6"/>
         <v>432</v>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="F436" s="3"/>
     </row>
-    <row r="437" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B437" s="2">
         <f t="shared" si="6"/>
         <v>433</v>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B438" s="2">
         <f t="shared" si="6"/>
         <v>434</v>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B439" s="2">
         <f t="shared" si="6"/>
         <v>435</v>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B440" s="2">
         <f t="shared" si="6"/>
         <v>436</v>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B441" s="2">
         <f t="shared" si="6"/>
         <v>437</v>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="F441" s="3"/>
     </row>
-    <row r="442" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B442" s="2">
         <f t="shared" si="6"/>
         <v>438</v>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <f t="shared" si="7"/>
         <v>463</v>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <f t="shared" si="8"/>
         <v>547</v>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <f t="shared" si="8"/>
         <v>548</v>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <f t="shared" si="8"/>
         <v>549</v>
@@ -12443,41 +12443,12 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="JALAL SONS  (COLLEGE ROAD) 02"/>
-        <filter val="Jalal sons  (Izmair Town) 01"/>
-        <filter val="Jalal sons (Askari 10 F sector ) 01"/>
-        <filter val="JALAL SONS (ASKARI 11 B BLOCK) 02"/>
-        <filter val="JALAL SONS (AYUBIA) 02"/>
-        <filter val="JALAL SONS (Bahira Orchard) 01"/>
-        <filter val="Jalal Sons (Bahria Town)  01"/>
-        <filter val="JALAL SONS (C BLOCK MODEL TOWN) 02"/>
-        <filter val="JALAL SONS (DHA C BLOCK,PHASE 6) 02"/>
-        <filter val="JALAL SONS (DHA PH IV) 02"/>
-        <filter val="JALAL SONS (DHA PH V) 02"/>
-        <filter val="JALAL SONS (DHA Y BLOCK) 02"/>
-        <filter val="JALAL SONS (EME) 02"/>
-        <filter val="JALAL SONS (FAISAL TOWN) 02"/>
-        <filter val="Jalal Sons (H Block) 01"/>
-        <filter val="JALAL SONS (HUSSAIN CHOWK GULBERG III) 02"/>
-        <filter val="JALAL SONS (IQBAL TOWN) 02"/>
-        <filter val="Jalal Sons (J.T Shadewal) 01"/>
-        <filter val="JALAL SONS (JOHER TOWN) 02"/>
-        <filter val="Jalal Sons (Lake City) 01"/>
-        <filter val="Jalal sons (Main Market) 01"/>
-        <filter val="JALAL SONS (MODEL TOWN LINK ROAD) 02"/>
-        <filter val="Jalal Sons (PAF Market) 01 main Market"/>
-        <filter val="JALAL SONS (PARAGON CITY) 02"/>
-        <filter val="JALAL SONS (PH VI) 02"/>
-        <filter val="JALAL SONS (PHASE 8 EX PARK VIEW) 02"/>
-        <filter val="JALAL SONS (REVAZ GARDEN) 02"/>
-        <filter val="JALAL SONS (SHADMAN) 02"/>
-        <filter val="JALAL SONS (SHAUKAT KHANUM) 02"/>
-        <filter val="JALAL SONS (STATE LIFE) 02"/>
-        <filter val="JALAL SONS (TALWAR CHOWK) 02"/>
-        <filter val="JALAL SONS (VALENCIA TOWN) 02"/>
-        <filter val="JALAL SONS (WAPDA TOWN) 02"/>
-        <filter val="JALAL SONS (XX) 02"/>
-        <filter val="Jalal Sons Askari X (01)"/>
+        <filter val="M.S Traders Harbanspura (Risen)"/>
+        <filter val="Risen / Gajjumata _FR TRADERS"/>
+        <filter val="Risen / Manawa _CB TRADERS"/>
+        <filter val="Risen / Sabzazar _SZ TRADERS"/>
+        <filter val="Risen / Shadbagh _SB Traders"/>
+        <filter val="Risen / TN Traders (Raiwind Road )"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BE8089-ABEE-424F-935C-06E38FD354DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F6B0E2-82CC-4771-8434-8C0A37836C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <f t="shared" si="7"/>
         <v>463</v>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="F501" s="3"/>
     </row>
-    <row r="502" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B502" s="2">
         <f t="shared" si="7"/>
         <v>498</v>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <f t="shared" si="8"/>
         <v>547</v>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <f t="shared" si="8"/>
         <v>548</v>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <f t="shared" si="8"/>
         <v>549</v>
@@ -12443,12 +12443,7 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="M.S Traders Harbanspura (Risen)"/>
-        <filter val="Risen / Gajjumata _FR TRADERS"/>
-        <filter val="Risen / Manawa _CB TRADERS"/>
-        <filter val="Risen / Sabzazar _SZ TRADERS"/>
-        <filter val="Risen / Shadbagh _SB Traders"/>
-        <filter val="Risen / TN Traders (Raiwind Road )"/>
+        <filter val="MS RUBAIKA CASH AND CARRY"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F6B0E2-82CC-4771-8434-8C0A37836C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621461D6-72CF-41BD-82A0-FFB68FCD2C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <f t="shared" si="7"/>
         <v>463</v>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="F501" s="3"/>
     </row>
-    <row r="502" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="502" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B502" s="2">
         <f t="shared" si="7"/>
         <v>498</v>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <f t="shared" si="8"/>
         <v>547</v>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <f t="shared" si="8"/>
         <v>548</v>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <f t="shared" si="8"/>
         <v>549</v>
@@ -12443,7 +12443,12 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="MS RUBAIKA CASH AND CARRY"/>
+        <filter val="M.S Traders Harbanspura (Risen)"/>
+        <filter val="Risen / Gajjumata _FR TRADERS"/>
+        <filter val="Risen / Manawa _CB TRADERS"/>
+        <filter val="Risen / Sabzazar _SZ TRADERS"/>
+        <filter val="Risen / Shadbagh _SB Traders"/>
+        <filter val="Risen / TN Traders (Raiwind Road )"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621461D6-72CF-41BD-82A0-FFB68FCD2C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25898809-F3E7-4004-A90A-FE068C23CFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B246" s="2">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B247" s="2">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B248" s="2">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="F248" s="3"/>
     </row>
-    <row r="249" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B249" s="2">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B250" s="2">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6805,7 +6805,7 @@
       </c>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B251" s="2">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B252" s="2">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B253" s="2">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B256" s="2">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B257" s="2">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B258" s="2">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B259" s="2">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B260" s="2">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B261" s="2">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B262" s="2">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B263" s="2">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B264" s="2">
         <f t="shared" si="3"/>
         <v>260</v>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <f t="shared" si="7"/>
         <v>463</v>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <f t="shared" si="8"/>
         <v>547</v>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <f t="shared" si="8"/>
         <v>548</v>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <f t="shared" si="8"/>
         <v>549</v>
@@ -12443,12 +12443,25 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="M.S Traders Harbanspura (Risen)"/>
-        <filter val="Risen / Gajjumata _FR TRADERS"/>
-        <filter val="Risen / Manawa _CB TRADERS"/>
-        <filter val="Risen / Sabzazar _SZ TRADERS"/>
-        <filter val="Risen / Shadbagh _SB Traders"/>
-        <filter val="Risen / TN Traders (Raiwind Road )"/>
+        <filter val="EURO RANJERS MART"/>
+        <filter val="Euro store  (Academy Road)"/>
+        <filter val="EURO STORE (N F C )"/>
+        <filter val="EURO STORE (Rahamt chowk)"/>
+        <filter val="Euro Store (Scheme Mor)"/>
+        <filter val="Euro Store Airport Road"/>
+        <filter val="Euro Store Bedian Road"/>
+        <filter val="Euro Store College Road"/>
+        <filter val="EURO STORE CROWN BEHRIA TOWN"/>
+        <filter val="Euro Store E-2 (Wapda Town)"/>
+        <filter val="EURO STORE FATAH GARH"/>
+        <filter val="Euro Store G.T Road"/>
+        <filter val="Euro Store Garhi Shahu"/>
+        <filter val="EURO Store Hypermarket (Raiwind Road)"/>
+        <filter val="Euro Store Iqbal Town"/>
+        <filter val="EURO STORE MARIYA STOP"/>
+        <filter val="EURO STORE PH VIII PARK VIEW"/>
+        <filter val="Euro Stores (G-1 Market)"/>
+        <filter val="EURO Stores (Nishat Colony)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25898809-F3E7-4004-A90A-FE068C23CFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285ADD0B-13D0-4182-9A4D-C0CD40DE8A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B246" s="2">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B247" s="2">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B248" s="2">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="F248" s="3"/>
     </row>
-    <row r="249" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B249" s="2">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B250" s="2">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6805,7 +6805,7 @@
       </c>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B251" s="2">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B252" s="2">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B253" s="2">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B256" s="2">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B257" s="2">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B258" s="2">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B259" s="2">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B260" s="2">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B261" s="2">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B262" s="2">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B263" s="2">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B264" s="2">
         <f t="shared" si="3"/>
         <v>260</v>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <f t="shared" si="7"/>
         <v>463</v>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <f t="shared" si="8"/>
         <v>547</v>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <f t="shared" si="8"/>
         <v>548</v>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <f t="shared" si="8"/>
         <v>549</v>
@@ -12443,25 +12443,12 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="EURO RANJERS MART"/>
-        <filter val="Euro store  (Academy Road)"/>
-        <filter val="EURO STORE (N F C )"/>
-        <filter val="EURO STORE (Rahamt chowk)"/>
-        <filter val="Euro Store (Scheme Mor)"/>
-        <filter val="Euro Store Airport Road"/>
-        <filter val="Euro Store Bedian Road"/>
-        <filter val="Euro Store College Road"/>
-        <filter val="EURO STORE CROWN BEHRIA TOWN"/>
-        <filter val="Euro Store E-2 (Wapda Town)"/>
-        <filter val="EURO STORE FATAH GARH"/>
-        <filter val="Euro Store G.T Road"/>
-        <filter val="Euro Store Garhi Shahu"/>
-        <filter val="EURO Store Hypermarket (Raiwind Road)"/>
-        <filter val="Euro Store Iqbal Town"/>
-        <filter val="EURO STORE MARIYA STOP"/>
-        <filter val="EURO STORE PH VIII PARK VIEW"/>
-        <filter val="Euro Stores (G-1 Market)"/>
-        <filter val="EURO Stores (Nishat Colony)"/>
+        <filter val="M.S Traders Harbanspura (Risen)"/>
+        <filter val="Risen / Gajjumata _FR TRADERS"/>
+        <filter val="Risen / Manawa _CB TRADERS"/>
+        <filter val="Risen / Sabzazar _SZ TRADERS"/>
+        <filter val="Risen / Shadbagh _SB Traders"/>
+        <filter val="Risen / TN Traders (Raiwind Road )"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285ADD0B-13D0-4182-9A4D-C0CD40DE8A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AEBC6CD-908B-4C02-84F9-3148FCA8AF6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AEBC6CD-908B-4C02-84F9-3148FCA8AF6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0224A5FD-EF55-4818-9526-2CD0C974BE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="F407" s="3"/>
     </row>
-    <row r="408" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B408" s="2">
         <f t="shared" si="6"/>
         <v>404</v>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="F408" s="3"/>
     </row>
-    <row r="409" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B409" s="2">
         <f t="shared" si="6"/>
         <v>405</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="F409" s="3"/>
     </row>
-    <row r="410" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B410" s="2">
         <f t="shared" si="6"/>
         <v>406</v>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="F410" s="3"/>
     </row>
-    <row r="411" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B411" s="2">
         <f t="shared" si="6"/>
         <v>407</v>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F411" s="3"/>
     </row>
-    <row r="412" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B412" s="2">
         <f t="shared" si="6"/>
         <v>408</v>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="F412" s="3"/>
     </row>
-    <row r="413" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B413" s="2">
         <f t="shared" si="6"/>
         <v>409</v>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="F413" s="3"/>
     </row>
-    <row r="414" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B414" s="2">
         <f t="shared" si="6"/>
         <v>410</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="F414" s="3"/>
     </row>
-    <row r="415" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B415" s="2">
         <f t="shared" si="6"/>
         <v>411</v>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B416" s="2">
         <f t="shared" si="6"/>
         <v>412</v>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="F416" s="3"/>
     </row>
-    <row r="417" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B417" s="2">
         <f t="shared" si="6"/>
         <v>413</v>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="F417" s="3"/>
     </row>
-    <row r="418" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B418" s="2">
         <f t="shared" si="6"/>
         <v>414</v>
@@ -9493,7 +9493,7 @@
       </c>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B419" s="2">
         <f t="shared" si="6"/>
         <v>415</v>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="F419" s="3"/>
     </row>
-    <row r="420" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B420" s="2">
         <f t="shared" si="6"/>
         <v>416</v>
@@ -9525,7 +9525,7 @@
       </c>
       <c r="F420" s="3"/>
     </row>
-    <row r="421" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B421" s="2">
         <f t="shared" si="6"/>
         <v>417</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B422" s="2">
         <f t="shared" si="6"/>
         <v>418</v>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B423" s="2">
         <f t="shared" si="6"/>
         <v>419</v>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="F423" s="3"/>
     </row>
-    <row r="424" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B424" s="2">
         <f t="shared" si="6"/>
         <v>420</v>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="F424" s="3"/>
     </row>
-    <row r="425" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B425" s="2">
         <f t="shared" si="6"/>
         <v>421</v>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="F425" s="3"/>
     </row>
-    <row r="426" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B426" s="2">
         <f t="shared" si="6"/>
         <v>422</v>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B428" s="2">
         <f t="shared" si="6"/>
         <v>424</v>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B429" s="2">
         <f t="shared" si="6"/>
         <v>425</v>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B430" s="2">
         <f t="shared" si="6"/>
         <v>426</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B431" s="2">
         <f t="shared" si="6"/>
         <v>427</v>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="F431" s="3"/>
     </row>
-    <row r="432" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B432" s="2">
         <f t="shared" si="6"/>
         <v>428</v>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B433" s="2">
         <f t="shared" si="6"/>
         <v>429</v>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B434" s="2">
         <f t="shared" si="6"/>
         <v>430</v>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="F434" s="3"/>
     </row>
-    <row r="435" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B435" s="2">
         <f t="shared" si="6"/>
         <v>431</v>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B436" s="2">
         <f t="shared" si="6"/>
         <v>432</v>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="F436" s="3"/>
     </row>
-    <row r="437" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B437" s="2">
         <f t="shared" si="6"/>
         <v>433</v>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B438" s="2">
         <f t="shared" si="6"/>
         <v>434</v>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B439" s="2">
         <f t="shared" si="6"/>
         <v>435</v>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B440" s="2">
         <f t="shared" si="6"/>
         <v>436</v>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B441" s="2">
         <f t="shared" si="6"/>
         <v>437</v>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="F441" s="3"/>
     </row>
-    <row r="442" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B442" s="2">
         <f t="shared" si="6"/>
         <v>438</v>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <f t="shared" si="7"/>
         <v>463</v>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <f t="shared" si="8"/>
         <v>547</v>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <f t="shared" si="8"/>
         <v>548</v>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <f t="shared" si="8"/>
         <v>549</v>
@@ -12443,12 +12443,41 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="M.S Traders Harbanspura (Risen)"/>
-        <filter val="Risen / Gajjumata _FR TRADERS"/>
-        <filter val="Risen / Manawa _CB TRADERS"/>
-        <filter val="Risen / Sabzazar _SZ TRADERS"/>
-        <filter val="Risen / Shadbagh _SB Traders"/>
-        <filter val="Risen / TN Traders (Raiwind Road )"/>
+        <filter val="JALAL SONS  (COLLEGE ROAD) 02"/>
+        <filter val="Jalal sons  (Izmair Town) 01"/>
+        <filter val="Jalal sons (Askari 10 F sector ) 01"/>
+        <filter val="JALAL SONS (ASKARI 11 B BLOCK) 02"/>
+        <filter val="JALAL SONS (AYUBIA) 02"/>
+        <filter val="JALAL SONS (Bahira Orchard) 01"/>
+        <filter val="Jalal Sons (Bahria Town)  01"/>
+        <filter val="JALAL SONS (C BLOCK MODEL TOWN) 02"/>
+        <filter val="JALAL SONS (DHA C BLOCK,PHASE 6) 02"/>
+        <filter val="JALAL SONS (DHA PH IV) 02"/>
+        <filter val="JALAL SONS (DHA PH V) 02"/>
+        <filter val="JALAL SONS (DHA Y BLOCK) 02"/>
+        <filter val="JALAL SONS (EME) 02"/>
+        <filter val="JALAL SONS (FAISAL TOWN) 02"/>
+        <filter val="Jalal Sons (H Block) 01"/>
+        <filter val="JALAL SONS (HUSSAIN CHOWK GULBERG III) 02"/>
+        <filter val="JALAL SONS (IQBAL TOWN) 02"/>
+        <filter val="Jalal Sons (J.T Shadewal) 01"/>
+        <filter val="JALAL SONS (JOHER TOWN) 02"/>
+        <filter val="Jalal Sons (Lake City) 01"/>
+        <filter val="Jalal sons (Main Market) 01"/>
+        <filter val="JALAL SONS (MODEL TOWN LINK ROAD) 02"/>
+        <filter val="Jalal Sons (PAF Market) 01 main Market"/>
+        <filter val="JALAL SONS (PARAGON CITY) 02"/>
+        <filter val="JALAL SONS (PH VI) 02"/>
+        <filter val="JALAL SONS (PHASE 8 EX PARK VIEW) 02"/>
+        <filter val="JALAL SONS (REVAZ GARDEN) 02"/>
+        <filter val="JALAL SONS (SHADMAN) 02"/>
+        <filter val="JALAL SONS (SHAUKAT KHANUM) 02"/>
+        <filter val="JALAL SONS (STATE LIFE) 02"/>
+        <filter val="JALAL SONS (TALWAR CHOWK) 02"/>
+        <filter val="JALAL SONS (VALENCIA TOWN) 02"/>
+        <filter val="JALAL SONS (WAPDA TOWN) 02"/>
+        <filter val="JALAL SONS (XX) 02"/>
+        <filter val="Jalal Sons Askari X (01)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0224A5FD-EF55-4818-9526-2CD0C974BE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B33040-BFC3-4183-97CA-B64D56BC8076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="F407" s="3"/>
     </row>
-    <row r="408" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B408" s="2">
         <f t="shared" si="6"/>
         <v>404</v>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="F408" s="3"/>
     </row>
-    <row r="409" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B409" s="2">
         <f t="shared" si="6"/>
         <v>405</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="F409" s="3"/>
     </row>
-    <row r="410" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B410" s="2">
         <f t="shared" si="6"/>
         <v>406</v>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="F410" s="3"/>
     </row>
-    <row r="411" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B411" s="2">
         <f t="shared" si="6"/>
         <v>407</v>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F411" s="3"/>
     </row>
-    <row r="412" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B412" s="2">
         <f t="shared" si="6"/>
         <v>408</v>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="F412" s="3"/>
     </row>
-    <row r="413" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B413" s="2">
         <f t="shared" si="6"/>
         <v>409</v>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="F413" s="3"/>
     </row>
-    <row r="414" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B414" s="2">
         <f t="shared" si="6"/>
         <v>410</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="F414" s="3"/>
     </row>
-    <row r="415" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B415" s="2">
         <f t="shared" si="6"/>
         <v>411</v>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B416" s="2">
         <f t="shared" si="6"/>
         <v>412</v>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="F416" s="3"/>
     </row>
-    <row r="417" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B417" s="2">
         <f t="shared" si="6"/>
         <v>413</v>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="F417" s="3"/>
     </row>
-    <row r="418" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B418" s="2">
         <f t="shared" si="6"/>
         <v>414</v>
@@ -9493,7 +9493,7 @@
       </c>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B419" s="2">
         <f t="shared" si="6"/>
         <v>415</v>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="F419" s="3"/>
     </row>
-    <row r="420" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B420" s="2">
         <f t="shared" si="6"/>
         <v>416</v>
@@ -9525,7 +9525,7 @@
       </c>
       <c r="F420" s="3"/>
     </row>
-    <row r="421" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B421" s="2">
         <f t="shared" si="6"/>
         <v>417</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B422" s="2">
         <f t="shared" si="6"/>
         <v>418</v>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B423" s="2">
         <f t="shared" si="6"/>
         <v>419</v>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="F423" s="3"/>
     </row>
-    <row r="424" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B424" s="2">
         <f t="shared" si="6"/>
         <v>420</v>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="F424" s="3"/>
     </row>
-    <row r="425" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B425" s="2">
         <f t="shared" si="6"/>
         <v>421</v>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="F425" s="3"/>
     </row>
-    <row r="426" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B426" s="2">
         <f t="shared" si="6"/>
         <v>422</v>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B428" s="2">
         <f t="shared" si="6"/>
         <v>424</v>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B429" s="2">
         <f t="shared" si="6"/>
         <v>425</v>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B430" s="2">
         <f t="shared" si="6"/>
         <v>426</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B431" s="2">
         <f t="shared" si="6"/>
         <v>427</v>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="F431" s="3"/>
     </row>
-    <row r="432" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B432" s="2">
         <f t="shared" si="6"/>
         <v>428</v>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B433" s="2">
         <f t="shared" si="6"/>
         <v>429</v>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B434" s="2">
         <f t="shared" si="6"/>
         <v>430</v>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="F434" s="3"/>
     </row>
-    <row r="435" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B435" s="2">
         <f t="shared" si="6"/>
         <v>431</v>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B436" s="2">
         <f t="shared" si="6"/>
         <v>432</v>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="F436" s="3"/>
     </row>
-    <row r="437" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B437" s="2">
         <f t="shared" si="6"/>
         <v>433</v>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B438" s="2">
         <f t="shared" si="6"/>
         <v>434</v>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B439" s="2">
         <f t="shared" si="6"/>
         <v>435</v>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B440" s="2">
         <f t="shared" si="6"/>
         <v>436</v>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B441" s="2">
         <f t="shared" si="6"/>
         <v>437</v>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="F441" s="3"/>
     </row>
-    <row r="442" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B442" s="2">
         <f t="shared" si="6"/>
         <v>438</v>
@@ -11349,7 +11349,7 @@
       </c>
       <c r="F534" s="3"/>
     </row>
-    <row r="535" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B535" s="2">
         <f t="shared" si="8"/>
         <v>531</v>
@@ -12443,41 +12443,7 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="JALAL SONS  (COLLEGE ROAD) 02"/>
-        <filter val="Jalal sons  (Izmair Town) 01"/>
-        <filter val="Jalal sons (Askari 10 F sector ) 01"/>
-        <filter val="JALAL SONS (ASKARI 11 B BLOCK) 02"/>
-        <filter val="JALAL SONS (AYUBIA) 02"/>
-        <filter val="JALAL SONS (Bahira Orchard) 01"/>
-        <filter val="Jalal Sons (Bahria Town)  01"/>
-        <filter val="JALAL SONS (C BLOCK MODEL TOWN) 02"/>
-        <filter val="JALAL SONS (DHA C BLOCK,PHASE 6) 02"/>
-        <filter val="JALAL SONS (DHA PH IV) 02"/>
-        <filter val="JALAL SONS (DHA PH V) 02"/>
-        <filter val="JALAL SONS (DHA Y BLOCK) 02"/>
-        <filter val="JALAL SONS (EME) 02"/>
-        <filter val="JALAL SONS (FAISAL TOWN) 02"/>
-        <filter val="Jalal Sons (H Block) 01"/>
-        <filter val="JALAL SONS (HUSSAIN CHOWK GULBERG III) 02"/>
-        <filter val="JALAL SONS (IQBAL TOWN) 02"/>
-        <filter val="Jalal Sons (J.T Shadewal) 01"/>
-        <filter val="JALAL SONS (JOHER TOWN) 02"/>
-        <filter val="Jalal Sons (Lake City) 01"/>
-        <filter val="Jalal sons (Main Market) 01"/>
-        <filter val="JALAL SONS (MODEL TOWN LINK ROAD) 02"/>
-        <filter val="Jalal Sons (PAF Market) 01 main Market"/>
-        <filter val="JALAL SONS (PARAGON CITY) 02"/>
-        <filter val="JALAL SONS (PH VI) 02"/>
-        <filter val="JALAL SONS (PHASE 8 EX PARK VIEW) 02"/>
-        <filter val="JALAL SONS (REVAZ GARDEN) 02"/>
-        <filter val="JALAL SONS (SHADMAN) 02"/>
-        <filter val="JALAL SONS (SHAUKAT KHANUM) 02"/>
-        <filter val="JALAL SONS (STATE LIFE) 02"/>
-        <filter val="JALAL SONS (TALWAR CHOWK) 02"/>
-        <filter val="JALAL SONS (VALENCIA TOWN) 02"/>
-        <filter val="JALAL SONS (WAPDA TOWN) 02"/>
-        <filter val="JALAL SONS (XX) 02"/>
-        <filter val="Jalal Sons Askari X (01)"/>
+        <filter val="Raheem Store Iqbal Town"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B33040-BFC3-4183-97CA-B64D56BC8076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2014B2-640F-438F-AF4B-9B147DBE5BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <f t="shared" si="7"/>
         <v>463</v>
@@ -11349,7 +11349,7 @@
       </c>
       <c r="F534" s="3"/>
     </row>
-    <row r="535" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="535" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B535" s="2">
         <f t="shared" si="8"/>
         <v>531</v>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <f t="shared" si="8"/>
         <v>547</v>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <f t="shared" si="8"/>
         <v>548</v>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <f t="shared" si="8"/>
         <v>549</v>
@@ -12443,7 +12443,12 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Raheem Store Iqbal Town"/>
+        <filter val="M.S Traders Harbanspura (Risen)"/>
+        <filter val="Risen / Gajjumata _FR TRADERS"/>
+        <filter val="Risen / Manawa _CB TRADERS"/>
+        <filter val="Risen / Sabzazar _SZ TRADERS"/>
+        <filter val="Risen / Shadbagh _SB Traders"/>
+        <filter val="Risen / TN Traders (Raiwind Road )"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2014B2-640F-438F-AF4B-9B147DBE5BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60D0A45-E865-47AD-BDBC-D1178172ADC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="F406" s="3"/>
     </row>
-    <row r="407" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B407" s="2">
         <f t="shared" si="6"/>
         <v>403</v>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <f t="shared" si="7"/>
         <v>463</v>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <f t="shared" si="8"/>
         <v>547</v>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <f t="shared" si="8"/>
         <v>548</v>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <f t="shared" si="8"/>
         <v>549</v>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="F587" s="3"/>
     </row>
-    <row r="588" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B588" s="2">
         <f t="shared" si="9"/>
         <v>584</v>
@@ -12443,12 +12443,8 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="M.S Traders Harbanspura (Risen)"/>
-        <filter val="Risen / Gajjumata _FR TRADERS"/>
-        <filter val="Risen / Manawa _CB TRADERS"/>
-        <filter val="Risen / Sabzazar _SZ TRADERS"/>
-        <filter val="Risen / Shadbagh _SB Traders"/>
-        <filter val="Risen / TN Traders (Raiwind Road )"/>
+        <filter val="Imperia Departmental Store"/>
+        <filter val="UMAIMA SUPER STORE IMPERIAL GARDEN"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60D0A45-E865-47AD-BDBC-D1178172ADC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE17C365-0783-4123-8649-466980DF4654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1047,9 +1047,6 @@
     <t>EURO Store Hypermarket (Raiwind Road)</t>
   </si>
   <si>
-    <t>Euro Store Iqbal Town</t>
-  </si>
-  <si>
     <t>EURO STORE MARIYA STOP</t>
   </si>
   <si>
@@ -2449,6 +2446,9 @@
   </si>
   <si>
     <t>NEMAT KHANA STORES (PRIVATE) LIMITED</t>
+  </si>
+  <si>
+    <t>Euro Store Iqbal Town (Ranchna)</t>
   </si>
 </sst>
 </file>
@@ -2870,7 +2870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -4475,7 +4475,7 @@
         <v>101</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>90</v>
@@ -6955,7 +6955,7 @@
         <v>256</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>339</v>
+        <v>806</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>319</v>
@@ -6971,7 +6971,7 @@
         <v>257</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>319</v>
@@ -6987,10 +6987,10 @@
         <v>258</v>
       </c>
       <c r="C262" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D262" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="D262" s="2" t="s">
-        <v>342</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>5</v>
@@ -7003,7 +7003,7 @@
         <v>259</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>319</v>
@@ -7019,10 +7019,10 @@
         <v>260</v>
       </c>
       <c r="C264" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D264" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>5</v>
@@ -7035,10 +7035,10 @@
         <v>261</v>
       </c>
       <c r="C265" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D265" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="D265" s="2" t="s">
-        <v>347</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>5</v>
@@ -7051,10 +7051,10 @@
         <v>262</v>
       </c>
       <c r="C266" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D266" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>349</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>5</v>
@@ -7067,13 +7067,13 @@
         <v>263</v>
       </c>
       <c r="C267" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E267" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="D267" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E267" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="F267" s="3"/>
     </row>
@@ -7083,10 +7083,10 @@
         <v>264</v>
       </c>
       <c r="C268" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D268" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="D268" s="2" t="s">
-        <v>353</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>5</v>
@@ -7099,10 +7099,10 @@
         <v>265</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>5</v>
@@ -7115,10 +7115,10 @@
         <v>266</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>5</v>
@@ -7131,10 +7131,10 @@
         <v>267</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>5</v>
@@ -7147,10 +7147,10 @@
         <v>268</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>5</v>
@@ -7163,10 +7163,10 @@
         <v>269</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>5</v>
@@ -7179,10 +7179,10 @@
         <v>270</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>5</v>
@@ -7195,10 +7195,10 @@
         <v>271</v>
       </c>
       <c r="C275" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D275" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="D275" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>5</v>
@@ -7211,10 +7211,10 @@
         <v>272</v>
       </c>
       <c r="C276" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D276" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="D276" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>5</v>
@@ -7227,10 +7227,10 @@
         <v>273</v>
       </c>
       <c r="C277" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D277" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="D277" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>5</v>
@@ -7243,13 +7243,13 @@
         <v>274</v>
       </c>
       <c r="C278" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E278" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="D278" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="F278" s="3"/>
     </row>
@@ -7259,10 +7259,10 @@
         <v>275</v>
       </c>
       <c r="C279" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D279" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="D279" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>5</v>
@@ -7275,10 +7275,10 @@
         <v>276</v>
       </c>
       <c r="C280" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D280" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="D280" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>5</v>
@@ -7291,10 +7291,10 @@
         <v>277</v>
       </c>
       <c r="C281" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D281" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="D281" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>5</v>
@@ -7307,10 +7307,10 @@
         <v>278</v>
       </c>
       <c r="C282" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D282" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="D282" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>5</v>
@@ -7323,10 +7323,10 @@
         <v>279</v>
       </c>
       <c r="C283" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D283" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="D283" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>5</v>
@@ -7339,10 +7339,10 @@
         <v>280</v>
       </c>
       <c r="C284" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D284" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>379</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>5</v>
@@ -7355,10 +7355,10 @@
         <v>281</v>
       </c>
       <c r="C285" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D285" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="D285" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>5</v>
@@ -7371,10 +7371,10 @@
         <v>282</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>5</v>
@@ -7387,10 +7387,10 @@
         <v>283</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>5</v>
@@ -7403,10 +7403,10 @@
         <v>284</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>5</v>
@@ -7419,10 +7419,10 @@
         <v>285</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>5</v>
@@ -7435,10 +7435,10 @@
         <v>286</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>5</v>
@@ -7451,10 +7451,10 @@
         <v>287</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>5</v>
@@ -7467,10 +7467,10 @@
         <v>288</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>5</v>
@@ -7483,10 +7483,10 @@
         <v>289</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>5</v>
@@ -7499,10 +7499,10 @@
         <v>290</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>5</v>
@@ -7515,10 +7515,10 @@
         <v>291</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>5</v>
@@ -7531,10 +7531,10 @@
         <v>292</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>5</v>
@@ -7547,10 +7547,10 @@
         <v>293</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>5</v>
@@ -7563,10 +7563,10 @@
         <v>294</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>5</v>
@@ -7579,10 +7579,10 @@
         <v>295</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>5</v>
@@ -7595,10 +7595,10 @@
         <v>296</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>5</v>
@@ -7611,10 +7611,10 @@
         <v>297</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>5</v>
@@ -7627,10 +7627,10 @@
         <v>298</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>5</v>
@@ -7643,10 +7643,10 @@
         <v>299</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>5</v>
@@ -7659,10 +7659,10 @@
         <v>300</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>5</v>
@@ -7675,10 +7675,10 @@
         <v>301</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>5</v>
@@ -7691,10 +7691,10 @@
         <v>302</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>5</v>
@@ -7707,10 +7707,10 @@
         <v>303</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>5</v>
@@ -7723,10 +7723,10 @@
         <v>304</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>5</v>
@@ -7739,10 +7739,10 @@
         <v>305</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>5</v>
@@ -7755,10 +7755,10 @@
         <v>306</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>5</v>
@@ -7771,10 +7771,10 @@
         <v>307</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>5</v>
@@ -7787,10 +7787,10 @@
         <v>308</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>5</v>
@@ -7803,10 +7803,10 @@
         <v>309</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>5</v>
@@ -7819,10 +7819,10 @@
         <v>310</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>5</v>
@@ -7835,10 +7835,10 @@
         <v>311</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>5</v>
@@ -7851,10 +7851,10 @@
         <v>312</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>5</v>
@@ -7867,10 +7867,10 @@
         <v>313</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>5</v>
@@ -7883,10 +7883,10 @@
         <v>314</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>5</v>
@@ -7899,10 +7899,10 @@
         <v>315</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>5</v>
@@ -7915,10 +7915,10 @@
         <v>316</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>5</v>
@@ -7931,10 +7931,10 @@
         <v>317</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>5</v>
@@ -7947,10 +7947,10 @@
         <v>318</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>5</v>
@@ -7963,10 +7963,10 @@
         <v>319</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>5</v>
@@ -7979,10 +7979,10 @@
         <v>320</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>5</v>
@@ -7995,10 +7995,10 @@
         <v>321</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>5</v>
@@ -8011,10 +8011,10 @@
         <v>322</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>5</v>
@@ -8027,10 +8027,10 @@
         <v>323</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>5</v>
@@ -8043,10 +8043,10 @@
         <v>324</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>5</v>
@@ -8059,10 +8059,10 @@
         <v>325</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>5</v>
@@ -8075,10 +8075,10 @@
         <v>326</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>5</v>
@@ -8091,10 +8091,10 @@
         <v>327</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>5</v>
@@ -8107,10 +8107,10 @@
         <v>328</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>5</v>
@@ -8123,10 +8123,10 @@
         <v>329</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>5</v>
@@ -8139,10 +8139,10 @@
         <v>330</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>5</v>
@@ -8155,10 +8155,10 @@
         <v>331</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>5</v>
@@ -8171,10 +8171,10 @@
         <v>332</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>5</v>
@@ -8187,10 +8187,10 @@
         <v>333</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>5</v>
@@ -8203,10 +8203,10 @@
         <v>334</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>5</v>
@@ -8219,10 +8219,10 @@
         <v>335</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>5</v>
@@ -8235,10 +8235,10 @@
         <v>336</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>5</v>
@@ -8251,10 +8251,10 @@
         <v>337</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>5</v>
@@ -8267,10 +8267,10 @@
         <v>338</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>5</v>
@@ -8283,10 +8283,10 @@
         <v>339</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>5</v>
@@ -8299,10 +8299,10 @@
         <v>340</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>5</v>
@@ -8315,10 +8315,10 @@
         <v>341</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>5</v>
@@ -8331,10 +8331,10 @@
         <v>342</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>5</v>
@@ -8347,10 +8347,10 @@
         <v>343</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>5</v>
@@ -8363,10 +8363,10 @@
         <v>344</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>5</v>
@@ -8379,10 +8379,10 @@
         <v>345</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>5</v>
@@ -8395,10 +8395,10 @@
         <v>346</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>5</v>
@@ -8411,10 +8411,10 @@
         <v>347</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>5</v>
@@ -8427,10 +8427,10 @@
         <v>348</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>5</v>
@@ -8443,10 +8443,10 @@
         <v>349</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>5</v>
@@ -8459,10 +8459,10 @@
         <v>350</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>5</v>
@@ -8475,10 +8475,10 @@
         <v>351</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>5</v>
@@ -8491,10 +8491,10 @@
         <v>352</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>5</v>
@@ -8507,10 +8507,10 @@
         <v>353</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>5</v>
@@ -8523,10 +8523,10 @@
         <v>354</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>5</v>
@@ -8539,10 +8539,10 @@
         <v>355</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>5</v>
@@ -8555,10 +8555,10 @@
         <v>356</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>5</v>
@@ -8571,10 +8571,10 @@
         <v>357</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>5</v>
@@ -8587,10 +8587,10 @@
         <v>358</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>5</v>
@@ -8603,10 +8603,10 @@
         <v>359</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>5</v>
@@ -8619,10 +8619,10 @@
         <v>360</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>5</v>
@@ -8635,10 +8635,10 @@
         <v>361</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>5</v>
@@ -8651,10 +8651,10 @@
         <v>362</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>5</v>
@@ -8667,10 +8667,10 @@
         <v>363</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>5</v>
@@ -8683,10 +8683,10 @@
         <v>364</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>5</v>
@@ -8699,10 +8699,10 @@
         <v>365</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>5</v>
@@ -8715,10 +8715,10 @@
         <v>366</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>5</v>
@@ -8731,10 +8731,10 @@
         <v>367</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>5</v>
@@ -8747,10 +8747,10 @@
         <v>368</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>5</v>
@@ -8763,10 +8763,10 @@
         <v>369</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>5</v>
@@ -8779,10 +8779,10 @@
         <v>370</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>5</v>
@@ -8795,10 +8795,10 @@
         <v>371</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>5</v>
@@ -8811,10 +8811,10 @@
         <v>372</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>5</v>
@@ -8827,10 +8827,10 @@
         <v>373</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>5</v>
@@ -8843,10 +8843,10 @@
         <v>374</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>5</v>
@@ -8859,10 +8859,10 @@
         <v>375</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>5</v>
@@ -8875,10 +8875,10 @@
         <v>376</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>5</v>
@@ -8891,10 +8891,10 @@
         <v>377</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>5</v>
@@ -8907,10 +8907,10 @@
         <v>378</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>5</v>
@@ -8923,10 +8923,10 @@
         <v>379</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>5</v>
@@ -8939,10 +8939,10 @@
         <v>380</v>
       </c>
       <c r="C384" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="D384" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="D384" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>5</v>
@@ -8955,10 +8955,10 @@
         <v>381</v>
       </c>
       <c r="C385" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D385" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="D385" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>5</v>
@@ -8971,10 +8971,10 @@
         <v>382</v>
       </c>
       <c r="C386" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D386" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="D386" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>5</v>
@@ -8987,10 +8987,10 @@
         <v>383</v>
       </c>
       <c r="C387" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D387" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="D387" s="2" t="s">
-        <v>487</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>5</v>
@@ -9003,10 +9003,10 @@
         <v>384</v>
       </c>
       <c r="C388" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D388" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="D388" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>5</v>
@@ -9019,10 +9019,10 @@
         <v>385</v>
       </c>
       <c r="C389" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="D389" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="D389" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>5</v>
@@ -9035,10 +9035,10 @@
         <v>386</v>
       </c>
       <c r="C390" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D390" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="D390" s="2" t="s">
-        <v>493</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>5</v>
@@ -9051,10 +9051,10 @@
         <v>387</v>
       </c>
       <c r="C391" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D391" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="D391" s="2" t="s">
-        <v>495</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>5</v>
@@ -9067,10 +9067,10 @@
         <v>388</v>
       </c>
       <c r="C392" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D392" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="D392" s="2" t="s">
-        <v>497</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>5</v>
@@ -9083,10 +9083,10 @@
         <v>389</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>5</v>
@@ -9099,10 +9099,10 @@
         <v>390</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>5</v>
@@ -9115,10 +9115,10 @@
         <v>391</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>5</v>
@@ -9131,10 +9131,10 @@
         <v>392</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>5</v>
@@ -9147,10 +9147,10 @@
         <v>393</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E397" s="2" t="s">
         <v>5</v>
@@ -9163,10 +9163,10 @@
         <v>394</v>
       </c>
       <c r="C398" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="D398" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="D398" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="E398" s="2" t="s">
         <v>5</v>
@@ -9179,13 +9179,13 @@
         <v>395</v>
       </c>
       <c r="C399" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D399" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E399" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="D399" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E399" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="F399" s="3"/>
     </row>
@@ -9195,10 +9195,10 @@
         <v>396</v>
       </c>
       <c r="C400" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D400" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="D400" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>5</v>
@@ -9211,10 +9211,10 @@
         <v>397</v>
       </c>
       <c r="C401" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D401" s="2" t="s">
         <v>509</v>
-      </c>
-      <c r="D401" s="2" t="s">
-        <v>510</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>5</v>
@@ -9227,10 +9227,10 @@
         <v>398</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>5</v>
@@ -9243,10 +9243,10 @@
         <v>399</v>
       </c>
       <c r="C403" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D403" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="D403" s="2" t="s">
-        <v>513</v>
       </c>
       <c r="E403" s="2" t="s">
         <v>5</v>
@@ -9259,10 +9259,10 @@
         <v>400</v>
       </c>
       <c r="C404" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="D404" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="D404" s="2" t="s">
-        <v>515</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>5</v>
@@ -9275,10 +9275,10 @@
         <v>401</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>5</v>
@@ -9291,26 +9291,26 @@
         <v>402</v>
       </c>
       <c r="C406" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="D406" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="D406" s="2" t="s">
-        <v>518</v>
-      </c>
       <c r="E406" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F406" s="3"/>
     </row>
-    <row r="407" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B407" s="2">
         <f t="shared" si="6"/>
         <v>403</v>
       </c>
       <c r="C407" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D407" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="D407" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>5</v>
@@ -9323,10 +9323,10 @@
         <v>404</v>
       </c>
       <c r="C408" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D408" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="D408" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>5</v>
@@ -9339,10 +9339,10 @@
         <v>405</v>
       </c>
       <c r="C409" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D409" s="2" t="s">
         <v>523</v>
-      </c>
-      <c r="D409" s="2" t="s">
-        <v>524</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>5</v>
@@ -9355,10 +9355,10 @@
         <v>406</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>5</v>
@@ -9371,10 +9371,10 @@
         <v>407</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>5</v>
@@ -9387,10 +9387,10 @@
         <v>408</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>5</v>
@@ -9403,10 +9403,10 @@
         <v>409</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>5</v>
@@ -9419,10 +9419,10 @@
         <v>410</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>5</v>
@@ -9435,10 +9435,10 @@
         <v>411</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>5</v>
@@ -9451,10 +9451,10 @@
         <v>412</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>5</v>
@@ -9467,10 +9467,10 @@
         <v>413</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>5</v>
@@ -9483,10 +9483,10 @@
         <v>414</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>5</v>
@@ -9499,10 +9499,10 @@
         <v>415</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E419" s="7">
         <v>3277876126916</v>
@@ -9515,10 +9515,10 @@
         <v>416</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>5</v>
@@ -9531,10 +9531,10 @@
         <v>417</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>5</v>
@@ -9547,10 +9547,10 @@
         <v>418</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>5</v>
@@ -9563,10 +9563,10 @@
         <v>419</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>5</v>
@@ -9579,10 +9579,10 @@
         <v>420</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>5</v>
@@ -9595,10 +9595,10 @@
         <v>421</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>5</v>
@@ -9611,10 +9611,10 @@
         <v>422</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>5</v>
@@ -9627,10 +9627,10 @@
         <v>423</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>5</v>
@@ -9643,10 +9643,10 @@
         <v>424</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>5</v>
@@ -9659,10 +9659,10 @@
         <v>425</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>5</v>
@@ -9675,10 +9675,10 @@
         <v>426</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E430" s="7">
         <v>3520255124113</v>
@@ -9691,10 +9691,10 @@
         <v>427</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>5</v>
@@ -9707,10 +9707,10 @@
         <v>428</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>5</v>
@@ -9723,10 +9723,10 @@
         <v>429</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>5</v>
@@ -9739,10 +9739,10 @@
         <v>430</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>5</v>
@@ -9755,10 +9755,10 @@
         <v>431</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>5</v>
@@ -9771,10 +9771,10 @@
         <v>432</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>5</v>
@@ -9787,10 +9787,10 @@
         <v>433</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>5</v>
@@ -9803,10 +9803,10 @@
         <v>434</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>5</v>
@@ -9819,10 +9819,10 @@
         <v>435</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>5</v>
@@ -9835,10 +9835,10 @@
         <v>436</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>5</v>
@@ -9851,10 +9851,10 @@
         <v>437</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>5</v>
@@ -9867,10 +9867,10 @@
         <v>438</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>5</v>
@@ -9883,10 +9883,10 @@
         <v>439</v>
       </c>
       <c r="C443" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="D443" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="D443" s="2" t="s">
-        <v>558</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>5</v>
@@ -9899,10 +9899,10 @@
         <v>440</v>
       </c>
       <c r="C444" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D444" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="D444" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>5</v>
@@ -9915,10 +9915,10 @@
         <v>441</v>
       </c>
       <c r="C445" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="D445" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="D445" s="2" t="s">
-        <v>562</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>5</v>
@@ -9931,10 +9931,10 @@
         <v>442</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>5</v>
@@ -9947,10 +9947,10 @@
         <v>443</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>5</v>
@@ -9963,10 +9963,10 @@
         <v>444</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>5</v>
@@ -9979,10 +9979,10 @@
         <v>445</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>5</v>
@@ -9995,10 +9995,10 @@
         <v>446</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>5</v>
@@ -10011,10 +10011,10 @@
         <v>447</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>5</v>
@@ -10027,10 +10027,10 @@
         <v>448</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>5</v>
@@ -10043,10 +10043,10 @@
         <v>449</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>5</v>
@@ -10059,10 +10059,10 @@
         <v>450</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>5</v>
@@ -10075,10 +10075,10 @@
         <v>451</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>5</v>
@@ -10091,10 +10091,10 @@
         <v>452</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>5</v>
@@ -10107,10 +10107,10 @@
         <v>453</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>5</v>
@@ -10123,10 +10123,10 @@
         <v>454</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>5</v>
@@ -10139,10 +10139,10 @@
         <v>455</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>5</v>
@@ -10155,10 +10155,10 @@
         <v>456</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>5</v>
@@ -10171,10 +10171,10 @@
         <v>457</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>5</v>
@@ -10187,10 +10187,10 @@
         <v>458</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>5</v>
@@ -10203,10 +10203,10 @@
         <v>459</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>5</v>
@@ -10219,10 +10219,10 @@
         <v>460</v>
       </c>
       <c r="C464" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="D464" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="D464" s="2" t="s">
-        <v>582</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>5</v>
@@ -10235,10 +10235,10 @@
         <v>461</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>5</v>
@@ -10251,10 +10251,10 @@
         <v>462</v>
       </c>
       <c r="C466" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="D466" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="D466" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>5</v>
@@ -10267,10 +10267,10 @@
         <v>463</v>
       </c>
       <c r="C467" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="D467" s="2" t="s">
         <v>586</v>
-      </c>
-      <c r="D467" s="2" t="s">
-        <v>587</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>5</v>
@@ -10283,10 +10283,10 @@
         <v>464</v>
       </c>
       <c r="C468" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="D468" s="2" t="s">
         <v>588</v>
-      </c>
-      <c r="D468" s="2" t="s">
-        <v>589</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>5</v>
@@ -10299,7 +10299,7 @@
         <v>465</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D469" s="2" t="s">
         <v>114</v>
@@ -10315,10 +10315,10 @@
         <v>466</v>
       </c>
       <c r="C470" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="D470" s="2" t="s">
         <v>591</v>
-      </c>
-      <c r="D470" s="2" t="s">
-        <v>592</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>5</v>
@@ -10331,7 +10331,7 @@
         <v>467</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D471" s="2" t="s">
         <v>114</v>
@@ -10347,7 +10347,7 @@
         <v>468</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D472" s="2" t="s">
         <v>114</v>
@@ -10363,7 +10363,7 @@
         <v>469</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D473" s="2" t="s">
         <v>177</v>
@@ -10379,7 +10379,7 @@
         <v>470</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D474" s="2" t="s">
         <v>235</v>
@@ -10395,10 +10395,10 @@
         <v>471</v>
       </c>
       <c r="C475" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="D475" s="2" t="s">
         <v>597</v>
-      </c>
-      <c r="D475" s="2" t="s">
-        <v>598</v>
       </c>
       <c r="E475" s="1" t="s">
         <v>5</v>
@@ -10411,13 +10411,13 @@
         <v>472</v>
       </c>
       <c r="C476" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D476" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E476" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="D476" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E476" s="2" t="s">
-        <v>600</v>
       </c>
       <c r="F476" s="3"/>
     </row>
@@ -10427,10 +10427,10 @@
         <v>473</v>
       </c>
       <c r="C477" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="D477" s="2" t="s">
         <v>601</v>
-      </c>
-      <c r="D477" s="2" t="s">
-        <v>602</v>
       </c>
       <c r="E477" s="1" t="s">
         <v>5</v>
@@ -10443,10 +10443,10 @@
         <v>474</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E478" s="1" t="s">
         <v>5</v>
@@ -10459,10 +10459,10 @@
         <v>475</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E479" s="1" t="s">
         <v>5</v>
@@ -10475,10 +10475,10 @@
         <v>476</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E480" s="1" t="s">
         <v>5</v>
@@ -10491,10 +10491,10 @@
         <v>477</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E481" s="1" t="s">
         <v>5</v>
@@ -10507,10 +10507,10 @@
         <v>478</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E482" s="1" t="s">
         <v>5</v>
@@ -10523,10 +10523,10 @@
         <v>479</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E483" s="1" t="s">
         <v>5</v>
@@ -10539,10 +10539,10 @@
         <v>480</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>5</v>
@@ -10555,10 +10555,10 @@
         <v>481</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>5</v>
@@ -10571,10 +10571,10 @@
         <v>482</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>5</v>
@@ -10587,10 +10587,10 @@
         <v>483</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>5</v>
@@ -10603,10 +10603,10 @@
         <v>484</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>5</v>
@@ -10619,10 +10619,10 @@
         <v>485</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E489" s="1" t="s">
         <v>5</v>
@@ -10635,10 +10635,10 @@
         <v>486</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E490" s="1" t="s">
         <v>5</v>
@@ -10651,10 +10651,10 @@
         <v>487</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>5</v>
@@ -10667,10 +10667,10 @@
         <v>488</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E492" s="1" t="s">
         <v>5</v>
@@ -10683,10 +10683,10 @@
         <v>489</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D493" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E493" s="1" t="s">
         <v>5</v>
@@ -10699,10 +10699,10 @@
         <v>490</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E494" s="1" t="s">
         <v>5</v>
@@ -10715,10 +10715,10 @@
         <v>491</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E495" s="1" t="s">
         <v>5</v>
@@ -10731,10 +10731,10 @@
         <v>492</v>
       </c>
       <c r="C496" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="D496" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="D496" s="2" t="s">
-        <v>622</v>
       </c>
       <c r="E496" s="2" t="s">
         <v>5</v>
@@ -10747,13 +10747,13 @@
         <v>493</v>
       </c>
       <c r="C497" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="D497" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E497" s="2" t="s">
         <v>623</v>
-      </c>
-      <c r="D497" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E497" s="2" t="s">
-        <v>624</v>
       </c>
       <c r="F497" s="3"/>
     </row>
@@ -10763,10 +10763,10 @@
         <v>494</v>
       </c>
       <c r="C498" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="D498" s="2" t="s">
         <v>625</v>
-      </c>
-      <c r="D498" s="2" t="s">
-        <v>626</v>
       </c>
       <c r="E498" s="2" t="s">
         <v>5</v>
@@ -10779,10 +10779,10 @@
         <v>495</v>
       </c>
       <c r="C499" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="D499" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="D499" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="E499" s="2" t="s">
         <v>5</v>
@@ -10795,13 +10795,13 @@
         <v>496</v>
       </c>
       <c r="C500" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="D500" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E500" s="2" t="s">
         <v>629</v>
-      </c>
-      <c r="D500" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E500" s="2" t="s">
-        <v>630</v>
       </c>
       <c r="F500" s="3"/>
     </row>
@@ -10811,10 +10811,10 @@
         <v>497</v>
       </c>
       <c r="C501" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D501" s="2" t="s">
         <v>631</v>
-      </c>
-      <c r="D501" s="2" t="s">
-        <v>632</v>
       </c>
       <c r="E501" s="1" t="s">
         <v>5</v>
@@ -10827,10 +10827,10 @@
         <v>498</v>
       </c>
       <c r="C502" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="D502" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="D502" s="2" t="s">
-        <v>634</v>
       </c>
       <c r="E502" s="1" t="s">
         <v>5</v>
@@ -10843,10 +10843,10 @@
         <v>499</v>
       </c>
       <c r="C503" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="D503" s="2" t="s">
         <v>635</v>
-      </c>
-      <c r="D503" s="2" t="s">
-        <v>636</v>
       </c>
       <c r="E503" s="1" t="s">
         <v>5</v>
@@ -10859,10 +10859,10 @@
         <v>500</v>
       </c>
       <c r="C504" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="D504" s="2" t="s">
         <v>637</v>
-      </c>
-      <c r="D504" s="2" t="s">
-        <v>638</v>
       </c>
       <c r="E504" s="1" t="s">
         <v>5</v>
@@ -10875,10 +10875,10 @@
         <v>501</v>
       </c>
       <c r="C505" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="D505" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="D505" s="2" t="s">
-        <v>640</v>
       </c>
       <c r="E505" s="1" t="s">
         <v>5</v>
@@ -10891,10 +10891,10 @@
         <v>502</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E506" s="1" t="s">
         <v>5</v>
@@ -10907,10 +10907,10 @@
         <v>503</v>
       </c>
       <c r="C507" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D507" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="D507" s="2" t="s">
-        <v>643</v>
       </c>
       <c r="E507" s="1" t="s">
         <v>5</v>
@@ -10923,10 +10923,10 @@
         <v>504</v>
       </c>
       <c r="C508" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="D508" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="D508" s="2" t="s">
-        <v>645</v>
       </c>
       <c r="E508" s="1" t="s">
         <v>5</v>
@@ -10939,10 +10939,10 @@
         <v>505</v>
       </c>
       <c r="C509" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="D509" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="D509" s="2" t="s">
-        <v>647</v>
       </c>
       <c r="E509" s="1" t="s">
         <v>5</v>
@@ -10955,10 +10955,10 @@
         <v>506</v>
       </c>
       <c r="C510" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="D510" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="D510" s="2" t="s">
-        <v>649</v>
       </c>
       <c r="E510" s="1" t="s">
         <v>5</v>
@@ -10971,10 +10971,10 @@
         <v>507</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E511" s="1" t="s">
         <v>5</v>
@@ -10987,10 +10987,10 @@
         <v>508</v>
       </c>
       <c r="C512" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="D512" s="2" t="s">
         <v>651</v>
-      </c>
-      <c r="D512" s="2" t="s">
-        <v>652</v>
       </c>
       <c r="E512" s="1" t="s">
         <v>5</v>
@@ -11003,10 +11003,10 @@
         <v>509</v>
       </c>
       <c r="C513" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="D513" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="D513" s="2" t="s">
-        <v>654</v>
       </c>
       <c r="E513" s="1" t="s">
         <v>5</v>
@@ -11019,10 +11019,10 @@
         <v>510</v>
       </c>
       <c r="C514" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="D514" s="2" t="s">
         <v>655</v>
-      </c>
-      <c r="D514" s="2" t="s">
-        <v>656</v>
       </c>
       <c r="E514" s="1" t="s">
         <v>5</v>
@@ -11035,10 +11035,10 @@
         <v>511</v>
       </c>
       <c r="C515" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D515" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="D515" s="2" t="s">
-        <v>658</v>
       </c>
       <c r="E515" s="1" t="s">
         <v>5</v>
@@ -11051,13 +11051,13 @@
         <v>512</v>
       </c>
       <c r="C516" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="D516" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E516" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="D516" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E516" s="2" t="s">
-        <v>660</v>
       </c>
       <c r="F516" s="3"/>
     </row>
@@ -11067,10 +11067,10 @@
         <v>513</v>
       </c>
       <c r="C517" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="D517" s="2" t="s">
         <v>661</v>
-      </c>
-      <c r="D517" s="2" t="s">
-        <v>662</v>
       </c>
       <c r="E517" s="1" t="s">
         <v>5</v>
@@ -11083,10 +11083,10 @@
         <v>514</v>
       </c>
       <c r="C518" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="D518" s="2" t="s">
         <v>663</v>
-      </c>
-      <c r="D518" s="2" t="s">
-        <v>664</v>
       </c>
       <c r="E518" s="1" t="s">
         <v>5</v>
@@ -11099,10 +11099,10 @@
         <v>515</v>
       </c>
       <c r="C519" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="D519" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="D519" s="2" t="s">
-        <v>666</v>
       </c>
       <c r="E519" s="1" t="s">
         <v>5</v>
@@ -11115,10 +11115,10 @@
         <v>516</v>
       </c>
       <c r="C520" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="D520" s="2" t="s">
         <v>667</v>
-      </c>
-      <c r="D520" s="2" t="s">
-        <v>668</v>
       </c>
       <c r="E520" s="1" t="s">
         <v>5</v>
@@ -11131,10 +11131,10 @@
         <v>517</v>
       </c>
       <c r="C521" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="D521" s="2" t="s">
         <v>669</v>
-      </c>
-      <c r="D521" s="2" t="s">
-        <v>670</v>
       </c>
       <c r="E521" s="1" t="s">
         <v>5</v>
@@ -11147,7 +11147,7 @@
         <v>518</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D522" s="2" t="s">
         <v>5</v>
@@ -11163,10 +11163,10 @@
         <v>519</v>
       </c>
       <c r="C523" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="D523" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="D523" s="2" t="s">
-        <v>673</v>
       </c>
       <c r="E523" s="1" t="s">
         <v>5</v>
@@ -11179,10 +11179,10 @@
         <v>520</v>
       </c>
       <c r="C524" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="D524" s="2" t="s">
         <v>674</v>
-      </c>
-      <c r="D524" s="2" t="s">
-        <v>675</v>
       </c>
       <c r="E524" s="1" t="s">
         <v>5</v>
@@ -11195,10 +11195,10 @@
         <v>521</v>
       </c>
       <c r="C525" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="D525" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="D525" s="2" t="s">
-        <v>677</v>
       </c>
       <c r="E525" s="1" t="s">
         <v>5</v>
@@ -11211,10 +11211,10 @@
         <v>522</v>
       </c>
       <c r="C526" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="D526" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="D526" s="2" t="s">
-        <v>679</v>
       </c>
       <c r="E526" s="1" t="s">
         <v>5</v>
@@ -11227,10 +11227,10 @@
         <v>523</v>
       </c>
       <c r="C527" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="D527" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="D527" s="2" t="s">
-        <v>681</v>
       </c>
       <c r="E527" s="1" t="s">
         <v>5</v>
@@ -11243,10 +11243,10 @@
         <v>524</v>
       </c>
       <c r="C528" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="D528" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="D528" s="2" t="s">
-        <v>683</v>
       </c>
       <c r="E528" s="1" t="s">
         <v>5</v>
@@ -11259,10 +11259,10 @@
         <v>525</v>
       </c>
       <c r="C529" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>5</v>
@@ -11275,7 +11275,7 @@
         <v>526</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D530" s="2" t="s">
         <v>5</v>
@@ -11291,10 +11291,10 @@
         <v>527</v>
       </c>
       <c r="C531" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="D531" s="2" t="s">
         <v>686</v>
-      </c>
-      <c r="D531" s="2" t="s">
-        <v>687</v>
       </c>
       <c r="E531" s="1" t="s">
         <v>5</v>
@@ -11307,10 +11307,10 @@
         <v>528</v>
       </c>
       <c r="C532" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="D532" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="D532" s="2" t="s">
-        <v>689</v>
       </c>
       <c r="E532" s="1" t="s">
         <v>5</v>
@@ -11323,10 +11323,10 @@
         <v>529</v>
       </c>
       <c r="C533" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="D533" s="2" t="s">
         <v>690</v>
-      </c>
-      <c r="D533" s="2" t="s">
-        <v>691</v>
       </c>
       <c r="E533" s="1" t="s">
         <v>5</v>
@@ -11339,10 +11339,10 @@
         <v>530</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D534" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E534" s="1" t="s">
         <v>5</v>
@@ -11355,10 +11355,10 @@
         <v>531</v>
       </c>
       <c r="C535" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="D535" s="2" t="s">
         <v>693</v>
-      </c>
-      <c r="D535" s="2" t="s">
-        <v>694</v>
       </c>
       <c r="E535" s="1" t="s">
         <v>5</v>
@@ -11371,10 +11371,10 @@
         <v>532</v>
       </c>
       <c r="C536" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="D536" s="2" t="s">
         <v>695</v>
-      </c>
-      <c r="D536" s="2" t="s">
-        <v>696</v>
       </c>
       <c r="E536" s="1" t="s">
         <v>5</v>
@@ -11387,10 +11387,10 @@
         <v>533</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D537" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E537" s="1" t="s">
         <v>5</v>
@@ -11403,10 +11403,10 @@
         <v>534</v>
       </c>
       <c r="C538" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="D538" s="2" t="s">
         <v>698</v>
-      </c>
-      <c r="D538" s="2" t="s">
-        <v>699</v>
       </c>
       <c r="E538" s="1" t="s">
         <v>5</v>
@@ -11419,10 +11419,10 @@
         <v>535</v>
       </c>
       <c r="C539" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E539" s="1" t="s">
         <v>5</v>
@@ -11435,10 +11435,10 @@
         <v>536</v>
       </c>
       <c r="C540" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D540" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E540" s="1" t="s">
         <v>5</v>
@@ -11451,10 +11451,10 @@
         <v>537</v>
       </c>
       <c r="C541" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D541" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E541" s="1" t="s">
         <v>5</v>
@@ -11467,10 +11467,10 @@
         <v>538</v>
       </c>
       <c r="C542" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D542" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E542" s="1" t="s">
         <v>5</v>
@@ -11483,10 +11483,10 @@
         <v>539</v>
       </c>
       <c r="C543" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D543" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E543" s="1" t="s">
         <v>5</v>
@@ -11499,10 +11499,10 @@
         <v>540</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D544" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E544" s="1" t="s">
         <v>5</v>
@@ -11515,10 +11515,10 @@
         <v>541</v>
       </c>
       <c r="C545" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="D545" s="2" t="s">
         <v>706</v>
-      </c>
-      <c r="D545" s="2" t="s">
-        <v>707</v>
       </c>
       <c r="E545" s="1" t="s">
         <v>5</v>
@@ -11531,13 +11531,13 @@
         <v>542</v>
       </c>
       <c r="C546" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="D546" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E546" s="2" t="s">
         <v>708</v>
-      </c>
-      <c r="D546" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E546" s="2" t="s">
-        <v>709</v>
       </c>
       <c r="F546" s="3"/>
     </row>
@@ -11547,13 +11547,13 @@
         <v>543</v>
       </c>
       <c r="C547" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="D547" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E547" s="2" t="s">
         <v>710</v>
-      </c>
-      <c r="D547" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E547" s="2" t="s">
-        <v>711</v>
       </c>
       <c r="F547" s="3"/>
     </row>
@@ -11563,10 +11563,10 @@
         <v>544</v>
       </c>
       <c r="C548" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="D548" s="2" t="s">
         <v>712</v>
-      </c>
-      <c r="D548" s="2" t="s">
-        <v>713</v>
       </c>
       <c r="E548" s="1" t="s">
         <v>5</v>
@@ -11579,10 +11579,10 @@
         <v>545</v>
       </c>
       <c r="C549" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="D549" s="2" t="s">
         <v>714</v>
-      </c>
-      <c r="D549" s="2" t="s">
-        <v>715</v>
       </c>
       <c r="E549" s="1" t="s">
         <v>5</v>
@@ -11595,10 +11595,10 @@
         <v>546</v>
       </c>
       <c r="C550" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="D550" s="2" t="s">
         <v>716</v>
-      </c>
-      <c r="D550" s="2" t="s">
-        <v>717</v>
       </c>
       <c r="E550" s="1" t="s">
         <v>5</v>
@@ -11611,10 +11611,10 @@
         <v>547</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D551" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E551" s="1" t="s">
         <v>5</v>
@@ -11627,10 +11627,10 @@
         <v>548</v>
       </c>
       <c r="C552" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="D552" s="2" t="s">
         <v>719</v>
-      </c>
-      <c r="D552" s="2" t="s">
-        <v>720</v>
       </c>
       <c r="E552" s="1" t="s">
         <v>5</v>
@@ -11643,13 +11643,13 @@
         <v>549</v>
       </c>
       <c r="C553" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D553" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="E553" s="13" t="s">
         <v>804</v>
-      </c>
-      <c r="E553" s="13" t="s">
-        <v>805</v>
       </c>
       <c r="F553" s="3"/>
     </row>
@@ -11659,10 +11659,10 @@
         <v>550</v>
       </c>
       <c r="C554" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="D554" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="D554" s="2" t="s">
-        <v>723</v>
       </c>
       <c r="E554" s="1" t="s">
         <v>5</v>
@@ -11675,10 +11675,10 @@
         <v>551</v>
       </c>
       <c r="C555" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D555" s="2" t="s">
         <v>724</v>
-      </c>
-      <c r="D555" s="2" t="s">
-        <v>725</v>
       </c>
       <c r="E555" s="1" t="s">
         <v>5</v>
@@ -11691,10 +11691,10 @@
         <v>552</v>
       </c>
       <c r="C556" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="D556" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="D556" s="2" t="s">
-        <v>727</v>
       </c>
       <c r="E556" s="1" t="s">
         <v>5</v>
@@ -11707,10 +11707,10 @@
         <v>553</v>
       </c>
       <c r="C557" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="D557" s="2" t="s">
         <v>728</v>
-      </c>
-      <c r="D557" s="2" t="s">
-        <v>729</v>
       </c>
       <c r="E557" s="1" t="s">
         <v>5</v>
@@ -11723,10 +11723,10 @@
         <v>554</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E558" s="1" t="s">
         <v>5</v>
@@ -11739,10 +11739,10 @@
         <v>555</v>
       </c>
       <c r="C559" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>5</v>
@@ -11755,7 +11755,7 @@
         <v>556</v>
       </c>
       <c r="C560" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D560" s="2" t="s">
         <v>161</v>
@@ -11771,10 +11771,10 @@
         <v>557</v>
       </c>
       <c r="C561" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="D561" s="2" t="s">
         <v>733</v>
-      </c>
-      <c r="D561" s="2" t="s">
-        <v>734</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>5</v>
@@ -11787,10 +11787,10 @@
         <v>558</v>
       </c>
       <c r="C562" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="D562" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="D562" s="2" t="s">
-        <v>736</v>
       </c>
       <c r="E562" s="1" t="s">
         <v>5</v>
@@ -11803,10 +11803,10 @@
         <v>559</v>
       </c>
       <c r="C563" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="D563" s="2" t="s">
         <v>737</v>
-      </c>
-      <c r="D563" s="2" t="s">
-        <v>738</v>
       </c>
       <c r="E563" s="1" t="s">
         <v>5</v>
@@ -11819,10 +11819,10 @@
         <v>560</v>
       </c>
       <c r="C564" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E564" s="1" t="s">
         <v>5</v>
@@ -11835,10 +11835,10 @@
         <v>561</v>
       </c>
       <c r="C565" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E565" s="1" t="s">
         <v>5</v>
@@ -11851,10 +11851,10 @@
         <v>562</v>
       </c>
       <c r="C566" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E566" s="1" t="s">
         <v>5</v>
@@ -11867,10 +11867,10 @@
         <v>563</v>
       </c>
       <c r="C567" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E567" s="1" t="s">
         <v>5</v>
@@ -11883,10 +11883,10 @@
         <v>564</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D568" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E568" s="1" t="s">
         <v>5</v>
@@ -11899,10 +11899,10 @@
         <v>565</v>
       </c>
       <c r="C569" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D569" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E569" s="1" t="s">
         <v>5</v>
@@ -11915,10 +11915,10 @@
         <v>566</v>
       </c>
       <c r="C570" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D570" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E570" s="1" t="s">
         <v>5</v>
@@ -11931,10 +11931,10 @@
         <v>567</v>
       </c>
       <c r="C571" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D571" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E571" s="1" t="s">
         <v>5</v>
@@ -11947,10 +11947,10 @@
         <v>568</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E572" s="1" t="s">
         <v>5</v>
@@ -11963,10 +11963,10 @@
         <v>569</v>
       </c>
       <c r="C573" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E573" s="1" t="s">
         <v>5</v>
@@ -11979,10 +11979,10 @@
         <v>570</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E574" s="1" t="s">
         <v>5</v>
@@ -11995,10 +11995,10 @@
         <v>571</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E575" s="1" t="s">
         <v>5</v>
@@ -12011,10 +12011,10 @@
         <v>572</v>
       </c>
       <c r="C576" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E576" s="1" t="s">
         <v>5</v>
@@ -12027,10 +12027,10 @@
         <v>573</v>
       </c>
       <c r="C577" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="D577" s="2" t="s">
         <v>752</v>
-      </c>
-      <c r="D577" s="2" t="s">
-        <v>753</v>
       </c>
       <c r="E577" s="2" t="s">
         <v>5</v>
@@ -12043,10 +12043,10 @@
         <v>574</v>
       </c>
       <c r="C578" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="D578" s="2" t="s">
         <v>754</v>
-      </c>
-      <c r="D578" s="2" t="s">
-        <v>755</v>
       </c>
       <c r="E578" s="1" t="s">
         <v>5</v>
@@ -12059,10 +12059,10 @@
         <v>575</v>
       </c>
       <c r="C579" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D579" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="D579" s="2" t="s">
-        <v>757</v>
       </c>
       <c r="E579" s="1" t="s">
         <v>5</v>
@@ -12075,10 +12075,10 @@
         <v>576</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E580" s="1" t="s">
         <v>5</v>
@@ -12091,10 +12091,10 @@
         <v>577</v>
       </c>
       <c r="C581" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="D581" s="2" t="s">
         <v>759</v>
-      </c>
-      <c r="D581" s="2" t="s">
-        <v>760</v>
       </c>
       <c r="E581" s="1" t="s">
         <v>5</v>
@@ -12107,10 +12107,10 @@
         <v>578</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D582" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E582" s="7">
         <v>3520268948847</v>
@@ -12123,10 +12123,10 @@
         <v>579</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D583" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E583" s="1" t="s">
         <v>5</v>
@@ -12139,10 +12139,10 @@
         <v>580</v>
       </c>
       <c r="C584" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="D584" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="D584" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="E584" s="1" t="s">
         <v>5</v>
@@ -12155,10 +12155,10 @@
         <v>581</v>
       </c>
       <c r="C585" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="D585" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="D585" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="E585" s="1" t="s">
         <v>5</v>
@@ -12171,10 +12171,10 @@
         <v>582</v>
       </c>
       <c r="C586" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D586" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E586" s="1" t="s">
         <v>5</v>
@@ -12187,26 +12187,26 @@
         <v>583</v>
       </c>
       <c r="C587" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="D587" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="D587" s="2" t="s">
-        <v>769</v>
-      </c>
       <c r="E587" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F587" s="3"/>
     </row>
-    <row r="588" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="588" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B588" s="2">
         <f t="shared" si="9"/>
         <v>584</v>
       </c>
       <c r="C588" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="D588" s="2" t="s">
         <v>770</v>
-      </c>
-      <c r="D588" s="2" t="s">
-        <v>771</v>
       </c>
       <c r="E588" s="1" t="s">
         <v>5</v>
@@ -12219,10 +12219,10 @@
         <v>585</v>
       </c>
       <c r="C589" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="D589" s="2" t="s">
         <v>772</v>
-      </c>
-      <c r="D589" s="2" t="s">
-        <v>773</v>
       </c>
       <c r="E589" s="1" t="s">
         <v>5</v>
@@ -12235,10 +12235,10 @@
         <v>586</v>
       </c>
       <c r="C590" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="D590" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="D590" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="E590" s="1" t="s">
         <v>5</v>
@@ -12251,10 +12251,10 @@
         <v>587</v>
       </c>
       <c r="C591" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="D591" s="2" t="s">
         <v>776</v>
-      </c>
-      <c r="D591" s="2" t="s">
-        <v>777</v>
       </c>
       <c r="E591" s="1" t="s">
         <v>5</v>
@@ -12267,10 +12267,10 @@
         <v>588</v>
       </c>
       <c r="C592" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="D592" s="2" t="s">
         <v>778</v>
-      </c>
-      <c r="D592" s="2" t="s">
-        <v>779</v>
       </c>
       <c r="E592" s="1" t="s">
         <v>5</v>
@@ -12283,10 +12283,10 @@
         <v>589</v>
       </c>
       <c r="C593" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="D593" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="D593" s="2" t="s">
-        <v>781</v>
       </c>
       <c r="E593" s="1" t="s">
         <v>5</v>
@@ -12299,10 +12299,10 @@
         <v>590</v>
       </c>
       <c r="C594" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="D594" s="2" t="s">
         <v>782</v>
-      </c>
-      <c r="D594" s="2" t="s">
-        <v>783</v>
       </c>
       <c r="E594" s="1" t="s">
         <v>5</v>
@@ -12315,10 +12315,10 @@
         <v>591</v>
       </c>
       <c r="C595" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="D595" s="2" t="s">
         <v>784</v>
-      </c>
-      <c r="D595" s="2" t="s">
-        <v>785</v>
       </c>
       <c r="E595" s="1" t="s">
         <v>5</v>
@@ -12331,10 +12331,10 @@
         <v>592</v>
       </c>
       <c r="C596" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="D596" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="D596" s="2" t="s">
-        <v>787</v>
       </c>
       <c r="E596" s="1" t="s">
         <v>5</v>
@@ -12347,10 +12347,10 @@
         <v>593</v>
       </c>
       <c r="C597" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="D597" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="D597" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="E597" s="1" t="s">
         <v>5</v>
@@ -12363,10 +12363,10 @@
         <v>594</v>
       </c>
       <c r="C598" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="D598" s="2" t="s">
         <v>790</v>
-      </c>
-      <c r="D598" s="2" t="s">
-        <v>791</v>
       </c>
       <c r="E598" s="1" t="s">
         <v>5</v>
@@ -12378,10 +12378,10 @@
         <v>595</v>
       </c>
       <c r="C599" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="D599" s="2" t="s">
         <v>792</v>
-      </c>
-      <c r="D599" s="2" t="s">
-        <v>793</v>
       </c>
       <c r="E599" s="5"/>
     </row>
@@ -12390,10 +12390,10 @@
         <v>596</v>
       </c>
       <c r="C600" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="D600" s="6" t="s">
         <v>794</v>
-      </c>
-      <c r="D600" s="6" t="s">
-        <v>795</v>
       </c>
       <c r="E600" s="5"/>
     </row>
@@ -12405,10 +12405,10 @@
         <v>509</v>
       </c>
       <c r="C602" s="4" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D602" s="8" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="603" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
@@ -12416,10 +12416,10 @@
         <v>334</v>
       </c>
       <c r="C603" s="10" t="s">
+        <v>799</v>
+      </c>
+      <c r="D603" t="s">
         <v>800</v>
-      </c>
-      <c r="D603" t="s">
-        <v>801</v>
       </c>
       <c r="E603" s="11">
         <v>3277876171384</v>
@@ -12430,10 +12430,10 @@
         <v>263</v>
       </c>
       <c r="C604" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="D604" s="12" t="s">
         <v>802</v>
-      </c>
-      <c r="D604" s="12" t="s">
-        <v>803</v>
       </c>
       <c r="E604" s="11">
         <v>3520210170957</v>
@@ -12443,8 +12443,7 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Imperia Departmental Store"/>
-        <filter val="UMAIMA SUPER STORE IMPERIAL GARDEN"/>
+        <filter val="24/7 MART ASKARI X SECTOR F"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE17C365-0783-4123-8649-466980DF4654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC07A32A-D051-4B67-8B12-2965C24E1D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="806">
   <si>
     <t>Sr#</t>
   </si>
@@ -1030,9 +1030,6 @@
   </si>
   <si>
     <t>2157875-3</t>
-  </si>
-  <si>
-    <t>5440099376763</t>
   </si>
   <si>
     <t>Euro Store G.T Road</t>
@@ -2870,7 +2867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -4475,7 +4472,7 @@
         <v>101</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>90</v>
@@ -6725,7 +6722,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B246" s="2">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6741,7 +6738,7 @@
       </c>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B247" s="2">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6757,7 +6754,7 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B248" s="2">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6773,7 +6770,7 @@
       </c>
       <c r="F248" s="3"/>
     </row>
-    <row r="249" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B249" s="2">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -6789,7 +6786,7 @@
       </c>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B250" s="2">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6805,7 +6802,7 @@
       </c>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B251" s="2">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6821,7 +6818,7 @@
       </c>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B252" s="2">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -6837,7 +6834,7 @@
       </c>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B253" s="2">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -6853,7 +6850,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -6869,7 +6866,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -6885,7 +6882,7 @@
       </c>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B256" s="2">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -6896,34 +6893,34 @@
       <c r="D256" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="E256" s="2" t="s">
-        <v>334</v>
+      <c r="E256" s="2">
+        <v>5440099376763</v>
       </c>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B257" s="2">
         <f t="shared" si="3"/>
         <v>253</v>
       </c>
       <c r="C257" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D257" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="D257" s="2" t="s">
-        <v>336</v>
-      </c>
       <c r="E257" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B258" s="2">
         <f t="shared" si="3"/>
         <v>254</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>319</v>
@@ -6933,13 +6930,13 @@
       </c>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B259" s="2">
         <f t="shared" si="3"/>
         <v>255</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>331</v>
@@ -6949,13 +6946,13 @@
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B260" s="2">
         <f t="shared" si="3"/>
         <v>256</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>319</v>
@@ -6965,13 +6962,13 @@
       </c>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B261" s="2">
         <f t="shared" si="3"/>
         <v>257</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>319</v>
@@ -6981,29 +6978,29 @@
       </c>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B262" s="2">
         <f t="shared" si="3"/>
         <v>258</v>
       </c>
       <c r="C262" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D262" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="D262" s="2" t="s">
-        <v>341</v>
-      </c>
       <c r="E262" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B263" s="2">
         <f t="shared" si="3"/>
         <v>259</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>319</v>
@@ -7013,16 +7010,16 @@
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B264" s="2">
         <f t="shared" si="3"/>
         <v>260</v>
       </c>
       <c r="C264" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D264" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>5</v>
@@ -7035,10 +7032,10 @@
         <v>261</v>
       </c>
       <c r="C265" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D265" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="D265" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>5</v>
@@ -7051,10 +7048,10 @@
         <v>262</v>
       </c>
       <c r="C266" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D266" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>348</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>5</v>
@@ -7067,13 +7064,13 @@
         <v>263</v>
       </c>
       <c r="C267" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E267" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="D267" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E267" s="2" t="s">
-        <v>350</v>
       </c>
       <c r="F267" s="3"/>
     </row>
@@ -7083,10 +7080,10 @@
         <v>264</v>
       </c>
       <c r="C268" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D268" s="2" t="s">
         <v>351</v>
-      </c>
-      <c r="D268" s="2" t="s">
-        <v>352</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>5</v>
@@ -7099,10 +7096,10 @@
         <v>265</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>5</v>
@@ -7115,10 +7112,10 @@
         <v>266</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>5</v>
@@ -7131,10 +7128,10 @@
         <v>267</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>5</v>
@@ -7147,10 +7144,10 @@
         <v>268</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>5</v>
@@ -7163,10 +7160,10 @@
         <v>269</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>5</v>
@@ -7179,10 +7176,10 @@
         <v>270</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>5</v>
@@ -7195,10 +7192,10 @@
         <v>271</v>
       </c>
       <c r="C275" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D275" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="D275" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>5</v>
@@ -7211,10 +7208,10 @@
         <v>272</v>
       </c>
       <c r="C276" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D276" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="D276" s="2" t="s">
-        <v>362</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>5</v>
@@ -7227,10 +7224,10 @@
         <v>273</v>
       </c>
       <c r="C277" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D277" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="D277" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>5</v>
@@ -7243,13 +7240,13 @@
         <v>274</v>
       </c>
       <c r="C278" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E278" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="D278" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="F278" s="3"/>
     </row>
@@ -7259,10 +7256,10 @@
         <v>275</v>
       </c>
       <c r="C279" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D279" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="D279" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>5</v>
@@ -7275,10 +7272,10 @@
         <v>276</v>
       </c>
       <c r="C280" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D280" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="D280" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>5</v>
@@ -7291,10 +7288,10 @@
         <v>277</v>
       </c>
       <c r="C281" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D281" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="D281" s="2" t="s">
-        <v>372</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>5</v>
@@ -7307,10 +7304,10 @@
         <v>278</v>
       </c>
       <c r="C282" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D282" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="D282" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>5</v>
@@ -7323,10 +7320,10 @@
         <v>279</v>
       </c>
       <c r="C283" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D283" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="D283" s="2" t="s">
-        <v>376</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>5</v>
@@ -7339,10 +7336,10 @@
         <v>280</v>
       </c>
       <c r="C284" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D284" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>5</v>
@@ -7355,10 +7352,10 @@
         <v>281</v>
       </c>
       <c r="C285" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D285" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="D285" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>5</v>
@@ -7371,10 +7368,10 @@
         <v>282</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>5</v>
@@ -7387,10 +7384,10 @@
         <v>283</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>5</v>
@@ -7403,10 +7400,10 @@
         <v>284</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>5</v>
@@ -7419,10 +7416,10 @@
         <v>285</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>5</v>
@@ -7435,10 +7432,10 @@
         <v>286</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>5</v>
@@ -7451,10 +7448,10 @@
         <v>287</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>5</v>
@@ -7467,10 +7464,10 @@
         <v>288</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>5</v>
@@ -7483,10 +7480,10 @@
         <v>289</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>5</v>
@@ -7499,10 +7496,10 @@
         <v>290</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>5</v>
@@ -7515,10 +7512,10 @@
         <v>291</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>5</v>
@@ -7531,10 +7528,10 @@
         <v>292</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>5</v>
@@ -7547,10 +7544,10 @@
         <v>293</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>5</v>
@@ -7563,10 +7560,10 @@
         <v>294</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>5</v>
@@ -7579,10 +7576,10 @@
         <v>295</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>5</v>
@@ -7595,10 +7592,10 @@
         <v>296</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>5</v>
@@ -7611,10 +7608,10 @@
         <v>297</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>5</v>
@@ -7627,10 +7624,10 @@
         <v>298</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>5</v>
@@ -7643,10 +7640,10 @@
         <v>299</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>5</v>
@@ -7659,10 +7656,10 @@
         <v>300</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>5</v>
@@ -7675,10 +7672,10 @@
         <v>301</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>5</v>
@@ -7691,10 +7688,10 @@
         <v>302</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>5</v>
@@ -7707,10 +7704,10 @@
         <v>303</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>5</v>
@@ -7723,10 +7720,10 @@
         <v>304</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>5</v>
@@ -7739,10 +7736,10 @@
         <v>305</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>5</v>
@@ -7755,10 +7752,10 @@
         <v>306</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>5</v>
@@ -7771,10 +7768,10 @@
         <v>307</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>5</v>
@@ -7787,10 +7784,10 @@
         <v>308</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>5</v>
@@ -7803,10 +7800,10 @@
         <v>309</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>5</v>
@@ -7819,10 +7816,10 @@
         <v>310</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>5</v>
@@ -7835,10 +7832,10 @@
         <v>311</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>5</v>
@@ -7851,10 +7848,10 @@
         <v>312</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>5</v>
@@ -7867,10 +7864,10 @@
         <v>313</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>5</v>
@@ -7883,10 +7880,10 @@
         <v>314</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>5</v>
@@ -7899,10 +7896,10 @@
         <v>315</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>5</v>
@@ -7915,10 +7912,10 @@
         <v>316</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>5</v>
@@ -7931,10 +7928,10 @@
         <v>317</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>5</v>
@@ -7947,10 +7944,10 @@
         <v>318</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>5</v>
@@ -7963,10 +7960,10 @@
         <v>319</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>5</v>
@@ -7979,10 +7976,10 @@
         <v>320</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>5</v>
@@ -7995,10 +7992,10 @@
         <v>321</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>5</v>
@@ -8011,10 +8008,10 @@
         <v>322</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>5</v>
@@ -8027,10 +8024,10 @@
         <v>323</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>5</v>
@@ -8043,10 +8040,10 @@
         <v>324</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>5</v>
@@ -8059,10 +8056,10 @@
         <v>325</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>5</v>
@@ -8075,10 +8072,10 @@
         <v>326</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>5</v>
@@ -8091,10 +8088,10 @@
         <v>327</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>5</v>
@@ -8107,10 +8104,10 @@
         <v>328</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>5</v>
@@ -8123,10 +8120,10 @@
         <v>329</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>5</v>
@@ -8139,10 +8136,10 @@
         <v>330</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>5</v>
@@ -8155,10 +8152,10 @@
         <v>331</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>5</v>
@@ -8171,10 +8168,10 @@
         <v>332</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>5</v>
@@ -8187,10 +8184,10 @@
         <v>333</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>5</v>
@@ -8203,10 +8200,10 @@
         <v>334</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>5</v>
@@ -8219,10 +8216,10 @@
         <v>335</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>5</v>
@@ -8235,10 +8232,10 @@
         <v>336</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>5</v>
@@ -8251,10 +8248,10 @@
         <v>337</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>5</v>
@@ -8267,10 +8264,10 @@
         <v>338</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>5</v>
@@ -8283,10 +8280,10 @@
         <v>339</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>5</v>
@@ -8299,10 +8296,10 @@
         <v>340</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>5</v>
@@ -8315,10 +8312,10 @@
         <v>341</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>5</v>
@@ -8331,10 +8328,10 @@
         <v>342</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>5</v>
@@ -8347,10 +8344,10 @@
         <v>343</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>5</v>
@@ -8363,10 +8360,10 @@
         <v>344</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>5</v>
@@ -8379,10 +8376,10 @@
         <v>345</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>5</v>
@@ -8395,10 +8392,10 @@
         <v>346</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>5</v>
@@ -8411,10 +8408,10 @@
         <v>347</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>5</v>
@@ -8427,10 +8424,10 @@
         <v>348</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>5</v>
@@ -8443,10 +8440,10 @@
         <v>349</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>5</v>
@@ -8459,10 +8456,10 @@
         <v>350</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>5</v>
@@ -8475,10 +8472,10 @@
         <v>351</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>5</v>
@@ -8491,10 +8488,10 @@
         <v>352</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>5</v>
@@ -8507,10 +8504,10 @@
         <v>353</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>5</v>
@@ -8523,10 +8520,10 @@
         <v>354</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>5</v>
@@ -8539,10 +8536,10 @@
         <v>355</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>5</v>
@@ -8555,10 +8552,10 @@
         <v>356</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>5</v>
@@ -8571,10 +8568,10 @@
         <v>357</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>5</v>
@@ -8587,10 +8584,10 @@
         <v>358</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>5</v>
@@ -8603,10 +8600,10 @@
         <v>359</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>5</v>
@@ -8619,10 +8616,10 @@
         <v>360</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>5</v>
@@ -8635,10 +8632,10 @@
         <v>361</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>5</v>
@@ -8651,10 +8648,10 @@
         <v>362</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>5</v>
@@ -8667,10 +8664,10 @@
         <v>363</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>5</v>
@@ -8683,10 +8680,10 @@
         <v>364</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>5</v>
@@ -8699,10 +8696,10 @@
         <v>365</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>5</v>
@@ -8715,10 +8712,10 @@
         <v>366</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>5</v>
@@ -8731,10 +8728,10 @@
         <v>367</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>5</v>
@@ -8747,10 +8744,10 @@
         <v>368</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>5</v>
@@ -8763,10 +8760,10 @@
         <v>369</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>5</v>
@@ -8779,10 +8776,10 @@
         <v>370</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>5</v>
@@ -8795,10 +8792,10 @@
         <v>371</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>5</v>
@@ -8811,10 +8808,10 @@
         <v>372</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>5</v>
@@ -8827,10 +8824,10 @@
         <v>373</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>5</v>
@@ -8843,10 +8840,10 @@
         <v>374</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>5</v>
@@ -8859,10 +8856,10 @@
         <v>375</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>5</v>
@@ -8875,10 +8872,10 @@
         <v>376</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>5</v>
@@ -8891,10 +8888,10 @@
         <v>377</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>5</v>
@@ -8907,10 +8904,10 @@
         <v>378</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>5</v>
@@ -8923,10 +8920,10 @@
         <v>379</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>5</v>
@@ -8939,10 +8936,10 @@
         <v>380</v>
       </c>
       <c r="C384" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="D384" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="D384" s="2" t="s">
-        <v>480</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>5</v>
@@ -8955,10 +8952,10 @@
         <v>381</v>
       </c>
       <c r="C385" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="D385" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="D385" s="2" t="s">
-        <v>482</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>5</v>
@@ -8971,10 +8968,10 @@
         <v>382</v>
       </c>
       <c r="C386" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D386" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="D386" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>5</v>
@@ -8987,10 +8984,10 @@
         <v>383</v>
       </c>
       <c r="C387" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="D387" s="2" t="s">
         <v>485</v>
-      </c>
-      <c r="D387" s="2" t="s">
-        <v>486</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>5</v>
@@ -9003,10 +9000,10 @@
         <v>384</v>
       </c>
       <c r="C388" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="D388" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="D388" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>5</v>
@@ -9019,10 +9016,10 @@
         <v>385</v>
       </c>
       <c r="C389" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D389" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="D389" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>5</v>
@@ -9035,10 +9032,10 @@
         <v>386</v>
       </c>
       <c r="C390" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D390" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="D390" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>5</v>
@@ -9051,10 +9048,10 @@
         <v>387</v>
       </c>
       <c r="C391" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D391" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="D391" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>5</v>
@@ -9067,10 +9064,10 @@
         <v>388</v>
       </c>
       <c r="C392" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D392" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="D392" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>5</v>
@@ -9083,10 +9080,10 @@
         <v>389</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>5</v>
@@ -9099,10 +9096,10 @@
         <v>390</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>5</v>
@@ -9115,10 +9112,10 @@
         <v>391</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>5</v>
@@ -9131,10 +9128,10 @@
         <v>392</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>5</v>
@@ -9147,10 +9144,10 @@
         <v>393</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E397" s="2" t="s">
         <v>5</v>
@@ -9163,10 +9160,10 @@
         <v>394</v>
       </c>
       <c r="C398" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D398" s="2" t="s">
         <v>502</v>
-      </c>
-      <c r="D398" s="2" t="s">
-        <v>503</v>
       </c>
       <c r="E398" s="2" t="s">
         <v>5</v>
@@ -9179,13 +9176,13 @@
         <v>395</v>
       </c>
       <c r="C399" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D399" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E399" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="D399" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E399" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="F399" s="3"/>
     </row>
@@ -9195,10 +9192,10 @@
         <v>396</v>
       </c>
       <c r="C400" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D400" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="D400" s="2" t="s">
-        <v>507</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>5</v>
@@ -9211,10 +9208,10 @@
         <v>397</v>
       </c>
       <c r="C401" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="D401" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="D401" s="2" t="s">
-        <v>509</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>5</v>
@@ -9227,10 +9224,10 @@
         <v>398</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>5</v>
@@ -9243,10 +9240,10 @@
         <v>399</v>
       </c>
       <c r="C403" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="D403" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="D403" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="E403" s="2" t="s">
         <v>5</v>
@@ -9259,10 +9256,10 @@
         <v>400</v>
       </c>
       <c r="C404" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="D404" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="D404" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>5</v>
@@ -9275,10 +9272,10 @@
         <v>401</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>5</v>
@@ -9291,10 +9288,10 @@
         <v>402</v>
       </c>
       <c r="C406" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="D406" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="D406" s="2" t="s">
-        <v>517</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>5</v>
@@ -9307,10 +9304,10 @@
         <v>403</v>
       </c>
       <c r="C407" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D407" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="D407" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>5</v>
@@ -9323,10 +9320,10 @@
         <v>404</v>
       </c>
       <c r="C408" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="D408" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="D408" s="2" t="s">
-        <v>521</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>5</v>
@@ -9339,10 +9336,10 @@
         <v>405</v>
       </c>
       <c r="C409" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="D409" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="D409" s="2" t="s">
-        <v>523</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>5</v>
@@ -9355,10 +9352,10 @@
         <v>406</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>5</v>
@@ -9371,10 +9368,10 @@
         <v>407</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>5</v>
@@ -9387,10 +9384,10 @@
         <v>408</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>5</v>
@@ -9403,10 +9400,10 @@
         <v>409</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>5</v>
@@ -9419,10 +9416,10 @@
         <v>410</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>5</v>
@@ -9435,10 +9432,10 @@
         <v>411</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>5</v>
@@ -9451,10 +9448,10 @@
         <v>412</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>5</v>
@@ -9467,10 +9464,10 @@
         <v>413</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>5</v>
@@ -9483,10 +9480,10 @@
         <v>414</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>5</v>
@@ -9499,10 +9496,10 @@
         <v>415</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E419" s="7">
         <v>3277876126916</v>
@@ -9515,10 +9512,10 @@
         <v>416</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>5</v>
@@ -9531,10 +9528,10 @@
         <v>417</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>5</v>
@@ -9547,10 +9544,10 @@
         <v>418</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>5</v>
@@ -9563,10 +9560,10 @@
         <v>419</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>5</v>
@@ -9579,10 +9576,10 @@
         <v>420</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>5</v>
@@ -9595,10 +9592,10 @@
         <v>421</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>5</v>
@@ -9611,10 +9608,10 @@
         <v>422</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>5</v>
@@ -9627,10 +9624,10 @@
         <v>423</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>5</v>
@@ -9643,10 +9640,10 @@
         <v>424</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>5</v>
@@ -9659,10 +9656,10 @@
         <v>425</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>5</v>
@@ -9675,10 +9672,10 @@
         <v>426</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E430" s="7">
         <v>3520255124113</v>
@@ -9691,10 +9688,10 @@
         <v>427</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>5</v>
@@ -9707,10 +9704,10 @@
         <v>428</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>5</v>
@@ -9723,10 +9720,10 @@
         <v>429</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>5</v>
@@ -9739,10 +9736,10 @@
         <v>430</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>5</v>
@@ -9755,10 +9752,10 @@
         <v>431</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>5</v>
@@ -9771,10 +9768,10 @@
         <v>432</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>5</v>
@@ -9787,10 +9784,10 @@
         <v>433</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>5</v>
@@ -9803,10 +9800,10 @@
         <v>434</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>5</v>
@@ -9819,10 +9816,10 @@
         <v>435</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>5</v>
@@ -9835,10 +9832,10 @@
         <v>436</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>5</v>
@@ -9851,10 +9848,10 @@
         <v>437</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>5</v>
@@ -9867,10 +9864,10 @@
         <v>438</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>5</v>
@@ -9883,10 +9880,10 @@
         <v>439</v>
       </c>
       <c r="C443" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D443" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="D443" s="2" t="s">
-        <v>557</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>5</v>
@@ -9899,10 +9896,10 @@
         <v>440</v>
       </c>
       <c r="C444" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="D444" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="D444" s="2" t="s">
-        <v>559</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>5</v>
@@ -9915,10 +9912,10 @@
         <v>441</v>
       </c>
       <c r="C445" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="D445" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="D445" s="2" t="s">
-        <v>561</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>5</v>
@@ -9931,10 +9928,10 @@
         <v>442</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>5</v>
@@ -9947,10 +9944,10 @@
         <v>443</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>5</v>
@@ -9963,10 +9960,10 @@
         <v>444</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>5</v>
@@ -9979,10 +9976,10 @@
         <v>445</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>5</v>
@@ -9995,10 +9992,10 @@
         <v>446</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>5</v>
@@ -10011,10 +10008,10 @@
         <v>447</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>5</v>
@@ -10027,10 +10024,10 @@
         <v>448</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>5</v>
@@ -10043,10 +10040,10 @@
         <v>449</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>5</v>
@@ -10059,10 +10056,10 @@
         <v>450</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>5</v>
@@ -10075,10 +10072,10 @@
         <v>451</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>5</v>
@@ -10091,10 +10088,10 @@
         <v>452</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>5</v>
@@ -10107,10 +10104,10 @@
         <v>453</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>5</v>
@@ -10123,10 +10120,10 @@
         <v>454</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>5</v>
@@ -10139,10 +10136,10 @@
         <v>455</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>5</v>
@@ -10155,10 +10152,10 @@
         <v>456</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>5</v>
@@ -10171,10 +10168,10 @@
         <v>457</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>5</v>
@@ -10187,10 +10184,10 @@
         <v>458</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>5</v>
@@ -10203,10 +10200,10 @@
         <v>459</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>5</v>
@@ -10219,10 +10216,10 @@
         <v>460</v>
       </c>
       <c r="C464" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D464" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="D464" s="2" t="s">
-        <v>581</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>5</v>
@@ -10235,10 +10232,10 @@
         <v>461</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>5</v>
@@ -10251,10 +10248,10 @@
         <v>462</v>
       </c>
       <c r="C466" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="D466" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="D466" s="2" t="s">
-        <v>584</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>5</v>
@@ -10267,10 +10264,10 @@
         <v>463</v>
       </c>
       <c r="C467" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D467" s="2" t="s">
         <v>585</v>
-      </c>
-      <c r="D467" s="2" t="s">
-        <v>586</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>5</v>
@@ -10283,10 +10280,10 @@
         <v>464</v>
       </c>
       <c r="C468" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="D468" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="D468" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>5</v>
@@ -10299,7 +10296,7 @@
         <v>465</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D469" s="2" t="s">
         <v>114</v>
@@ -10315,10 +10312,10 @@
         <v>466</v>
       </c>
       <c r="C470" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="D470" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="D470" s="2" t="s">
-        <v>591</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>5</v>
@@ -10331,7 +10328,7 @@
         <v>467</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D471" s="2" t="s">
         <v>114</v>
@@ -10347,7 +10344,7 @@
         <v>468</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D472" s="2" t="s">
         <v>114</v>
@@ -10363,7 +10360,7 @@
         <v>469</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D473" s="2" t="s">
         <v>177</v>
@@ -10379,7 +10376,7 @@
         <v>470</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D474" s="2" t="s">
         <v>235</v>
@@ -10395,10 +10392,10 @@
         <v>471</v>
       </c>
       <c r="C475" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="D475" s="2" t="s">
         <v>596</v>
-      </c>
-      <c r="D475" s="2" t="s">
-        <v>597</v>
       </c>
       <c r="E475" s="1" t="s">
         <v>5</v>
@@ -10411,13 +10408,13 @@
         <v>472</v>
       </c>
       <c r="C476" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="D476" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E476" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="D476" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E476" s="2" t="s">
-        <v>599</v>
       </c>
       <c r="F476" s="3"/>
     </row>
@@ -10427,10 +10424,10 @@
         <v>473</v>
       </c>
       <c r="C477" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="D477" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="D477" s="2" t="s">
-        <v>601</v>
       </c>
       <c r="E477" s="1" t="s">
         <v>5</v>
@@ -10443,10 +10440,10 @@
         <v>474</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E478" s="1" t="s">
         <v>5</v>
@@ -10459,10 +10456,10 @@
         <v>475</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E479" s="1" t="s">
         <v>5</v>
@@ -10475,10 +10472,10 @@
         <v>476</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E480" s="1" t="s">
         <v>5</v>
@@ -10491,10 +10488,10 @@
         <v>477</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E481" s="1" t="s">
         <v>5</v>
@@ -10507,10 +10504,10 @@
         <v>478</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E482" s="1" t="s">
         <v>5</v>
@@ -10523,10 +10520,10 @@
         <v>479</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E483" s="1" t="s">
         <v>5</v>
@@ -10539,10 +10536,10 @@
         <v>480</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>5</v>
@@ -10555,10 +10552,10 @@
         <v>481</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>5</v>
@@ -10571,10 +10568,10 @@
         <v>482</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>5</v>
@@ -10587,10 +10584,10 @@
         <v>483</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>5</v>
@@ -10603,10 +10600,10 @@
         <v>484</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>5</v>
@@ -10619,10 +10616,10 @@
         <v>485</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E489" s="1" t="s">
         <v>5</v>
@@ -10635,10 +10632,10 @@
         <v>486</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E490" s="1" t="s">
         <v>5</v>
@@ -10651,10 +10648,10 @@
         <v>487</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>5</v>
@@ -10667,10 +10664,10 @@
         <v>488</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E492" s="1" t="s">
         <v>5</v>
@@ -10683,10 +10680,10 @@
         <v>489</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D493" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E493" s="1" t="s">
         <v>5</v>
@@ -10699,10 +10696,10 @@
         <v>490</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E494" s="1" t="s">
         <v>5</v>
@@ -10715,10 +10712,10 @@
         <v>491</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E495" s="1" t="s">
         <v>5</v>
@@ -10731,10 +10728,10 @@
         <v>492</v>
       </c>
       <c r="C496" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="D496" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="D496" s="2" t="s">
-        <v>621</v>
       </c>
       <c r="E496" s="2" t="s">
         <v>5</v>
@@ -10747,13 +10744,13 @@
         <v>493</v>
       </c>
       <c r="C497" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="D497" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E497" s="2" t="s">
         <v>622</v>
-      </c>
-      <c r="D497" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E497" s="2" t="s">
-        <v>623</v>
       </c>
       <c r="F497" s="3"/>
     </row>
@@ -10763,10 +10760,10 @@
         <v>494</v>
       </c>
       <c r="C498" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="D498" s="2" t="s">
         <v>624</v>
-      </c>
-      <c r="D498" s="2" t="s">
-        <v>625</v>
       </c>
       <c r="E498" s="2" t="s">
         <v>5</v>
@@ -10779,10 +10776,10 @@
         <v>495</v>
       </c>
       <c r="C499" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="D499" s="2" t="s">
         <v>626</v>
-      </c>
-      <c r="D499" s="2" t="s">
-        <v>627</v>
       </c>
       <c r="E499" s="2" t="s">
         <v>5</v>
@@ -10795,13 +10792,13 @@
         <v>496</v>
       </c>
       <c r="C500" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="D500" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E500" s="2" t="s">
         <v>628</v>
-      </c>
-      <c r="D500" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E500" s="2" t="s">
-        <v>629</v>
       </c>
       <c r="F500" s="3"/>
     </row>
@@ -10811,10 +10808,10 @@
         <v>497</v>
       </c>
       <c r="C501" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="D501" s="2" t="s">
         <v>630</v>
-      </c>
-      <c r="D501" s="2" t="s">
-        <v>631</v>
       </c>
       <c r="E501" s="1" t="s">
         <v>5</v>
@@ -10827,10 +10824,10 @@
         <v>498</v>
       </c>
       <c r="C502" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="D502" s="2" t="s">
         <v>632</v>
-      </c>
-      <c r="D502" s="2" t="s">
-        <v>633</v>
       </c>
       <c r="E502" s="1" t="s">
         <v>5</v>
@@ -10843,10 +10840,10 @@
         <v>499</v>
       </c>
       <c r="C503" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D503" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="D503" s="2" t="s">
-        <v>635</v>
       </c>
       <c r="E503" s="1" t="s">
         <v>5</v>
@@ -10859,10 +10856,10 @@
         <v>500</v>
       </c>
       <c r="C504" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="D504" s="2" t="s">
         <v>636</v>
-      </c>
-      <c r="D504" s="2" t="s">
-        <v>637</v>
       </c>
       <c r="E504" s="1" t="s">
         <v>5</v>
@@ -10875,10 +10872,10 @@
         <v>501</v>
       </c>
       <c r="C505" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="D505" s="2" t="s">
         <v>638</v>
-      </c>
-      <c r="D505" s="2" t="s">
-        <v>639</v>
       </c>
       <c r="E505" s="1" t="s">
         <v>5</v>
@@ -10891,10 +10888,10 @@
         <v>502</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E506" s="1" t="s">
         <v>5</v>
@@ -10907,10 +10904,10 @@
         <v>503</v>
       </c>
       <c r="C507" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D507" s="2" t="s">
         <v>641</v>
-      </c>
-      <c r="D507" s="2" t="s">
-        <v>642</v>
       </c>
       <c r="E507" s="1" t="s">
         <v>5</v>
@@ -10923,10 +10920,10 @@
         <v>504</v>
       </c>
       <c r="C508" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="D508" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="D508" s="2" t="s">
-        <v>644</v>
       </c>
       <c r="E508" s="1" t="s">
         <v>5</v>
@@ -10939,10 +10936,10 @@
         <v>505</v>
       </c>
       <c r="C509" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="D509" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="D509" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="E509" s="1" t="s">
         <v>5</v>
@@ -10955,10 +10952,10 @@
         <v>506</v>
       </c>
       <c r="C510" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="D510" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="D510" s="2" t="s">
-        <v>648</v>
       </c>
       <c r="E510" s="1" t="s">
         <v>5</v>
@@ -10971,10 +10968,10 @@
         <v>507</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E511" s="1" t="s">
         <v>5</v>
@@ -10987,10 +10984,10 @@
         <v>508</v>
       </c>
       <c r="C512" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="D512" s="2" t="s">
         <v>650</v>
-      </c>
-      <c r="D512" s="2" t="s">
-        <v>651</v>
       </c>
       <c r="E512" s="1" t="s">
         <v>5</v>
@@ -11003,10 +11000,10 @@
         <v>509</v>
       </c>
       <c r="C513" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="D513" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="D513" s="2" t="s">
-        <v>653</v>
       </c>
       <c r="E513" s="1" t="s">
         <v>5</v>
@@ -11019,10 +11016,10 @@
         <v>510</v>
       </c>
       <c r="C514" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D514" s="2" t="s">
         <v>654</v>
-      </c>
-      <c r="D514" s="2" t="s">
-        <v>655</v>
       </c>
       <c r="E514" s="1" t="s">
         <v>5</v>
@@ -11035,10 +11032,10 @@
         <v>511</v>
       </c>
       <c r="C515" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="D515" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="D515" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="E515" s="1" t="s">
         <v>5</v>
@@ -11051,13 +11048,13 @@
         <v>512</v>
       </c>
       <c r="C516" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="D516" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E516" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="D516" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E516" s="2" t="s">
-        <v>659</v>
       </c>
       <c r="F516" s="3"/>
     </row>
@@ -11067,10 +11064,10 @@
         <v>513</v>
       </c>
       <c r="C517" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="D517" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="D517" s="2" t="s">
-        <v>661</v>
       </c>
       <c r="E517" s="1" t="s">
         <v>5</v>
@@ -11083,10 +11080,10 @@
         <v>514</v>
       </c>
       <c r="C518" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="D518" s="2" t="s">
         <v>662</v>
-      </c>
-      <c r="D518" s="2" t="s">
-        <v>663</v>
       </c>
       <c r="E518" s="1" t="s">
         <v>5</v>
@@ -11099,10 +11096,10 @@
         <v>515</v>
       </c>
       <c r="C519" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="D519" s="2" t="s">
         <v>664</v>
-      </c>
-      <c r="D519" s="2" t="s">
-        <v>665</v>
       </c>
       <c r="E519" s="1" t="s">
         <v>5</v>
@@ -11115,10 +11112,10 @@
         <v>516</v>
       </c>
       <c r="C520" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="D520" s="2" t="s">
         <v>666</v>
-      </c>
-      <c r="D520" s="2" t="s">
-        <v>667</v>
       </c>
       <c r="E520" s="1" t="s">
         <v>5</v>
@@ -11131,10 +11128,10 @@
         <v>517</v>
       </c>
       <c r="C521" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="D521" s="2" t="s">
         <v>668</v>
-      </c>
-      <c r="D521" s="2" t="s">
-        <v>669</v>
       </c>
       <c r="E521" s="1" t="s">
         <v>5</v>
@@ -11147,7 +11144,7 @@
         <v>518</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D522" s="2" t="s">
         <v>5</v>
@@ -11163,10 +11160,10 @@
         <v>519</v>
       </c>
       <c r="C523" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D523" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="D523" s="2" t="s">
-        <v>672</v>
       </c>
       <c r="E523" s="1" t="s">
         <v>5</v>
@@ -11179,10 +11176,10 @@
         <v>520</v>
       </c>
       <c r="C524" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="D524" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="D524" s="2" t="s">
-        <v>674</v>
       </c>
       <c r="E524" s="1" t="s">
         <v>5</v>
@@ -11195,10 +11192,10 @@
         <v>521</v>
       </c>
       <c r="C525" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="D525" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="D525" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="E525" s="1" t="s">
         <v>5</v>
@@ -11211,10 +11208,10 @@
         <v>522</v>
       </c>
       <c r="C526" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="D526" s="2" t="s">
         <v>677</v>
-      </c>
-      <c r="D526" s="2" t="s">
-        <v>678</v>
       </c>
       <c r="E526" s="1" t="s">
         <v>5</v>
@@ -11227,10 +11224,10 @@
         <v>523</v>
       </c>
       <c r="C527" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="D527" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="D527" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="E527" s="1" t="s">
         <v>5</v>
@@ -11243,10 +11240,10 @@
         <v>524</v>
       </c>
       <c r="C528" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="D528" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="D528" s="2" t="s">
-        <v>682</v>
       </c>
       <c r="E528" s="1" t="s">
         <v>5</v>
@@ -11259,10 +11256,10 @@
         <v>525</v>
       </c>
       <c r="C529" s="1" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>5</v>
@@ -11275,7 +11272,7 @@
         <v>526</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D530" s="2" t="s">
         <v>5</v>
@@ -11291,10 +11288,10 @@
         <v>527</v>
       </c>
       <c r="C531" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="D531" s="2" t="s">
         <v>685</v>
-      </c>
-      <c r="D531" s="2" t="s">
-        <v>686</v>
       </c>
       <c r="E531" s="1" t="s">
         <v>5</v>
@@ -11307,10 +11304,10 @@
         <v>528</v>
       </c>
       <c r="C532" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="D532" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="D532" s="2" t="s">
-        <v>688</v>
       </c>
       <c r="E532" s="1" t="s">
         <v>5</v>
@@ -11323,10 +11320,10 @@
         <v>529</v>
       </c>
       <c r="C533" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="D533" s="2" t="s">
         <v>689</v>
-      </c>
-      <c r="D533" s="2" t="s">
-        <v>690</v>
       </c>
       <c r="E533" s="1" t="s">
         <v>5</v>
@@ -11339,10 +11336,10 @@
         <v>530</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D534" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E534" s="1" t="s">
         <v>5</v>
@@ -11355,10 +11352,10 @@
         <v>531</v>
       </c>
       <c r="C535" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="D535" s="2" t="s">
         <v>692</v>
-      </c>
-      <c r="D535" s="2" t="s">
-        <v>693</v>
       </c>
       <c r="E535" s="1" t="s">
         <v>5</v>
@@ -11371,10 +11368,10 @@
         <v>532</v>
       </c>
       <c r="C536" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="D536" s="2" t="s">
         <v>694</v>
-      </c>
-      <c r="D536" s="2" t="s">
-        <v>695</v>
       </c>
       <c r="E536" s="1" t="s">
         <v>5</v>
@@ -11387,10 +11384,10 @@
         <v>533</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D537" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E537" s="1" t="s">
         <v>5</v>
@@ -11403,10 +11400,10 @@
         <v>534</v>
       </c>
       <c r="C538" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="D538" s="2" t="s">
         <v>697</v>
-      </c>
-      <c r="D538" s="2" t="s">
-        <v>698</v>
       </c>
       <c r="E538" s="1" t="s">
         <v>5</v>
@@ -11419,10 +11416,10 @@
         <v>535</v>
       </c>
       <c r="C539" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E539" s="1" t="s">
         <v>5</v>
@@ -11435,10 +11432,10 @@
         <v>536</v>
       </c>
       <c r="C540" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D540" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E540" s="1" t="s">
         <v>5</v>
@@ -11451,10 +11448,10 @@
         <v>537</v>
       </c>
       <c r="C541" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D541" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E541" s="1" t="s">
         <v>5</v>
@@ -11467,10 +11464,10 @@
         <v>538</v>
       </c>
       <c r="C542" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D542" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E542" s="1" t="s">
         <v>5</v>
@@ -11483,10 +11480,10 @@
         <v>539</v>
       </c>
       <c r="C543" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D543" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E543" s="1" t="s">
         <v>5</v>
@@ -11499,10 +11496,10 @@
         <v>540</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D544" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E544" s="1" t="s">
         <v>5</v>
@@ -11515,10 +11512,10 @@
         <v>541</v>
       </c>
       <c r="C545" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="D545" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="D545" s="2" t="s">
-        <v>706</v>
       </c>
       <c r="E545" s="1" t="s">
         <v>5</v>
@@ -11531,13 +11528,13 @@
         <v>542</v>
       </c>
       <c r="C546" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="D546" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E546" s="2" t="s">
         <v>707</v>
-      </c>
-      <c r="D546" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E546" s="2" t="s">
-        <v>708</v>
       </c>
       <c r="F546" s="3"/>
     </row>
@@ -11547,13 +11544,13 @@
         <v>543</v>
       </c>
       <c r="C547" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="D547" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E547" s="2" t="s">
         <v>709</v>
-      </c>
-      <c r="D547" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E547" s="2" t="s">
-        <v>710</v>
       </c>
       <c r="F547" s="3"/>
     </row>
@@ -11563,10 +11560,10 @@
         <v>544</v>
       </c>
       <c r="C548" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="D548" s="2" t="s">
         <v>711</v>
-      </c>
-      <c r="D548" s="2" t="s">
-        <v>712</v>
       </c>
       <c r="E548" s="1" t="s">
         <v>5</v>
@@ -11579,10 +11576,10 @@
         <v>545</v>
       </c>
       <c r="C549" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="D549" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="D549" s="2" t="s">
-        <v>714</v>
       </c>
       <c r="E549" s="1" t="s">
         <v>5</v>
@@ -11595,10 +11592,10 @@
         <v>546</v>
       </c>
       <c r="C550" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="D550" s="2" t="s">
         <v>715</v>
-      </c>
-      <c r="D550" s="2" t="s">
-        <v>716</v>
       </c>
       <c r="E550" s="1" t="s">
         <v>5</v>
@@ -11611,10 +11608,10 @@
         <v>547</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D551" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E551" s="1" t="s">
         <v>5</v>
@@ -11627,10 +11624,10 @@
         <v>548</v>
       </c>
       <c r="C552" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="D552" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="D552" s="2" t="s">
-        <v>719</v>
       </c>
       <c r="E552" s="1" t="s">
         <v>5</v>
@@ -11643,13 +11640,13 @@
         <v>549</v>
       </c>
       <c r="C553" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D553" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="E553" s="13" t="s">
         <v>803</v>
-      </c>
-      <c r="E553" s="13" t="s">
-        <v>804</v>
       </c>
       <c r="F553" s="3"/>
     </row>
@@ -11659,10 +11656,10 @@
         <v>550</v>
       </c>
       <c r="C554" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="D554" s="2" t="s">
         <v>721</v>
-      </c>
-      <c r="D554" s="2" t="s">
-        <v>722</v>
       </c>
       <c r="E554" s="1" t="s">
         <v>5</v>
@@ -11675,10 +11672,10 @@
         <v>551</v>
       </c>
       <c r="C555" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="D555" s="2" t="s">
         <v>723</v>
-      </c>
-      <c r="D555" s="2" t="s">
-        <v>724</v>
       </c>
       <c r="E555" s="1" t="s">
         <v>5</v>
@@ -11691,10 +11688,10 @@
         <v>552</v>
       </c>
       <c r="C556" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="D556" s="2" t="s">
         <v>725</v>
-      </c>
-      <c r="D556" s="2" t="s">
-        <v>726</v>
       </c>
       <c r="E556" s="1" t="s">
         <v>5</v>
@@ -11707,10 +11704,10 @@
         <v>553</v>
       </c>
       <c r="C557" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="D557" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="D557" s="2" t="s">
-        <v>728</v>
       </c>
       <c r="E557" s="1" t="s">
         <v>5</v>
@@ -11723,10 +11720,10 @@
         <v>554</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E558" s="1" t="s">
         <v>5</v>
@@ -11739,10 +11736,10 @@
         <v>555</v>
       </c>
       <c r="C559" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>5</v>
@@ -11755,7 +11752,7 @@
         <v>556</v>
       </c>
       <c r="C560" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D560" s="2" t="s">
         <v>161</v>
@@ -11771,10 +11768,10 @@
         <v>557</v>
       </c>
       <c r="C561" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="D561" s="2" t="s">
         <v>732</v>
-      </c>
-      <c r="D561" s="2" t="s">
-        <v>733</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>5</v>
@@ -11787,10 +11784,10 @@
         <v>558</v>
       </c>
       <c r="C562" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="D562" s="2" t="s">
         <v>734</v>
-      </c>
-      <c r="D562" s="2" t="s">
-        <v>735</v>
       </c>
       <c r="E562" s="1" t="s">
         <v>5</v>
@@ -11803,10 +11800,10 @@
         <v>559</v>
       </c>
       <c r="C563" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="D563" s="2" t="s">
         <v>736</v>
-      </c>
-      <c r="D563" s="2" t="s">
-        <v>737</v>
       </c>
       <c r="E563" s="1" t="s">
         <v>5</v>
@@ -11819,10 +11816,10 @@
         <v>560</v>
       </c>
       <c r="C564" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E564" s="1" t="s">
         <v>5</v>
@@ -11835,10 +11832,10 @@
         <v>561</v>
       </c>
       <c r="C565" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E565" s="1" t="s">
         <v>5</v>
@@ -11851,10 +11848,10 @@
         <v>562</v>
       </c>
       <c r="C566" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E566" s="1" t="s">
         <v>5</v>
@@ -11867,10 +11864,10 @@
         <v>563</v>
       </c>
       <c r="C567" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E567" s="1" t="s">
         <v>5</v>
@@ -11883,10 +11880,10 @@
         <v>564</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D568" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E568" s="1" t="s">
         <v>5</v>
@@ -11899,10 +11896,10 @@
         <v>565</v>
       </c>
       <c r="C569" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D569" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E569" s="1" t="s">
         <v>5</v>
@@ -11915,10 +11912,10 @@
         <v>566</v>
       </c>
       <c r="C570" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D570" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E570" s="1" t="s">
         <v>5</v>
@@ -11931,10 +11928,10 @@
         <v>567</v>
       </c>
       <c r="C571" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D571" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E571" s="1" t="s">
         <v>5</v>
@@ -11947,10 +11944,10 @@
         <v>568</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E572" s="1" t="s">
         <v>5</v>
@@ -11963,10 +11960,10 @@
         <v>569</v>
       </c>
       <c r="C573" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E573" s="1" t="s">
         <v>5</v>
@@ -11979,10 +11976,10 @@
         <v>570</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E574" s="1" t="s">
         <v>5</v>
@@ -11995,10 +11992,10 @@
         <v>571</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E575" s="1" t="s">
         <v>5</v>
@@ -12011,10 +12008,10 @@
         <v>572</v>
       </c>
       <c r="C576" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E576" s="1" t="s">
         <v>5</v>
@@ -12027,10 +12024,10 @@
         <v>573</v>
       </c>
       <c r="C577" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="D577" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="D577" s="2" t="s">
-        <v>752</v>
       </c>
       <c r="E577" s="2" t="s">
         <v>5</v>
@@ -12043,10 +12040,10 @@
         <v>574</v>
       </c>
       <c r="C578" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="D578" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="D578" s="2" t="s">
-        <v>754</v>
       </c>
       <c r="E578" s="1" t="s">
         <v>5</v>
@@ -12059,10 +12056,10 @@
         <v>575</v>
       </c>
       <c r="C579" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="D579" s="2" t="s">
         <v>755</v>
-      </c>
-      <c r="D579" s="2" t="s">
-        <v>756</v>
       </c>
       <c r="E579" s="1" t="s">
         <v>5</v>
@@ -12075,10 +12072,10 @@
         <v>576</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E580" s="1" t="s">
         <v>5</v>
@@ -12091,10 +12088,10 @@
         <v>577</v>
       </c>
       <c r="C581" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="D581" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="D581" s="2" t="s">
-        <v>759</v>
       </c>
       <c r="E581" s="1" t="s">
         <v>5</v>
@@ -12107,10 +12104,10 @@
         <v>578</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D582" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E582" s="7">
         <v>3520268948847</v>
@@ -12123,10 +12120,10 @@
         <v>579</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D583" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E583" s="1" t="s">
         <v>5</v>
@@ -12139,10 +12136,10 @@
         <v>580</v>
       </c>
       <c r="C584" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="D584" s="2" t="s">
         <v>762</v>
-      </c>
-      <c r="D584" s="2" t="s">
-        <v>763</v>
       </c>
       <c r="E584" s="1" t="s">
         <v>5</v>
@@ -12155,10 +12152,10 @@
         <v>581</v>
       </c>
       <c r="C585" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="D585" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="D585" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="E585" s="1" t="s">
         <v>5</v>
@@ -12171,10 +12168,10 @@
         <v>582</v>
       </c>
       <c r="C586" s="1" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D586" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E586" s="1" t="s">
         <v>5</v>
@@ -12187,10 +12184,10 @@
         <v>583</v>
       </c>
       <c r="C587" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="D587" s="2" t="s">
         <v>767</v>
-      </c>
-      <c r="D587" s="2" t="s">
-        <v>768</v>
       </c>
       <c r="E587" s="1" t="s">
         <v>5</v>
@@ -12203,10 +12200,10 @@
         <v>584</v>
       </c>
       <c r="C588" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="D588" s="2" t="s">
         <v>769</v>
-      </c>
-      <c r="D588" s="2" t="s">
-        <v>770</v>
       </c>
       <c r="E588" s="1" t="s">
         <v>5</v>
@@ -12219,10 +12216,10 @@
         <v>585</v>
       </c>
       <c r="C589" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="D589" s="2" t="s">
         <v>771</v>
-      </c>
-      <c r="D589" s="2" t="s">
-        <v>772</v>
       </c>
       <c r="E589" s="1" t="s">
         <v>5</v>
@@ -12235,10 +12232,10 @@
         <v>586</v>
       </c>
       <c r="C590" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="D590" s="2" t="s">
         <v>773</v>
-      </c>
-      <c r="D590" s="2" t="s">
-        <v>774</v>
       </c>
       <c r="E590" s="1" t="s">
         <v>5</v>
@@ -12251,10 +12248,10 @@
         <v>587</v>
       </c>
       <c r="C591" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="D591" s="2" t="s">
         <v>775</v>
-      </c>
-      <c r="D591" s="2" t="s">
-        <v>776</v>
       </c>
       <c r="E591" s="1" t="s">
         <v>5</v>
@@ -12267,10 +12264,10 @@
         <v>588</v>
       </c>
       <c r="C592" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="D592" s="2" t="s">
         <v>777</v>
-      </c>
-      <c r="D592" s="2" t="s">
-        <v>778</v>
       </c>
       <c r="E592" s="1" t="s">
         <v>5</v>
@@ -12283,10 +12280,10 @@
         <v>589</v>
       </c>
       <c r="C593" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="D593" s="2" t="s">
         <v>779</v>
-      </c>
-      <c r="D593" s="2" t="s">
-        <v>780</v>
       </c>
       <c r="E593" s="1" t="s">
         <v>5</v>
@@ -12299,10 +12296,10 @@
         <v>590</v>
       </c>
       <c r="C594" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="D594" s="2" t="s">
         <v>781</v>
-      </c>
-      <c r="D594" s="2" t="s">
-        <v>782</v>
       </c>
       <c r="E594" s="1" t="s">
         <v>5</v>
@@ -12315,10 +12312,10 @@
         <v>591</v>
       </c>
       <c r="C595" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="D595" s="2" t="s">
         <v>783</v>
-      </c>
-      <c r="D595" s="2" t="s">
-        <v>784</v>
       </c>
       <c r="E595" s="1" t="s">
         <v>5</v>
@@ -12331,10 +12328,10 @@
         <v>592</v>
       </c>
       <c r="C596" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="D596" s="2" t="s">
         <v>785</v>
-      </c>
-      <c r="D596" s="2" t="s">
-        <v>786</v>
       </c>
       <c r="E596" s="1" t="s">
         <v>5</v>
@@ -12347,10 +12344,10 @@
         <v>593</v>
       </c>
       <c r="C597" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="D597" s="2" t="s">
         <v>787</v>
-      </c>
-      <c r="D597" s="2" t="s">
-        <v>788</v>
       </c>
       <c r="E597" s="1" t="s">
         <v>5</v>
@@ -12363,10 +12360,10 @@
         <v>594</v>
       </c>
       <c r="C598" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="D598" s="2" t="s">
         <v>789</v>
-      </c>
-      <c r="D598" s="2" t="s">
-        <v>790</v>
       </c>
       <c r="E598" s="1" t="s">
         <v>5</v>
@@ -12378,10 +12375,10 @@
         <v>595</v>
       </c>
       <c r="C599" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="D599" s="2" t="s">
         <v>791</v>
-      </c>
-      <c r="D599" s="2" t="s">
-        <v>792</v>
       </c>
       <c r="E599" s="5"/>
     </row>
@@ -12390,10 +12387,10 @@
         <v>596</v>
       </c>
       <c r="C600" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="D600" s="6" t="s">
         <v>793</v>
-      </c>
-      <c r="D600" s="6" t="s">
-        <v>794</v>
       </c>
       <c r="E600" s="5"/>
     </row>
@@ -12405,10 +12402,10 @@
         <v>509</v>
       </c>
       <c r="C602" s="4" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D602" s="8" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="603" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
@@ -12416,10 +12413,10 @@
         <v>334</v>
       </c>
       <c r="C603" s="10" t="s">
+        <v>798</v>
+      </c>
+      <c r="D603" t="s">
         <v>799</v>
-      </c>
-      <c r="D603" t="s">
-        <v>800</v>
       </c>
       <c r="E603" s="11">
         <v>3277876171384</v>
@@ -12430,10 +12427,10 @@
         <v>263</v>
       </c>
       <c r="C604" s="10" t="s">
+        <v>800</v>
+      </c>
+      <c r="D604" s="12" t="s">
         <v>801</v>
-      </c>
-      <c r="D604" s="12" t="s">
-        <v>802</v>
       </c>
       <c r="E604" s="11">
         <v>3520210170957</v>
@@ -12443,7 +12440,25 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="24/7 MART ASKARI X SECTOR F"/>
+        <filter val="EURO RANJERS MART"/>
+        <filter val="Euro store  (Academy Road)"/>
+        <filter val="EURO STORE (N F C )"/>
+        <filter val="EURO STORE (Rahamt chowk)"/>
+        <filter val="Euro Store (Scheme Mor)"/>
+        <filter val="Euro Store Airport Road"/>
+        <filter val="Euro Store Bedian Road"/>
+        <filter val="Euro Store College Road"/>
+        <filter val="EURO STORE CROWN BEHRIA TOWN"/>
+        <filter val="Euro Store E-2 (Wapda Town)"/>
+        <filter val="EURO STORE FATAH GARH"/>
+        <filter val="Euro Store G.T Road"/>
+        <filter val="Euro Store Garhi Shahu"/>
+        <filter val="EURO Store Hypermarket (Raiwind Road)"/>
+        <filter val="Euro Store Iqbal Town (Ranchna)"/>
+        <filter val="EURO STORE MARIYA STOP"/>
+        <filter val="EURO STORE PH VIII PARK VIEW"/>
+        <filter val="Euro Stores (G-1 Market)"/>
+        <filter val="EURO Stores (Nishat Colony)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC07A32A-D051-4B67-8B12-2965C24E1D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A57CC52-93F5-4DE9-85F2-EBC9C7769AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1011,9 +1011,6 @@
     <t>6616156-4</t>
   </si>
   <si>
-    <t>Euro Store College Road</t>
-  </si>
-  <si>
     <t>EURO STORE CROWN BEHRIA TOWN</t>
   </si>
   <si>
@@ -2446,6 +2443,9 @@
   </si>
   <si>
     <t>Euro Store Iqbal Town (Ranchna)</t>
+  </si>
+  <si>
+    <t>Euro Store College Road (Model Town)</t>
   </si>
 </sst>
 </file>
@@ -4472,7 +4472,7 @@
         <v>101</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>90</v>
@@ -6840,7 +6840,7 @@
         <v>249</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>327</v>
+        <v>805</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>319</v>
@@ -6856,10 +6856,10 @@
         <v>250</v>
       </c>
       <c r="C254" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D254" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="D254" s="2" t="s">
-        <v>329</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>5</v>
@@ -6872,10 +6872,10 @@
         <v>251</v>
       </c>
       <c r="C255" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D255" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="D255" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>5</v>
@@ -6888,10 +6888,10 @@
         <v>252</v>
       </c>
       <c r="C256" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D256" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="D256" s="2" t="s">
-        <v>333</v>
       </c>
       <c r="E256" s="2">
         <v>5440099376763</v>
@@ -6904,10 +6904,10 @@
         <v>253</v>
       </c>
       <c r="C257" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D257" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="D257" s="2" t="s">
-        <v>335</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>5</v>
@@ -6920,7 +6920,7 @@
         <v>254</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>319</v>
@@ -6936,10 +6936,10 @@
         <v>255</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>5</v>
@@ -6952,7 +6952,7 @@
         <v>256</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>319</v>
@@ -6968,7 +6968,7 @@
         <v>257</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>319</v>
@@ -6984,10 +6984,10 @@
         <v>258</v>
       </c>
       <c r="C262" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D262" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="D262" s="2" t="s">
-        <v>340</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>5</v>
@@ -7000,7 +7000,7 @@
         <v>259</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>319</v>
@@ -7016,10 +7016,10 @@
         <v>260</v>
       </c>
       <c r="C264" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D264" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>5</v>
@@ -7032,10 +7032,10 @@
         <v>261</v>
       </c>
       <c r="C265" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D265" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="D265" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>5</v>
@@ -7048,10 +7048,10 @@
         <v>262</v>
       </c>
       <c r="C266" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D266" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>347</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>5</v>
@@ -7064,13 +7064,13 @@
         <v>263</v>
       </c>
       <c r="C267" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E267" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="D267" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E267" s="2" t="s">
-        <v>349</v>
       </c>
       <c r="F267" s="3"/>
     </row>
@@ -7080,10 +7080,10 @@
         <v>264</v>
       </c>
       <c r="C268" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D268" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="D268" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>5</v>
@@ -7096,10 +7096,10 @@
         <v>265</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>5</v>
@@ -7112,10 +7112,10 @@
         <v>266</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>5</v>
@@ -7128,10 +7128,10 @@
         <v>267</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>5</v>
@@ -7144,10 +7144,10 @@
         <v>268</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>5</v>
@@ -7160,10 +7160,10 @@
         <v>269</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>5</v>
@@ -7176,10 +7176,10 @@
         <v>270</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>5</v>
@@ -7192,10 +7192,10 @@
         <v>271</v>
       </c>
       <c r="C275" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D275" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="D275" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>5</v>
@@ -7208,10 +7208,10 @@
         <v>272</v>
       </c>
       <c r="C276" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D276" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="D276" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>5</v>
@@ -7224,10 +7224,10 @@
         <v>273</v>
       </c>
       <c r="C277" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D277" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="D277" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>5</v>
@@ -7240,13 +7240,13 @@
         <v>274</v>
       </c>
       <c r="C278" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E278" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="D278" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="F278" s="3"/>
     </row>
@@ -7256,10 +7256,10 @@
         <v>275</v>
       </c>
       <c r="C279" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D279" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="D279" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>5</v>
@@ -7272,10 +7272,10 @@
         <v>276</v>
       </c>
       <c r="C280" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D280" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="D280" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>5</v>
@@ -7288,10 +7288,10 @@
         <v>277</v>
       </c>
       <c r="C281" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D281" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="D281" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>5</v>
@@ -7304,10 +7304,10 @@
         <v>278</v>
       </c>
       <c r="C282" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D282" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="D282" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>5</v>
@@ -7320,10 +7320,10 @@
         <v>279</v>
       </c>
       <c r="C283" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D283" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="D283" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>5</v>
@@ -7336,10 +7336,10 @@
         <v>280</v>
       </c>
       <c r="C284" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D284" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>5</v>
@@ -7352,10 +7352,10 @@
         <v>281</v>
       </c>
       <c r="C285" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D285" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="D285" s="2" t="s">
-        <v>379</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>5</v>
@@ -7368,10 +7368,10 @@
         <v>282</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>5</v>
@@ -7384,10 +7384,10 @@
         <v>283</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>5</v>
@@ -7400,10 +7400,10 @@
         <v>284</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>5</v>
@@ -7416,10 +7416,10 @@
         <v>285</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>5</v>
@@ -7432,10 +7432,10 @@
         <v>286</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>5</v>
@@ -7448,10 +7448,10 @@
         <v>287</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>5</v>
@@ -7464,10 +7464,10 @@
         <v>288</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>5</v>
@@ -7480,10 +7480,10 @@
         <v>289</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>5</v>
@@ -7496,10 +7496,10 @@
         <v>290</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>5</v>
@@ -7512,10 +7512,10 @@
         <v>291</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>5</v>
@@ -7528,10 +7528,10 @@
         <v>292</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>5</v>
@@ -7544,10 +7544,10 @@
         <v>293</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>5</v>
@@ -7560,10 +7560,10 @@
         <v>294</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>5</v>
@@ -7576,10 +7576,10 @@
         <v>295</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>5</v>
@@ -7592,10 +7592,10 @@
         <v>296</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>5</v>
@@ -7608,10 +7608,10 @@
         <v>297</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>5</v>
@@ -7624,10 +7624,10 @@
         <v>298</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>5</v>
@@ -7640,10 +7640,10 @@
         <v>299</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>5</v>
@@ -7656,10 +7656,10 @@
         <v>300</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>5</v>
@@ -7672,10 +7672,10 @@
         <v>301</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>5</v>
@@ -7688,10 +7688,10 @@
         <v>302</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>5</v>
@@ -7704,10 +7704,10 @@
         <v>303</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>5</v>
@@ -7720,10 +7720,10 @@
         <v>304</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>5</v>
@@ -7736,10 +7736,10 @@
         <v>305</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>5</v>
@@ -7752,10 +7752,10 @@
         <v>306</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>5</v>
@@ -7768,10 +7768,10 @@
         <v>307</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>5</v>
@@ -7784,10 +7784,10 @@
         <v>308</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>5</v>
@@ -7800,10 +7800,10 @@
         <v>309</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>5</v>
@@ -7816,10 +7816,10 @@
         <v>310</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>5</v>
@@ -7832,10 +7832,10 @@
         <v>311</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>5</v>
@@ -7848,10 +7848,10 @@
         <v>312</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>5</v>
@@ -7864,10 +7864,10 @@
         <v>313</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>5</v>
@@ -7880,10 +7880,10 @@
         <v>314</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>5</v>
@@ -7896,10 +7896,10 @@
         <v>315</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>5</v>
@@ -7912,10 +7912,10 @@
         <v>316</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>5</v>
@@ -7928,10 +7928,10 @@
         <v>317</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>5</v>
@@ -7944,10 +7944,10 @@
         <v>318</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>5</v>
@@ -7960,10 +7960,10 @@
         <v>319</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>5</v>
@@ -7976,10 +7976,10 @@
         <v>320</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>5</v>
@@ -7992,10 +7992,10 @@
         <v>321</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>5</v>
@@ -8008,10 +8008,10 @@
         <v>322</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>5</v>
@@ -8024,10 +8024,10 @@
         <v>323</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>5</v>
@@ -8040,10 +8040,10 @@
         <v>324</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>5</v>
@@ -8056,10 +8056,10 @@
         <v>325</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>5</v>
@@ -8072,10 +8072,10 @@
         <v>326</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>5</v>
@@ -8088,10 +8088,10 @@
         <v>327</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>5</v>
@@ -8104,10 +8104,10 @@
         <v>328</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>5</v>
@@ -8120,10 +8120,10 @@
         <v>329</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>5</v>
@@ -8136,10 +8136,10 @@
         <v>330</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>5</v>
@@ -8152,10 +8152,10 @@
         <v>331</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>5</v>
@@ -8168,10 +8168,10 @@
         <v>332</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>5</v>
@@ -8184,10 +8184,10 @@
         <v>333</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>5</v>
@@ -8200,10 +8200,10 @@
         <v>334</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>5</v>
@@ -8216,10 +8216,10 @@
         <v>335</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>5</v>
@@ -8232,10 +8232,10 @@
         <v>336</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>5</v>
@@ -8248,10 +8248,10 @@
         <v>337</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>5</v>
@@ -8264,10 +8264,10 @@
         <v>338</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>5</v>
@@ -8280,10 +8280,10 @@
         <v>339</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>5</v>
@@ -8296,10 +8296,10 @@
         <v>340</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>5</v>
@@ -8312,10 +8312,10 @@
         <v>341</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>5</v>
@@ -8328,10 +8328,10 @@
         <v>342</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>5</v>
@@ -8344,10 +8344,10 @@
         <v>343</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>5</v>
@@ -8360,10 +8360,10 @@
         <v>344</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>5</v>
@@ -8376,10 +8376,10 @@
         <v>345</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>5</v>
@@ -8392,10 +8392,10 @@
         <v>346</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>5</v>
@@ -8408,10 +8408,10 @@
         <v>347</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>5</v>
@@ -8424,10 +8424,10 @@
         <v>348</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>5</v>
@@ -8440,10 +8440,10 @@
         <v>349</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>5</v>
@@ -8456,10 +8456,10 @@
         <v>350</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>5</v>
@@ -8472,10 +8472,10 @@
         <v>351</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>5</v>
@@ -8488,10 +8488,10 @@
         <v>352</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>5</v>
@@ -8504,10 +8504,10 @@
         <v>353</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>5</v>
@@ -8520,10 +8520,10 @@
         <v>354</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>5</v>
@@ -8536,10 +8536,10 @@
         <v>355</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>5</v>
@@ -8552,10 +8552,10 @@
         <v>356</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>5</v>
@@ -8568,10 +8568,10 @@
         <v>357</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>5</v>
@@ -8584,10 +8584,10 @@
         <v>358</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>5</v>
@@ -8600,10 +8600,10 @@
         <v>359</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>5</v>
@@ -8616,10 +8616,10 @@
         <v>360</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>5</v>
@@ -8632,10 +8632,10 @@
         <v>361</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>5</v>
@@ -8648,10 +8648,10 @@
         <v>362</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>5</v>
@@ -8664,10 +8664,10 @@
         <v>363</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>5</v>
@@ -8680,10 +8680,10 @@
         <v>364</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>5</v>
@@ -8696,10 +8696,10 @@
         <v>365</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>5</v>
@@ -8712,10 +8712,10 @@
         <v>366</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>5</v>
@@ -8728,10 +8728,10 @@
         <v>367</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>5</v>
@@ -8744,10 +8744,10 @@
         <v>368</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>5</v>
@@ -8760,10 +8760,10 @@
         <v>369</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>5</v>
@@ -8776,10 +8776,10 @@
         <v>370</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>5</v>
@@ -8792,10 +8792,10 @@
         <v>371</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>5</v>
@@ -8808,10 +8808,10 @@
         <v>372</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>5</v>
@@ -8824,10 +8824,10 @@
         <v>373</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>5</v>
@@ -8840,10 +8840,10 @@
         <v>374</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>5</v>
@@ -8856,10 +8856,10 @@
         <v>375</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>5</v>
@@ -8872,10 +8872,10 @@
         <v>376</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>5</v>
@@ -8888,10 +8888,10 @@
         <v>377</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>5</v>
@@ -8904,10 +8904,10 @@
         <v>378</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>5</v>
@@ -8920,10 +8920,10 @@
         <v>379</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>5</v>
@@ -8936,10 +8936,10 @@
         <v>380</v>
       </c>
       <c r="C384" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="D384" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="D384" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>5</v>
@@ -8952,10 +8952,10 @@
         <v>381</v>
       </c>
       <c r="C385" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="D385" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="D385" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>5</v>
@@ -8968,10 +8968,10 @@
         <v>382</v>
       </c>
       <c r="C386" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D386" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="D386" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>5</v>
@@ -8984,10 +8984,10 @@
         <v>383</v>
       </c>
       <c r="C387" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D387" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="D387" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>5</v>
@@ -9000,10 +9000,10 @@
         <v>384</v>
       </c>
       <c r="C388" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D388" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="D388" s="2" t="s">
-        <v>487</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>5</v>
@@ -9016,10 +9016,10 @@
         <v>385</v>
       </c>
       <c r="C389" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D389" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="D389" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>5</v>
@@ -9032,10 +9032,10 @@
         <v>386</v>
       </c>
       <c r="C390" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="D390" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="D390" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>5</v>
@@ -9048,10 +9048,10 @@
         <v>387</v>
       </c>
       <c r="C391" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D391" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="D391" s="2" t="s">
-        <v>493</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>5</v>
@@ -9064,10 +9064,10 @@
         <v>388</v>
       </c>
       <c r="C392" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D392" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="D392" s="2" t="s">
-        <v>495</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>5</v>
@@ -9080,10 +9080,10 @@
         <v>389</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>5</v>
@@ -9096,10 +9096,10 @@
         <v>390</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>5</v>
@@ -9112,10 +9112,10 @@
         <v>391</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>5</v>
@@ -9128,10 +9128,10 @@
         <v>392</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>5</v>
@@ -9144,10 +9144,10 @@
         <v>393</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E397" s="2" t="s">
         <v>5</v>
@@ -9160,10 +9160,10 @@
         <v>394</v>
       </c>
       <c r="C398" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D398" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="D398" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="E398" s="2" t="s">
         <v>5</v>
@@ -9176,13 +9176,13 @@
         <v>395</v>
       </c>
       <c r="C399" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="D399" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E399" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="D399" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E399" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="F399" s="3"/>
     </row>
@@ -9192,10 +9192,10 @@
         <v>396</v>
       </c>
       <c r="C400" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D400" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="D400" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>5</v>
@@ -9208,10 +9208,10 @@
         <v>397</v>
       </c>
       <c r="C401" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D401" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="D401" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>5</v>
@@ -9224,10 +9224,10 @@
         <v>398</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>5</v>
@@ -9240,10 +9240,10 @@
         <v>399</v>
       </c>
       <c r="C403" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D403" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="D403" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="E403" s="2" t="s">
         <v>5</v>
@@ -9256,10 +9256,10 @@
         <v>400</v>
       </c>
       <c r="C404" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D404" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="D404" s="2" t="s">
-        <v>513</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>5</v>
@@ -9272,10 +9272,10 @@
         <v>401</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>5</v>
@@ -9288,10 +9288,10 @@
         <v>402</v>
       </c>
       <c r="C406" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D406" s="2" t="s">
         <v>515</v>
-      </c>
-      <c r="D406" s="2" t="s">
-        <v>516</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>5</v>
@@ -9304,10 +9304,10 @@
         <v>403</v>
       </c>
       <c r="C407" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="D407" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="D407" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>5</v>
@@ -9320,10 +9320,10 @@
         <v>404</v>
       </c>
       <c r="C408" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D408" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="D408" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>5</v>
@@ -9336,10 +9336,10 @@
         <v>405</v>
       </c>
       <c r="C409" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D409" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="D409" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>5</v>
@@ -9352,10 +9352,10 @@
         <v>406</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>5</v>
@@ -9368,10 +9368,10 @@
         <v>407</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>5</v>
@@ -9384,10 +9384,10 @@
         <v>408</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>5</v>
@@ -9400,10 +9400,10 @@
         <v>409</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>5</v>
@@ -9416,10 +9416,10 @@
         <v>410</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>5</v>
@@ -9432,10 +9432,10 @@
         <v>411</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>5</v>
@@ -9448,10 +9448,10 @@
         <v>412</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>5</v>
@@ -9464,10 +9464,10 @@
         <v>413</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>5</v>
@@ -9480,10 +9480,10 @@
         <v>414</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>5</v>
@@ -9496,10 +9496,10 @@
         <v>415</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E419" s="7">
         <v>3277876126916</v>
@@ -9512,10 +9512,10 @@
         <v>416</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>5</v>
@@ -9528,10 +9528,10 @@
         <v>417</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>5</v>
@@ -9544,10 +9544,10 @@
         <v>418</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>5</v>
@@ -9560,10 +9560,10 @@
         <v>419</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>5</v>
@@ -9576,10 +9576,10 @@
         <v>420</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>5</v>
@@ -9592,10 +9592,10 @@
         <v>421</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>5</v>
@@ -9608,10 +9608,10 @@
         <v>422</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>5</v>
@@ -9624,10 +9624,10 @@
         <v>423</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>5</v>
@@ -9640,10 +9640,10 @@
         <v>424</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>5</v>
@@ -9656,10 +9656,10 @@
         <v>425</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>5</v>
@@ -9672,10 +9672,10 @@
         <v>426</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E430" s="7">
         <v>3520255124113</v>
@@ -9688,10 +9688,10 @@
         <v>427</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>5</v>
@@ -9704,10 +9704,10 @@
         <v>428</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>5</v>
@@ -9720,10 +9720,10 @@
         <v>429</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>5</v>
@@ -9736,10 +9736,10 @@
         <v>430</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>5</v>
@@ -9752,10 +9752,10 @@
         <v>431</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>5</v>
@@ -9768,10 +9768,10 @@
         <v>432</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>5</v>
@@ -9784,10 +9784,10 @@
         <v>433</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>5</v>
@@ -9800,10 +9800,10 @@
         <v>434</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>5</v>
@@ -9816,10 +9816,10 @@
         <v>435</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>5</v>
@@ -9832,10 +9832,10 @@
         <v>436</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>5</v>
@@ -9848,10 +9848,10 @@
         <v>437</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>5</v>
@@ -9864,10 +9864,10 @@
         <v>438</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>5</v>
@@ -9880,10 +9880,10 @@
         <v>439</v>
       </c>
       <c r="C443" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="D443" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="D443" s="2" t="s">
-        <v>556</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>5</v>
@@ -9896,10 +9896,10 @@
         <v>440</v>
       </c>
       <c r="C444" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="D444" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="D444" s="2" t="s">
-        <v>558</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>5</v>
@@ -9912,10 +9912,10 @@
         <v>441</v>
       </c>
       <c r="C445" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D445" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="D445" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>5</v>
@@ -9928,10 +9928,10 @@
         <v>442</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>5</v>
@@ -9944,10 +9944,10 @@
         <v>443</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>5</v>
@@ -9960,10 +9960,10 @@
         <v>444</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>5</v>
@@ -9976,10 +9976,10 @@
         <v>445</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>5</v>
@@ -9992,10 +9992,10 @@
         <v>446</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>5</v>
@@ -10008,10 +10008,10 @@
         <v>447</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>5</v>
@@ -10024,10 +10024,10 @@
         <v>448</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>5</v>
@@ -10040,10 +10040,10 @@
         <v>449</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>5</v>
@@ -10056,10 +10056,10 @@
         <v>450</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>5</v>
@@ -10072,10 +10072,10 @@
         <v>451</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>5</v>
@@ -10088,10 +10088,10 @@
         <v>452</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>5</v>
@@ -10104,10 +10104,10 @@
         <v>453</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>5</v>
@@ -10120,10 +10120,10 @@
         <v>454</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>5</v>
@@ -10136,10 +10136,10 @@
         <v>455</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>5</v>
@@ -10152,10 +10152,10 @@
         <v>456</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>5</v>
@@ -10168,10 +10168,10 @@
         <v>457</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>5</v>
@@ -10184,10 +10184,10 @@
         <v>458</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>5</v>
@@ -10200,10 +10200,10 @@
         <v>459</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>5</v>
@@ -10216,10 +10216,10 @@
         <v>460</v>
       </c>
       <c r="C464" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D464" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="D464" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>5</v>
@@ -10232,10 +10232,10 @@
         <v>461</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>5</v>
@@ -10248,10 +10248,10 @@
         <v>462</v>
       </c>
       <c r="C466" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D466" s="2" t="s">
         <v>582</v>
-      </c>
-      <c r="D466" s="2" t="s">
-        <v>583</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>5</v>
@@ -10264,10 +10264,10 @@
         <v>463</v>
       </c>
       <c r="C467" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="D467" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="D467" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>5</v>
@@ -10280,10 +10280,10 @@
         <v>464</v>
       </c>
       <c r="C468" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="D468" s="2" t="s">
         <v>586</v>
-      </c>
-      <c r="D468" s="2" t="s">
-        <v>587</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>5</v>
@@ -10296,7 +10296,7 @@
         <v>465</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D469" s="2" t="s">
         <v>114</v>
@@ -10312,10 +10312,10 @@
         <v>466</v>
       </c>
       <c r="C470" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="D470" s="2" t="s">
         <v>589</v>
-      </c>
-      <c r="D470" s="2" t="s">
-        <v>590</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>5</v>
@@ -10328,7 +10328,7 @@
         <v>467</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D471" s="2" t="s">
         <v>114</v>
@@ -10344,7 +10344,7 @@
         <v>468</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D472" s="2" t="s">
         <v>114</v>
@@ -10360,7 +10360,7 @@
         <v>469</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D473" s="2" t="s">
         <v>177</v>
@@ -10376,7 +10376,7 @@
         <v>470</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D474" s="2" t="s">
         <v>235</v>
@@ -10392,10 +10392,10 @@
         <v>471</v>
       </c>
       <c r="C475" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="D475" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="D475" s="2" t="s">
-        <v>596</v>
       </c>
       <c r="E475" s="1" t="s">
         <v>5</v>
@@ -10408,13 +10408,13 @@
         <v>472</v>
       </c>
       <c r="C476" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="D476" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E476" s="2" t="s">
         <v>597</v>
-      </c>
-      <c r="D476" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E476" s="2" t="s">
-        <v>598</v>
       </c>
       <c r="F476" s="3"/>
     </row>
@@ -10424,10 +10424,10 @@
         <v>473</v>
       </c>
       <c r="C477" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D477" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="D477" s="2" t="s">
-        <v>600</v>
       </c>
       <c r="E477" s="1" t="s">
         <v>5</v>
@@ -10440,10 +10440,10 @@
         <v>474</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E478" s="1" t="s">
         <v>5</v>
@@ -10456,10 +10456,10 @@
         <v>475</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E479" s="1" t="s">
         <v>5</v>
@@ -10472,10 +10472,10 @@
         <v>476</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E480" s="1" t="s">
         <v>5</v>
@@ -10488,10 +10488,10 @@
         <v>477</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E481" s="1" t="s">
         <v>5</v>
@@ -10504,10 +10504,10 @@
         <v>478</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E482" s="1" t="s">
         <v>5</v>
@@ -10520,10 +10520,10 @@
         <v>479</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E483" s="1" t="s">
         <v>5</v>
@@ -10536,10 +10536,10 @@
         <v>480</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>5</v>
@@ -10552,10 +10552,10 @@
         <v>481</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>5</v>
@@ -10568,10 +10568,10 @@
         <v>482</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>5</v>
@@ -10584,10 +10584,10 @@
         <v>483</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>5</v>
@@ -10600,10 +10600,10 @@
         <v>484</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>5</v>
@@ -10616,10 +10616,10 @@
         <v>485</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E489" s="1" t="s">
         <v>5</v>
@@ -10632,10 +10632,10 @@
         <v>486</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E490" s="1" t="s">
         <v>5</v>
@@ -10648,10 +10648,10 @@
         <v>487</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>5</v>
@@ -10664,10 +10664,10 @@
         <v>488</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E492" s="1" t="s">
         <v>5</v>
@@ -10680,10 +10680,10 @@
         <v>489</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D493" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E493" s="1" t="s">
         <v>5</v>
@@ -10696,10 +10696,10 @@
         <v>490</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E494" s="1" t="s">
         <v>5</v>
@@ -10712,10 +10712,10 @@
         <v>491</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E495" s="1" t="s">
         <v>5</v>
@@ -10728,10 +10728,10 @@
         <v>492</v>
       </c>
       <c r="C496" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="D496" s="2" t="s">
         <v>619</v>
-      </c>
-      <c r="D496" s="2" t="s">
-        <v>620</v>
       </c>
       <c r="E496" s="2" t="s">
         <v>5</v>
@@ -10744,13 +10744,13 @@
         <v>493</v>
       </c>
       <c r="C497" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="D497" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E497" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="D497" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E497" s="2" t="s">
-        <v>622</v>
       </c>
       <c r="F497" s="3"/>
     </row>
@@ -10760,10 +10760,10 @@
         <v>494</v>
       </c>
       <c r="C498" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="D498" s="2" t="s">
         <v>623</v>
-      </c>
-      <c r="D498" s="2" t="s">
-        <v>624</v>
       </c>
       <c r="E498" s="2" t="s">
         <v>5</v>
@@ -10776,10 +10776,10 @@
         <v>495</v>
       </c>
       <c r="C499" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="D499" s="2" t="s">
         <v>625</v>
-      </c>
-      <c r="D499" s="2" t="s">
-        <v>626</v>
       </c>
       <c r="E499" s="2" t="s">
         <v>5</v>
@@ -10792,13 +10792,13 @@
         <v>496</v>
       </c>
       <c r="C500" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="D500" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E500" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="D500" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E500" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="F500" s="3"/>
     </row>
@@ -10808,10 +10808,10 @@
         <v>497</v>
       </c>
       <c r="C501" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="D501" s="2" t="s">
         <v>629</v>
-      </c>
-      <c r="D501" s="2" t="s">
-        <v>630</v>
       </c>
       <c r="E501" s="1" t="s">
         <v>5</v>
@@ -10824,10 +10824,10 @@
         <v>498</v>
       </c>
       <c r="C502" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D502" s="2" t="s">
         <v>631</v>
-      </c>
-      <c r="D502" s="2" t="s">
-        <v>632</v>
       </c>
       <c r="E502" s="1" t="s">
         <v>5</v>
@@ -10840,10 +10840,10 @@
         <v>499</v>
       </c>
       <c r="C503" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="D503" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="D503" s="2" t="s">
-        <v>634</v>
       </c>
       <c r="E503" s="1" t="s">
         <v>5</v>
@@ -10856,10 +10856,10 @@
         <v>500</v>
       </c>
       <c r="C504" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="D504" s="2" t="s">
         <v>635</v>
-      </c>
-      <c r="D504" s="2" t="s">
-        <v>636</v>
       </c>
       <c r="E504" s="1" t="s">
         <v>5</v>
@@ -10872,10 +10872,10 @@
         <v>501</v>
       </c>
       <c r="C505" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="D505" s="2" t="s">
         <v>637</v>
-      </c>
-      <c r="D505" s="2" t="s">
-        <v>638</v>
       </c>
       <c r="E505" s="1" t="s">
         <v>5</v>
@@ -10888,10 +10888,10 @@
         <v>502</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E506" s="1" t="s">
         <v>5</v>
@@ -10904,10 +10904,10 @@
         <v>503</v>
       </c>
       <c r="C507" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D507" s="2" t="s">
         <v>640</v>
-      </c>
-      <c r="D507" s="2" t="s">
-        <v>641</v>
       </c>
       <c r="E507" s="1" t="s">
         <v>5</v>
@@ -10920,10 +10920,10 @@
         <v>504</v>
       </c>
       <c r="C508" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D508" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="D508" s="2" t="s">
-        <v>643</v>
       </c>
       <c r="E508" s="1" t="s">
         <v>5</v>
@@ -10936,10 +10936,10 @@
         <v>505</v>
       </c>
       <c r="C509" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="D509" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="D509" s="2" t="s">
-        <v>645</v>
       </c>
       <c r="E509" s="1" t="s">
         <v>5</v>
@@ -10952,10 +10952,10 @@
         <v>506</v>
       </c>
       <c r="C510" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="D510" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="D510" s="2" t="s">
-        <v>647</v>
       </c>
       <c r="E510" s="1" t="s">
         <v>5</v>
@@ -10968,10 +10968,10 @@
         <v>507</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E511" s="1" t="s">
         <v>5</v>
@@ -10984,10 +10984,10 @@
         <v>508</v>
       </c>
       <c r="C512" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="D512" s="2" t="s">
         <v>649</v>
-      </c>
-      <c r="D512" s="2" t="s">
-        <v>650</v>
       </c>
       <c r="E512" s="1" t="s">
         <v>5</v>
@@ -11000,10 +11000,10 @@
         <v>509</v>
       </c>
       <c r="C513" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="D513" s="2" t="s">
         <v>651</v>
-      </c>
-      <c r="D513" s="2" t="s">
-        <v>652</v>
       </c>
       <c r="E513" s="1" t="s">
         <v>5</v>
@@ -11016,10 +11016,10 @@
         <v>510</v>
       </c>
       <c r="C514" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="D514" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="D514" s="2" t="s">
-        <v>654</v>
       </c>
       <c r="E514" s="1" t="s">
         <v>5</v>
@@ -11032,10 +11032,10 @@
         <v>511</v>
       </c>
       <c r="C515" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="D515" s="2" t="s">
         <v>655</v>
-      </c>
-      <c r="D515" s="2" t="s">
-        <v>656</v>
       </c>
       <c r="E515" s="1" t="s">
         <v>5</v>
@@ -11048,13 +11048,13 @@
         <v>512</v>
       </c>
       <c r="C516" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D516" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E516" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="D516" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E516" s="2" t="s">
-        <v>658</v>
       </c>
       <c r="F516" s="3"/>
     </row>
@@ -11064,10 +11064,10 @@
         <v>513</v>
       </c>
       <c r="C517" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="D517" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="D517" s="2" t="s">
-        <v>660</v>
       </c>
       <c r="E517" s="1" t="s">
         <v>5</v>
@@ -11080,10 +11080,10 @@
         <v>514</v>
       </c>
       <c r="C518" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="D518" s="2" t="s">
         <v>661</v>
-      </c>
-      <c r="D518" s="2" t="s">
-        <v>662</v>
       </c>
       <c r="E518" s="1" t="s">
         <v>5</v>
@@ -11096,10 +11096,10 @@
         <v>515</v>
       </c>
       <c r="C519" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="D519" s="2" t="s">
         <v>663</v>
-      </c>
-      <c r="D519" s="2" t="s">
-        <v>664</v>
       </c>
       <c r="E519" s="1" t="s">
         <v>5</v>
@@ -11112,10 +11112,10 @@
         <v>516</v>
       </c>
       <c r="C520" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="D520" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="D520" s="2" t="s">
-        <v>666</v>
       </c>
       <c r="E520" s="1" t="s">
         <v>5</v>
@@ -11128,10 +11128,10 @@
         <v>517</v>
       </c>
       <c r="C521" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="D521" s="2" t="s">
         <v>667</v>
-      </c>
-      <c r="D521" s="2" t="s">
-        <v>668</v>
       </c>
       <c r="E521" s="1" t="s">
         <v>5</v>
@@ -11144,7 +11144,7 @@
         <v>518</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D522" s="2" t="s">
         <v>5</v>
@@ -11160,10 +11160,10 @@
         <v>519</v>
       </c>
       <c r="C523" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="D523" s="2" t="s">
         <v>670</v>
-      </c>
-      <c r="D523" s="2" t="s">
-        <v>671</v>
       </c>
       <c r="E523" s="1" t="s">
         <v>5</v>
@@ -11176,10 +11176,10 @@
         <v>520</v>
       </c>
       <c r="C524" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="D524" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="D524" s="2" t="s">
-        <v>673</v>
       </c>
       <c r="E524" s="1" t="s">
         <v>5</v>
@@ -11192,10 +11192,10 @@
         <v>521</v>
       </c>
       <c r="C525" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="D525" s="2" t="s">
         <v>674</v>
-      </c>
-      <c r="D525" s="2" t="s">
-        <v>675</v>
       </c>
       <c r="E525" s="1" t="s">
         <v>5</v>
@@ -11208,10 +11208,10 @@
         <v>522</v>
       </c>
       <c r="C526" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="D526" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="D526" s="2" t="s">
-        <v>677</v>
       </c>
       <c r="E526" s="1" t="s">
         <v>5</v>
@@ -11224,10 +11224,10 @@
         <v>523</v>
       </c>
       <c r="C527" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="D527" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="D527" s="2" t="s">
-        <v>679</v>
       </c>
       <c r="E527" s="1" t="s">
         <v>5</v>
@@ -11240,10 +11240,10 @@
         <v>524</v>
       </c>
       <c r="C528" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="D528" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="D528" s="2" t="s">
-        <v>681</v>
       </c>
       <c r="E528" s="1" t="s">
         <v>5</v>
@@ -11256,10 +11256,10 @@
         <v>525</v>
       </c>
       <c r="C529" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>5</v>
@@ -11272,7 +11272,7 @@
         <v>526</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D530" s="2" t="s">
         <v>5</v>
@@ -11288,10 +11288,10 @@
         <v>527</v>
       </c>
       <c r="C531" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="D531" s="2" t="s">
         <v>684</v>
-      </c>
-      <c r="D531" s="2" t="s">
-        <v>685</v>
       </c>
       <c r="E531" s="1" t="s">
         <v>5</v>
@@ -11304,10 +11304,10 @@
         <v>528</v>
       </c>
       <c r="C532" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="D532" s="2" t="s">
         <v>686</v>
-      </c>
-      <c r="D532" s="2" t="s">
-        <v>687</v>
       </c>
       <c r="E532" s="1" t="s">
         <v>5</v>
@@ -11320,10 +11320,10 @@
         <v>529</v>
       </c>
       <c r="C533" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="D533" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="D533" s="2" t="s">
-        <v>689</v>
       </c>
       <c r="E533" s="1" t="s">
         <v>5</v>
@@ -11336,10 +11336,10 @@
         <v>530</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D534" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E534" s="1" t="s">
         <v>5</v>
@@ -11352,10 +11352,10 @@
         <v>531</v>
       </c>
       <c r="C535" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="D535" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="D535" s="2" t="s">
-        <v>692</v>
       </c>
       <c r="E535" s="1" t="s">
         <v>5</v>
@@ -11368,10 +11368,10 @@
         <v>532</v>
       </c>
       <c r="C536" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="D536" s="2" t="s">
         <v>693</v>
-      </c>
-      <c r="D536" s="2" t="s">
-        <v>694</v>
       </c>
       <c r="E536" s="1" t="s">
         <v>5</v>
@@ -11384,10 +11384,10 @@
         <v>533</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D537" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E537" s="1" t="s">
         <v>5</v>
@@ -11400,10 +11400,10 @@
         <v>534</v>
       </c>
       <c r="C538" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="D538" s="2" t="s">
         <v>696</v>
-      </c>
-      <c r="D538" s="2" t="s">
-        <v>697</v>
       </c>
       <c r="E538" s="1" t="s">
         <v>5</v>
@@ -11416,10 +11416,10 @@
         <v>535</v>
       </c>
       <c r="C539" s="1" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E539" s="1" t="s">
         <v>5</v>
@@ -11432,10 +11432,10 @@
         <v>536</v>
       </c>
       <c r="C540" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D540" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E540" s="1" t="s">
         <v>5</v>
@@ -11448,10 +11448,10 @@
         <v>537</v>
       </c>
       <c r="C541" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D541" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E541" s="1" t="s">
         <v>5</v>
@@ -11464,10 +11464,10 @@
         <v>538</v>
       </c>
       <c r="C542" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D542" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E542" s="1" t="s">
         <v>5</v>
@@ -11480,10 +11480,10 @@
         <v>539</v>
       </c>
       <c r="C543" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D543" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E543" s="1" t="s">
         <v>5</v>
@@ -11496,10 +11496,10 @@
         <v>540</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D544" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E544" s="1" t="s">
         <v>5</v>
@@ -11512,10 +11512,10 @@
         <v>541</v>
       </c>
       <c r="C545" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="D545" s="2" t="s">
         <v>704</v>
-      </c>
-      <c r="D545" s="2" t="s">
-        <v>705</v>
       </c>
       <c r="E545" s="1" t="s">
         <v>5</v>
@@ -11528,13 +11528,13 @@
         <v>542</v>
       </c>
       <c r="C546" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="D546" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E546" s="2" t="s">
         <v>706</v>
-      </c>
-      <c r="D546" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E546" s="2" t="s">
-        <v>707</v>
       </c>
       <c r="F546" s="3"/>
     </row>
@@ -11544,13 +11544,13 @@
         <v>543</v>
       </c>
       <c r="C547" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="D547" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E547" s="2" t="s">
         <v>708</v>
-      </c>
-      <c r="D547" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E547" s="2" t="s">
-        <v>709</v>
       </c>
       <c r="F547" s="3"/>
     </row>
@@ -11560,10 +11560,10 @@
         <v>544</v>
       </c>
       <c r="C548" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="D548" s="2" t="s">
         <v>710</v>
-      </c>
-      <c r="D548" s="2" t="s">
-        <v>711</v>
       </c>
       <c r="E548" s="1" t="s">
         <v>5</v>
@@ -11576,10 +11576,10 @@
         <v>545</v>
       </c>
       <c r="C549" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="D549" s="2" t="s">
         <v>712</v>
-      </c>
-      <c r="D549" s="2" t="s">
-        <v>713</v>
       </c>
       <c r="E549" s="1" t="s">
         <v>5</v>
@@ -11592,10 +11592,10 @@
         <v>546</v>
       </c>
       <c r="C550" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="D550" s="2" t="s">
         <v>714</v>
-      </c>
-      <c r="D550" s="2" t="s">
-        <v>715</v>
       </c>
       <c r="E550" s="1" t="s">
         <v>5</v>
@@ -11608,10 +11608,10 @@
         <v>547</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D551" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E551" s="1" t="s">
         <v>5</v>
@@ -11624,10 +11624,10 @@
         <v>548</v>
       </c>
       <c r="C552" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="D552" s="2" t="s">
         <v>717</v>
-      </c>
-      <c r="D552" s="2" t="s">
-        <v>718</v>
       </c>
       <c r="E552" s="1" t="s">
         <v>5</v>
@@ -11640,13 +11640,13 @@
         <v>549</v>
       </c>
       <c r="C553" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D553" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="E553" s="13" t="s">
         <v>802</v>
-      </c>
-      <c r="E553" s="13" t="s">
-        <v>803</v>
       </c>
       <c r="F553" s="3"/>
     </row>
@@ -11656,10 +11656,10 @@
         <v>550</v>
       </c>
       <c r="C554" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="D554" s="2" t="s">
         <v>720</v>
-      </c>
-      <c r="D554" s="2" t="s">
-        <v>721</v>
       </c>
       <c r="E554" s="1" t="s">
         <v>5</v>
@@ -11672,10 +11672,10 @@
         <v>551</v>
       </c>
       <c r="C555" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="D555" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="D555" s="2" t="s">
-        <v>723</v>
       </c>
       <c r="E555" s="1" t="s">
         <v>5</v>
@@ -11688,10 +11688,10 @@
         <v>552</v>
       </c>
       <c r="C556" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D556" s="2" t="s">
         <v>724</v>
-      </c>
-      <c r="D556" s="2" t="s">
-        <v>725</v>
       </c>
       <c r="E556" s="1" t="s">
         <v>5</v>
@@ -11704,10 +11704,10 @@
         <v>553</v>
       </c>
       <c r="C557" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="D557" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="D557" s="2" t="s">
-        <v>727</v>
       </c>
       <c r="E557" s="1" t="s">
         <v>5</v>
@@ -11720,10 +11720,10 @@
         <v>554</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E558" s="1" t="s">
         <v>5</v>
@@ -11736,10 +11736,10 @@
         <v>555</v>
       </c>
       <c r="C559" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>5</v>
@@ -11752,7 +11752,7 @@
         <v>556</v>
       </c>
       <c r="C560" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D560" s="2" t="s">
         <v>161</v>
@@ -11768,10 +11768,10 @@
         <v>557</v>
       </c>
       <c r="C561" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="D561" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="D561" s="2" t="s">
-        <v>732</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>5</v>
@@ -11784,10 +11784,10 @@
         <v>558</v>
       </c>
       <c r="C562" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="D562" s="2" t="s">
         <v>733</v>
-      </c>
-      <c r="D562" s="2" t="s">
-        <v>734</v>
       </c>
       <c r="E562" s="1" t="s">
         <v>5</v>
@@ -11800,10 +11800,10 @@
         <v>559</v>
       </c>
       <c r="C563" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="D563" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="D563" s="2" t="s">
-        <v>736</v>
       </c>
       <c r="E563" s="1" t="s">
         <v>5</v>
@@ -11816,10 +11816,10 @@
         <v>560</v>
       </c>
       <c r="C564" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E564" s="1" t="s">
         <v>5</v>
@@ -11832,10 +11832,10 @@
         <v>561</v>
       </c>
       <c r="C565" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E565" s="1" t="s">
         <v>5</v>
@@ -11848,10 +11848,10 @@
         <v>562</v>
       </c>
       <c r="C566" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E566" s="1" t="s">
         <v>5</v>
@@ -11864,10 +11864,10 @@
         <v>563</v>
       </c>
       <c r="C567" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E567" s="1" t="s">
         <v>5</v>
@@ -11880,10 +11880,10 @@
         <v>564</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D568" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E568" s="1" t="s">
         <v>5</v>
@@ -11896,10 +11896,10 @@
         <v>565</v>
       </c>
       <c r="C569" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D569" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E569" s="1" t="s">
         <v>5</v>
@@ -11912,10 +11912,10 @@
         <v>566</v>
       </c>
       <c r="C570" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D570" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E570" s="1" t="s">
         <v>5</v>
@@ -11928,10 +11928,10 @@
         <v>567</v>
       </c>
       <c r="C571" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D571" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E571" s="1" t="s">
         <v>5</v>
@@ -11944,10 +11944,10 @@
         <v>568</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E572" s="1" t="s">
         <v>5</v>
@@ -11960,10 +11960,10 @@
         <v>569</v>
       </c>
       <c r="C573" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E573" s="1" t="s">
         <v>5</v>
@@ -11976,10 +11976,10 @@
         <v>570</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E574" s="1" t="s">
         <v>5</v>
@@ -11992,10 +11992,10 @@
         <v>571</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E575" s="1" t="s">
         <v>5</v>
@@ -12008,10 +12008,10 @@
         <v>572</v>
       </c>
       <c r="C576" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E576" s="1" t="s">
         <v>5</v>
@@ -12024,10 +12024,10 @@
         <v>573</v>
       </c>
       <c r="C577" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="D577" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="D577" s="2" t="s">
-        <v>751</v>
       </c>
       <c r="E577" s="2" t="s">
         <v>5</v>
@@ -12040,10 +12040,10 @@
         <v>574</v>
       </c>
       <c r="C578" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="D578" s="2" t="s">
         <v>752</v>
-      </c>
-      <c r="D578" s="2" t="s">
-        <v>753</v>
       </c>
       <c r="E578" s="1" t="s">
         <v>5</v>
@@ -12056,10 +12056,10 @@
         <v>575</v>
       </c>
       <c r="C579" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="D579" s="2" t="s">
         <v>754</v>
-      </c>
-      <c r="D579" s="2" t="s">
-        <v>755</v>
       </c>
       <c r="E579" s="1" t="s">
         <v>5</v>
@@ -12072,10 +12072,10 @@
         <v>576</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E580" s="1" t="s">
         <v>5</v>
@@ -12088,10 +12088,10 @@
         <v>577</v>
       </c>
       <c r="C581" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="D581" s="2" t="s">
         <v>757</v>
-      </c>
-      <c r="D581" s="2" t="s">
-        <v>758</v>
       </c>
       <c r="E581" s="1" t="s">
         <v>5</v>
@@ -12104,10 +12104,10 @@
         <v>578</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D582" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E582" s="7">
         <v>3520268948847</v>
@@ -12120,10 +12120,10 @@
         <v>579</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D583" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E583" s="1" t="s">
         <v>5</v>
@@ -12136,10 +12136,10 @@
         <v>580</v>
       </c>
       <c r="C584" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="D584" s="2" t="s">
         <v>761</v>
-      </c>
-      <c r="D584" s="2" t="s">
-        <v>762</v>
       </c>
       <c r="E584" s="1" t="s">
         <v>5</v>
@@ -12152,10 +12152,10 @@
         <v>581</v>
       </c>
       <c r="C585" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="D585" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="D585" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="E585" s="1" t="s">
         <v>5</v>
@@ -12168,10 +12168,10 @@
         <v>582</v>
       </c>
       <c r="C586" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D586" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E586" s="1" t="s">
         <v>5</v>
@@ -12184,10 +12184,10 @@
         <v>583</v>
       </c>
       <c r="C587" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="D587" s="2" t="s">
         <v>766</v>
-      </c>
-      <c r="D587" s="2" t="s">
-        <v>767</v>
       </c>
       <c r="E587" s="1" t="s">
         <v>5</v>
@@ -12200,10 +12200,10 @@
         <v>584</v>
       </c>
       <c r="C588" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="D588" s="2" t="s">
         <v>768</v>
-      </c>
-      <c r="D588" s="2" t="s">
-        <v>769</v>
       </c>
       <c r="E588" s="1" t="s">
         <v>5</v>
@@ -12216,10 +12216,10 @@
         <v>585</v>
       </c>
       <c r="C589" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="D589" s="2" t="s">
         <v>770</v>
-      </c>
-      <c r="D589" s="2" t="s">
-        <v>771</v>
       </c>
       <c r="E589" s="1" t="s">
         <v>5</v>
@@ -12232,10 +12232,10 @@
         <v>586</v>
       </c>
       <c r="C590" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="D590" s="2" t="s">
         <v>772</v>
-      </c>
-      <c r="D590" s="2" t="s">
-        <v>773</v>
       </c>
       <c r="E590" s="1" t="s">
         <v>5</v>
@@ -12248,10 +12248,10 @@
         <v>587</v>
       </c>
       <c r="C591" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="D591" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="D591" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="E591" s="1" t="s">
         <v>5</v>
@@ -12264,10 +12264,10 @@
         <v>588</v>
       </c>
       <c r="C592" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="D592" s="2" t="s">
         <v>776</v>
-      </c>
-      <c r="D592" s="2" t="s">
-        <v>777</v>
       </c>
       <c r="E592" s="1" t="s">
         <v>5</v>
@@ -12280,10 +12280,10 @@
         <v>589</v>
       </c>
       <c r="C593" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="D593" s="2" t="s">
         <v>778</v>
-      </c>
-      <c r="D593" s="2" t="s">
-        <v>779</v>
       </c>
       <c r="E593" s="1" t="s">
         <v>5</v>
@@ -12296,10 +12296,10 @@
         <v>590</v>
       </c>
       <c r="C594" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="D594" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="D594" s="2" t="s">
-        <v>781</v>
       </c>
       <c r="E594" s="1" t="s">
         <v>5</v>
@@ -12312,10 +12312,10 @@
         <v>591</v>
       </c>
       <c r="C595" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="D595" s="2" t="s">
         <v>782</v>
-      </c>
-      <c r="D595" s="2" t="s">
-        <v>783</v>
       </c>
       <c r="E595" s="1" t="s">
         <v>5</v>
@@ -12328,10 +12328,10 @@
         <v>592</v>
       </c>
       <c r="C596" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="D596" s="2" t="s">
         <v>784</v>
-      </c>
-      <c r="D596" s="2" t="s">
-        <v>785</v>
       </c>
       <c r="E596" s="1" t="s">
         <v>5</v>
@@ -12344,10 +12344,10 @@
         <v>593</v>
       </c>
       <c r="C597" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="D597" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="D597" s="2" t="s">
-        <v>787</v>
       </c>
       <c r="E597" s="1" t="s">
         <v>5</v>
@@ -12360,10 +12360,10 @@
         <v>594</v>
       </c>
       <c r="C598" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="D598" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="D598" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="E598" s="1" t="s">
         <v>5</v>
@@ -12375,10 +12375,10 @@
         <v>595</v>
       </c>
       <c r="C599" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="D599" s="2" t="s">
         <v>790</v>
-      </c>
-      <c r="D599" s="2" t="s">
-        <v>791</v>
       </c>
       <c r="E599" s="5"/>
     </row>
@@ -12387,10 +12387,10 @@
         <v>596</v>
       </c>
       <c r="C600" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="D600" s="6" t="s">
         <v>792</v>
-      </c>
-      <c r="D600" s="6" t="s">
-        <v>793</v>
       </c>
       <c r="E600" s="5"/>
     </row>
@@ -12402,10 +12402,10 @@
         <v>509</v>
       </c>
       <c r="C602" s="4" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D602" s="8" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="603" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
@@ -12413,10 +12413,10 @@
         <v>334</v>
       </c>
       <c r="C603" s="10" t="s">
+        <v>797</v>
+      </c>
+      <c r="D603" t="s">
         <v>798</v>
-      </c>
-      <c r="D603" t="s">
-        <v>799</v>
       </c>
       <c r="E603" s="11">
         <v>3277876171384</v>
@@ -12427,10 +12427,10 @@
         <v>263</v>
       </c>
       <c r="C604" s="10" t="s">
+        <v>799</v>
+      </c>
+      <c r="D604" s="12" t="s">
         <v>800</v>
-      </c>
-      <c r="D604" s="12" t="s">
-        <v>801</v>
       </c>
       <c r="E604" s="11">
         <v>3520210170957</v>

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A57CC52-93F5-4DE9-85F2-EBC9C7769AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2E96C2-C788-4342-A537-B4BE57E89448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2E96C2-C788-4342-A537-B4BE57E89448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF7D396-F696-46AE-8829-9A540A29CE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B246" s="2">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B247" s="2">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B248" s="2">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="F248" s="3"/>
     </row>
-    <row r="249" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B249" s="2">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B250" s="2">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B251" s="2">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B252" s="2">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B253" s="2">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B256" s="2">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B257" s="2">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B258" s="2">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B259" s="2">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B260" s="2">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B261" s="2">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B262" s="2">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B263" s="2">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B264" s="2">
         <f t="shared" si="3"/>
         <v>260</v>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="F407" s="3"/>
     </row>
-    <row r="408" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B408" s="2">
         <f t="shared" si="6"/>
         <v>404</v>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="F408" s="3"/>
     </row>
-    <row r="409" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B409" s="2">
         <f t="shared" si="6"/>
         <v>405</v>
@@ -9346,7 +9346,7 @@
       </c>
       <c r="F409" s="3"/>
     </row>
-    <row r="410" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B410" s="2">
         <f t="shared" si="6"/>
         <v>406</v>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="F410" s="3"/>
     </row>
-    <row r="411" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B411" s="2">
         <f t="shared" si="6"/>
         <v>407</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="F411" s="3"/>
     </row>
-    <row r="412" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B412" s="2">
         <f t="shared" si="6"/>
         <v>408</v>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="F412" s="3"/>
     </row>
-    <row r="413" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B413" s="2">
         <f t="shared" si="6"/>
         <v>409</v>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="F413" s="3"/>
     </row>
-    <row r="414" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B414" s="2">
         <f t="shared" si="6"/>
         <v>410</v>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="F414" s="3"/>
     </row>
-    <row r="415" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B415" s="2">
         <f t="shared" si="6"/>
         <v>411</v>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B416" s="2">
         <f t="shared" si="6"/>
         <v>412</v>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="F416" s="3"/>
     </row>
-    <row r="417" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B417" s="2">
         <f t="shared" si="6"/>
         <v>413</v>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="F417" s="3"/>
     </row>
-    <row r="418" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B418" s="2">
         <f t="shared" si="6"/>
         <v>414</v>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B419" s="2">
         <f t="shared" si="6"/>
         <v>415</v>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="F419" s="3"/>
     </row>
-    <row r="420" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B420" s="2">
         <f t="shared" si="6"/>
         <v>416</v>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="F420" s="3"/>
     </row>
-    <row r="421" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B421" s="2">
         <f t="shared" si="6"/>
         <v>417</v>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B422" s="2">
         <f t="shared" si="6"/>
         <v>418</v>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B423" s="2">
         <f t="shared" si="6"/>
         <v>419</v>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="F423" s="3"/>
     </row>
-    <row r="424" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B424" s="2">
         <f t="shared" si="6"/>
         <v>420</v>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="F424" s="3"/>
     </row>
-    <row r="425" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B425" s="2">
         <f t="shared" si="6"/>
         <v>421</v>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="F425" s="3"/>
     </row>
-    <row r="426" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B426" s="2">
         <f t="shared" si="6"/>
         <v>422</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B428" s="2">
         <f t="shared" si="6"/>
         <v>424</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B429" s="2">
         <f t="shared" si="6"/>
         <v>425</v>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B430" s="2">
         <f t="shared" si="6"/>
         <v>426</v>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B431" s="2">
         <f t="shared" si="6"/>
         <v>427</v>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="F431" s="3"/>
     </row>
-    <row r="432" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B432" s="2">
         <f t="shared" si="6"/>
         <v>428</v>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B433" s="2">
         <f t="shared" si="6"/>
         <v>429</v>
@@ -9730,7 +9730,7 @@
       </c>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B434" s="2">
         <f t="shared" si="6"/>
         <v>430</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="F434" s="3"/>
     </row>
-    <row r="435" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B435" s="2">
         <f t="shared" si="6"/>
         <v>431</v>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B436" s="2">
         <f t="shared" si="6"/>
         <v>432</v>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="F436" s="3"/>
     </row>
-    <row r="437" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B437" s="2">
         <f t="shared" si="6"/>
         <v>433</v>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B438" s="2">
         <f t="shared" si="6"/>
         <v>434</v>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B439" s="2">
         <f t="shared" si="6"/>
         <v>435</v>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B440" s="2">
         <f t="shared" si="6"/>
         <v>436</v>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B441" s="2">
         <f t="shared" si="6"/>
         <v>437</v>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="F441" s="3"/>
     </row>
-    <row r="442" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B442" s="2">
         <f t="shared" si="6"/>
         <v>438</v>
@@ -12440,25 +12440,41 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="EURO RANJERS MART"/>
-        <filter val="Euro store  (Academy Road)"/>
-        <filter val="EURO STORE (N F C )"/>
-        <filter val="EURO STORE (Rahamt chowk)"/>
-        <filter val="Euro Store (Scheme Mor)"/>
-        <filter val="Euro Store Airport Road"/>
-        <filter val="Euro Store Bedian Road"/>
-        <filter val="Euro Store College Road"/>
-        <filter val="EURO STORE CROWN BEHRIA TOWN"/>
-        <filter val="Euro Store E-2 (Wapda Town)"/>
-        <filter val="EURO STORE FATAH GARH"/>
-        <filter val="Euro Store G.T Road"/>
-        <filter val="Euro Store Garhi Shahu"/>
-        <filter val="EURO Store Hypermarket (Raiwind Road)"/>
-        <filter val="Euro Store Iqbal Town (Ranchna)"/>
-        <filter val="EURO STORE MARIYA STOP"/>
-        <filter val="EURO STORE PH VIII PARK VIEW"/>
-        <filter val="Euro Stores (G-1 Market)"/>
-        <filter val="EURO Stores (Nishat Colony)"/>
+        <filter val="JALAL SONS  (COLLEGE ROAD) 02"/>
+        <filter val="Jalal sons  (Izmair Town) 01"/>
+        <filter val="Jalal sons (Askari 10 F sector ) 01"/>
+        <filter val="JALAL SONS (ASKARI 11 B BLOCK) 02"/>
+        <filter val="JALAL SONS (AYUBIA) 02"/>
+        <filter val="JALAL SONS (Bahira Orchard) 01"/>
+        <filter val="Jalal Sons (Bahria Town)  01"/>
+        <filter val="JALAL SONS (C BLOCK MODEL TOWN) 02"/>
+        <filter val="JALAL SONS (DHA C BLOCK,PHASE 6) 02"/>
+        <filter val="JALAL SONS (DHA PH IV) 02"/>
+        <filter val="JALAL SONS (DHA PH V) 02"/>
+        <filter val="JALAL SONS (DHA Y BLOCK) 02"/>
+        <filter val="JALAL SONS (EME) 02"/>
+        <filter val="JALAL SONS (FAISAL TOWN) 02"/>
+        <filter val="Jalal Sons (H Block) 01"/>
+        <filter val="JALAL SONS (HUSSAIN CHOWK GULBERG III) 02"/>
+        <filter val="JALAL SONS (IQBAL TOWN) 02"/>
+        <filter val="Jalal Sons (J.T Shadewal) 01"/>
+        <filter val="JALAL SONS (JOHER TOWN) 02"/>
+        <filter val="Jalal Sons (Lake City) 01"/>
+        <filter val="Jalal sons (Main Market) 01"/>
+        <filter val="JALAL SONS (MODEL TOWN LINK ROAD) 02"/>
+        <filter val="Jalal Sons (PAF Market) 01 main Market"/>
+        <filter val="JALAL SONS (PARAGON CITY) 02"/>
+        <filter val="JALAL SONS (PH VI) 02"/>
+        <filter val="JALAL SONS (PHASE 8 EX PARK VIEW) 02"/>
+        <filter val="JALAL SONS (REVAZ GARDEN) 02"/>
+        <filter val="JALAL SONS (SHADMAN) 02"/>
+        <filter val="JALAL SONS (SHAUKAT KHANUM) 02"/>
+        <filter val="JALAL SONS (STATE LIFE) 02"/>
+        <filter val="JALAL SONS (TALWAR CHOWK) 02"/>
+        <filter val="JALAL SONS (VALENCIA TOWN) 02"/>
+        <filter val="JALAL SONS (WAPDA TOWN) 02"/>
+        <filter val="JALAL SONS (XX) 02"/>
+        <filter val="Jalal Sons Askari X (01)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF7D396-F696-46AE-8829-9A540A29CE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20D1F60-6F22-42C2-B378-46C0FFDE00B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="807">
   <si>
     <t>Sr#</t>
   </si>
@@ -2446,6 +2446,9 @@
   </si>
   <si>
     <t>Euro Store College Road (Model Town)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joher Town </t>
   </si>
 </sst>
 </file>
@@ -2867,7 +2870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -4578,7 +4581,7 @@
       </c>
       <c r="F111" s="3"/>
     </row>
-    <row r="112" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B112" s="2">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -4594,7 +4597,7 @@
       </c>
       <c r="F112" s="3"/>
     </row>
-    <row r="113" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B113" s="2">
         <f t="shared" si="1"/>
         <v>109</v>
@@ -4802,7 +4805,7 @@
       </c>
       <c r="F125" s="3"/>
     </row>
-    <row r="126" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B126" s="2">
         <f t="shared" si="1"/>
         <v>122</v>
@@ -5506,7 +5509,7 @@
       </c>
       <c r="F169" s="3"/>
     </row>
-    <row r="170" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B170" s="2">
         <f t="shared" si="2"/>
         <v>166</v>
@@ -6290,7 +6293,7 @@
       </c>
       <c r="F218" s="3"/>
     </row>
-    <row r="219" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B219" s="2">
         <f t="shared" si="3"/>
         <v>215</v>
@@ -6546,7 +6549,7 @@
       </c>
       <c r="F234" s="3"/>
     </row>
-    <row r="235" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B235" s="2">
         <f t="shared" si="3"/>
         <v>231</v>
@@ -7282,7 +7285,7 @@
       </c>
       <c r="F280" s="3"/>
     </row>
-    <row r="281" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B281" s="2">
         <f t="shared" si="4"/>
         <v>277</v>
@@ -9202,7 +9205,7 @@
       </c>
       <c r="F400" s="3"/>
     </row>
-    <row r="401" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B401" s="2">
         <f t="shared" si="6"/>
         <v>397</v>
@@ -9314,7 +9317,7 @@
       </c>
       <c r="F407" s="3"/>
     </row>
-    <row r="408" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B408" s="2">
         <f t="shared" si="6"/>
         <v>404</v>
@@ -9330,7 +9333,7 @@
       </c>
       <c r="F408" s="3"/>
     </row>
-    <row r="409" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B409" s="2">
         <f t="shared" si="6"/>
         <v>405</v>
@@ -9378,7 +9381,7 @@
       </c>
       <c r="F411" s="3"/>
     </row>
-    <row r="412" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B412" s="2">
         <f t="shared" si="6"/>
         <v>408</v>
@@ -9394,7 +9397,7 @@
       </c>
       <c r="F412" s="3"/>
     </row>
-    <row r="413" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B413" s="2">
         <f t="shared" si="6"/>
         <v>409</v>
@@ -9410,7 +9413,7 @@
       </c>
       <c r="F413" s="3"/>
     </row>
-    <row r="414" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B414" s="2">
         <f t="shared" si="6"/>
         <v>410</v>
@@ -9426,7 +9429,7 @@
       </c>
       <c r="F414" s="3"/>
     </row>
-    <row r="415" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B415" s="2">
         <f t="shared" si="6"/>
         <v>411</v>
@@ -9442,7 +9445,7 @@
       </c>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B416" s="2">
         <f t="shared" si="6"/>
         <v>412</v>
@@ -9458,7 +9461,7 @@
       </c>
       <c r="F416" s="3"/>
     </row>
-    <row r="417" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B417" s="2">
         <f t="shared" si="6"/>
         <v>413</v>
@@ -9474,7 +9477,7 @@
       </c>
       <c r="F417" s="3"/>
     </row>
-    <row r="418" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B418" s="2">
         <f t="shared" si="6"/>
         <v>414</v>
@@ -9490,7 +9493,7 @@
       </c>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B419" s="2">
         <f t="shared" si="6"/>
         <v>415</v>
@@ -9506,7 +9509,7 @@
       </c>
       <c r="F419" s="3"/>
     </row>
-    <row r="420" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B420" s="2">
         <f t="shared" si="6"/>
         <v>416</v>
@@ -9522,7 +9525,7 @@
       </c>
       <c r="F420" s="3"/>
     </row>
-    <row r="421" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B421" s="2">
         <f t="shared" si="6"/>
         <v>417</v>
@@ -9538,7 +9541,7 @@
       </c>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B422" s="2">
         <f t="shared" si="6"/>
         <v>418</v>
@@ -9554,7 +9557,7 @@
       </c>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B423" s="2">
         <f t="shared" si="6"/>
         <v>419</v>
@@ -9570,7 +9573,7 @@
       </c>
       <c r="F423" s="3"/>
     </row>
-    <row r="424" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B424" s="2">
         <f t="shared" si="6"/>
         <v>420</v>
@@ -9586,7 +9589,7 @@
       </c>
       <c r="F424" s="3"/>
     </row>
-    <row r="425" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B425" s="2">
         <f t="shared" si="6"/>
         <v>421</v>
@@ -9602,7 +9605,7 @@
       </c>
       <c r="F425" s="3"/>
     </row>
-    <row r="426" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B426" s="2">
         <f t="shared" si="6"/>
         <v>422</v>
@@ -9618,7 +9621,7 @@
       </c>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
@@ -9634,7 +9637,7 @@
       </c>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B428" s="2">
         <f t="shared" si="6"/>
         <v>424</v>
@@ -9650,7 +9653,7 @@
       </c>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B429" s="2">
         <f t="shared" si="6"/>
         <v>425</v>
@@ -9666,7 +9669,7 @@
       </c>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B430" s="2">
         <f t="shared" si="6"/>
         <v>426</v>
@@ -9682,7 +9685,7 @@
       </c>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B431" s="2">
         <f t="shared" si="6"/>
         <v>427</v>
@@ -9698,7 +9701,7 @@
       </c>
       <c r="F431" s="3"/>
     </row>
-    <row r="432" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B432" s="2">
         <f t="shared" si="6"/>
         <v>428</v>
@@ -9714,7 +9717,7 @@
       </c>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B433" s="2">
         <f t="shared" si="6"/>
         <v>429</v>
@@ -9730,7 +9733,7 @@
       </c>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B434" s="2">
         <f t="shared" si="6"/>
         <v>430</v>
@@ -9746,7 +9749,7 @@
       </c>
       <c r="F434" s="3"/>
     </row>
-    <row r="435" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B435" s="2">
         <f t="shared" si="6"/>
         <v>431</v>
@@ -9762,7 +9765,7 @@
       </c>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B436" s="2">
         <f t="shared" si="6"/>
         <v>432</v>
@@ -9778,7 +9781,7 @@
       </c>
       <c r="F436" s="3"/>
     </row>
-    <row r="437" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B437" s="2">
         <f t="shared" si="6"/>
         <v>433</v>
@@ -9794,7 +9797,7 @@
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B438" s="2">
         <f t="shared" si="6"/>
         <v>434</v>
@@ -9810,7 +9813,7 @@
       </c>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B439" s="2">
         <f t="shared" si="6"/>
         <v>435</v>
@@ -9826,7 +9829,7 @@
       </c>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B440" s="2">
         <f t="shared" si="6"/>
         <v>436</v>
@@ -9842,7 +9845,7 @@
       </c>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B441" s="2">
         <f t="shared" si="6"/>
         <v>437</v>
@@ -10786,7 +10789,7 @@
       </c>
       <c r="F499" s="3"/>
     </row>
-    <row r="500" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B500" s="2">
         <f t="shared" si="7"/>
         <v>496</v>
@@ -11234,7 +11237,7 @@
       </c>
       <c r="F527" s="3"/>
     </row>
-    <row r="528" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B528" s="2">
         <f t="shared" si="8"/>
         <v>524</v>
@@ -11310,7 +11313,7 @@
         <v>686</v>
       </c>
       <c r="E532" s="1" t="s">
-        <v>5</v>
+        <v>806</v>
       </c>
       <c r="F532" s="3"/>
     </row>
@@ -12440,41 +12443,20 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="JALAL SONS  (COLLEGE ROAD) 02"/>
-        <filter val="Jalal sons  (Izmair Town) 01"/>
+        <filter val="24/7 MART ASKARI X SECTOR F"/>
+        <filter val="Askari  Depsrtmental Store Punjab Society"/>
+        <filter val="Askari Departmental Store College Road"/>
+        <filter val="BASHIR SONS PHARMACY (ASKARI XI)"/>
+        <filter val="BUNDU KHAN ASKARI 11"/>
+        <filter val="CLINIX PHARMACY ASKARI 11"/>
+        <filter val="CSD Askari X"/>
+        <filter val="FRESHLY MART SECTOR B ASKARI 11"/>
+        <filter val="HIKMA SUPER STORE ASKARI 11"/>
         <filter val="Jalal sons (Askari 10 F sector ) 01"/>
         <filter val="JALAL SONS (ASKARI 11 B BLOCK) 02"/>
-        <filter val="JALAL SONS (AYUBIA) 02"/>
-        <filter val="JALAL SONS (Bahira Orchard) 01"/>
-        <filter val="Jalal Sons (Bahria Town)  01"/>
-        <filter val="JALAL SONS (C BLOCK MODEL TOWN) 02"/>
-        <filter val="JALAL SONS (DHA C BLOCK,PHASE 6) 02"/>
-        <filter val="JALAL SONS (DHA PH IV) 02"/>
-        <filter val="JALAL SONS (DHA PH V) 02"/>
-        <filter val="JALAL SONS (DHA Y BLOCK) 02"/>
-        <filter val="JALAL SONS (EME) 02"/>
-        <filter val="JALAL SONS (FAISAL TOWN) 02"/>
-        <filter val="Jalal Sons (H Block) 01"/>
-        <filter val="JALAL SONS (HUSSAIN CHOWK GULBERG III) 02"/>
-        <filter val="JALAL SONS (IQBAL TOWN) 02"/>
-        <filter val="Jalal Sons (J.T Shadewal) 01"/>
-        <filter val="JALAL SONS (JOHER TOWN) 02"/>
-        <filter val="Jalal Sons (Lake City) 01"/>
-        <filter val="Jalal sons (Main Market) 01"/>
-        <filter val="JALAL SONS (MODEL TOWN LINK ROAD) 02"/>
-        <filter val="Jalal Sons (PAF Market) 01 main Market"/>
-        <filter val="JALAL SONS (PARAGON CITY) 02"/>
-        <filter val="JALAL SONS (PH VI) 02"/>
-        <filter val="JALAL SONS (PHASE 8 EX PARK VIEW) 02"/>
-        <filter val="JALAL SONS (REVAZ GARDEN) 02"/>
-        <filter val="JALAL SONS (SHADMAN) 02"/>
-        <filter val="JALAL SONS (SHAUKAT KHANUM) 02"/>
-        <filter val="JALAL SONS (STATE LIFE) 02"/>
-        <filter val="JALAL SONS (TALWAR CHOWK) 02"/>
-        <filter val="JALAL SONS (VALENCIA TOWN) 02"/>
-        <filter val="JALAL SONS (WAPDA TOWN) 02"/>
-        <filter val="JALAL SONS (XX) 02"/>
         <filter val="Jalal Sons Askari X (01)"/>
+        <filter val="MM CASH &amp; CARRY ASKARI XI"/>
+        <filter val="PUNJAB CASH &amp; CARRY (ASKARI 11)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20D1F60-6F22-42C2-B378-46C0FFDE00B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F421035-E4F6-4B4E-85E0-D8E3E8FE21D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2840,7 +2840,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="B2:F604"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2885,7 +2884,7 @@
       </c>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <f>B5+1</f>
         <v>2</v>
@@ -2901,7 +2900,7 @@
       </c>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <f>B6+1</f>
         <v>3</v>
@@ -2917,7 +2916,7 @@
       </c>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <f>B7+1</f>
         <v>4</v>
@@ -2933,7 +2932,7 @@
       </c>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <f>B8+1</f>
         <v>5</v>
@@ -2949,7 +2948,7 @@
       </c>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <f t="shared" ref="B10:B73" si="0">B9+1</f>
         <v>6</v>
@@ -2965,7 +2964,7 @@
       </c>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2981,7 +2980,7 @@
       </c>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2997,7 +2996,7 @@
       </c>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3013,7 +3012,7 @@
       </c>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3029,7 +3028,7 @@
       </c>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3045,7 +3044,7 @@
       </c>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -3061,7 +3060,7 @@
       </c>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -3077,7 +3076,7 @@
       </c>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -3093,7 +3092,7 @@
       </c>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -3109,7 +3108,7 @@
       </c>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -3125,7 +3124,7 @@
       </c>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -3141,7 +3140,7 @@
       </c>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -3157,7 +3156,7 @@
       </c>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -3173,7 +3172,7 @@
       </c>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -3189,7 +3188,7 @@
       </c>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -3205,7 +3204,7 @@
       </c>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -3221,7 +3220,7 @@
       </c>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -3237,7 +3236,7 @@
       </c>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3253,7 +3252,7 @@
       </c>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -3269,7 +3268,7 @@
       </c>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -3285,7 +3284,7 @@
       </c>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -3301,7 +3300,7 @@
       </c>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B32" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -3317,7 +3316,7 @@
       </c>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B33" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -3333,7 +3332,7 @@
       </c>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B34" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -3349,7 +3348,7 @@
       </c>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B35" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -3365,7 +3364,7 @@
       </c>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B36" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -3381,7 +3380,7 @@
       </c>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -3397,7 +3396,7 @@
       </c>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -3413,7 +3412,7 @@
       </c>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B39" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -3429,7 +3428,7 @@
       </c>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B40" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -3445,7 +3444,7 @@
       </c>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B41" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -3461,7 +3460,7 @@
       </c>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -3477,7 +3476,7 @@
       </c>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -3493,7 +3492,7 @@
       </c>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -3509,7 +3508,7 @@
       </c>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B45" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -3525,7 +3524,7 @@
       </c>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -3541,7 +3540,7 @@
       </c>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -3557,7 +3556,7 @@
       </c>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -3573,7 +3572,7 @@
       </c>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3589,7 +3588,7 @@
       </c>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3605,7 +3604,7 @@
       </c>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B51" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3621,7 +3620,7 @@
       </c>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B52" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -3637,7 +3636,7 @@
       </c>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B53" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -3653,7 +3652,7 @@
       </c>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B54" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -3669,7 +3668,7 @@
       </c>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B55" s="2">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -3685,7 +3684,7 @@
       </c>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B56" s="2">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -3701,7 +3700,7 @@
       </c>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B57" s="2">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -3717,7 +3716,7 @@
       </c>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B58" s="2">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -3733,7 +3732,7 @@
       </c>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B59" s="2">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -3749,7 +3748,7 @@
       </c>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B60" s="2">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -3765,7 +3764,7 @@
       </c>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B61" s="2">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -3781,7 +3780,7 @@
       </c>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B62" s="2">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -3797,7 +3796,7 @@
       </c>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B63" s="2">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -3813,7 +3812,7 @@
       </c>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B64" s="2">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -3829,7 +3828,7 @@
       </c>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B65" s="2">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -3845,7 +3844,7 @@
       </c>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B66" s="2">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -3861,7 +3860,7 @@
       </c>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B67" s="2">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -3877,7 +3876,7 @@
       </c>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B68" s="2">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -3893,7 +3892,7 @@
       </c>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B69" s="2">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -3909,7 +3908,7 @@
       </c>
       <c r="F69" s="3"/>
     </row>
-    <row r="70" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B70" s="2">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -3925,7 +3924,7 @@
       </c>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B71" s="2">
         <f t="shared" si="0"/>
         <v>67</v>
@@ -3941,7 +3940,7 @@
       </c>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B72" s="2">
         <f t="shared" si="0"/>
         <v>68</v>
@@ -3957,7 +3956,7 @@
       </c>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B73" s="2">
         <f t="shared" si="0"/>
         <v>69</v>
@@ -3973,7 +3972,7 @@
       </c>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B74" s="2">
         <f t="shared" ref="B74:B137" si="1">B73+1</f>
         <v>70</v>
@@ -3989,7 +3988,7 @@
       </c>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B75" s="2">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -4005,7 +4004,7 @@
       </c>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B76" s="2">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -4021,7 +4020,7 @@
       </c>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B77" s="2">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -4037,7 +4036,7 @@
       </c>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B78" s="2">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -4053,7 +4052,7 @@
       </c>
       <c r="F78" s="3"/>
     </row>
-    <row r="79" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B79" s="2">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -4069,7 +4068,7 @@
       </c>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B80" s="2">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -4085,7 +4084,7 @@
       </c>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B81" s="2">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -4101,7 +4100,7 @@
       </c>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B82" s="2">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -4117,7 +4116,7 @@
       </c>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B83" s="2">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -4133,7 +4132,7 @@
       </c>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B84" s="2">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -4149,7 +4148,7 @@
       </c>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B85" s="2">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -4165,7 +4164,7 @@
       </c>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B86" s="2">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -4181,7 +4180,7 @@
       </c>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B87" s="2">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -4197,7 +4196,7 @@
       </c>
       <c r="F87" s="3"/>
     </row>
-    <row r="88" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B88" s="2">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -4213,7 +4212,7 @@
       </c>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B89" s="2">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -4229,7 +4228,7 @@
       </c>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B90" s="2">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -4245,7 +4244,7 @@
       </c>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B91" s="2">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -4261,7 +4260,7 @@
       </c>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B92" s="2">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -4277,7 +4276,7 @@
       </c>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B93" s="2">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -4293,7 +4292,7 @@
       </c>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B94" s="2">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -4309,7 +4308,7 @@
       </c>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B95" s="2">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -4325,7 +4324,7 @@
       </c>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B96" s="2">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -4341,7 +4340,7 @@
       </c>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B97" s="2">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -4357,7 +4356,7 @@
       </c>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B98" s="2">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -4373,7 +4372,7 @@
       </c>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B99" s="2">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -4389,7 +4388,7 @@
       </c>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B100" s="2">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -4405,7 +4404,7 @@
       </c>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B101" s="2">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -4421,7 +4420,7 @@
       </c>
       <c r="F101" s="3"/>
     </row>
-    <row r="102" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B102" s="2">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -4437,7 +4436,7 @@
       </c>
       <c r="F102" s="3"/>
     </row>
-    <row r="103" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B103" s="2">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -4453,7 +4452,7 @@
       </c>
       <c r="F103" s="3"/>
     </row>
-    <row r="104" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B104" s="2">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -4469,7 +4468,7 @@
       </c>
       <c r="F104" s="3"/>
     </row>
-    <row r="105" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B105" s="2">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -4485,7 +4484,7 @@
       </c>
       <c r="F105" s="3"/>
     </row>
-    <row r="106" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B106" s="2">
         <f t="shared" si="1"/>
         <v>102</v>
@@ -4501,7 +4500,7 @@
       </c>
       <c r="F106" s="3"/>
     </row>
-    <row r="107" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B107" s="2">
         <f t="shared" si="1"/>
         <v>103</v>
@@ -4517,7 +4516,7 @@
       </c>
       <c r="F107" s="3"/>
     </row>
-    <row r="108" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B108" s="2">
         <f t="shared" si="1"/>
         <v>104</v>
@@ -4533,7 +4532,7 @@
       </c>
       <c r="F108" s="3"/>
     </row>
-    <row r="109" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B109" s="2">
         <f t="shared" si="1"/>
         <v>105</v>
@@ -4549,7 +4548,7 @@
       </c>
       <c r="F109" s="3"/>
     </row>
-    <row r="110" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B110" s="2">
         <f t="shared" si="1"/>
         <v>106</v>
@@ -4565,7 +4564,7 @@
       </c>
       <c r="F110" s="3"/>
     </row>
-    <row r="111" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B111" s="2">
         <f t="shared" si="1"/>
         <v>107</v>
@@ -4613,7 +4612,7 @@
       </c>
       <c r="F113" s="3"/>
     </row>
-    <row r="114" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B114" s="2">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -4629,7 +4628,7 @@
       </c>
       <c r="F114" s="3"/>
     </row>
-    <row r="115" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B115" s="2">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -4645,7 +4644,7 @@
       </c>
       <c r="F115" s="3"/>
     </row>
-    <row r="116" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B116" s="2">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -4661,7 +4660,7 @@
       </c>
       <c r="F116" s="3"/>
     </row>
-    <row r="117" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B117" s="2">
         <f t="shared" si="1"/>
         <v>113</v>
@@ -4677,7 +4676,7 @@
       </c>
       <c r="F117" s="3"/>
     </row>
-    <row r="118" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B118" s="2">
         <f t="shared" si="1"/>
         <v>114</v>
@@ -4693,7 +4692,7 @@
       </c>
       <c r="F118" s="3"/>
     </row>
-    <row r="119" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B119" s="2">
         <f t="shared" si="1"/>
         <v>115</v>
@@ -4709,7 +4708,7 @@
       </c>
       <c r="F119" s="3"/>
     </row>
-    <row r="120" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B120" s="2">
         <f t="shared" si="1"/>
         <v>116</v>
@@ -4725,7 +4724,7 @@
       </c>
       <c r="F120" s="3"/>
     </row>
-    <row r="121" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B121" s="2">
         <f t="shared" si="1"/>
         <v>117</v>
@@ -4741,7 +4740,7 @@
       </c>
       <c r="F121" s="3"/>
     </row>
-    <row r="122" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B122" s="2">
         <f t="shared" si="1"/>
         <v>118</v>
@@ -4757,7 +4756,7 @@
       </c>
       <c r="F122" s="3"/>
     </row>
-    <row r="123" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B123" s="2">
         <f t="shared" si="1"/>
         <v>119</v>
@@ -4773,7 +4772,7 @@
       </c>
       <c r="F123" s="3"/>
     </row>
-    <row r="124" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B124" s="2">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -4789,7 +4788,7 @@
       </c>
       <c r="F124" s="3"/>
     </row>
-    <row r="125" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B125" s="2">
         <f t="shared" si="1"/>
         <v>121</v>
@@ -4821,7 +4820,7 @@
       </c>
       <c r="F126" s="3"/>
     </row>
-    <row r="127" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B127" s="2">
         <f t="shared" si="1"/>
         <v>123</v>
@@ -4837,7 +4836,7 @@
       </c>
       <c r="F127" s="3"/>
     </row>
-    <row r="128" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B128" s="2">
         <f t="shared" si="1"/>
         <v>124</v>
@@ -4853,7 +4852,7 @@
       </c>
       <c r="F128" s="3"/>
     </row>
-    <row r="129" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B129" s="2">
         <f t="shared" si="1"/>
         <v>125</v>
@@ -4869,7 +4868,7 @@
       </c>
       <c r="F129" s="3"/>
     </row>
-    <row r="130" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B130" s="2">
         <f t="shared" si="1"/>
         <v>126</v>
@@ -4885,7 +4884,7 @@
       </c>
       <c r="F130" s="3"/>
     </row>
-    <row r="131" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B131" s="2">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -4901,7 +4900,7 @@
       </c>
       <c r="F131" s="3"/>
     </row>
-    <row r="132" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B132" s="2">
         <f t="shared" si="1"/>
         <v>128</v>
@@ -4917,7 +4916,7 @@
       </c>
       <c r="F132" s="3"/>
     </row>
-    <row r="133" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B133" s="2">
         <f t="shared" si="1"/>
         <v>129</v>
@@ -4933,7 +4932,7 @@
       </c>
       <c r="F133" s="3"/>
     </row>
-    <row r="134" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B134" s="2">
         <f t="shared" si="1"/>
         <v>130</v>
@@ -4949,7 +4948,7 @@
       </c>
       <c r="F134" s="3"/>
     </row>
-    <row r="135" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B135" s="2">
         <f t="shared" si="1"/>
         <v>131</v>
@@ -4965,7 +4964,7 @@
       </c>
       <c r="F135" s="3"/>
     </row>
-    <row r="136" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B136" s="2">
         <f t="shared" si="1"/>
         <v>132</v>
@@ -4981,7 +4980,7 @@
       </c>
       <c r="F136" s="3"/>
     </row>
-    <row r="137" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B137" s="2">
         <f t="shared" si="1"/>
         <v>133</v>
@@ -4997,7 +4996,7 @@
       </c>
       <c r="F137" s="3"/>
     </row>
-    <row r="138" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B138" s="2">
         <f t="shared" ref="B138:B201" si="2">B137+1</f>
         <v>134</v>
@@ -5013,7 +5012,7 @@
       </c>
       <c r="F138" s="3"/>
     </row>
-    <row r="139" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B139" s="2">
         <f t="shared" si="2"/>
         <v>135</v>
@@ -5029,7 +5028,7 @@
       </c>
       <c r="F139" s="3"/>
     </row>
-    <row r="140" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B140" s="2">
         <f t="shared" si="2"/>
         <v>136</v>
@@ -5045,7 +5044,7 @@
       </c>
       <c r="F140" s="3"/>
     </row>
-    <row r="141" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B141" s="2">
         <f t="shared" si="2"/>
         <v>137</v>
@@ -5061,7 +5060,7 @@
       </c>
       <c r="F141" s="3"/>
     </row>
-    <row r="142" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B142" s="2">
         <f t="shared" si="2"/>
         <v>138</v>
@@ -5077,7 +5076,7 @@
       </c>
       <c r="F142" s="3"/>
     </row>
-    <row r="143" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B143" s="2">
         <f t="shared" si="2"/>
         <v>139</v>
@@ -5093,7 +5092,7 @@
       </c>
       <c r="F143" s="3"/>
     </row>
-    <row r="144" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B144" s="2">
         <f t="shared" si="2"/>
         <v>140</v>
@@ -5109,7 +5108,7 @@
       </c>
       <c r="F144" s="3"/>
     </row>
-    <row r="145" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B145" s="2">
         <f t="shared" si="2"/>
         <v>141</v>
@@ -5125,7 +5124,7 @@
       </c>
       <c r="F145" s="3"/>
     </row>
-    <row r="146" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B146" s="2">
         <f t="shared" si="2"/>
         <v>142</v>
@@ -5141,7 +5140,7 @@
       </c>
       <c r="F146" s="3"/>
     </row>
-    <row r="147" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B147" s="2">
         <f t="shared" si="2"/>
         <v>143</v>
@@ -5157,7 +5156,7 @@
       </c>
       <c r="F147" s="3"/>
     </row>
-    <row r="148" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B148" s="2">
         <f t="shared" si="2"/>
         <v>144</v>
@@ -5173,7 +5172,7 @@
       </c>
       <c r="F148" s="3"/>
     </row>
-    <row r="149" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B149" s="2">
         <f t="shared" si="2"/>
         <v>145</v>
@@ -5189,7 +5188,7 @@
       </c>
       <c r="F149" s="3"/>
     </row>
-    <row r="150" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B150" s="2">
         <f t="shared" si="2"/>
         <v>146</v>
@@ -5205,7 +5204,7 @@
       </c>
       <c r="F150" s="3"/>
     </row>
-    <row r="151" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B151" s="2">
         <f t="shared" si="2"/>
         <v>147</v>
@@ -5221,7 +5220,7 @@
       </c>
       <c r="F151" s="3"/>
     </row>
-    <row r="152" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B152" s="2">
         <f t="shared" si="2"/>
         <v>148</v>
@@ -5237,7 +5236,7 @@
       </c>
       <c r="F152" s="3"/>
     </row>
-    <row r="153" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B153" s="2">
         <f t="shared" si="2"/>
         <v>149</v>
@@ -5253,7 +5252,7 @@
       </c>
       <c r="F153" s="3"/>
     </row>
-    <row r="154" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B154" s="2">
         <f t="shared" si="2"/>
         <v>150</v>
@@ -5269,7 +5268,7 @@
       </c>
       <c r="F154" s="3"/>
     </row>
-    <row r="155" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B155" s="2">
         <f t="shared" si="2"/>
         <v>151</v>
@@ -5285,7 +5284,7 @@
       </c>
       <c r="F155" s="3"/>
     </row>
-    <row r="156" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B156" s="2">
         <f t="shared" si="2"/>
         <v>152</v>
@@ -5301,7 +5300,7 @@
       </c>
       <c r="F156" s="3"/>
     </row>
-    <row r="157" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B157" s="2">
         <f t="shared" si="2"/>
         <v>153</v>
@@ -5317,7 +5316,7 @@
       </c>
       <c r="F157" s="3"/>
     </row>
-    <row r="158" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B158" s="2">
         <f t="shared" si="2"/>
         <v>154</v>
@@ -5333,7 +5332,7 @@
       </c>
       <c r="F158" s="3"/>
     </row>
-    <row r="159" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B159" s="2">
         <f t="shared" si="2"/>
         <v>155</v>
@@ -5349,7 +5348,7 @@
       </c>
       <c r="F159" s="3"/>
     </row>
-    <row r="160" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B160" s="2">
         <f t="shared" si="2"/>
         <v>156</v>
@@ -5365,7 +5364,7 @@
       </c>
       <c r="F160" s="3"/>
     </row>
-    <row r="161" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B161" s="2">
         <f t="shared" si="2"/>
         <v>157</v>
@@ -5381,7 +5380,7 @@
       </c>
       <c r="F161" s="3"/>
     </row>
-    <row r="162" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B162" s="2">
         <f t="shared" si="2"/>
         <v>158</v>
@@ -5397,7 +5396,7 @@
       </c>
       <c r="F162" s="3"/>
     </row>
-    <row r="163" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B163" s="2">
         <f t="shared" si="2"/>
         <v>159</v>
@@ -5413,7 +5412,7 @@
       </c>
       <c r="F163" s="3"/>
     </row>
-    <row r="164" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B164" s="2">
         <f t="shared" si="2"/>
         <v>160</v>
@@ -5429,7 +5428,7 @@
       </c>
       <c r="F164" s="3"/>
     </row>
-    <row r="165" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B165" s="2">
         <f t="shared" si="2"/>
         <v>161</v>
@@ -5445,7 +5444,7 @@
       </c>
       <c r="F165" s="3"/>
     </row>
-    <row r="166" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B166" s="2">
         <f t="shared" si="2"/>
         <v>162</v>
@@ -5461,7 +5460,7 @@
       </c>
       <c r="F166" s="3"/>
     </row>
-    <row r="167" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B167" s="2">
         <f t="shared" si="2"/>
         <v>163</v>
@@ -5477,7 +5476,7 @@
       </c>
       <c r="F167" s="3"/>
     </row>
-    <row r="168" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B168" s="2">
         <f t="shared" si="2"/>
         <v>164</v>
@@ -5493,7 +5492,7 @@
       </c>
       <c r="F168" s="3"/>
     </row>
-    <row r="169" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B169" s="2">
         <f t="shared" si="2"/>
         <v>165</v>
@@ -5525,7 +5524,7 @@
       </c>
       <c r="F170" s="3"/>
     </row>
-    <row r="171" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B171" s="2">
         <f t="shared" si="2"/>
         <v>167</v>
@@ -5541,7 +5540,7 @@
       </c>
       <c r="F171" s="3"/>
     </row>
-    <row r="172" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B172" s="2">
         <f t="shared" si="2"/>
         <v>168</v>
@@ -5557,7 +5556,7 @@
       </c>
       <c r="F172" s="3"/>
     </row>
-    <row r="173" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B173" s="2">
         <f t="shared" si="2"/>
         <v>169</v>
@@ -5573,7 +5572,7 @@
       </c>
       <c r="F173" s="3"/>
     </row>
-    <row r="174" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B174" s="2">
         <f t="shared" si="2"/>
         <v>170</v>
@@ -5589,7 +5588,7 @@
       </c>
       <c r="F174" s="3"/>
     </row>
-    <row r="175" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B175" s="2">
         <f t="shared" si="2"/>
         <v>171</v>
@@ -5605,7 +5604,7 @@
       </c>
       <c r="F175" s="3"/>
     </row>
-    <row r="176" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B176" s="2">
         <f t="shared" si="2"/>
         <v>172</v>
@@ -5621,7 +5620,7 @@
       </c>
       <c r="F176" s="3"/>
     </row>
-    <row r="177" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B177" s="2">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -5637,7 +5636,7 @@
       </c>
       <c r="F177" s="3"/>
     </row>
-    <row r="178" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B178" s="2">
         <f t="shared" si="2"/>
         <v>174</v>
@@ -5653,7 +5652,7 @@
       </c>
       <c r="F178" s="3"/>
     </row>
-    <row r="179" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B179" s="2">
         <f t="shared" si="2"/>
         <v>175</v>
@@ -5669,7 +5668,7 @@
       </c>
       <c r="F179" s="3"/>
     </row>
-    <row r="180" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B180" s="2">
         <f t="shared" si="2"/>
         <v>176</v>
@@ -5685,7 +5684,7 @@
       </c>
       <c r="F180" s="3"/>
     </row>
-    <row r="181" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B181" s="2">
         <f t="shared" si="2"/>
         <v>177</v>
@@ -5701,7 +5700,7 @@
       </c>
       <c r="F181" s="3"/>
     </row>
-    <row r="182" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B182" s="2">
         <f t="shared" si="2"/>
         <v>178</v>
@@ -5717,7 +5716,7 @@
       </c>
       <c r="F182" s="3"/>
     </row>
-    <row r="183" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B183" s="2">
         <f t="shared" si="2"/>
         <v>179</v>
@@ -5733,7 +5732,7 @@
       </c>
       <c r="F183" s="3"/>
     </row>
-    <row r="184" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B184" s="2">
         <f t="shared" si="2"/>
         <v>180</v>
@@ -5749,7 +5748,7 @@
       </c>
       <c r="F184" s="3"/>
     </row>
-    <row r="185" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B185" s="2">
         <f t="shared" si="2"/>
         <v>181</v>
@@ -5765,7 +5764,7 @@
       </c>
       <c r="F185" s="3"/>
     </row>
-    <row r="186" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B186" s="2">
         <f t="shared" si="2"/>
         <v>182</v>
@@ -5781,7 +5780,7 @@
       </c>
       <c r="F186" s="3"/>
     </row>
-    <row r="187" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B187" s="2">
         <f t="shared" si="2"/>
         <v>183</v>
@@ -5797,7 +5796,7 @@
       </c>
       <c r="F187" s="3"/>
     </row>
-    <row r="188" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B188" s="2">
         <f t="shared" si="2"/>
         <v>184</v>
@@ -5813,7 +5812,7 @@
       </c>
       <c r="F188" s="3"/>
     </row>
-    <row r="189" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B189" s="2">
         <f t="shared" si="2"/>
         <v>185</v>
@@ -5829,7 +5828,7 @@
       </c>
       <c r="F189" s="3"/>
     </row>
-    <row r="190" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B190" s="2">
         <f t="shared" si="2"/>
         <v>186</v>
@@ -5845,7 +5844,7 @@
       </c>
       <c r="F190" s="3"/>
     </row>
-    <row r="191" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B191" s="2">
         <f t="shared" si="2"/>
         <v>187</v>
@@ -5861,7 +5860,7 @@
       </c>
       <c r="F191" s="3"/>
     </row>
-    <row r="192" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B192" s="2">
         <f t="shared" si="2"/>
         <v>188</v>
@@ -5877,7 +5876,7 @@
       </c>
       <c r="F192" s="3"/>
     </row>
-    <row r="193" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B193" s="2">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -5893,7 +5892,7 @@
       </c>
       <c r="F193" s="3"/>
     </row>
-    <row r="194" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B194" s="2">
         <f t="shared" si="2"/>
         <v>190</v>
@@ -5909,7 +5908,7 @@
       </c>
       <c r="F194" s="3"/>
     </row>
-    <row r="195" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B195" s="2">
         <f t="shared" si="2"/>
         <v>191</v>
@@ -5925,7 +5924,7 @@
       </c>
       <c r="F195" s="3"/>
     </row>
-    <row r="196" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B196" s="2">
         <f t="shared" si="2"/>
         <v>192</v>
@@ -5941,7 +5940,7 @@
       </c>
       <c r="F196" s="3"/>
     </row>
-    <row r="197" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B197" s="2">
         <f t="shared" si="2"/>
         <v>193</v>
@@ -5957,7 +5956,7 @@
       </c>
       <c r="F197" s="3"/>
     </row>
-    <row r="198" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B198" s="2">
         <f t="shared" si="2"/>
         <v>194</v>
@@ -5973,7 +5972,7 @@
       </c>
       <c r="F198" s="3"/>
     </row>
-    <row r="199" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B199" s="2">
         <f t="shared" si="2"/>
         <v>195</v>
@@ -5989,7 +5988,7 @@
       </c>
       <c r="F199" s="3"/>
     </row>
-    <row r="200" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B200" s="2">
         <f t="shared" si="2"/>
         <v>196</v>
@@ -6005,7 +6004,7 @@
       </c>
       <c r="F200" s="3"/>
     </row>
-    <row r="201" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B201" s="2">
         <f t="shared" si="2"/>
         <v>197</v>
@@ -6021,7 +6020,7 @@
       </c>
       <c r="F201" s="3"/>
     </row>
-    <row r="202" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B202" s="2">
         <f t="shared" ref="B202:B265" si="3">B201+1</f>
         <v>198</v>
@@ -6037,7 +6036,7 @@
       </c>
       <c r="F202" s="3"/>
     </row>
-    <row r="203" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B203" s="2">
         <f t="shared" si="3"/>
         <v>199</v>
@@ -6053,7 +6052,7 @@
       </c>
       <c r="F203" s="3"/>
     </row>
-    <row r="204" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B204" s="2">
         <f t="shared" si="3"/>
         <v>200</v>
@@ -6069,7 +6068,7 @@
       </c>
       <c r="F204" s="3"/>
     </row>
-    <row r="205" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B205" s="2">
         <f t="shared" si="3"/>
         <v>201</v>
@@ -6085,7 +6084,7 @@
       </c>
       <c r="F205" s="3"/>
     </row>
-    <row r="206" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B206" s="2">
         <f t="shared" si="3"/>
         <v>202</v>
@@ -6101,7 +6100,7 @@
       </c>
       <c r="F206" s="3"/>
     </row>
-    <row r="207" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B207" s="2">
         <f t="shared" si="3"/>
         <v>203</v>
@@ -6117,7 +6116,7 @@
       </c>
       <c r="F207" s="3"/>
     </row>
-    <row r="208" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B208" s="2">
         <f t="shared" si="3"/>
         <v>204</v>
@@ -6133,7 +6132,7 @@
       </c>
       <c r="F208" s="3"/>
     </row>
-    <row r="209" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B209" s="2">
         <f t="shared" si="3"/>
         <v>205</v>
@@ -6149,7 +6148,7 @@
       </c>
       <c r="F209" s="3"/>
     </row>
-    <row r="210" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B210" s="2">
         <f t="shared" si="3"/>
         <v>206</v>
@@ -6165,7 +6164,7 @@
       </c>
       <c r="F210" s="3"/>
     </row>
-    <row r="211" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B211" s="2">
         <f t="shared" si="3"/>
         <v>207</v>
@@ -6181,7 +6180,7 @@
       </c>
       <c r="F211" s="3"/>
     </row>
-    <row r="212" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B212" s="2">
         <f t="shared" si="3"/>
         <v>208</v>
@@ -6197,7 +6196,7 @@
       </c>
       <c r="F212" s="3"/>
     </row>
-    <row r="213" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B213" s="2">
         <f t="shared" si="3"/>
         <v>209</v>
@@ -6213,7 +6212,7 @@
       </c>
       <c r="F213" s="3"/>
     </row>
-    <row r="214" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B214" s="2">
         <f t="shared" si="3"/>
         <v>210</v>
@@ -6229,7 +6228,7 @@
       </c>
       <c r="F214" s="3"/>
     </row>
-    <row r="215" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B215" s="2">
         <f t="shared" si="3"/>
         <v>211</v>
@@ -6245,7 +6244,7 @@
       </c>
       <c r="F215" s="3"/>
     </row>
-    <row r="216" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B216" s="2">
         <f t="shared" si="3"/>
         <v>212</v>
@@ -6261,7 +6260,7 @@
       </c>
       <c r="F216" s="3"/>
     </row>
-    <row r="217" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B217" s="2">
         <f t="shared" si="3"/>
         <v>213</v>
@@ -6277,7 +6276,7 @@
       </c>
       <c r="F217" s="3"/>
     </row>
-    <row r="218" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B218" s="2">
         <f t="shared" si="3"/>
         <v>214</v>
@@ -6309,7 +6308,7 @@
       </c>
       <c r="F219" s="3"/>
     </row>
-    <row r="220" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B220" s="2">
         <f t="shared" si="3"/>
         <v>216</v>
@@ -6325,7 +6324,7 @@
       </c>
       <c r="F220" s="3"/>
     </row>
-    <row r="221" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B221" s="2">
         <f t="shared" si="3"/>
         <v>217</v>
@@ -6341,7 +6340,7 @@
       </c>
       <c r="F221" s="3"/>
     </row>
-    <row r="222" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B222" s="2">
         <f t="shared" si="3"/>
         <v>218</v>
@@ -6357,7 +6356,7 @@
       </c>
       <c r="F222" s="3"/>
     </row>
-    <row r="223" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B223" s="2">
         <f t="shared" si="3"/>
         <v>219</v>
@@ -6373,7 +6372,7 @@
       </c>
       <c r="F223" s="3"/>
     </row>
-    <row r="224" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B224" s="2">
         <f t="shared" si="3"/>
         <v>220</v>
@@ -6389,7 +6388,7 @@
       </c>
       <c r="F224" s="3"/>
     </row>
-    <row r="225" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B225" s="2">
         <f t="shared" si="3"/>
         <v>221</v>
@@ -6405,7 +6404,7 @@
       </c>
       <c r="F225" s="3"/>
     </row>
-    <row r="226" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B226" s="2">
         <f t="shared" si="3"/>
         <v>222</v>
@@ -6421,7 +6420,7 @@
       </c>
       <c r="F226" s="3"/>
     </row>
-    <row r="227" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B227" s="2">
         <f t="shared" si="3"/>
         <v>223</v>
@@ -6437,7 +6436,7 @@
       </c>
       <c r="F227" s="3"/>
     </row>
-    <row r="228" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B228" s="2">
         <f t="shared" si="3"/>
         <v>224</v>
@@ -6453,7 +6452,7 @@
       </c>
       <c r="F228" s="3"/>
     </row>
-    <row r="229" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B229" s="2">
         <f t="shared" si="3"/>
         <v>225</v>
@@ -6469,7 +6468,7 @@
       </c>
       <c r="F229" s="3"/>
     </row>
-    <row r="230" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B230" s="2">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -6485,7 +6484,7 @@
       </c>
       <c r="F230" s="3"/>
     </row>
-    <row r="231" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B231" s="2">
         <f t="shared" si="3"/>
         <v>227</v>
@@ -6501,7 +6500,7 @@
       </c>
       <c r="F231" s="3"/>
     </row>
-    <row r="232" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B232" s="2">
         <f t="shared" si="3"/>
         <v>228</v>
@@ -6517,7 +6516,7 @@
       </c>
       <c r="F232" s="3"/>
     </row>
-    <row r="233" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B233" s="2">
         <f t="shared" si="3"/>
         <v>229</v>
@@ -6533,7 +6532,7 @@
       </c>
       <c r="F233" s="3"/>
     </row>
-    <row r="234" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B234" s="2">
         <f t="shared" si="3"/>
         <v>230</v>
@@ -6565,7 +6564,7 @@
       </c>
       <c r="F235" s="3"/>
     </row>
-    <row r="236" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B236" s="2">
         <f t="shared" si="3"/>
         <v>232</v>
@@ -6581,7 +6580,7 @@
       </c>
       <c r="F236" s="3"/>
     </row>
-    <row r="237" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B237" s="2">
         <f t="shared" si="3"/>
         <v>233</v>
@@ -6597,7 +6596,7 @@
       </c>
       <c r="F237" s="3"/>
     </row>
-    <row r="238" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B238" s="2">
         <f t="shared" si="3"/>
         <v>234</v>
@@ -6613,7 +6612,7 @@
       </c>
       <c r="F238" s="3"/>
     </row>
-    <row r="239" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B239" s="2">
         <f t="shared" si="3"/>
         <v>235</v>
@@ -6629,7 +6628,7 @@
       </c>
       <c r="F239" s="3"/>
     </row>
-    <row r="240" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B240" s="2">
         <f t="shared" si="3"/>
         <v>236</v>
@@ -6645,7 +6644,7 @@
       </c>
       <c r="F240" s="3"/>
     </row>
-    <row r="241" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B241" s="2">
         <f t="shared" si="3"/>
         <v>237</v>
@@ -6661,7 +6660,7 @@
       </c>
       <c r="F241" s="3"/>
     </row>
-    <row r="242" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B242" s="2">
         <f t="shared" si="3"/>
         <v>238</v>
@@ -6677,7 +6676,7 @@
       </c>
       <c r="F242" s="3"/>
     </row>
-    <row r="243" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B243" s="2">
         <f t="shared" si="3"/>
         <v>239</v>
@@ -6693,7 +6692,7 @@
       </c>
       <c r="F243" s="3"/>
     </row>
-    <row r="244" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B244" s="2">
         <f t="shared" si="3"/>
         <v>240</v>
@@ -6709,7 +6708,7 @@
       </c>
       <c r="F244" s="3"/>
     </row>
-    <row r="245" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B245" s="2">
         <f t="shared" si="3"/>
         <v>241</v>
@@ -6725,7 +6724,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B246" s="2">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6741,7 +6740,7 @@
       </c>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B247" s="2">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6757,7 +6756,7 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B248" s="2">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6773,7 +6772,7 @@
       </c>
       <c r="F248" s="3"/>
     </row>
-    <row r="249" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B249" s="2">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -6789,7 +6788,7 @@
       </c>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B250" s="2">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6805,7 +6804,7 @@
       </c>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B251" s="2">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6821,7 +6820,7 @@
       </c>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B252" s="2">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -6837,7 +6836,7 @@
       </c>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B253" s="2">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -6853,7 +6852,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -6869,7 +6868,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -6885,7 +6884,7 @@
       </c>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B256" s="2">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -6901,7 +6900,7 @@
       </c>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B257" s="2">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -6917,7 +6916,7 @@
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B258" s="2">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -6933,7 +6932,7 @@
       </c>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B259" s="2">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -6949,7 +6948,7 @@
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B260" s="2">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -6965,7 +6964,7 @@
       </c>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B261" s="2">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -6981,7 +6980,7 @@
       </c>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B262" s="2">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -6997,7 +6996,7 @@
       </c>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B263" s="2">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -7013,7 +7012,7 @@
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B264" s="2">
         <f t="shared" si="3"/>
         <v>260</v>
@@ -7029,7 +7028,7 @@
       </c>
       <c r="F264" s="3"/>
     </row>
-    <row r="265" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B265" s="2">
         <f t="shared" si="3"/>
         <v>261</v>
@@ -7045,7 +7044,7 @@
       </c>
       <c r="F265" s="3"/>
     </row>
-    <row r="266" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B266" s="2">
         <f t="shared" ref="B266:B329" si="4">B265+1</f>
         <v>262</v>
@@ -7061,7 +7060,7 @@
       </c>
       <c r="F266" s="3"/>
     </row>
-    <row r="267" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B267" s="2">
         <f t="shared" si="4"/>
         <v>263</v>
@@ -7077,7 +7076,7 @@
       </c>
       <c r="F267" s="3"/>
     </row>
-    <row r="268" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B268" s="2">
         <f t="shared" si="4"/>
         <v>264</v>
@@ -7093,7 +7092,7 @@
       </c>
       <c r="F268" s="3"/>
     </row>
-    <row r="269" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B269" s="2">
         <f t="shared" si="4"/>
         <v>265</v>
@@ -7109,7 +7108,7 @@
       </c>
       <c r="F269" s="3"/>
     </row>
-    <row r="270" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B270" s="2">
         <f t="shared" si="4"/>
         <v>266</v>
@@ -7125,7 +7124,7 @@
       </c>
       <c r="F270" s="3"/>
     </row>
-    <row r="271" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B271" s="2">
         <f t="shared" si="4"/>
         <v>267</v>
@@ -7141,7 +7140,7 @@
       </c>
       <c r="F271" s="3"/>
     </row>
-    <row r="272" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B272" s="2">
         <f t="shared" si="4"/>
         <v>268</v>
@@ -7157,7 +7156,7 @@
       </c>
       <c r="F272" s="3"/>
     </row>
-    <row r="273" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B273" s="2">
         <f t="shared" si="4"/>
         <v>269</v>
@@ -7173,7 +7172,7 @@
       </c>
       <c r="F273" s="3"/>
     </row>
-    <row r="274" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B274" s="2">
         <f t="shared" si="4"/>
         <v>270</v>
@@ -7189,7 +7188,7 @@
       </c>
       <c r="F274" s="3"/>
     </row>
-    <row r="275" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B275" s="2">
         <f t="shared" si="4"/>
         <v>271</v>
@@ -7205,7 +7204,7 @@
       </c>
       <c r="F275" s="3"/>
     </row>
-    <row r="276" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B276" s="2">
         <f t="shared" si="4"/>
         <v>272</v>
@@ -7221,7 +7220,7 @@
       </c>
       <c r="F276" s="3"/>
     </row>
-    <row r="277" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B277" s="2">
         <f t="shared" si="4"/>
         <v>273</v>
@@ -7237,7 +7236,7 @@
       </c>
       <c r="F277" s="3"/>
     </row>
-    <row r="278" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B278" s="2">
         <f t="shared" si="4"/>
         <v>274</v>
@@ -7253,7 +7252,7 @@
       </c>
       <c r="F278" s="3"/>
     </row>
-    <row r="279" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B279" s="2">
         <f t="shared" si="4"/>
         <v>275</v>
@@ -7269,7 +7268,7 @@
       </c>
       <c r="F279" s="3"/>
     </row>
-    <row r="280" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B280" s="2">
         <f t="shared" si="4"/>
         <v>276</v>
@@ -7301,7 +7300,7 @@
       </c>
       <c r="F281" s="3"/>
     </row>
-    <row r="282" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B282" s="2">
         <f t="shared" si="4"/>
         <v>278</v>
@@ -7317,7 +7316,7 @@
       </c>
       <c r="F282" s="3"/>
     </row>
-    <row r="283" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B283" s="2">
         <f t="shared" si="4"/>
         <v>279</v>
@@ -7333,7 +7332,7 @@
       </c>
       <c r="F283" s="3"/>
     </row>
-    <row r="284" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B284" s="2">
         <f t="shared" si="4"/>
         <v>280</v>
@@ -7349,7 +7348,7 @@
       </c>
       <c r="F284" s="3"/>
     </row>
-    <row r="285" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B285" s="2">
         <f t="shared" si="4"/>
         <v>281</v>
@@ -7365,7 +7364,7 @@
       </c>
       <c r="F285" s="3"/>
     </row>
-    <row r="286" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B286" s="2">
         <f t="shared" si="4"/>
         <v>282</v>
@@ -7381,7 +7380,7 @@
       </c>
       <c r="F286" s="3"/>
     </row>
-    <row r="287" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B287" s="2">
         <f t="shared" si="4"/>
         <v>283</v>
@@ -7397,7 +7396,7 @@
       </c>
       <c r="F287" s="3"/>
     </row>
-    <row r="288" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B288" s="2">
         <f t="shared" si="4"/>
         <v>284</v>
@@ -7413,7 +7412,7 @@
       </c>
       <c r="F288" s="3"/>
     </row>
-    <row r="289" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B289" s="2">
         <f t="shared" si="4"/>
         <v>285</v>
@@ -7429,7 +7428,7 @@
       </c>
       <c r="F289" s="3"/>
     </row>
-    <row r="290" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B290" s="2">
         <f t="shared" si="4"/>
         <v>286</v>
@@ -7445,7 +7444,7 @@
       </c>
       <c r="F290" s="3"/>
     </row>
-    <row r="291" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B291" s="2">
         <f t="shared" si="4"/>
         <v>287</v>
@@ -7461,7 +7460,7 @@
       </c>
       <c r="F291" s="3"/>
     </row>
-    <row r="292" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B292" s="2">
         <f t="shared" si="4"/>
         <v>288</v>
@@ -7477,7 +7476,7 @@
       </c>
       <c r="F292" s="3"/>
     </row>
-    <row r="293" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B293" s="2">
         <f t="shared" si="4"/>
         <v>289</v>
@@ -7493,7 +7492,7 @@
       </c>
       <c r="F293" s="3"/>
     </row>
-    <row r="294" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B294" s="2">
         <f t="shared" si="4"/>
         <v>290</v>
@@ -7509,7 +7508,7 @@
       </c>
       <c r="F294" s="3"/>
     </row>
-    <row r="295" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B295" s="2">
         <f t="shared" si="4"/>
         <v>291</v>
@@ -7525,7 +7524,7 @@
       </c>
       <c r="F295" s="3"/>
     </row>
-    <row r="296" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B296" s="2">
         <f t="shared" si="4"/>
         <v>292</v>
@@ -7541,7 +7540,7 @@
       </c>
       <c r="F296" s="3"/>
     </row>
-    <row r="297" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B297" s="2">
         <f t="shared" si="4"/>
         <v>293</v>
@@ -7557,7 +7556,7 @@
       </c>
       <c r="F297" s="3"/>
     </row>
-    <row r="298" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B298" s="2">
         <f t="shared" si="4"/>
         <v>294</v>
@@ -7573,7 +7572,7 @@
       </c>
       <c r="F298" s="3"/>
     </row>
-    <row r="299" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B299" s="2">
         <f t="shared" si="4"/>
         <v>295</v>
@@ -7589,7 +7588,7 @@
       </c>
       <c r="F299" s="3"/>
     </row>
-    <row r="300" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B300" s="2">
         <f t="shared" si="4"/>
         <v>296</v>
@@ -7605,7 +7604,7 @@
       </c>
       <c r="F300" s="3"/>
     </row>
-    <row r="301" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B301" s="2">
         <f t="shared" si="4"/>
         <v>297</v>
@@ -7621,7 +7620,7 @@
       </c>
       <c r="F301" s="3"/>
     </row>
-    <row r="302" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B302" s="2">
         <f t="shared" si="4"/>
         <v>298</v>
@@ -7637,7 +7636,7 @@
       </c>
       <c r="F302" s="3"/>
     </row>
-    <row r="303" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B303" s="2">
         <f t="shared" si="4"/>
         <v>299</v>
@@ -7653,7 +7652,7 @@
       </c>
       <c r="F303" s="3"/>
     </row>
-    <row r="304" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B304" s="2">
         <f t="shared" si="4"/>
         <v>300</v>
@@ -7669,7 +7668,7 @@
       </c>
       <c r="F304" s="3"/>
     </row>
-    <row r="305" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B305" s="2">
         <f t="shared" si="4"/>
         <v>301</v>
@@ -7685,7 +7684,7 @@
       </c>
       <c r="F305" s="3"/>
     </row>
-    <row r="306" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B306" s="2">
         <f t="shared" si="4"/>
         <v>302</v>
@@ -7701,7 +7700,7 @@
       </c>
       <c r="F306" s="3"/>
     </row>
-    <row r="307" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B307" s="2">
         <f t="shared" si="4"/>
         <v>303</v>
@@ -7717,7 +7716,7 @@
       </c>
       <c r="F307" s="3"/>
     </row>
-    <row r="308" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B308" s="2">
         <f t="shared" si="4"/>
         <v>304</v>
@@ -7733,7 +7732,7 @@
       </c>
       <c r="F308" s="3"/>
     </row>
-    <row r="309" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B309" s="2">
         <f t="shared" si="4"/>
         <v>305</v>
@@ -7749,7 +7748,7 @@
       </c>
       <c r="F309" s="3"/>
     </row>
-    <row r="310" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B310" s="2">
         <f t="shared" si="4"/>
         <v>306</v>
@@ -7765,7 +7764,7 @@
       </c>
       <c r="F310" s="3"/>
     </row>
-    <row r="311" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B311" s="2">
         <f t="shared" si="4"/>
         <v>307</v>
@@ -7781,7 +7780,7 @@
       </c>
       <c r="F311" s="3"/>
     </row>
-    <row r="312" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B312" s="2">
         <f t="shared" si="4"/>
         <v>308</v>
@@ -7797,7 +7796,7 @@
       </c>
       <c r="F312" s="3"/>
     </row>
-    <row r="313" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B313" s="2">
         <f t="shared" si="4"/>
         <v>309</v>
@@ -7813,7 +7812,7 @@
       </c>
       <c r="F313" s="3"/>
     </row>
-    <row r="314" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B314" s="2">
         <f t="shared" si="4"/>
         <v>310</v>
@@ -7829,7 +7828,7 @@
       </c>
       <c r="F314" s="3"/>
     </row>
-    <row r="315" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B315" s="2">
         <f t="shared" si="4"/>
         <v>311</v>
@@ -7845,7 +7844,7 @@
       </c>
       <c r="F315" s="3"/>
     </row>
-    <row r="316" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B316" s="2">
         <f t="shared" si="4"/>
         <v>312</v>
@@ -7861,7 +7860,7 @@
       </c>
       <c r="F316" s="3"/>
     </row>
-    <row r="317" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B317" s="2">
         <f t="shared" si="4"/>
         <v>313</v>
@@ -7877,7 +7876,7 @@
       </c>
       <c r="F317" s="3"/>
     </row>
-    <row r="318" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B318" s="2">
         <f t="shared" si="4"/>
         <v>314</v>
@@ -7893,7 +7892,7 @@
       </c>
       <c r="F318" s="3"/>
     </row>
-    <row r="319" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B319" s="2">
         <f t="shared" si="4"/>
         <v>315</v>
@@ -7909,7 +7908,7 @@
       </c>
       <c r="F319" s="3"/>
     </row>
-    <row r="320" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B320" s="2">
         <f t="shared" si="4"/>
         <v>316</v>
@@ -7925,7 +7924,7 @@
       </c>
       <c r="F320" s="3"/>
     </row>
-    <row r="321" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B321" s="2">
         <f t="shared" si="4"/>
         <v>317</v>
@@ -7941,7 +7940,7 @@
       </c>
       <c r="F321" s="3"/>
     </row>
-    <row r="322" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B322" s="2">
         <f t="shared" si="4"/>
         <v>318</v>
@@ -7957,7 +7956,7 @@
       </c>
       <c r="F322" s="3"/>
     </row>
-    <row r="323" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B323" s="2">
         <f t="shared" si="4"/>
         <v>319</v>
@@ -7973,7 +7972,7 @@
       </c>
       <c r="F323" s="3"/>
     </row>
-    <row r="324" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B324" s="2">
         <f t="shared" si="4"/>
         <v>320</v>
@@ -7989,7 +7988,7 @@
       </c>
       <c r="F324" s="3"/>
     </row>
-    <row r="325" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B325" s="2">
         <f t="shared" si="4"/>
         <v>321</v>
@@ -8005,7 +8004,7 @@
       </c>
       <c r="F325" s="3"/>
     </row>
-    <row r="326" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B326" s="2">
         <f t="shared" si="4"/>
         <v>322</v>
@@ -8021,7 +8020,7 @@
       </c>
       <c r="F326" s="3"/>
     </row>
-    <row r="327" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B327" s="2">
         <f t="shared" si="4"/>
         <v>323</v>
@@ -8037,7 +8036,7 @@
       </c>
       <c r="F327" s="3"/>
     </row>
-    <row r="328" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B328" s="2">
         <f t="shared" si="4"/>
         <v>324</v>
@@ -8053,7 +8052,7 @@
       </c>
       <c r="F328" s="3"/>
     </row>
-    <row r="329" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B329" s="2">
         <f t="shared" si="4"/>
         <v>325</v>
@@ -8069,7 +8068,7 @@
       </c>
       <c r="F329" s="3"/>
     </row>
-    <row r="330" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B330" s="2">
         <f t="shared" ref="B330:B393" si="5">B329+1</f>
         <v>326</v>
@@ -8085,7 +8084,7 @@
       </c>
       <c r="F330" s="3"/>
     </row>
-    <row r="331" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B331" s="2">
         <f t="shared" si="5"/>
         <v>327</v>
@@ -8101,7 +8100,7 @@
       </c>
       <c r="F331" s="3"/>
     </row>
-    <row r="332" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B332" s="2">
         <f t="shared" si="5"/>
         <v>328</v>
@@ -8117,7 +8116,7 @@
       </c>
       <c r="F332" s="3"/>
     </row>
-    <row r="333" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B333" s="2">
         <f t="shared" si="5"/>
         <v>329</v>
@@ -8133,7 +8132,7 @@
       </c>
       <c r="F333" s="3"/>
     </row>
-    <row r="334" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B334" s="2">
         <f t="shared" si="5"/>
         <v>330</v>
@@ -8149,7 +8148,7 @@
       </c>
       <c r="F334" s="3"/>
     </row>
-    <row r="335" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B335" s="2">
         <f t="shared" si="5"/>
         <v>331</v>
@@ -8165,7 +8164,7 @@
       </c>
       <c r="F335" s="3"/>
     </row>
-    <row r="336" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B336" s="2">
         <f t="shared" si="5"/>
         <v>332</v>
@@ -8181,7 +8180,7 @@
       </c>
       <c r="F336" s="3"/>
     </row>
-    <row r="337" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B337" s="2">
         <f t="shared" si="5"/>
         <v>333</v>
@@ -8197,7 +8196,7 @@
       </c>
       <c r="F337" s="3"/>
     </row>
-    <row r="338" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B338" s="2">
         <f t="shared" si="5"/>
         <v>334</v>
@@ -8213,7 +8212,7 @@
       </c>
       <c r="F338" s="3"/>
     </row>
-    <row r="339" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B339" s="2">
         <f t="shared" si="5"/>
         <v>335</v>
@@ -8229,7 +8228,7 @@
       </c>
       <c r="F339" s="3"/>
     </row>
-    <row r="340" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B340" s="2">
         <f t="shared" si="5"/>
         <v>336</v>
@@ -8245,7 +8244,7 @@
       </c>
       <c r="F340" s="3"/>
     </row>
-    <row r="341" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B341" s="2">
         <f t="shared" si="5"/>
         <v>337</v>
@@ -8261,7 +8260,7 @@
       </c>
       <c r="F341" s="3"/>
     </row>
-    <row r="342" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B342" s="2">
         <f t="shared" si="5"/>
         <v>338</v>
@@ -8277,7 +8276,7 @@
       </c>
       <c r="F342" s="3"/>
     </row>
-    <row r="343" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B343" s="2">
         <f t="shared" si="5"/>
         <v>339</v>
@@ -8293,7 +8292,7 @@
       </c>
       <c r="F343" s="3"/>
     </row>
-    <row r="344" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B344" s="2">
         <f t="shared" si="5"/>
         <v>340</v>
@@ -8309,7 +8308,7 @@
       </c>
       <c r="F344" s="3"/>
     </row>
-    <row r="345" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B345" s="2">
         <f t="shared" si="5"/>
         <v>341</v>
@@ -8325,7 +8324,7 @@
       </c>
       <c r="F345" s="3"/>
     </row>
-    <row r="346" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B346" s="2">
         <f t="shared" si="5"/>
         <v>342</v>
@@ -8341,7 +8340,7 @@
       </c>
       <c r="F346" s="3"/>
     </row>
-    <row r="347" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B347" s="2">
         <f t="shared" si="5"/>
         <v>343</v>
@@ -8357,7 +8356,7 @@
       </c>
       <c r="F347" s="3"/>
     </row>
-    <row r="348" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B348" s="2">
         <f t="shared" si="5"/>
         <v>344</v>
@@ -8373,7 +8372,7 @@
       </c>
       <c r="F348" s="3"/>
     </row>
-    <row r="349" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B349" s="2">
         <f t="shared" si="5"/>
         <v>345</v>
@@ -8389,7 +8388,7 @@
       </c>
       <c r="F349" s="3"/>
     </row>
-    <row r="350" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B350" s="2">
         <f t="shared" si="5"/>
         <v>346</v>
@@ -8405,7 +8404,7 @@
       </c>
       <c r="F350" s="3"/>
     </row>
-    <row r="351" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B351" s="2">
         <f t="shared" si="5"/>
         <v>347</v>
@@ -8421,7 +8420,7 @@
       </c>
       <c r="F351" s="3"/>
     </row>
-    <row r="352" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B352" s="2">
         <f t="shared" si="5"/>
         <v>348</v>
@@ -8437,7 +8436,7 @@
       </c>
       <c r="F352" s="3"/>
     </row>
-    <row r="353" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B353" s="2">
         <f t="shared" si="5"/>
         <v>349</v>
@@ -8453,7 +8452,7 @@
       </c>
       <c r="F353" s="3"/>
     </row>
-    <row r="354" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B354" s="2">
         <f t="shared" si="5"/>
         <v>350</v>
@@ -8469,7 +8468,7 @@
       </c>
       <c r="F354" s="3"/>
     </row>
-    <row r="355" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B355" s="2">
         <f t="shared" si="5"/>
         <v>351</v>
@@ -8485,7 +8484,7 @@
       </c>
       <c r="F355" s="3"/>
     </row>
-    <row r="356" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B356" s="2">
         <f t="shared" si="5"/>
         <v>352</v>
@@ -8501,7 +8500,7 @@
       </c>
       <c r="F356" s="3"/>
     </row>
-    <row r="357" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B357" s="2">
         <f t="shared" si="5"/>
         <v>353</v>
@@ -8517,7 +8516,7 @@
       </c>
       <c r="F357" s="3"/>
     </row>
-    <row r="358" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B358" s="2">
         <f t="shared" si="5"/>
         <v>354</v>
@@ -8533,7 +8532,7 @@
       </c>
       <c r="F358" s="3"/>
     </row>
-    <row r="359" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B359" s="2">
         <f t="shared" si="5"/>
         <v>355</v>
@@ -8549,7 +8548,7 @@
       </c>
       <c r="F359" s="3"/>
     </row>
-    <row r="360" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B360" s="2">
         <f t="shared" si="5"/>
         <v>356</v>
@@ -8565,7 +8564,7 @@
       </c>
       <c r="F360" s="3"/>
     </row>
-    <row r="361" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B361" s="2">
         <f t="shared" si="5"/>
         <v>357</v>
@@ -8581,7 +8580,7 @@
       </c>
       <c r="F361" s="3"/>
     </row>
-    <row r="362" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B362" s="2">
         <f t="shared" si="5"/>
         <v>358</v>
@@ -8597,7 +8596,7 @@
       </c>
       <c r="F362" s="3"/>
     </row>
-    <row r="363" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B363" s="2">
         <f t="shared" si="5"/>
         <v>359</v>
@@ -8613,7 +8612,7 @@
       </c>
       <c r="F363" s="3"/>
     </row>
-    <row r="364" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B364" s="2">
         <f t="shared" si="5"/>
         <v>360</v>
@@ -8629,7 +8628,7 @@
       </c>
       <c r="F364" s="3"/>
     </row>
-    <row r="365" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B365" s="2">
         <f t="shared" si="5"/>
         <v>361</v>
@@ -8645,7 +8644,7 @@
       </c>
       <c r="F365" s="3"/>
     </row>
-    <row r="366" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B366" s="2">
         <f t="shared" si="5"/>
         <v>362</v>
@@ -8661,7 +8660,7 @@
       </c>
       <c r="F366" s="3"/>
     </row>
-    <row r="367" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B367" s="2">
         <f t="shared" si="5"/>
         <v>363</v>
@@ -8677,7 +8676,7 @@
       </c>
       <c r="F367" s="3"/>
     </row>
-    <row r="368" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B368" s="2">
         <f t="shared" si="5"/>
         <v>364</v>
@@ -8693,7 +8692,7 @@
       </c>
       <c r="F368" s="3"/>
     </row>
-    <row r="369" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B369" s="2">
         <f t="shared" si="5"/>
         <v>365</v>
@@ -8709,7 +8708,7 @@
       </c>
       <c r="F369" s="3"/>
     </row>
-    <row r="370" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B370" s="2">
         <f t="shared" si="5"/>
         <v>366</v>
@@ -8725,7 +8724,7 @@
       </c>
       <c r="F370" s="3"/>
     </row>
-    <row r="371" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B371" s="2">
         <f t="shared" si="5"/>
         <v>367</v>
@@ -8741,7 +8740,7 @@
       </c>
       <c r="F371" s="3"/>
     </row>
-    <row r="372" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B372" s="2">
         <f t="shared" si="5"/>
         <v>368</v>
@@ -8757,7 +8756,7 @@
       </c>
       <c r="F372" s="3"/>
     </row>
-    <row r="373" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B373" s="2">
         <f t="shared" si="5"/>
         <v>369</v>
@@ -8773,7 +8772,7 @@
       </c>
       <c r="F373" s="3"/>
     </row>
-    <row r="374" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B374" s="2">
         <f t="shared" si="5"/>
         <v>370</v>
@@ -8789,7 +8788,7 @@
       </c>
       <c r="F374" s="3"/>
     </row>
-    <row r="375" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B375" s="2">
         <f t="shared" si="5"/>
         <v>371</v>
@@ -8805,7 +8804,7 @@
       </c>
       <c r="F375" s="3"/>
     </row>
-    <row r="376" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B376" s="2">
         <f t="shared" si="5"/>
         <v>372</v>
@@ -8821,7 +8820,7 @@
       </c>
       <c r="F376" s="3"/>
     </row>
-    <row r="377" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B377" s="2">
         <f t="shared" si="5"/>
         <v>373</v>
@@ -8837,7 +8836,7 @@
       </c>
       <c r="F377" s="3"/>
     </row>
-    <row r="378" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B378" s="2">
         <f t="shared" si="5"/>
         <v>374</v>
@@ -8853,7 +8852,7 @@
       </c>
       <c r="F378" s="3"/>
     </row>
-    <row r="379" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B379" s="2">
         <f t="shared" si="5"/>
         <v>375</v>
@@ -8869,7 +8868,7 @@
       </c>
       <c r="F379" s="3"/>
     </row>
-    <row r="380" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B380" s="2">
         <f t="shared" si="5"/>
         <v>376</v>
@@ -8885,7 +8884,7 @@
       </c>
       <c r="F380" s="3"/>
     </row>
-    <row r="381" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B381" s="2">
         <f t="shared" si="5"/>
         <v>377</v>
@@ -8901,7 +8900,7 @@
       </c>
       <c r="F381" s="3"/>
     </row>
-    <row r="382" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B382" s="2">
         <f t="shared" si="5"/>
         <v>378</v>
@@ -8917,7 +8916,7 @@
       </c>
       <c r="F382" s="3"/>
     </row>
-    <row r="383" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B383" s="2">
         <f t="shared" si="5"/>
         <v>379</v>
@@ -8933,7 +8932,7 @@
       </c>
       <c r="F383" s="3"/>
     </row>
-    <row r="384" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B384" s="2">
         <f t="shared" si="5"/>
         <v>380</v>
@@ -8949,7 +8948,7 @@
       </c>
       <c r="F384" s="3"/>
     </row>
-    <row r="385" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B385" s="2">
         <f t="shared" si="5"/>
         <v>381</v>
@@ -8965,7 +8964,7 @@
       </c>
       <c r="F385" s="3"/>
     </row>
-    <row r="386" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B386" s="2">
         <f t="shared" si="5"/>
         <v>382</v>
@@ -8981,7 +8980,7 @@
       </c>
       <c r="F386" s="3"/>
     </row>
-    <row r="387" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B387" s="2">
         <f t="shared" si="5"/>
         <v>383</v>
@@ -8997,7 +8996,7 @@
       </c>
       <c r="F387" s="3"/>
     </row>
-    <row r="388" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B388" s="2">
         <f t="shared" si="5"/>
         <v>384</v>
@@ -9013,7 +9012,7 @@
       </c>
       <c r="F388" s="3"/>
     </row>
-    <row r="389" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B389" s="2">
         <f t="shared" si="5"/>
         <v>385</v>
@@ -9029,7 +9028,7 @@
       </c>
       <c r="F389" s="3"/>
     </row>
-    <row r="390" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B390" s="2">
         <f t="shared" si="5"/>
         <v>386</v>
@@ -9045,7 +9044,7 @@
       </c>
       <c r="F390" s="3"/>
     </row>
-    <row r="391" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B391" s="2">
         <f t="shared" si="5"/>
         <v>387</v>
@@ -9061,7 +9060,7 @@
       </c>
       <c r="F391" s="3"/>
     </row>
-    <row r="392" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B392" s="2">
         <f t="shared" si="5"/>
         <v>388</v>
@@ -9077,7 +9076,7 @@
       </c>
       <c r="F392" s="3"/>
     </row>
-    <row r="393" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B393" s="2">
         <f t="shared" si="5"/>
         <v>389</v>
@@ -9093,7 +9092,7 @@
       </c>
       <c r="F393" s="3"/>
     </row>
-    <row r="394" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B394" s="2">
         <f t="shared" ref="B394:B457" si="6">B393+1</f>
         <v>390</v>
@@ -9109,7 +9108,7 @@
       </c>
       <c r="F394" s="3"/>
     </row>
-    <row r="395" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B395" s="2">
         <f t="shared" si="6"/>
         <v>391</v>
@@ -9125,7 +9124,7 @@
       </c>
       <c r="F395" s="3"/>
     </row>
-    <row r="396" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B396" s="2">
         <f t="shared" si="6"/>
         <v>392</v>
@@ -9141,7 +9140,7 @@
       </c>
       <c r="F396" s="3"/>
     </row>
-    <row r="397" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B397" s="2">
         <f t="shared" si="6"/>
         <v>393</v>
@@ -9157,7 +9156,7 @@
       </c>
       <c r="F397" s="3"/>
     </row>
-    <row r="398" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B398" s="2">
         <f t="shared" si="6"/>
         <v>394</v>
@@ -9173,7 +9172,7 @@
       </c>
       <c r="F398" s="3"/>
     </row>
-    <row r="399" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B399" s="2">
         <f t="shared" si="6"/>
         <v>395</v>
@@ -9189,7 +9188,7 @@
       </c>
       <c r="F399" s="3"/>
     </row>
-    <row r="400" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B400" s="2">
         <f t="shared" si="6"/>
         <v>396</v>
@@ -9221,7 +9220,7 @@
       </c>
       <c r="F401" s="3"/>
     </row>
-    <row r="402" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B402" s="2">
         <f t="shared" si="6"/>
         <v>398</v>
@@ -9237,7 +9236,7 @@
       </c>
       <c r="F402" s="3"/>
     </row>
-    <row r="403" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B403" s="2">
         <f t="shared" si="6"/>
         <v>399</v>
@@ -9253,7 +9252,7 @@
       </c>
       <c r="F403" s="3"/>
     </row>
-    <row r="404" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B404" s="2">
         <f t="shared" si="6"/>
         <v>400</v>
@@ -9269,7 +9268,7 @@
       </c>
       <c r="F404" s="3"/>
     </row>
-    <row r="405" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B405" s="2">
         <f t="shared" si="6"/>
         <v>401</v>
@@ -9285,7 +9284,7 @@
       </c>
       <c r="F405" s="3"/>
     </row>
-    <row r="406" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B406" s="2">
         <f t="shared" si="6"/>
         <v>402</v>
@@ -9301,7 +9300,7 @@
       </c>
       <c r="F406" s="3"/>
     </row>
-    <row r="407" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B407" s="2">
         <f t="shared" si="6"/>
         <v>403</v>
@@ -9317,7 +9316,7 @@
       </c>
       <c r="F407" s="3"/>
     </row>
-    <row r="408" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B408" s="2">
         <f t="shared" si="6"/>
         <v>404</v>
@@ -9333,7 +9332,7 @@
       </c>
       <c r="F408" s="3"/>
     </row>
-    <row r="409" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B409" s="2">
         <f t="shared" si="6"/>
         <v>405</v>
@@ -9381,7 +9380,7 @@
       </c>
       <c r="F411" s="3"/>
     </row>
-    <row r="412" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B412" s="2">
         <f t="shared" si="6"/>
         <v>408</v>
@@ -9397,7 +9396,7 @@
       </c>
       <c r="F412" s="3"/>
     </row>
-    <row r="413" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B413" s="2">
         <f t="shared" si="6"/>
         <v>409</v>
@@ -9413,7 +9412,7 @@
       </c>
       <c r="F413" s="3"/>
     </row>
-    <row r="414" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B414" s="2">
         <f t="shared" si="6"/>
         <v>410</v>
@@ -9429,7 +9428,7 @@
       </c>
       <c r="F414" s="3"/>
     </row>
-    <row r="415" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B415" s="2">
         <f t="shared" si="6"/>
         <v>411</v>
@@ -9445,7 +9444,7 @@
       </c>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B416" s="2">
         <f t="shared" si="6"/>
         <v>412</v>
@@ -9461,7 +9460,7 @@
       </c>
       <c r="F416" s="3"/>
     </row>
-    <row r="417" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B417" s="2">
         <f t="shared" si="6"/>
         <v>413</v>
@@ -9477,7 +9476,7 @@
       </c>
       <c r="F417" s="3"/>
     </row>
-    <row r="418" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B418" s="2">
         <f t="shared" si="6"/>
         <v>414</v>
@@ -9493,7 +9492,7 @@
       </c>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B419" s="2">
         <f t="shared" si="6"/>
         <v>415</v>
@@ -9509,7 +9508,7 @@
       </c>
       <c r="F419" s="3"/>
     </row>
-    <row r="420" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B420" s="2">
         <f t="shared" si="6"/>
         <v>416</v>
@@ -9525,7 +9524,7 @@
       </c>
       <c r="F420" s="3"/>
     </row>
-    <row r="421" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B421" s="2">
         <f t="shared" si="6"/>
         <v>417</v>
@@ -9541,7 +9540,7 @@
       </c>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B422" s="2">
         <f t="shared" si="6"/>
         <v>418</v>
@@ -9557,7 +9556,7 @@
       </c>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B423" s="2">
         <f t="shared" si="6"/>
         <v>419</v>
@@ -9573,7 +9572,7 @@
       </c>
       <c r="F423" s="3"/>
     </row>
-    <row r="424" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B424" s="2">
         <f t="shared" si="6"/>
         <v>420</v>
@@ -9589,7 +9588,7 @@
       </c>
       <c r="F424" s="3"/>
     </row>
-    <row r="425" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B425" s="2">
         <f t="shared" si="6"/>
         <v>421</v>
@@ -9605,7 +9604,7 @@
       </c>
       <c r="F425" s="3"/>
     </row>
-    <row r="426" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B426" s="2">
         <f t="shared" si="6"/>
         <v>422</v>
@@ -9621,7 +9620,7 @@
       </c>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
@@ -9637,7 +9636,7 @@
       </c>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B428" s="2">
         <f t="shared" si="6"/>
         <v>424</v>
@@ -9653,7 +9652,7 @@
       </c>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B429" s="2">
         <f t="shared" si="6"/>
         <v>425</v>
@@ -9669,7 +9668,7 @@
       </c>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B430" s="2">
         <f t="shared" si="6"/>
         <v>426</v>
@@ -9685,7 +9684,7 @@
       </c>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B431" s="2">
         <f t="shared" si="6"/>
         <v>427</v>
@@ -9701,7 +9700,7 @@
       </c>
       <c r="F431" s="3"/>
     </row>
-    <row r="432" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B432" s="2">
         <f t="shared" si="6"/>
         <v>428</v>
@@ -9717,7 +9716,7 @@
       </c>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B433" s="2">
         <f t="shared" si="6"/>
         <v>429</v>
@@ -9733,7 +9732,7 @@
       </c>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B434" s="2">
         <f t="shared" si="6"/>
         <v>430</v>
@@ -9749,7 +9748,7 @@
       </c>
       <c r="F434" s="3"/>
     </row>
-    <row r="435" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B435" s="2">
         <f t="shared" si="6"/>
         <v>431</v>
@@ -9765,7 +9764,7 @@
       </c>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B436" s="2">
         <f t="shared" si="6"/>
         <v>432</v>
@@ -9781,7 +9780,7 @@
       </c>
       <c r="F436" s="3"/>
     </row>
-    <row r="437" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B437" s="2">
         <f t="shared" si="6"/>
         <v>433</v>
@@ -9797,7 +9796,7 @@
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B438" s="2">
         <f t="shared" si="6"/>
         <v>434</v>
@@ -9813,7 +9812,7 @@
       </c>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B439" s="2">
         <f t="shared" si="6"/>
         <v>435</v>
@@ -9829,7 +9828,7 @@
       </c>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B440" s="2">
         <f t="shared" si="6"/>
         <v>436</v>
@@ -9845,7 +9844,7 @@
       </c>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B441" s="2">
         <f t="shared" si="6"/>
         <v>437</v>
@@ -9877,7 +9876,7 @@
       </c>
       <c r="F442" s="3"/>
     </row>
-    <row r="443" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B443" s="2">
         <f t="shared" si="6"/>
         <v>439</v>
@@ -9893,7 +9892,7 @@
       </c>
       <c r="F443" s="3"/>
     </row>
-    <row r="444" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B444" s="2">
         <f t="shared" si="6"/>
         <v>440</v>
@@ -9909,7 +9908,7 @@
       </c>
       <c r="F444" s="3"/>
     </row>
-    <row r="445" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B445" s="2">
         <f t="shared" si="6"/>
         <v>441</v>
@@ -9925,7 +9924,7 @@
       </c>
       <c r="F445" s="3"/>
     </row>
-    <row r="446" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B446" s="2">
         <f t="shared" si="6"/>
         <v>442</v>
@@ -9941,7 +9940,7 @@
       </c>
       <c r="F446" s="3"/>
     </row>
-    <row r="447" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B447" s="2">
         <f t="shared" si="6"/>
         <v>443</v>
@@ -9957,7 +9956,7 @@
       </c>
       <c r="F447" s="3"/>
     </row>
-    <row r="448" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B448" s="2">
         <f t="shared" si="6"/>
         <v>444</v>
@@ -9973,7 +9972,7 @@
       </c>
       <c r="F448" s="3"/>
     </row>
-    <row r="449" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B449" s="2">
         <f t="shared" si="6"/>
         <v>445</v>
@@ -9989,7 +9988,7 @@
       </c>
       <c r="F449" s="3"/>
     </row>
-    <row r="450" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B450" s="2">
         <f t="shared" si="6"/>
         <v>446</v>
@@ -10005,7 +10004,7 @@
       </c>
       <c r="F450" s="3"/>
     </row>
-    <row r="451" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B451" s="2">
         <f t="shared" si="6"/>
         <v>447</v>
@@ -10021,7 +10020,7 @@
       </c>
       <c r="F451" s="3"/>
     </row>
-    <row r="452" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B452" s="2">
         <f t="shared" si="6"/>
         <v>448</v>
@@ -10037,7 +10036,7 @@
       </c>
       <c r="F452" s="3"/>
     </row>
-    <row r="453" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B453" s="2">
         <f t="shared" si="6"/>
         <v>449</v>
@@ -10053,7 +10052,7 @@
       </c>
       <c r="F453" s="3"/>
     </row>
-    <row r="454" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B454" s="2">
         <f t="shared" si="6"/>
         <v>450</v>
@@ -10069,7 +10068,7 @@
       </c>
       <c r="F454" s="3"/>
     </row>
-    <row r="455" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B455" s="2">
         <f t="shared" si="6"/>
         <v>451</v>
@@ -10085,7 +10084,7 @@
       </c>
       <c r="F455" s="3"/>
     </row>
-    <row r="456" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B456" s="2">
         <f t="shared" si="6"/>
         <v>452</v>
@@ -10101,7 +10100,7 @@
       </c>
       <c r="F456" s="3"/>
     </row>
-    <row r="457" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B457" s="2">
         <f t="shared" si="6"/>
         <v>453</v>
@@ -10117,7 +10116,7 @@
       </c>
       <c r="F457" s="3"/>
     </row>
-    <row r="458" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B458" s="2">
         <f t="shared" ref="B458:B521" si="7">B457+1</f>
         <v>454</v>
@@ -10133,7 +10132,7 @@
       </c>
       <c r="F458" s="3"/>
     </row>
-    <row r="459" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B459" s="2">
         <f t="shared" si="7"/>
         <v>455</v>
@@ -10149,7 +10148,7 @@
       </c>
       <c r="F459" s="3"/>
     </row>
-    <row r="460" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B460" s="2">
         <f t="shared" si="7"/>
         <v>456</v>
@@ -10165,7 +10164,7 @@
       </c>
       <c r="F460" s="3"/>
     </row>
-    <row r="461" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B461" s="2">
         <f t="shared" si="7"/>
         <v>457</v>
@@ -10181,7 +10180,7 @@
       </c>
       <c r="F461" s="3"/>
     </row>
-    <row r="462" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B462" s="2">
         <f t="shared" si="7"/>
         <v>458</v>
@@ -10197,7 +10196,7 @@
       </c>
       <c r="F462" s="3"/>
     </row>
-    <row r="463" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B463" s="2">
         <f t="shared" si="7"/>
         <v>459</v>
@@ -10213,7 +10212,7 @@
       </c>
       <c r="F463" s="3"/>
     </row>
-    <row r="464" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B464" s="2">
         <f t="shared" si="7"/>
         <v>460</v>
@@ -10229,7 +10228,7 @@
       </c>
       <c r="F464" s="3"/>
     </row>
-    <row r="465" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B465" s="2">
         <f t="shared" si="7"/>
         <v>461</v>
@@ -10245,7 +10244,7 @@
       </c>
       <c r="F465" s="3"/>
     </row>
-    <row r="466" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B466" s="2">
         <f t="shared" si="7"/>
         <v>462</v>
@@ -10261,7 +10260,7 @@
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <f t="shared" si="7"/>
         <v>463</v>
@@ -10277,7 +10276,7 @@
       </c>
       <c r="F467" s="3"/>
     </row>
-    <row r="468" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B468" s="2">
         <f t="shared" si="7"/>
         <v>464</v>
@@ -10293,7 +10292,7 @@
       </c>
       <c r="F468" s="3"/>
     </row>
-    <row r="469" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B469" s="2">
         <f t="shared" si="7"/>
         <v>465</v>
@@ -10309,7 +10308,7 @@
       </c>
       <c r="F469" s="3"/>
     </row>
-    <row r="470" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B470" s="2">
         <f t="shared" si="7"/>
         <v>466</v>
@@ -10325,7 +10324,7 @@
       </c>
       <c r="F470" s="3"/>
     </row>
-    <row r="471" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B471" s="2">
         <f t="shared" si="7"/>
         <v>467</v>
@@ -10341,7 +10340,7 @@
       </c>
       <c r="F471" s="3"/>
     </row>
-    <row r="472" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B472" s="2">
         <f t="shared" si="7"/>
         <v>468</v>
@@ -10357,7 +10356,7 @@
       </c>
       <c r="F472" s="3"/>
     </row>
-    <row r="473" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B473" s="2">
         <f t="shared" si="7"/>
         <v>469</v>
@@ -10373,7 +10372,7 @@
       </c>
       <c r="F473" s="3"/>
     </row>
-    <row r="474" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B474" s="2">
         <f t="shared" si="7"/>
         <v>470</v>
@@ -10389,7 +10388,7 @@
       </c>
       <c r="F474" s="3"/>
     </row>
-    <row r="475" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B475" s="2">
         <f t="shared" si="7"/>
         <v>471</v>
@@ -10405,7 +10404,7 @@
       </c>
       <c r="F475" s="3"/>
     </row>
-    <row r="476" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B476" s="2">
         <f t="shared" si="7"/>
         <v>472</v>
@@ -10421,7 +10420,7 @@
       </c>
       <c r="F476" s="3"/>
     </row>
-    <row r="477" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B477" s="2">
         <f t="shared" si="7"/>
         <v>473</v>
@@ -10437,7 +10436,7 @@
       </c>
       <c r="F477" s="3"/>
     </row>
-    <row r="478" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B478" s="2">
         <f t="shared" si="7"/>
         <v>474</v>
@@ -10453,7 +10452,7 @@
       </c>
       <c r="F478" s="3"/>
     </row>
-    <row r="479" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B479" s="2">
         <f t="shared" si="7"/>
         <v>475</v>
@@ -10469,7 +10468,7 @@
       </c>
       <c r="F479" s="3"/>
     </row>
-    <row r="480" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B480" s="2">
         <f t="shared" si="7"/>
         <v>476</v>
@@ -10485,7 +10484,7 @@
       </c>
       <c r="F480" s="3"/>
     </row>
-    <row r="481" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B481" s="2">
         <f t="shared" si="7"/>
         <v>477</v>
@@ -10501,7 +10500,7 @@
       </c>
       <c r="F481" s="3"/>
     </row>
-    <row r="482" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B482" s="2">
         <f t="shared" si="7"/>
         <v>478</v>
@@ -10517,7 +10516,7 @@
       </c>
       <c r="F482" s="3"/>
     </row>
-    <row r="483" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B483" s="2">
         <f t="shared" si="7"/>
         <v>479</v>
@@ -10533,7 +10532,7 @@
       </c>
       <c r="F483" s="3"/>
     </row>
-    <row r="484" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B484" s="2">
         <f t="shared" si="7"/>
         <v>480</v>
@@ -10549,7 +10548,7 @@
       </c>
       <c r="F484" s="3"/>
     </row>
-    <row r="485" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B485" s="2">
         <f t="shared" si="7"/>
         <v>481</v>
@@ -10565,7 +10564,7 @@
       </c>
       <c r="F485" s="3"/>
     </row>
-    <row r="486" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B486" s="2">
         <f t="shared" si="7"/>
         <v>482</v>
@@ -10581,7 +10580,7 @@
       </c>
       <c r="F486" s="3"/>
     </row>
-    <row r="487" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B487" s="2">
         <f t="shared" si="7"/>
         <v>483</v>
@@ -10597,7 +10596,7 @@
       </c>
       <c r="F487" s="3"/>
     </row>
-    <row r="488" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B488" s="2">
         <f t="shared" si="7"/>
         <v>484</v>
@@ -10613,7 +10612,7 @@
       </c>
       <c r="F488" s="3"/>
     </row>
-    <row r="489" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B489" s="2">
         <f t="shared" si="7"/>
         <v>485</v>
@@ -10629,7 +10628,7 @@
       </c>
       <c r="F489" s="3"/>
     </row>
-    <row r="490" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B490" s="2">
         <f t="shared" si="7"/>
         <v>486</v>
@@ -10645,7 +10644,7 @@
       </c>
       <c r="F490" s="3"/>
     </row>
-    <row r="491" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B491" s="2">
         <f t="shared" si="7"/>
         <v>487</v>
@@ -10661,7 +10660,7 @@
       </c>
       <c r="F491" s="3"/>
     </row>
-    <row r="492" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B492" s="2">
         <f t="shared" si="7"/>
         <v>488</v>
@@ -10677,7 +10676,7 @@
       </c>
       <c r="F492" s="3"/>
     </row>
-    <row r="493" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B493" s="2">
         <f t="shared" si="7"/>
         <v>489</v>
@@ -10693,7 +10692,7 @@
       </c>
       <c r="F493" s="3"/>
     </row>
-    <row r="494" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B494" s="2">
         <f t="shared" si="7"/>
         <v>490</v>
@@ -10709,7 +10708,7 @@
       </c>
       <c r="F494" s="3"/>
     </row>
-    <row r="495" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B495" s="2">
         <f t="shared" si="7"/>
         <v>491</v>
@@ -10725,7 +10724,7 @@
       </c>
       <c r="F495" s="3"/>
     </row>
-    <row r="496" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B496" s="2">
         <f t="shared" si="7"/>
         <v>492</v>
@@ -10741,7 +10740,7 @@
       </c>
       <c r="F496" s="3"/>
     </row>
-    <row r="497" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B497" s="2">
         <f t="shared" si="7"/>
         <v>493</v>
@@ -10757,7 +10756,7 @@
       </c>
       <c r="F497" s="3"/>
     </row>
-    <row r="498" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B498" s="2">
         <f t="shared" si="7"/>
         <v>494</v>
@@ -10773,7 +10772,7 @@
       </c>
       <c r="F498" s="3"/>
     </row>
-    <row r="499" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B499" s="2">
         <f t="shared" si="7"/>
         <v>495</v>
@@ -10805,7 +10804,7 @@
       </c>
       <c r="F500" s="3"/>
     </row>
-    <row r="501" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B501" s="2">
         <f t="shared" si="7"/>
         <v>497</v>
@@ -10821,7 +10820,7 @@
       </c>
       <c r="F501" s="3"/>
     </row>
-    <row r="502" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B502" s="2">
         <f t="shared" si="7"/>
         <v>498</v>
@@ -10837,7 +10836,7 @@
       </c>
       <c r="F502" s="3"/>
     </row>
-    <row r="503" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B503" s="2">
         <f t="shared" si="7"/>
         <v>499</v>
@@ -10853,7 +10852,7 @@
       </c>
       <c r="F503" s="3"/>
     </row>
-    <row r="504" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B504" s="2">
         <f t="shared" si="7"/>
         <v>500</v>
@@ -10869,7 +10868,7 @@
       </c>
       <c r="F504" s="3"/>
     </row>
-    <row r="505" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B505" s="2">
         <f t="shared" si="7"/>
         <v>501</v>
@@ -10885,7 +10884,7 @@
       </c>
       <c r="F505" s="3"/>
     </row>
-    <row r="506" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B506" s="2">
         <f t="shared" si="7"/>
         <v>502</v>
@@ -10901,7 +10900,7 @@
       </c>
       <c r="F506" s="3"/>
     </row>
-    <row r="507" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B507" s="2">
         <f t="shared" si="7"/>
         <v>503</v>
@@ -10917,7 +10916,7 @@
       </c>
       <c r="F507" s="3"/>
     </row>
-    <row r="508" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B508" s="2">
         <f t="shared" si="7"/>
         <v>504</v>
@@ -10933,7 +10932,7 @@
       </c>
       <c r="F508" s="3"/>
     </row>
-    <row r="509" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B509" s="2">
         <f t="shared" si="7"/>
         <v>505</v>
@@ -10949,7 +10948,7 @@
       </c>
       <c r="F509" s="3"/>
     </row>
-    <row r="510" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B510" s="2">
         <f t="shared" si="7"/>
         <v>506</v>
@@ -10965,7 +10964,7 @@
       </c>
       <c r="F510" s="3"/>
     </row>
-    <row r="511" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B511" s="2">
         <f t="shared" si="7"/>
         <v>507</v>
@@ -10981,7 +10980,7 @@
       </c>
       <c r="F511" s="3"/>
     </row>
-    <row r="512" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B512" s="2">
         <f t="shared" si="7"/>
         <v>508</v>
@@ -10997,7 +10996,7 @@
       </c>
       <c r="F512" s="3"/>
     </row>
-    <row r="513" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B513" s="2">
         <f t="shared" si="7"/>
         <v>509</v>
@@ -11013,7 +11012,7 @@
       </c>
       <c r="F513" s="3"/>
     </row>
-    <row r="514" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B514" s="2">
         <f t="shared" si="7"/>
         <v>510</v>
@@ -11029,7 +11028,7 @@
       </c>
       <c r="F514" s="3"/>
     </row>
-    <row r="515" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B515" s="2">
         <f t="shared" si="7"/>
         <v>511</v>
@@ -11045,7 +11044,7 @@
       </c>
       <c r="F515" s="3"/>
     </row>
-    <row r="516" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B516" s="2">
         <f t="shared" si="7"/>
         <v>512</v>
@@ -11061,7 +11060,7 @@
       </c>
       <c r="F516" s="3"/>
     </row>
-    <row r="517" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B517" s="2">
         <f t="shared" si="7"/>
         <v>513</v>
@@ -11077,7 +11076,7 @@
       </c>
       <c r="F517" s="3"/>
     </row>
-    <row r="518" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B518" s="2">
         <f t="shared" si="7"/>
         <v>514</v>
@@ -11093,7 +11092,7 @@
       </c>
       <c r="F518" s="3"/>
     </row>
-    <row r="519" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B519" s="2">
         <f t="shared" si="7"/>
         <v>515</v>
@@ -11109,7 +11108,7 @@
       </c>
       <c r="F519" s="3"/>
     </row>
-    <row r="520" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B520" s="2">
         <f t="shared" si="7"/>
         <v>516</v>
@@ -11125,7 +11124,7 @@
       </c>
       <c r="F520" s="3"/>
     </row>
-    <row r="521" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B521" s="2">
         <f t="shared" si="7"/>
         <v>517</v>
@@ -11141,7 +11140,7 @@
       </c>
       <c r="F521" s="3"/>
     </row>
-    <row r="522" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B522" s="2">
         <f t="shared" ref="B522:B585" si="8">B521+1</f>
         <v>518</v>
@@ -11157,7 +11156,7 @@
       </c>
       <c r="F522" s="3"/>
     </row>
-    <row r="523" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B523" s="2">
         <f t="shared" si="8"/>
         <v>519</v>
@@ -11173,7 +11172,7 @@
       </c>
       <c r="F523" s="3"/>
     </row>
-    <row r="524" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B524" s="2">
         <f t="shared" si="8"/>
         <v>520</v>
@@ -11189,7 +11188,7 @@
       </c>
       <c r="F524" s="3"/>
     </row>
-    <row r="525" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B525" s="2">
         <f t="shared" si="8"/>
         <v>521</v>
@@ -11205,7 +11204,7 @@
       </c>
       <c r="F525" s="3"/>
     </row>
-    <row r="526" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B526" s="2">
         <f t="shared" si="8"/>
         <v>522</v>
@@ -11221,7 +11220,7 @@
       </c>
       <c r="F526" s="3"/>
     </row>
-    <row r="527" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B527" s="2">
         <f t="shared" si="8"/>
         <v>523</v>
@@ -11253,7 +11252,7 @@
       </c>
       <c r="F528" s="3"/>
     </row>
-    <row r="529" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B529" s="2">
         <f t="shared" si="8"/>
         <v>525</v>
@@ -11269,7 +11268,7 @@
       </c>
       <c r="F529" s="3"/>
     </row>
-    <row r="530" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B530" s="2">
         <f t="shared" si="8"/>
         <v>526</v>
@@ -11285,7 +11284,7 @@
       </c>
       <c r="F530" s="3"/>
     </row>
-    <row r="531" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B531" s="2">
         <f t="shared" si="8"/>
         <v>527</v>
@@ -11301,7 +11300,7 @@
       </c>
       <c r="F531" s="3"/>
     </row>
-    <row r="532" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B532" s="2">
         <f t="shared" si="8"/>
         <v>528</v>
@@ -11317,7 +11316,7 @@
       </c>
       <c r="F532" s="3"/>
     </row>
-    <row r="533" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B533" s="2">
         <f t="shared" si="8"/>
         <v>529</v>
@@ -11333,7 +11332,7 @@
       </c>
       <c r="F533" s="3"/>
     </row>
-    <row r="534" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B534" s="2">
         <f t="shared" si="8"/>
         <v>530</v>
@@ -11349,7 +11348,7 @@
       </c>
       <c r="F534" s="3"/>
     </row>
-    <row r="535" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B535" s="2">
         <f t="shared" si="8"/>
         <v>531</v>
@@ -11365,7 +11364,7 @@
       </c>
       <c r="F535" s="3"/>
     </row>
-    <row r="536" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B536" s="2">
         <f t="shared" si="8"/>
         <v>532</v>
@@ -11381,7 +11380,7 @@
       </c>
       <c r="F536" s="3"/>
     </row>
-    <row r="537" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B537" s="2">
         <f t="shared" si="8"/>
         <v>533</v>
@@ -11397,7 +11396,7 @@
       </c>
       <c r="F537" s="3"/>
     </row>
-    <row r="538" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B538" s="2">
         <f t="shared" si="8"/>
         <v>534</v>
@@ -11413,7 +11412,7 @@
       </c>
       <c r="F538" s="3"/>
     </row>
-    <row r="539" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B539" s="2">
         <f t="shared" si="8"/>
         <v>535</v>
@@ -11429,7 +11428,7 @@
       </c>
       <c r="F539" s="3"/>
     </row>
-    <row r="540" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B540" s="2">
         <f t="shared" si="8"/>
         <v>536</v>
@@ -11445,7 +11444,7 @@
       </c>
       <c r="F540" s="3"/>
     </row>
-    <row r="541" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B541" s="2">
         <f t="shared" si="8"/>
         <v>537</v>
@@ -11461,7 +11460,7 @@
       </c>
       <c r="F541" s="3"/>
     </row>
-    <row r="542" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B542" s="2">
         <f t="shared" si="8"/>
         <v>538</v>
@@ -11477,7 +11476,7 @@
       </c>
       <c r="F542" s="3"/>
     </row>
-    <row r="543" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B543" s="2">
         <f t="shared" si="8"/>
         <v>539</v>
@@ -11493,7 +11492,7 @@
       </c>
       <c r="F543" s="3"/>
     </row>
-    <row r="544" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B544" s="2">
         <f t="shared" si="8"/>
         <v>540</v>
@@ -11509,7 +11508,7 @@
       </c>
       <c r="F544" s="3"/>
     </row>
-    <row r="545" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B545" s="2">
         <f t="shared" si="8"/>
         <v>541</v>
@@ -11525,7 +11524,7 @@
       </c>
       <c r="F545" s="3"/>
     </row>
-    <row r="546" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B546" s="2">
         <f t="shared" si="8"/>
         <v>542</v>
@@ -11541,7 +11540,7 @@
       </c>
       <c r="F546" s="3"/>
     </row>
-    <row r="547" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B547" s="2">
         <f t="shared" si="8"/>
         <v>543</v>
@@ -11557,7 +11556,7 @@
       </c>
       <c r="F547" s="3"/>
     </row>
-    <row r="548" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B548" s="2">
         <f t="shared" si="8"/>
         <v>544</v>
@@ -11573,7 +11572,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -11589,7 +11588,7 @@
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -11605,7 +11604,7 @@
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <f t="shared" si="8"/>
         <v>547</v>
@@ -11621,7 +11620,7 @@
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <f t="shared" si="8"/>
         <v>548</v>
@@ -11637,7 +11636,7 @@
       </c>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <f t="shared" si="8"/>
         <v>549</v>
@@ -11653,7 +11652,7 @@
       </c>
       <c r="F553" s="3"/>
     </row>
-    <row r="554" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B554" s="2">
         <f t="shared" si="8"/>
         <v>550</v>
@@ -11669,7 +11668,7 @@
       </c>
       <c r="F554" s="3"/>
     </row>
-    <row r="555" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B555" s="2">
         <f t="shared" si="8"/>
         <v>551</v>
@@ -11685,7 +11684,7 @@
       </c>
       <c r="F555" s="3"/>
     </row>
-    <row r="556" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B556" s="2">
         <f t="shared" si="8"/>
         <v>552</v>
@@ -11701,7 +11700,7 @@
       </c>
       <c r="F556" s="3"/>
     </row>
-    <row r="557" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B557" s="2">
         <f t="shared" si="8"/>
         <v>553</v>
@@ -11717,7 +11716,7 @@
       </c>
       <c r="F557" s="3"/>
     </row>
-    <row r="558" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B558" s="2">
         <f t="shared" si="8"/>
         <v>554</v>
@@ -11733,7 +11732,7 @@
       </c>
       <c r="F558" s="3"/>
     </row>
-    <row r="559" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B559" s="2">
         <f t="shared" si="8"/>
         <v>555</v>
@@ -11749,7 +11748,7 @@
       </c>
       <c r="F559" s="3"/>
     </row>
-    <row r="560" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B560" s="2">
         <f t="shared" si="8"/>
         <v>556</v>
@@ -11765,7 +11764,7 @@
       </c>
       <c r="F560" s="3"/>
     </row>
-    <row r="561" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B561" s="2">
         <f t="shared" si="8"/>
         <v>557</v>
@@ -11781,7 +11780,7 @@
       </c>
       <c r="F561" s="3"/>
     </row>
-    <row r="562" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B562" s="2">
         <f t="shared" si="8"/>
         <v>558</v>
@@ -11797,7 +11796,7 @@
       </c>
       <c r="F562" s="3"/>
     </row>
-    <row r="563" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B563" s="2">
         <f t="shared" si="8"/>
         <v>559</v>
@@ -11813,7 +11812,7 @@
       </c>
       <c r="F563" s="3"/>
     </row>
-    <row r="564" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B564" s="2">
         <f t="shared" si="8"/>
         <v>560</v>
@@ -11829,7 +11828,7 @@
       </c>
       <c r="F564" s="3"/>
     </row>
-    <row r="565" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B565" s="2">
         <f t="shared" si="8"/>
         <v>561</v>
@@ -11845,7 +11844,7 @@
       </c>
       <c r="F565" s="3"/>
     </row>
-    <row r="566" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B566" s="2">
         <f t="shared" si="8"/>
         <v>562</v>
@@ -11861,7 +11860,7 @@
       </c>
       <c r="F566" s="3"/>
     </row>
-    <row r="567" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B567" s="2">
         <f t="shared" si="8"/>
         <v>563</v>
@@ -11877,7 +11876,7 @@
       </c>
       <c r="F567" s="3"/>
     </row>
-    <row r="568" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B568" s="2">
         <f t="shared" si="8"/>
         <v>564</v>
@@ -11893,7 +11892,7 @@
       </c>
       <c r="F568" s="3"/>
     </row>
-    <row r="569" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B569" s="2">
         <f t="shared" si="8"/>
         <v>565</v>
@@ -11909,7 +11908,7 @@
       </c>
       <c r="F569" s="3"/>
     </row>
-    <row r="570" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B570" s="2">
         <f t="shared" si="8"/>
         <v>566</v>
@@ -11925,7 +11924,7 @@
       </c>
       <c r="F570" s="3"/>
     </row>
-    <row r="571" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B571" s="2">
         <f t="shared" si="8"/>
         <v>567</v>
@@ -11941,7 +11940,7 @@
       </c>
       <c r="F571" s="3"/>
     </row>
-    <row r="572" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B572" s="2">
         <f t="shared" si="8"/>
         <v>568</v>
@@ -11957,7 +11956,7 @@
       </c>
       <c r="F572" s="3"/>
     </row>
-    <row r="573" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B573" s="2">
         <f t="shared" si="8"/>
         <v>569</v>
@@ -11973,7 +11972,7 @@
       </c>
       <c r="F573" s="3"/>
     </row>
-    <row r="574" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B574" s="2">
         <f t="shared" si="8"/>
         <v>570</v>
@@ -11989,7 +11988,7 @@
       </c>
       <c r="F574" s="3"/>
     </row>
-    <row r="575" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B575" s="2">
         <f t="shared" si="8"/>
         <v>571</v>
@@ -12005,7 +12004,7 @@
       </c>
       <c r="F575" s="3"/>
     </row>
-    <row r="576" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B576" s="2">
         <f t="shared" si="8"/>
         <v>572</v>
@@ -12021,7 +12020,7 @@
       </c>
       <c r="F576" s="3"/>
     </row>
-    <row r="577" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B577" s="2">
         <f t="shared" si="8"/>
         <v>573</v>
@@ -12037,7 +12036,7 @@
       </c>
       <c r="F577" s="3"/>
     </row>
-    <row r="578" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B578" s="2">
         <f t="shared" si="8"/>
         <v>574</v>
@@ -12053,7 +12052,7 @@
       </c>
       <c r="F578" s="3"/>
     </row>
-    <row r="579" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B579" s="2">
         <f t="shared" si="8"/>
         <v>575</v>
@@ -12069,7 +12068,7 @@
       </c>
       <c r="F579" s="3"/>
     </row>
-    <row r="580" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B580" s="2">
         <f t="shared" si="8"/>
         <v>576</v>
@@ -12085,7 +12084,7 @@
       </c>
       <c r="F580" s="3"/>
     </row>
-    <row r="581" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B581" s="2">
         <f t="shared" si="8"/>
         <v>577</v>
@@ -12101,7 +12100,7 @@
       </c>
       <c r="F581" s="3"/>
     </row>
-    <row r="582" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B582" s="2">
         <f t="shared" si="8"/>
         <v>578</v>
@@ -12117,7 +12116,7 @@
       </c>
       <c r="F582" s="3"/>
     </row>
-    <row r="583" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B583" s="2">
         <f t="shared" si="8"/>
         <v>579</v>
@@ -12133,7 +12132,7 @@
       </c>
       <c r="F583" s="3"/>
     </row>
-    <row r="584" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B584" s="2">
         <f t="shared" si="8"/>
         <v>580</v>
@@ -12149,7 +12148,7 @@
       </c>
       <c r="F584" s="3"/>
     </row>
-    <row r="585" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B585" s="2">
         <f t="shared" si="8"/>
         <v>581</v>
@@ -12165,7 +12164,7 @@
       </c>
       <c r="F585" s="3"/>
     </row>
-    <row r="586" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B586" s="2">
         <f t="shared" ref="B586:B598" si="9">B585+1</f>
         <v>582</v>
@@ -12181,7 +12180,7 @@
       </c>
       <c r="F586" s="3"/>
     </row>
-    <row r="587" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B587" s="2">
         <f t="shared" si="9"/>
         <v>583</v>
@@ -12197,7 +12196,7 @@
       </c>
       <c r="F587" s="3"/>
     </row>
-    <row r="588" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B588" s="2">
         <f t="shared" si="9"/>
         <v>584</v>
@@ -12213,7 +12212,7 @@
       </c>
       <c r="F588" s="3"/>
     </row>
-    <row r="589" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B589" s="2">
         <f t="shared" si="9"/>
         <v>585</v>
@@ -12229,7 +12228,7 @@
       </c>
       <c r="F589" s="3"/>
     </row>
-    <row r="590" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B590" s="2">
         <f t="shared" si="9"/>
         <v>586</v>
@@ -12245,7 +12244,7 @@
       </c>
       <c r="F590" s="3"/>
     </row>
-    <row r="591" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B591" s="2">
         <f t="shared" si="9"/>
         <v>587</v>
@@ -12261,7 +12260,7 @@
       </c>
       <c r="F591" s="3"/>
     </row>
-    <row r="592" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B592" s="2">
         <f t="shared" si="9"/>
         <v>588</v>
@@ -12277,7 +12276,7 @@
       </c>
       <c r="F592" s="3"/>
     </row>
-    <row r="593" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B593" s="2">
         <f t="shared" si="9"/>
         <v>589</v>
@@ -12293,7 +12292,7 @@
       </c>
       <c r="F593" s="3"/>
     </row>
-    <row r="594" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B594" s="2">
         <f t="shared" si="9"/>
         <v>590</v>
@@ -12309,7 +12308,7 @@
       </c>
       <c r="F594" s="3"/>
     </row>
-    <row r="595" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B595" s="2">
         <f t="shared" si="9"/>
         <v>591</v>
@@ -12325,7 +12324,7 @@
       </c>
       <c r="F595" s="3"/>
     </row>
-    <row r="596" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B596" s="2">
         <f t="shared" si="9"/>
         <v>592</v>
@@ -12341,7 +12340,7 @@
       </c>
       <c r="F596" s="3"/>
     </row>
-    <row r="597" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B597" s="2">
         <f t="shared" si="9"/>
         <v>593</v>
@@ -12357,7 +12356,7 @@
       </c>
       <c r="F597" s="3"/>
     </row>
-    <row r="598" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B598" s="2">
         <f t="shared" si="9"/>
         <v>594</v>
@@ -12373,7 +12372,7 @@
       </c>
       <c r="F598" s="3"/>
     </row>
-    <row r="599" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B599" s="6">
         <v>595</v>
       </c>
@@ -12385,7 +12384,7 @@
       </c>
       <c r="E599" s="5"/>
     </row>
-    <row r="600" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B600" s="6">
         <v>596</v>
       </c>
@@ -12397,10 +12396,10 @@
       </c>
       <c r="E600" s="5"/>
     </row>
-    <row r="601" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="C601" s="4"/>
     </row>
-    <row r="602" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B602" s="2">
         <v>509</v>
       </c>
@@ -12411,7 +12410,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="603" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B603">
         <v>334</v>
       </c>
@@ -12425,7 +12424,7 @@
         <v>3277876171384</v>
       </c>
     </row>
-    <row r="604" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B604">
         <v>263</v>
       </c>
@@ -12441,24 +12440,6 @@
     </row>
   </sheetData>
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="24/7 MART ASKARI X SECTOR F"/>
-        <filter val="Askari  Depsrtmental Store Punjab Society"/>
-        <filter val="Askari Departmental Store College Road"/>
-        <filter val="BASHIR SONS PHARMACY (ASKARI XI)"/>
-        <filter val="BUNDU KHAN ASKARI 11"/>
-        <filter val="CLINIX PHARMACY ASKARI 11"/>
-        <filter val="CSD Askari X"/>
-        <filter val="FRESHLY MART SECTOR B ASKARI 11"/>
-        <filter val="HIKMA SUPER STORE ASKARI 11"/>
-        <filter val="Jalal sons (Askari 10 F sector ) 01"/>
-        <filter val="JALAL SONS (ASKARI 11 B BLOCK) 02"/>
-        <filter val="Jalal Sons Askari X (01)"/>
-        <filter val="MM CASH &amp; CARRY ASKARI XI"/>
-        <filter val="PUNJAB CASH &amp; CARRY (ASKARI 11)"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">
       <sortCondition ref="C4"/>
     </sortState>

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F421035-E4F6-4B4E-85E0-D8E3E8FE21D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40D0489-ED81-447D-968C-A746EE7EC9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2163,9 +2163,6 @@
     <t>A336292-7</t>
   </si>
   <si>
-    <t>Risen / Gajjumata _FR TRADERS</t>
-  </si>
-  <si>
     <t>4692648-8</t>
   </si>
   <si>
@@ -2175,9 +2172,6 @@
     <t>4987374-2</t>
   </si>
   <si>
-    <t>Risen / Sabzazar _SZ TRADERS</t>
-  </si>
-  <si>
     <t>Risen / Shadbagh _SB Traders</t>
   </si>
   <si>
@@ -2449,6 +2443,12 @@
   </si>
   <si>
     <t xml:space="preserve">Joher Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen / Sabzazar _Rafaqat Sons </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen / Gajjumata _Rafaqat Sons </t>
   </si>
 </sst>
 </file>
@@ -2840,6 +2840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="B2:F604"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2869,7 +2870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -2884,7 +2885,7 @@
       </c>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <f>B5+1</f>
         <v>2</v>
@@ -2900,7 +2901,7 @@
       </c>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <f>B6+1</f>
         <v>3</v>
@@ -2916,7 +2917,7 @@
       </c>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <f>B7+1</f>
         <v>4</v>
@@ -2932,7 +2933,7 @@
       </c>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <f>B8+1</f>
         <v>5</v>
@@ -2948,7 +2949,7 @@
       </c>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <f t="shared" ref="B10:B73" si="0">B9+1</f>
         <v>6</v>
@@ -2964,7 +2965,7 @@
       </c>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2980,7 +2981,7 @@
       </c>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2996,7 +2997,7 @@
       </c>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3012,7 +3013,7 @@
       </c>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3028,7 +3029,7 @@
       </c>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3044,7 +3045,7 @@
       </c>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -3060,7 +3061,7 @@
       </c>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -3076,7 +3077,7 @@
       </c>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -3092,7 +3093,7 @@
       </c>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -3108,7 +3109,7 @@
       </c>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -3124,7 +3125,7 @@
       </c>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -3140,7 +3141,7 @@
       </c>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -3156,7 +3157,7 @@
       </c>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -3172,7 +3173,7 @@
       </c>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -3188,7 +3189,7 @@
       </c>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -3204,7 +3205,7 @@
       </c>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -3220,7 +3221,7 @@
       </c>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -3236,7 +3237,7 @@
       </c>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3252,7 +3253,7 @@
       </c>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -3268,7 +3269,7 @@
       </c>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -3284,7 +3285,7 @@
       </c>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -3300,7 +3301,7 @@
       </c>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B32" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -3316,7 +3317,7 @@
       </c>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B33" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -3332,7 +3333,7 @@
       </c>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B34" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -3348,7 +3349,7 @@
       </c>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B35" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -3364,7 +3365,7 @@
       </c>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B36" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -3380,7 +3381,7 @@
       </c>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -3396,7 +3397,7 @@
       </c>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -3412,7 +3413,7 @@
       </c>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B39" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -3428,7 +3429,7 @@
       </c>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B40" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -3444,7 +3445,7 @@
       </c>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B41" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -3460,7 +3461,7 @@
       </c>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -3476,7 +3477,7 @@
       </c>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -3492,7 +3493,7 @@
       </c>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -3508,7 +3509,7 @@
       </c>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B45" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -3524,7 +3525,7 @@
       </c>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -3540,7 +3541,7 @@
       </c>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -3556,7 +3557,7 @@
       </c>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -3572,7 +3573,7 @@
       </c>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3588,7 +3589,7 @@
       </c>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3604,7 +3605,7 @@
       </c>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B51" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3620,7 +3621,7 @@
       </c>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B52" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -3636,7 +3637,7 @@
       </c>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B53" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -3652,7 +3653,7 @@
       </c>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B54" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -3668,7 +3669,7 @@
       </c>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B55" s="2">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -3684,7 +3685,7 @@
       </c>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B56" s="2">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -3700,7 +3701,7 @@
       </c>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B57" s="2">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -3716,7 +3717,7 @@
       </c>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B58" s="2">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -3732,7 +3733,7 @@
       </c>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B59" s="2">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -3748,7 +3749,7 @@
       </c>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B60" s="2">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -3764,7 +3765,7 @@
       </c>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B61" s="2">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -3780,7 +3781,7 @@
       </c>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B62" s="2">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -3796,7 +3797,7 @@
       </c>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B63" s="2">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -3812,7 +3813,7 @@
       </c>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B64" s="2">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -3828,7 +3829,7 @@
       </c>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B65" s="2">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -3844,7 +3845,7 @@
       </c>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B66" s="2">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -3860,7 +3861,7 @@
       </c>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B67" s="2">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -3876,7 +3877,7 @@
       </c>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B68" s="2">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -3892,7 +3893,7 @@
       </c>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B69" s="2">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -3908,7 +3909,7 @@
       </c>
       <c r="F69" s="3"/>
     </row>
-    <row r="70" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B70" s="2">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -3924,7 +3925,7 @@
       </c>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B71" s="2">
         <f t="shared" si="0"/>
         <v>67</v>
@@ -3940,7 +3941,7 @@
       </c>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B72" s="2">
         <f t="shared" si="0"/>
         <v>68</v>
@@ -3956,7 +3957,7 @@
       </c>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B73" s="2">
         <f t="shared" si="0"/>
         <v>69</v>
@@ -3972,7 +3973,7 @@
       </c>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B74" s="2">
         <f t="shared" ref="B74:B137" si="1">B73+1</f>
         <v>70</v>
@@ -3988,7 +3989,7 @@
       </c>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B75" s="2">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -4004,7 +4005,7 @@
       </c>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B76" s="2">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -4020,7 +4021,7 @@
       </c>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B77" s="2">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -4036,7 +4037,7 @@
       </c>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B78" s="2">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -4052,7 +4053,7 @@
       </c>
       <c r="F78" s="3"/>
     </row>
-    <row r="79" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B79" s="2">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -4068,7 +4069,7 @@
       </c>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B80" s="2">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -4084,7 +4085,7 @@
       </c>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B81" s="2">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -4100,7 +4101,7 @@
       </c>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B82" s="2">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -4116,7 +4117,7 @@
       </c>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B83" s="2">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -4132,7 +4133,7 @@
       </c>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B84" s="2">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -4148,7 +4149,7 @@
       </c>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B85" s="2">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -4164,7 +4165,7 @@
       </c>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B86" s="2">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -4180,7 +4181,7 @@
       </c>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B87" s="2">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -4196,7 +4197,7 @@
       </c>
       <c r="F87" s="3"/>
     </row>
-    <row r="88" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B88" s="2">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -4212,7 +4213,7 @@
       </c>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B89" s="2">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -4228,7 +4229,7 @@
       </c>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B90" s="2">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -4244,7 +4245,7 @@
       </c>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B91" s="2">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -4260,7 +4261,7 @@
       </c>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B92" s="2">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -4276,7 +4277,7 @@
       </c>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B93" s="2">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -4292,7 +4293,7 @@
       </c>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B94" s="2">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -4308,7 +4309,7 @@
       </c>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B95" s="2">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -4324,7 +4325,7 @@
       </c>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B96" s="2">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -4340,7 +4341,7 @@
       </c>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B97" s="2">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -4356,7 +4357,7 @@
       </c>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B98" s="2">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -4372,7 +4373,7 @@
       </c>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B99" s="2">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -4388,7 +4389,7 @@
       </c>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B100" s="2">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -4404,7 +4405,7 @@
       </c>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B101" s="2">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -4420,7 +4421,7 @@
       </c>
       <c r="F101" s="3"/>
     </row>
-    <row r="102" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B102" s="2">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -4436,7 +4437,7 @@
       </c>
       <c r="F102" s="3"/>
     </row>
-    <row r="103" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B103" s="2">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -4452,7 +4453,7 @@
       </c>
       <c r="F103" s="3"/>
     </row>
-    <row r="104" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B104" s="2">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -4468,13 +4469,13 @@
       </c>
       <c r="F104" s="3"/>
     </row>
-    <row r="105" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B105" s="2">
         <f t="shared" si="1"/>
         <v>101</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>90</v>
@@ -4484,7 +4485,7 @@
       </c>
       <c r="F105" s="3"/>
     </row>
-    <row r="106" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B106" s="2">
         <f t="shared" si="1"/>
         <v>102</v>
@@ -4500,7 +4501,7 @@
       </c>
       <c r="F106" s="3"/>
     </row>
-    <row r="107" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B107" s="2">
         <f t="shared" si="1"/>
         <v>103</v>
@@ -4516,7 +4517,7 @@
       </c>
       <c r="F107" s="3"/>
     </row>
-    <row r="108" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B108" s="2">
         <f t="shared" si="1"/>
         <v>104</v>
@@ -4532,7 +4533,7 @@
       </c>
       <c r="F108" s="3"/>
     </row>
-    <row r="109" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B109" s="2">
         <f t="shared" si="1"/>
         <v>105</v>
@@ -4548,7 +4549,7 @@
       </c>
       <c r="F109" s="3"/>
     </row>
-    <row r="110" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B110" s="2">
         <f t="shared" si="1"/>
         <v>106</v>
@@ -4564,7 +4565,7 @@
       </c>
       <c r="F110" s="3"/>
     </row>
-    <row r="111" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B111" s="2">
         <f t="shared" si="1"/>
         <v>107</v>
@@ -4580,7 +4581,7 @@
       </c>
       <c r="F111" s="3"/>
     </row>
-    <row r="112" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B112" s="2">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -4596,7 +4597,7 @@
       </c>
       <c r="F112" s="3"/>
     </row>
-    <row r="113" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B113" s="2">
         <f t="shared" si="1"/>
         <v>109</v>
@@ -4612,7 +4613,7 @@
       </c>
       <c r="F113" s="3"/>
     </row>
-    <row r="114" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B114" s="2">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -4628,7 +4629,7 @@
       </c>
       <c r="F114" s="3"/>
     </row>
-    <row r="115" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B115" s="2">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -4644,7 +4645,7 @@
       </c>
       <c r="F115" s="3"/>
     </row>
-    <row r="116" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B116" s="2">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -4660,7 +4661,7 @@
       </c>
       <c r="F116" s="3"/>
     </row>
-    <row r="117" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B117" s="2">
         <f t="shared" si="1"/>
         <v>113</v>
@@ -4676,7 +4677,7 @@
       </c>
       <c r="F117" s="3"/>
     </row>
-    <row r="118" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B118" s="2">
         <f t="shared" si="1"/>
         <v>114</v>
@@ -4692,7 +4693,7 @@
       </c>
       <c r="F118" s="3"/>
     </row>
-    <row r="119" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B119" s="2">
         <f t="shared" si="1"/>
         <v>115</v>
@@ -4708,7 +4709,7 @@
       </c>
       <c r="F119" s="3"/>
     </row>
-    <row r="120" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B120" s="2">
         <f t="shared" si="1"/>
         <v>116</v>
@@ -4724,7 +4725,7 @@
       </c>
       <c r="F120" s="3"/>
     </row>
-    <row r="121" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B121" s="2">
         <f t="shared" si="1"/>
         <v>117</v>
@@ -4740,7 +4741,7 @@
       </c>
       <c r="F121" s="3"/>
     </row>
-    <row r="122" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B122" s="2">
         <f t="shared" si="1"/>
         <v>118</v>
@@ -4756,7 +4757,7 @@
       </c>
       <c r="F122" s="3"/>
     </row>
-    <row r="123" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B123" s="2">
         <f t="shared" si="1"/>
         <v>119</v>
@@ -4772,7 +4773,7 @@
       </c>
       <c r="F123" s="3"/>
     </row>
-    <row r="124" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B124" s="2">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -4788,7 +4789,7 @@
       </c>
       <c r="F124" s="3"/>
     </row>
-    <row r="125" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B125" s="2">
         <f t="shared" si="1"/>
         <v>121</v>
@@ -4804,7 +4805,7 @@
       </c>
       <c r="F125" s="3"/>
     </row>
-    <row r="126" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B126" s="2">
         <f t="shared" si="1"/>
         <v>122</v>
@@ -4820,7 +4821,7 @@
       </c>
       <c r="F126" s="3"/>
     </row>
-    <row r="127" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B127" s="2">
         <f t="shared" si="1"/>
         <v>123</v>
@@ -4836,7 +4837,7 @@
       </c>
       <c r="F127" s="3"/>
     </row>
-    <row r="128" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B128" s="2">
         <f t="shared" si="1"/>
         <v>124</v>
@@ -4852,7 +4853,7 @@
       </c>
       <c r="F128" s="3"/>
     </row>
-    <row r="129" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B129" s="2">
         <f t="shared" si="1"/>
         <v>125</v>
@@ -4868,7 +4869,7 @@
       </c>
       <c r="F129" s="3"/>
     </row>
-    <row r="130" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B130" s="2">
         <f t="shared" si="1"/>
         <v>126</v>
@@ -4884,7 +4885,7 @@
       </c>
       <c r="F130" s="3"/>
     </row>
-    <row r="131" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B131" s="2">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -4900,7 +4901,7 @@
       </c>
       <c r="F131" s="3"/>
     </row>
-    <row r="132" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B132" s="2">
         <f t="shared" si="1"/>
         <v>128</v>
@@ -4916,7 +4917,7 @@
       </c>
       <c r="F132" s="3"/>
     </row>
-    <row r="133" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B133" s="2">
         <f t="shared" si="1"/>
         <v>129</v>
@@ -4932,7 +4933,7 @@
       </c>
       <c r="F133" s="3"/>
     </row>
-    <row r="134" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B134" s="2">
         <f t="shared" si="1"/>
         <v>130</v>
@@ -4948,7 +4949,7 @@
       </c>
       <c r="F134" s="3"/>
     </row>
-    <row r="135" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B135" s="2">
         <f t="shared" si="1"/>
         <v>131</v>
@@ -4964,7 +4965,7 @@
       </c>
       <c r="F135" s="3"/>
     </row>
-    <row r="136" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B136" s="2">
         <f t="shared" si="1"/>
         <v>132</v>
@@ -4980,7 +4981,7 @@
       </c>
       <c r="F136" s="3"/>
     </row>
-    <row r="137" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B137" s="2">
         <f t="shared" si="1"/>
         <v>133</v>
@@ -4996,7 +4997,7 @@
       </c>
       <c r="F137" s="3"/>
     </row>
-    <row r="138" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B138" s="2">
         <f t="shared" ref="B138:B201" si="2">B137+1</f>
         <v>134</v>
@@ -5012,7 +5013,7 @@
       </c>
       <c r="F138" s="3"/>
     </row>
-    <row r="139" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B139" s="2">
         <f t="shared" si="2"/>
         <v>135</v>
@@ -5028,7 +5029,7 @@
       </c>
       <c r="F139" s="3"/>
     </row>
-    <row r="140" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B140" s="2">
         <f t="shared" si="2"/>
         <v>136</v>
@@ -5044,7 +5045,7 @@
       </c>
       <c r="F140" s="3"/>
     </row>
-    <row r="141" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B141" s="2">
         <f t="shared" si="2"/>
         <v>137</v>
@@ -5060,7 +5061,7 @@
       </c>
       <c r="F141" s="3"/>
     </row>
-    <row r="142" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B142" s="2">
         <f t="shared" si="2"/>
         <v>138</v>
@@ -5076,7 +5077,7 @@
       </c>
       <c r="F142" s="3"/>
     </row>
-    <row r="143" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B143" s="2">
         <f t="shared" si="2"/>
         <v>139</v>
@@ -5092,7 +5093,7 @@
       </c>
       <c r="F143" s="3"/>
     </row>
-    <row r="144" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B144" s="2">
         <f t="shared" si="2"/>
         <v>140</v>
@@ -5108,7 +5109,7 @@
       </c>
       <c r="F144" s="3"/>
     </row>
-    <row r="145" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B145" s="2">
         <f t="shared" si="2"/>
         <v>141</v>
@@ -5124,7 +5125,7 @@
       </c>
       <c r="F145" s="3"/>
     </row>
-    <row r="146" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B146" s="2">
         <f t="shared" si="2"/>
         <v>142</v>
@@ -5140,7 +5141,7 @@
       </c>
       <c r="F146" s="3"/>
     </row>
-    <row r="147" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B147" s="2">
         <f t="shared" si="2"/>
         <v>143</v>
@@ -5156,7 +5157,7 @@
       </c>
       <c r="F147" s="3"/>
     </row>
-    <row r="148" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B148" s="2">
         <f t="shared" si="2"/>
         <v>144</v>
@@ -5172,7 +5173,7 @@
       </c>
       <c r="F148" s="3"/>
     </row>
-    <row r="149" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B149" s="2">
         <f t="shared" si="2"/>
         <v>145</v>
@@ -5188,7 +5189,7 @@
       </c>
       <c r="F149" s="3"/>
     </row>
-    <row r="150" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B150" s="2">
         <f t="shared" si="2"/>
         <v>146</v>
@@ -5204,7 +5205,7 @@
       </c>
       <c r="F150" s="3"/>
     </row>
-    <row r="151" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B151" s="2">
         <f t="shared" si="2"/>
         <v>147</v>
@@ -5220,7 +5221,7 @@
       </c>
       <c r="F151" s="3"/>
     </row>
-    <row r="152" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B152" s="2">
         <f t="shared" si="2"/>
         <v>148</v>
@@ -5236,7 +5237,7 @@
       </c>
       <c r="F152" s="3"/>
     </row>
-    <row r="153" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B153" s="2">
         <f t="shared" si="2"/>
         <v>149</v>
@@ -5252,7 +5253,7 @@
       </c>
       <c r="F153" s="3"/>
     </row>
-    <row r="154" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B154" s="2">
         <f t="shared" si="2"/>
         <v>150</v>
@@ -5268,7 +5269,7 @@
       </c>
       <c r="F154" s="3"/>
     </row>
-    <row r="155" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B155" s="2">
         <f t="shared" si="2"/>
         <v>151</v>
@@ -5284,7 +5285,7 @@
       </c>
       <c r="F155" s="3"/>
     </row>
-    <row r="156" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B156" s="2">
         <f t="shared" si="2"/>
         <v>152</v>
@@ -5300,7 +5301,7 @@
       </c>
       <c r="F156" s="3"/>
     </row>
-    <row r="157" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B157" s="2">
         <f t="shared" si="2"/>
         <v>153</v>
@@ -5316,7 +5317,7 @@
       </c>
       <c r="F157" s="3"/>
     </row>
-    <row r="158" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B158" s="2">
         <f t="shared" si="2"/>
         <v>154</v>
@@ -5332,7 +5333,7 @@
       </c>
       <c r="F158" s="3"/>
     </row>
-    <row r="159" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B159" s="2">
         <f t="shared" si="2"/>
         <v>155</v>
@@ -5348,7 +5349,7 @@
       </c>
       <c r="F159" s="3"/>
     </row>
-    <row r="160" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B160" s="2">
         <f t="shared" si="2"/>
         <v>156</v>
@@ -5364,7 +5365,7 @@
       </c>
       <c r="F160" s="3"/>
     </row>
-    <row r="161" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B161" s="2">
         <f t="shared" si="2"/>
         <v>157</v>
@@ -5380,7 +5381,7 @@
       </c>
       <c r="F161" s="3"/>
     </row>
-    <row r="162" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B162" s="2">
         <f t="shared" si="2"/>
         <v>158</v>
@@ -5396,7 +5397,7 @@
       </c>
       <c r="F162" s="3"/>
     </row>
-    <row r="163" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B163" s="2">
         <f t="shared" si="2"/>
         <v>159</v>
@@ -5412,7 +5413,7 @@
       </c>
       <c r="F163" s="3"/>
     </row>
-    <row r="164" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B164" s="2">
         <f t="shared" si="2"/>
         <v>160</v>
@@ -5428,7 +5429,7 @@
       </c>
       <c r="F164" s="3"/>
     </row>
-    <row r="165" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B165" s="2">
         <f t="shared" si="2"/>
         <v>161</v>
@@ -5444,7 +5445,7 @@
       </c>
       <c r="F165" s="3"/>
     </row>
-    <row r="166" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B166" s="2">
         <f t="shared" si="2"/>
         <v>162</v>
@@ -5460,7 +5461,7 @@
       </c>
       <c r="F166" s="3"/>
     </row>
-    <row r="167" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B167" s="2">
         <f t="shared" si="2"/>
         <v>163</v>
@@ -5476,7 +5477,7 @@
       </c>
       <c r="F167" s="3"/>
     </row>
-    <row r="168" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B168" s="2">
         <f t="shared" si="2"/>
         <v>164</v>
@@ -5492,7 +5493,7 @@
       </c>
       <c r="F168" s="3"/>
     </row>
-    <row r="169" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B169" s="2">
         <f t="shared" si="2"/>
         <v>165</v>
@@ -5508,7 +5509,7 @@
       </c>
       <c r="F169" s="3"/>
     </row>
-    <row r="170" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B170" s="2">
         <f t="shared" si="2"/>
         <v>166</v>
@@ -5524,7 +5525,7 @@
       </c>
       <c r="F170" s="3"/>
     </row>
-    <row r="171" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B171" s="2">
         <f t="shared" si="2"/>
         <v>167</v>
@@ -5540,7 +5541,7 @@
       </c>
       <c r="F171" s="3"/>
     </row>
-    <row r="172" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B172" s="2">
         <f t="shared" si="2"/>
         <v>168</v>
@@ -5556,7 +5557,7 @@
       </c>
       <c r="F172" s="3"/>
     </row>
-    <row r="173" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B173" s="2">
         <f t="shared" si="2"/>
         <v>169</v>
@@ -5572,7 +5573,7 @@
       </c>
       <c r="F173" s="3"/>
     </row>
-    <row r="174" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B174" s="2">
         <f t="shared" si="2"/>
         <v>170</v>
@@ -5588,7 +5589,7 @@
       </c>
       <c r="F174" s="3"/>
     </row>
-    <row r="175" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B175" s="2">
         <f t="shared" si="2"/>
         <v>171</v>
@@ -5604,7 +5605,7 @@
       </c>
       <c r="F175" s="3"/>
     </row>
-    <row r="176" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B176" s="2">
         <f t="shared" si="2"/>
         <v>172</v>
@@ -5620,7 +5621,7 @@
       </c>
       <c r="F176" s="3"/>
     </row>
-    <row r="177" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B177" s="2">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -5636,7 +5637,7 @@
       </c>
       <c r="F177" s="3"/>
     </row>
-    <row r="178" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B178" s="2">
         <f t="shared" si="2"/>
         <v>174</v>
@@ -5652,7 +5653,7 @@
       </c>
       <c r="F178" s="3"/>
     </row>
-    <row r="179" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B179" s="2">
         <f t="shared" si="2"/>
         <v>175</v>
@@ -5668,7 +5669,7 @@
       </c>
       <c r="F179" s="3"/>
     </row>
-    <row r="180" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B180" s="2">
         <f t="shared" si="2"/>
         <v>176</v>
@@ -5684,7 +5685,7 @@
       </c>
       <c r="F180" s="3"/>
     </row>
-    <row r="181" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B181" s="2">
         <f t="shared" si="2"/>
         <v>177</v>
@@ -5700,7 +5701,7 @@
       </c>
       <c r="F181" s="3"/>
     </row>
-    <row r="182" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B182" s="2">
         <f t="shared" si="2"/>
         <v>178</v>
@@ -5716,7 +5717,7 @@
       </c>
       <c r="F182" s="3"/>
     </row>
-    <row r="183" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B183" s="2">
         <f t="shared" si="2"/>
         <v>179</v>
@@ -5732,7 +5733,7 @@
       </c>
       <c r="F183" s="3"/>
     </row>
-    <row r="184" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B184" s="2">
         <f t="shared" si="2"/>
         <v>180</v>
@@ -5748,7 +5749,7 @@
       </c>
       <c r="F184" s="3"/>
     </row>
-    <row r="185" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B185" s="2">
         <f t="shared" si="2"/>
         <v>181</v>
@@ -5764,7 +5765,7 @@
       </c>
       <c r="F185" s="3"/>
     </row>
-    <row r="186" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B186" s="2">
         <f t="shared" si="2"/>
         <v>182</v>
@@ -5780,7 +5781,7 @@
       </c>
       <c r="F186" s="3"/>
     </row>
-    <row r="187" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B187" s="2">
         <f t="shared" si="2"/>
         <v>183</v>
@@ -5796,7 +5797,7 @@
       </c>
       <c r="F187" s="3"/>
     </row>
-    <row r="188" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B188" s="2">
         <f t="shared" si="2"/>
         <v>184</v>
@@ -5812,7 +5813,7 @@
       </c>
       <c r="F188" s="3"/>
     </row>
-    <row r="189" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B189" s="2">
         <f t="shared" si="2"/>
         <v>185</v>
@@ -5828,7 +5829,7 @@
       </c>
       <c r="F189" s="3"/>
     </row>
-    <row r="190" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B190" s="2">
         <f t="shared" si="2"/>
         <v>186</v>
@@ -5844,7 +5845,7 @@
       </c>
       <c r="F190" s="3"/>
     </row>
-    <row r="191" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B191" s="2">
         <f t="shared" si="2"/>
         <v>187</v>
@@ -5860,7 +5861,7 @@
       </c>
       <c r="F191" s="3"/>
     </row>
-    <row r="192" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B192" s="2">
         <f t="shared" si="2"/>
         <v>188</v>
@@ -5876,7 +5877,7 @@
       </c>
       <c r="F192" s="3"/>
     </row>
-    <row r="193" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B193" s="2">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -5892,7 +5893,7 @@
       </c>
       <c r="F193" s="3"/>
     </row>
-    <row r="194" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B194" s="2">
         <f t="shared" si="2"/>
         <v>190</v>
@@ -5908,7 +5909,7 @@
       </c>
       <c r="F194" s="3"/>
     </row>
-    <row r="195" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B195" s="2">
         <f t="shared" si="2"/>
         <v>191</v>
@@ -5924,7 +5925,7 @@
       </c>
       <c r="F195" s="3"/>
     </row>
-    <row r="196" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B196" s="2">
         <f t="shared" si="2"/>
         <v>192</v>
@@ -5940,7 +5941,7 @@
       </c>
       <c r="F196" s="3"/>
     </row>
-    <row r="197" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B197" s="2">
         <f t="shared" si="2"/>
         <v>193</v>
@@ -5956,7 +5957,7 @@
       </c>
       <c r="F197" s="3"/>
     </row>
-    <row r="198" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B198" s="2">
         <f t="shared" si="2"/>
         <v>194</v>
@@ -5972,7 +5973,7 @@
       </c>
       <c r="F198" s="3"/>
     </row>
-    <row r="199" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B199" s="2">
         <f t="shared" si="2"/>
         <v>195</v>
@@ -5988,7 +5989,7 @@
       </c>
       <c r="F199" s="3"/>
     </row>
-    <row r="200" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B200" s="2">
         <f t="shared" si="2"/>
         <v>196</v>
@@ -6004,7 +6005,7 @@
       </c>
       <c r="F200" s="3"/>
     </row>
-    <row r="201" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B201" s="2">
         <f t="shared" si="2"/>
         <v>197</v>
@@ -6020,7 +6021,7 @@
       </c>
       <c r="F201" s="3"/>
     </row>
-    <row r="202" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B202" s="2">
         <f t="shared" ref="B202:B265" si="3">B201+1</f>
         <v>198</v>
@@ -6036,7 +6037,7 @@
       </c>
       <c r="F202" s="3"/>
     </row>
-    <row r="203" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B203" s="2">
         <f t="shared" si="3"/>
         <v>199</v>
@@ -6052,7 +6053,7 @@
       </c>
       <c r="F203" s="3"/>
     </row>
-    <row r="204" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B204" s="2">
         <f t="shared" si="3"/>
         <v>200</v>
@@ -6068,7 +6069,7 @@
       </c>
       <c r="F204" s="3"/>
     </row>
-    <row r="205" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B205" s="2">
         <f t="shared" si="3"/>
         <v>201</v>
@@ -6084,7 +6085,7 @@
       </c>
       <c r="F205" s="3"/>
     </row>
-    <row r="206" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B206" s="2">
         <f t="shared" si="3"/>
         <v>202</v>
@@ -6100,7 +6101,7 @@
       </c>
       <c r="F206" s="3"/>
     </row>
-    <row r="207" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B207" s="2">
         <f t="shared" si="3"/>
         <v>203</v>
@@ -6116,7 +6117,7 @@
       </c>
       <c r="F207" s="3"/>
     </row>
-    <row r="208" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B208" s="2">
         <f t="shared" si="3"/>
         <v>204</v>
@@ -6132,7 +6133,7 @@
       </c>
       <c r="F208" s="3"/>
     </row>
-    <row r="209" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B209" s="2">
         <f t="shared" si="3"/>
         <v>205</v>
@@ -6148,7 +6149,7 @@
       </c>
       <c r="F209" s="3"/>
     </row>
-    <row r="210" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B210" s="2">
         <f t="shared" si="3"/>
         <v>206</v>
@@ -6164,7 +6165,7 @@
       </c>
       <c r="F210" s="3"/>
     </row>
-    <row r="211" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B211" s="2">
         <f t="shared" si="3"/>
         <v>207</v>
@@ -6180,7 +6181,7 @@
       </c>
       <c r="F211" s="3"/>
     </row>
-    <row r="212" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B212" s="2">
         <f t="shared" si="3"/>
         <v>208</v>
@@ -6196,7 +6197,7 @@
       </c>
       <c r="F212" s="3"/>
     </row>
-    <row r="213" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B213" s="2">
         <f t="shared" si="3"/>
         <v>209</v>
@@ -6212,7 +6213,7 @@
       </c>
       <c r="F213" s="3"/>
     </row>
-    <row r="214" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B214" s="2">
         <f t="shared" si="3"/>
         <v>210</v>
@@ -6228,7 +6229,7 @@
       </c>
       <c r="F214" s="3"/>
     </row>
-    <row r="215" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B215" s="2">
         <f t="shared" si="3"/>
         <v>211</v>
@@ -6244,7 +6245,7 @@
       </c>
       <c r="F215" s="3"/>
     </row>
-    <row r="216" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B216" s="2">
         <f t="shared" si="3"/>
         <v>212</v>
@@ -6260,7 +6261,7 @@
       </c>
       <c r="F216" s="3"/>
     </row>
-    <row r="217" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B217" s="2">
         <f t="shared" si="3"/>
         <v>213</v>
@@ -6276,7 +6277,7 @@
       </c>
       <c r="F217" s="3"/>
     </row>
-    <row r="218" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B218" s="2">
         <f t="shared" si="3"/>
         <v>214</v>
@@ -6292,7 +6293,7 @@
       </c>
       <c r="F218" s="3"/>
     </row>
-    <row r="219" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B219" s="2">
         <f t="shared" si="3"/>
         <v>215</v>
@@ -6308,7 +6309,7 @@
       </c>
       <c r="F219" s="3"/>
     </row>
-    <row r="220" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B220" s="2">
         <f t="shared" si="3"/>
         <v>216</v>
@@ -6324,7 +6325,7 @@
       </c>
       <c r="F220" s="3"/>
     </row>
-    <row r="221" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B221" s="2">
         <f t="shared" si="3"/>
         <v>217</v>
@@ -6340,7 +6341,7 @@
       </c>
       <c r="F221" s="3"/>
     </row>
-    <row r="222" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B222" s="2">
         <f t="shared" si="3"/>
         <v>218</v>
@@ -6356,7 +6357,7 @@
       </c>
       <c r="F222" s="3"/>
     </row>
-    <row r="223" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B223" s="2">
         <f t="shared" si="3"/>
         <v>219</v>
@@ -6372,7 +6373,7 @@
       </c>
       <c r="F223" s="3"/>
     </row>
-    <row r="224" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B224" s="2">
         <f t="shared" si="3"/>
         <v>220</v>
@@ -6388,7 +6389,7 @@
       </c>
       <c r="F224" s="3"/>
     </row>
-    <row r="225" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B225" s="2">
         <f t="shared" si="3"/>
         <v>221</v>
@@ -6404,7 +6405,7 @@
       </c>
       <c r="F225" s="3"/>
     </row>
-    <row r="226" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B226" s="2">
         <f t="shared" si="3"/>
         <v>222</v>
@@ -6420,7 +6421,7 @@
       </c>
       <c r="F226" s="3"/>
     </row>
-    <row r="227" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B227" s="2">
         <f t="shared" si="3"/>
         <v>223</v>
@@ -6436,7 +6437,7 @@
       </c>
       <c r="F227" s="3"/>
     </row>
-    <row r="228" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B228" s="2">
         <f t="shared" si="3"/>
         <v>224</v>
@@ -6452,7 +6453,7 @@
       </c>
       <c r="F228" s="3"/>
     </row>
-    <row r="229" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B229" s="2">
         <f t="shared" si="3"/>
         <v>225</v>
@@ -6468,7 +6469,7 @@
       </c>
       <c r="F229" s="3"/>
     </row>
-    <row r="230" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B230" s="2">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -6484,7 +6485,7 @@
       </c>
       <c r="F230" s="3"/>
     </row>
-    <row r="231" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B231" s="2">
         <f t="shared" si="3"/>
         <v>227</v>
@@ -6500,7 +6501,7 @@
       </c>
       <c r="F231" s="3"/>
     </row>
-    <row r="232" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B232" s="2">
         <f t="shared" si="3"/>
         <v>228</v>
@@ -6516,7 +6517,7 @@
       </c>
       <c r="F232" s="3"/>
     </row>
-    <row r="233" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B233" s="2">
         <f t="shared" si="3"/>
         <v>229</v>
@@ -6532,7 +6533,7 @@
       </c>
       <c r="F233" s="3"/>
     </row>
-    <row r="234" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B234" s="2">
         <f t="shared" si="3"/>
         <v>230</v>
@@ -6548,7 +6549,7 @@
       </c>
       <c r="F234" s="3"/>
     </row>
-    <row r="235" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B235" s="2">
         <f t="shared" si="3"/>
         <v>231</v>
@@ -6564,7 +6565,7 @@
       </c>
       <c r="F235" s="3"/>
     </row>
-    <row r="236" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B236" s="2">
         <f t="shared" si="3"/>
         <v>232</v>
@@ -6580,7 +6581,7 @@
       </c>
       <c r="F236" s="3"/>
     </row>
-    <row r="237" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B237" s="2">
         <f t="shared" si="3"/>
         <v>233</v>
@@ -6596,7 +6597,7 @@
       </c>
       <c r="F237" s="3"/>
     </row>
-    <row r="238" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B238" s="2">
         <f t="shared" si="3"/>
         <v>234</v>
@@ -6612,7 +6613,7 @@
       </c>
       <c r="F238" s="3"/>
     </row>
-    <row r="239" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B239" s="2">
         <f t="shared" si="3"/>
         <v>235</v>
@@ -6628,7 +6629,7 @@
       </c>
       <c r="F239" s="3"/>
     </row>
-    <row r="240" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B240" s="2">
         <f t="shared" si="3"/>
         <v>236</v>
@@ -6644,7 +6645,7 @@
       </c>
       <c r="F240" s="3"/>
     </row>
-    <row r="241" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B241" s="2">
         <f t="shared" si="3"/>
         <v>237</v>
@@ -6660,7 +6661,7 @@
       </c>
       <c r="F241" s="3"/>
     </row>
-    <row r="242" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B242" s="2">
         <f t="shared" si="3"/>
         <v>238</v>
@@ -6676,7 +6677,7 @@
       </c>
       <c r="F242" s="3"/>
     </row>
-    <row r="243" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B243" s="2">
         <f t="shared" si="3"/>
         <v>239</v>
@@ -6692,7 +6693,7 @@
       </c>
       <c r="F243" s="3"/>
     </row>
-    <row r="244" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B244" s="2">
         <f t="shared" si="3"/>
         <v>240</v>
@@ -6708,7 +6709,7 @@
       </c>
       <c r="F244" s="3"/>
     </row>
-    <row r="245" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B245" s="2">
         <f t="shared" si="3"/>
         <v>241</v>
@@ -6724,7 +6725,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B246" s="2">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6740,7 +6741,7 @@
       </c>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B247" s="2">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6756,7 +6757,7 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B248" s="2">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6772,7 +6773,7 @@
       </c>
       <c r="F248" s="3"/>
     </row>
-    <row r="249" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B249" s="2">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -6788,7 +6789,7 @@
       </c>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B250" s="2">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6804,7 +6805,7 @@
       </c>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B251" s="2">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6820,7 +6821,7 @@
       </c>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B252" s="2">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -6836,13 +6837,13 @@
       </c>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B253" s="2">
         <f t="shared" si="3"/>
         <v>249</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>319</v>
@@ -6852,7 +6853,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -6868,7 +6869,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -6884,7 +6885,7 @@
       </c>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B256" s="2">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -6900,7 +6901,7 @@
       </c>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B257" s="2">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -6916,7 +6917,7 @@
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B258" s="2">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -6932,7 +6933,7 @@
       </c>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B259" s="2">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -6948,13 +6949,13 @@
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B260" s="2">
         <f t="shared" si="3"/>
         <v>256</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>319</v>
@@ -6964,7 +6965,7 @@
       </c>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B261" s="2">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -6980,7 +6981,7 @@
       </c>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B262" s="2">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -6996,7 +6997,7 @@
       </c>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B263" s="2">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -7012,7 +7013,7 @@
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B264" s="2">
         <f t="shared" si="3"/>
         <v>260</v>
@@ -7028,7 +7029,7 @@
       </c>
       <c r="F264" s="3"/>
     </row>
-    <row r="265" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B265" s="2">
         <f t="shared" si="3"/>
         <v>261</v>
@@ -7044,7 +7045,7 @@
       </c>
       <c r="F265" s="3"/>
     </row>
-    <row r="266" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B266" s="2">
         <f t="shared" ref="B266:B329" si="4">B265+1</f>
         <v>262</v>
@@ -7060,7 +7061,7 @@
       </c>
       <c r="F266" s="3"/>
     </row>
-    <row r="267" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B267" s="2">
         <f t="shared" si="4"/>
         <v>263</v>
@@ -7076,7 +7077,7 @@
       </c>
       <c r="F267" s="3"/>
     </row>
-    <row r="268" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B268" s="2">
         <f t="shared" si="4"/>
         <v>264</v>
@@ -7092,7 +7093,7 @@
       </c>
       <c r="F268" s="3"/>
     </row>
-    <row r="269" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B269" s="2">
         <f t="shared" si="4"/>
         <v>265</v>
@@ -7108,7 +7109,7 @@
       </c>
       <c r="F269" s="3"/>
     </row>
-    <row r="270" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B270" s="2">
         <f t="shared" si="4"/>
         <v>266</v>
@@ -7124,7 +7125,7 @@
       </c>
       <c r="F270" s="3"/>
     </row>
-    <row r="271" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B271" s="2">
         <f t="shared" si="4"/>
         <v>267</v>
@@ -7140,7 +7141,7 @@
       </c>
       <c r="F271" s="3"/>
     </row>
-    <row r="272" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B272" s="2">
         <f t="shared" si="4"/>
         <v>268</v>
@@ -7156,7 +7157,7 @@
       </c>
       <c r="F272" s="3"/>
     </row>
-    <row r="273" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B273" s="2">
         <f t="shared" si="4"/>
         <v>269</v>
@@ -7172,7 +7173,7 @@
       </c>
       <c r="F273" s="3"/>
     </row>
-    <row r="274" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B274" s="2">
         <f t="shared" si="4"/>
         <v>270</v>
@@ -7188,7 +7189,7 @@
       </c>
       <c r="F274" s="3"/>
     </row>
-    <row r="275" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B275" s="2">
         <f t="shared" si="4"/>
         <v>271</v>
@@ -7204,7 +7205,7 @@
       </c>
       <c r="F275" s="3"/>
     </row>
-    <row r="276" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B276" s="2">
         <f t="shared" si="4"/>
         <v>272</v>
@@ -7220,7 +7221,7 @@
       </c>
       <c r="F276" s="3"/>
     </row>
-    <row r="277" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B277" s="2">
         <f t="shared" si="4"/>
         <v>273</v>
@@ -7236,7 +7237,7 @@
       </c>
       <c r="F277" s="3"/>
     </row>
-    <row r="278" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B278" s="2">
         <f t="shared" si="4"/>
         <v>274</v>
@@ -7252,7 +7253,7 @@
       </c>
       <c r="F278" s="3"/>
     </row>
-    <row r="279" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B279" s="2">
         <f t="shared" si="4"/>
         <v>275</v>
@@ -7268,7 +7269,7 @@
       </c>
       <c r="F279" s="3"/>
     </row>
-    <row r="280" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B280" s="2">
         <f t="shared" si="4"/>
         <v>276</v>
@@ -7284,7 +7285,7 @@
       </c>
       <c r="F280" s="3"/>
     </row>
-    <row r="281" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B281" s="2">
         <f t="shared" si="4"/>
         <v>277</v>
@@ -7300,7 +7301,7 @@
       </c>
       <c r="F281" s="3"/>
     </row>
-    <row r="282" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B282" s="2">
         <f t="shared" si="4"/>
         <v>278</v>
@@ -7316,7 +7317,7 @@
       </c>
       <c r="F282" s="3"/>
     </row>
-    <row r="283" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B283" s="2">
         <f t="shared" si="4"/>
         <v>279</v>
@@ -7332,7 +7333,7 @@
       </c>
       <c r="F283" s="3"/>
     </row>
-    <row r="284" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B284" s="2">
         <f t="shared" si="4"/>
         <v>280</v>
@@ -7348,7 +7349,7 @@
       </c>
       <c r="F284" s="3"/>
     </row>
-    <row r="285" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B285" s="2">
         <f t="shared" si="4"/>
         <v>281</v>
@@ -7364,7 +7365,7 @@
       </c>
       <c r="F285" s="3"/>
     </row>
-    <row r="286" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B286" s="2">
         <f t="shared" si="4"/>
         <v>282</v>
@@ -7380,7 +7381,7 @@
       </c>
       <c r="F286" s="3"/>
     </row>
-    <row r="287" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B287" s="2">
         <f t="shared" si="4"/>
         <v>283</v>
@@ -7396,7 +7397,7 @@
       </c>
       <c r="F287" s="3"/>
     </row>
-    <row r="288" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B288" s="2">
         <f t="shared" si="4"/>
         <v>284</v>
@@ -7412,7 +7413,7 @@
       </c>
       <c r="F288" s="3"/>
     </row>
-    <row r="289" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B289" s="2">
         <f t="shared" si="4"/>
         <v>285</v>
@@ -7428,7 +7429,7 @@
       </c>
       <c r="F289" s="3"/>
     </row>
-    <row r="290" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B290" s="2">
         <f t="shared" si="4"/>
         <v>286</v>
@@ -7444,7 +7445,7 @@
       </c>
       <c r="F290" s="3"/>
     </row>
-    <row r="291" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B291" s="2">
         <f t="shared" si="4"/>
         <v>287</v>
@@ -7460,7 +7461,7 @@
       </c>
       <c r="F291" s="3"/>
     </row>
-    <row r="292" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B292" s="2">
         <f t="shared" si="4"/>
         <v>288</v>
@@ -7476,7 +7477,7 @@
       </c>
       <c r="F292" s="3"/>
     </row>
-    <row r="293" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B293" s="2">
         <f t="shared" si="4"/>
         <v>289</v>
@@ -7492,7 +7493,7 @@
       </c>
       <c r="F293" s="3"/>
     </row>
-    <row r="294" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B294" s="2">
         <f t="shared" si="4"/>
         <v>290</v>
@@ -7508,7 +7509,7 @@
       </c>
       <c r="F294" s="3"/>
     </row>
-    <row r="295" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B295" s="2">
         <f t="shared" si="4"/>
         <v>291</v>
@@ -7524,7 +7525,7 @@
       </c>
       <c r="F295" s="3"/>
     </row>
-    <row r="296" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B296" s="2">
         <f t="shared" si="4"/>
         <v>292</v>
@@ -7540,7 +7541,7 @@
       </c>
       <c r="F296" s="3"/>
     </row>
-    <row r="297" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B297" s="2">
         <f t="shared" si="4"/>
         <v>293</v>
@@ -7556,7 +7557,7 @@
       </c>
       <c r="F297" s="3"/>
     </row>
-    <row r="298" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B298" s="2">
         <f t="shared" si="4"/>
         <v>294</v>
@@ -7572,7 +7573,7 @@
       </c>
       <c r="F298" s="3"/>
     </row>
-    <row r="299" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B299" s="2">
         <f t="shared" si="4"/>
         <v>295</v>
@@ -7588,7 +7589,7 @@
       </c>
       <c r="F299" s="3"/>
     </row>
-    <row r="300" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B300" s="2">
         <f t="shared" si="4"/>
         <v>296</v>
@@ -7604,7 +7605,7 @@
       </c>
       <c r="F300" s="3"/>
     </row>
-    <row r="301" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B301" s="2">
         <f t="shared" si="4"/>
         <v>297</v>
@@ -7620,7 +7621,7 @@
       </c>
       <c r="F301" s="3"/>
     </row>
-    <row r="302" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B302" s="2">
         <f t="shared" si="4"/>
         <v>298</v>
@@ -7636,7 +7637,7 @@
       </c>
       <c r="F302" s="3"/>
     </row>
-    <row r="303" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B303" s="2">
         <f t="shared" si="4"/>
         <v>299</v>
@@ -7652,7 +7653,7 @@
       </c>
       <c r="F303" s="3"/>
     </row>
-    <row r="304" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B304" s="2">
         <f t="shared" si="4"/>
         <v>300</v>
@@ -7668,7 +7669,7 @@
       </c>
       <c r="F304" s="3"/>
     </row>
-    <row r="305" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B305" s="2">
         <f t="shared" si="4"/>
         <v>301</v>
@@ -7684,7 +7685,7 @@
       </c>
       <c r="F305" s="3"/>
     </row>
-    <row r="306" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B306" s="2">
         <f t="shared" si="4"/>
         <v>302</v>
@@ -7700,7 +7701,7 @@
       </c>
       <c r="F306" s="3"/>
     </row>
-    <row r="307" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B307" s="2">
         <f t="shared" si="4"/>
         <v>303</v>
@@ -7716,7 +7717,7 @@
       </c>
       <c r="F307" s="3"/>
     </row>
-    <row r="308" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B308" s="2">
         <f t="shared" si="4"/>
         <v>304</v>
@@ -7732,7 +7733,7 @@
       </c>
       <c r="F308" s="3"/>
     </row>
-    <row r="309" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B309" s="2">
         <f t="shared" si="4"/>
         <v>305</v>
@@ -7748,7 +7749,7 @@
       </c>
       <c r="F309" s="3"/>
     </row>
-    <row r="310" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B310" s="2">
         <f t="shared" si="4"/>
         <v>306</v>
@@ -7764,7 +7765,7 @@
       </c>
       <c r="F310" s="3"/>
     </row>
-    <row r="311" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B311" s="2">
         <f t="shared" si="4"/>
         <v>307</v>
@@ -7780,7 +7781,7 @@
       </c>
       <c r="F311" s="3"/>
     </row>
-    <row r="312" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B312" s="2">
         <f t="shared" si="4"/>
         <v>308</v>
@@ -7796,7 +7797,7 @@
       </c>
       <c r="F312" s="3"/>
     </row>
-    <row r="313" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B313" s="2">
         <f t="shared" si="4"/>
         <v>309</v>
@@ -7812,7 +7813,7 @@
       </c>
       <c r="F313" s="3"/>
     </row>
-    <row r="314" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B314" s="2">
         <f t="shared" si="4"/>
         <v>310</v>
@@ -7828,7 +7829,7 @@
       </c>
       <c r="F314" s="3"/>
     </row>
-    <row r="315" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B315" s="2">
         <f t="shared" si="4"/>
         <v>311</v>
@@ -7844,7 +7845,7 @@
       </c>
       <c r="F315" s="3"/>
     </row>
-    <row r="316" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B316" s="2">
         <f t="shared" si="4"/>
         <v>312</v>
@@ -7860,7 +7861,7 @@
       </c>
       <c r="F316" s="3"/>
     </row>
-    <row r="317" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B317" s="2">
         <f t="shared" si="4"/>
         <v>313</v>
@@ -7876,7 +7877,7 @@
       </c>
       <c r="F317" s="3"/>
     </row>
-    <row r="318" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B318" s="2">
         <f t="shared" si="4"/>
         <v>314</v>
@@ -7892,7 +7893,7 @@
       </c>
       <c r="F318" s="3"/>
     </row>
-    <row r="319" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B319" s="2">
         <f t="shared" si="4"/>
         <v>315</v>
@@ -7908,7 +7909,7 @@
       </c>
       <c r="F319" s="3"/>
     </row>
-    <row r="320" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B320" s="2">
         <f t="shared" si="4"/>
         <v>316</v>
@@ -7924,7 +7925,7 @@
       </c>
       <c r="F320" s="3"/>
     </row>
-    <row r="321" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B321" s="2">
         <f t="shared" si="4"/>
         <v>317</v>
@@ -7940,7 +7941,7 @@
       </c>
       <c r="F321" s="3"/>
     </row>
-    <row r="322" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B322" s="2">
         <f t="shared" si="4"/>
         <v>318</v>
@@ -7956,7 +7957,7 @@
       </c>
       <c r="F322" s="3"/>
     </row>
-    <row r="323" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B323" s="2">
         <f t="shared" si="4"/>
         <v>319</v>
@@ -7972,7 +7973,7 @@
       </c>
       <c r="F323" s="3"/>
     </row>
-    <row r="324" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B324" s="2">
         <f t="shared" si="4"/>
         <v>320</v>
@@ -7988,7 +7989,7 @@
       </c>
       <c r="F324" s="3"/>
     </row>
-    <row r="325" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B325" s="2">
         <f t="shared" si="4"/>
         <v>321</v>
@@ -8004,7 +8005,7 @@
       </c>
       <c r="F325" s="3"/>
     </row>
-    <row r="326" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B326" s="2">
         <f t="shared" si="4"/>
         <v>322</v>
@@ -8020,7 +8021,7 @@
       </c>
       <c r="F326" s="3"/>
     </row>
-    <row r="327" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B327" s="2">
         <f t="shared" si="4"/>
         <v>323</v>
@@ -8036,7 +8037,7 @@
       </c>
       <c r="F327" s="3"/>
     </row>
-    <row r="328" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B328" s="2">
         <f t="shared" si="4"/>
         <v>324</v>
@@ -8052,7 +8053,7 @@
       </c>
       <c r="F328" s="3"/>
     </row>
-    <row r="329" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B329" s="2">
         <f t="shared" si="4"/>
         <v>325</v>
@@ -8068,7 +8069,7 @@
       </c>
       <c r="F329" s="3"/>
     </row>
-    <row r="330" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B330" s="2">
         <f t="shared" ref="B330:B393" si="5">B329+1</f>
         <v>326</v>
@@ -8084,7 +8085,7 @@
       </c>
       <c r="F330" s="3"/>
     </row>
-    <row r="331" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B331" s="2">
         <f t="shared" si="5"/>
         <v>327</v>
@@ -8100,7 +8101,7 @@
       </c>
       <c r="F331" s="3"/>
     </row>
-    <row r="332" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B332" s="2">
         <f t="shared" si="5"/>
         <v>328</v>
@@ -8116,7 +8117,7 @@
       </c>
       <c r="F332" s="3"/>
     </row>
-    <row r="333" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B333" s="2">
         <f t="shared" si="5"/>
         <v>329</v>
@@ -8132,7 +8133,7 @@
       </c>
       <c r="F333" s="3"/>
     </row>
-    <row r="334" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B334" s="2">
         <f t="shared" si="5"/>
         <v>330</v>
@@ -8148,7 +8149,7 @@
       </c>
       <c r="F334" s="3"/>
     </row>
-    <row r="335" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B335" s="2">
         <f t="shared" si="5"/>
         <v>331</v>
@@ -8164,7 +8165,7 @@
       </c>
       <c r="F335" s="3"/>
     </row>
-    <row r="336" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B336" s="2">
         <f t="shared" si="5"/>
         <v>332</v>
@@ -8180,7 +8181,7 @@
       </c>
       <c r="F336" s="3"/>
     </row>
-    <row r="337" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B337" s="2">
         <f t="shared" si="5"/>
         <v>333</v>
@@ -8196,7 +8197,7 @@
       </c>
       <c r="F337" s="3"/>
     </row>
-    <row r="338" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B338" s="2">
         <f t="shared" si="5"/>
         <v>334</v>
@@ -8212,7 +8213,7 @@
       </c>
       <c r="F338" s="3"/>
     </row>
-    <row r="339" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B339" s="2">
         <f t="shared" si="5"/>
         <v>335</v>
@@ -8228,7 +8229,7 @@
       </c>
       <c r="F339" s="3"/>
     </row>
-    <row r="340" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B340" s="2">
         <f t="shared" si="5"/>
         <v>336</v>
@@ -8244,7 +8245,7 @@
       </c>
       <c r="F340" s="3"/>
     </row>
-    <row r="341" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B341" s="2">
         <f t="shared" si="5"/>
         <v>337</v>
@@ -8260,7 +8261,7 @@
       </c>
       <c r="F341" s="3"/>
     </row>
-    <row r="342" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B342" s="2">
         <f t="shared" si="5"/>
         <v>338</v>
@@ -8276,7 +8277,7 @@
       </c>
       <c r="F342" s="3"/>
     </row>
-    <row r="343" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B343" s="2">
         <f t="shared" si="5"/>
         <v>339</v>
@@ -8292,7 +8293,7 @@
       </c>
       <c r="F343" s="3"/>
     </row>
-    <row r="344" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B344" s="2">
         <f t="shared" si="5"/>
         <v>340</v>
@@ -8308,7 +8309,7 @@
       </c>
       <c r="F344" s="3"/>
     </row>
-    <row r="345" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B345" s="2">
         <f t="shared" si="5"/>
         <v>341</v>
@@ -8324,7 +8325,7 @@
       </c>
       <c r="F345" s="3"/>
     </row>
-    <row r="346" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B346" s="2">
         <f t="shared" si="5"/>
         <v>342</v>
@@ -8340,7 +8341,7 @@
       </c>
       <c r="F346" s="3"/>
     </row>
-    <row r="347" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B347" s="2">
         <f t="shared" si="5"/>
         <v>343</v>
@@ -8356,7 +8357,7 @@
       </c>
       <c r="F347" s="3"/>
     </row>
-    <row r="348" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B348" s="2">
         <f t="shared" si="5"/>
         <v>344</v>
@@ -8372,7 +8373,7 @@
       </c>
       <c r="F348" s="3"/>
     </row>
-    <row r="349" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B349" s="2">
         <f t="shared" si="5"/>
         <v>345</v>
@@ -8388,7 +8389,7 @@
       </c>
       <c r="F349" s="3"/>
     </row>
-    <row r="350" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B350" s="2">
         <f t="shared" si="5"/>
         <v>346</v>
@@ -8404,7 +8405,7 @@
       </c>
       <c r="F350" s="3"/>
     </row>
-    <row r="351" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B351" s="2">
         <f t="shared" si="5"/>
         <v>347</v>
@@ -8420,7 +8421,7 @@
       </c>
       <c r="F351" s="3"/>
     </row>
-    <row r="352" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B352" s="2">
         <f t="shared" si="5"/>
         <v>348</v>
@@ -8436,7 +8437,7 @@
       </c>
       <c r="F352" s="3"/>
     </row>
-    <row r="353" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B353" s="2">
         <f t="shared" si="5"/>
         <v>349</v>
@@ -8452,7 +8453,7 @@
       </c>
       <c r="F353" s="3"/>
     </row>
-    <row r="354" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B354" s="2">
         <f t="shared" si="5"/>
         <v>350</v>
@@ -8468,7 +8469,7 @@
       </c>
       <c r="F354" s="3"/>
     </row>
-    <row r="355" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B355" s="2">
         <f t="shared" si="5"/>
         <v>351</v>
@@ -8484,7 +8485,7 @@
       </c>
       <c r="F355" s="3"/>
     </row>
-    <row r="356" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B356" s="2">
         <f t="shared" si="5"/>
         <v>352</v>
@@ -8500,7 +8501,7 @@
       </c>
       <c r="F356" s="3"/>
     </row>
-    <row r="357" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B357" s="2">
         <f t="shared" si="5"/>
         <v>353</v>
@@ -8516,7 +8517,7 @@
       </c>
       <c r="F357" s="3"/>
     </row>
-    <row r="358" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B358" s="2">
         <f t="shared" si="5"/>
         <v>354</v>
@@ -8532,7 +8533,7 @@
       </c>
       <c r="F358" s="3"/>
     </row>
-    <row r="359" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B359" s="2">
         <f t="shared" si="5"/>
         <v>355</v>
@@ -8548,7 +8549,7 @@
       </c>
       <c r="F359" s="3"/>
     </row>
-    <row r="360" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B360" s="2">
         <f t="shared" si="5"/>
         <v>356</v>
@@ -8564,7 +8565,7 @@
       </c>
       <c r="F360" s="3"/>
     </row>
-    <row r="361" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B361" s="2">
         <f t="shared" si="5"/>
         <v>357</v>
@@ -8580,7 +8581,7 @@
       </c>
       <c r="F361" s="3"/>
     </row>
-    <row r="362" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B362" s="2">
         <f t="shared" si="5"/>
         <v>358</v>
@@ -8596,7 +8597,7 @@
       </c>
       <c r="F362" s="3"/>
     </row>
-    <row r="363" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B363" s="2">
         <f t="shared" si="5"/>
         <v>359</v>
@@ -8612,7 +8613,7 @@
       </c>
       <c r="F363" s="3"/>
     </row>
-    <row r="364" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B364" s="2">
         <f t="shared" si="5"/>
         <v>360</v>
@@ -8628,7 +8629,7 @@
       </c>
       <c r="F364" s="3"/>
     </row>
-    <row r="365" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B365" s="2">
         <f t="shared" si="5"/>
         <v>361</v>
@@ -8644,7 +8645,7 @@
       </c>
       <c r="F365" s="3"/>
     </row>
-    <row r="366" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B366" s="2">
         <f t="shared" si="5"/>
         <v>362</v>
@@ -8660,7 +8661,7 @@
       </c>
       <c r="F366" s="3"/>
     </row>
-    <row r="367" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B367" s="2">
         <f t="shared" si="5"/>
         <v>363</v>
@@ -8676,7 +8677,7 @@
       </c>
       <c r="F367" s="3"/>
     </row>
-    <row r="368" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B368" s="2">
         <f t="shared" si="5"/>
         <v>364</v>
@@ -8692,7 +8693,7 @@
       </c>
       <c r="F368" s="3"/>
     </row>
-    <row r="369" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="369" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B369" s="2">
         <f t="shared" si="5"/>
         <v>365</v>
@@ -8708,7 +8709,7 @@
       </c>
       <c r="F369" s="3"/>
     </row>
-    <row r="370" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="370" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B370" s="2">
         <f t="shared" si="5"/>
         <v>366</v>
@@ -8724,7 +8725,7 @@
       </c>
       <c r="F370" s="3"/>
     </row>
-    <row r="371" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B371" s="2">
         <f t="shared" si="5"/>
         <v>367</v>
@@ -8740,7 +8741,7 @@
       </c>
       <c r="F371" s="3"/>
     </row>
-    <row r="372" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="372" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B372" s="2">
         <f t="shared" si="5"/>
         <v>368</v>
@@ -8756,7 +8757,7 @@
       </c>
       <c r="F372" s="3"/>
     </row>
-    <row r="373" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="373" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B373" s="2">
         <f t="shared" si="5"/>
         <v>369</v>
@@ -8772,7 +8773,7 @@
       </c>
       <c r="F373" s="3"/>
     </row>
-    <row r="374" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="374" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B374" s="2">
         <f t="shared" si="5"/>
         <v>370</v>
@@ -8788,7 +8789,7 @@
       </c>
       <c r="F374" s="3"/>
     </row>
-    <row r="375" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="375" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B375" s="2">
         <f t="shared" si="5"/>
         <v>371</v>
@@ -8804,7 +8805,7 @@
       </c>
       <c r="F375" s="3"/>
     </row>
-    <row r="376" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B376" s="2">
         <f t="shared" si="5"/>
         <v>372</v>
@@ -8820,7 +8821,7 @@
       </c>
       <c r="F376" s="3"/>
     </row>
-    <row r="377" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="377" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B377" s="2">
         <f t="shared" si="5"/>
         <v>373</v>
@@ -8836,7 +8837,7 @@
       </c>
       <c r="F377" s="3"/>
     </row>
-    <row r="378" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="378" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B378" s="2">
         <f t="shared" si="5"/>
         <v>374</v>
@@ -8852,7 +8853,7 @@
       </c>
       <c r="F378" s="3"/>
     </row>
-    <row r="379" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="379" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B379" s="2">
         <f t="shared" si="5"/>
         <v>375</v>
@@ -8868,7 +8869,7 @@
       </c>
       <c r="F379" s="3"/>
     </row>
-    <row r="380" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="380" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B380" s="2">
         <f t="shared" si="5"/>
         <v>376</v>
@@ -8884,7 +8885,7 @@
       </c>
       <c r="F380" s="3"/>
     </row>
-    <row r="381" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="381" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B381" s="2">
         <f t="shared" si="5"/>
         <v>377</v>
@@ -8900,7 +8901,7 @@
       </c>
       <c r="F381" s="3"/>
     </row>
-    <row r="382" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="382" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B382" s="2">
         <f t="shared" si="5"/>
         <v>378</v>
@@ -8916,7 +8917,7 @@
       </c>
       <c r="F382" s="3"/>
     </row>
-    <row r="383" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="383" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B383" s="2">
         <f t="shared" si="5"/>
         <v>379</v>
@@ -8932,7 +8933,7 @@
       </c>
       <c r="F383" s="3"/>
     </row>
-    <row r="384" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B384" s="2">
         <f t="shared" si="5"/>
         <v>380</v>
@@ -8948,7 +8949,7 @@
       </c>
       <c r="F384" s="3"/>
     </row>
-    <row r="385" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B385" s="2">
         <f t="shared" si="5"/>
         <v>381</v>
@@ -8964,7 +8965,7 @@
       </c>
       <c r="F385" s="3"/>
     </row>
-    <row r="386" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B386" s="2">
         <f t="shared" si="5"/>
         <v>382</v>
@@ -8980,7 +8981,7 @@
       </c>
       <c r="F386" s="3"/>
     </row>
-    <row r="387" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B387" s="2">
         <f t="shared" si="5"/>
         <v>383</v>
@@ -8996,7 +8997,7 @@
       </c>
       <c r="F387" s="3"/>
     </row>
-    <row r="388" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B388" s="2">
         <f t="shared" si="5"/>
         <v>384</v>
@@ -9012,7 +9013,7 @@
       </c>
       <c r="F388" s="3"/>
     </row>
-    <row r="389" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B389" s="2">
         <f t="shared" si="5"/>
         <v>385</v>
@@ -9028,7 +9029,7 @@
       </c>
       <c r="F389" s="3"/>
     </row>
-    <row r="390" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B390" s="2">
         <f t="shared" si="5"/>
         <v>386</v>
@@ -9044,7 +9045,7 @@
       </c>
       <c r="F390" s="3"/>
     </row>
-    <row r="391" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B391" s="2">
         <f t="shared" si="5"/>
         <v>387</v>
@@ -9060,7 +9061,7 @@
       </c>
       <c r="F391" s="3"/>
     </row>
-    <row r="392" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B392" s="2">
         <f t="shared" si="5"/>
         <v>388</v>
@@ -9076,7 +9077,7 @@
       </c>
       <c r="F392" s="3"/>
     </row>
-    <row r="393" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B393" s="2">
         <f t="shared" si="5"/>
         <v>389</v>
@@ -9092,7 +9093,7 @@
       </c>
       <c r="F393" s="3"/>
     </row>
-    <row r="394" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B394" s="2">
         <f t="shared" ref="B394:B457" si="6">B393+1</f>
         <v>390</v>
@@ -9108,7 +9109,7 @@
       </c>
       <c r="F394" s="3"/>
     </row>
-    <row r="395" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B395" s="2">
         <f t="shared" si="6"/>
         <v>391</v>
@@ -9124,7 +9125,7 @@
       </c>
       <c r="F395" s="3"/>
     </row>
-    <row r="396" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B396" s="2">
         <f t="shared" si="6"/>
         <v>392</v>
@@ -9140,7 +9141,7 @@
       </c>
       <c r="F396" s="3"/>
     </row>
-    <row r="397" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B397" s="2">
         <f t="shared" si="6"/>
         <v>393</v>
@@ -9156,7 +9157,7 @@
       </c>
       <c r="F397" s="3"/>
     </row>
-    <row r="398" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B398" s="2">
         <f t="shared" si="6"/>
         <v>394</v>
@@ -9172,7 +9173,7 @@
       </c>
       <c r="F398" s="3"/>
     </row>
-    <row r="399" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B399" s="2">
         <f t="shared" si="6"/>
         <v>395</v>
@@ -9188,7 +9189,7 @@
       </c>
       <c r="F399" s="3"/>
     </row>
-    <row r="400" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B400" s="2">
         <f t="shared" si="6"/>
         <v>396</v>
@@ -9204,7 +9205,7 @@
       </c>
       <c r="F400" s="3"/>
     </row>
-    <row r="401" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B401" s="2">
         <f t="shared" si="6"/>
         <v>397</v>
@@ -9220,7 +9221,7 @@
       </c>
       <c r="F401" s="3"/>
     </row>
-    <row r="402" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B402" s="2">
         <f t="shared" si="6"/>
         <v>398</v>
@@ -9236,7 +9237,7 @@
       </c>
       <c r="F402" s="3"/>
     </row>
-    <row r="403" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B403" s="2">
         <f t="shared" si="6"/>
         <v>399</v>
@@ -9252,7 +9253,7 @@
       </c>
       <c r="F403" s="3"/>
     </row>
-    <row r="404" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B404" s="2">
         <f t="shared" si="6"/>
         <v>400</v>
@@ -9268,7 +9269,7 @@
       </c>
       <c r="F404" s="3"/>
     </row>
-    <row r="405" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B405" s="2">
         <f t="shared" si="6"/>
         <v>401</v>
@@ -9284,7 +9285,7 @@
       </c>
       <c r="F405" s="3"/>
     </row>
-    <row r="406" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B406" s="2">
         <f t="shared" si="6"/>
         <v>402</v>
@@ -9300,7 +9301,7 @@
       </c>
       <c r="F406" s="3"/>
     </row>
-    <row r="407" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B407" s="2">
         <f t="shared" si="6"/>
         <v>403</v>
@@ -9316,7 +9317,7 @@
       </c>
       <c r="F407" s="3"/>
     </row>
-    <row r="408" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B408" s="2">
         <f t="shared" si="6"/>
         <v>404</v>
@@ -9332,7 +9333,7 @@
       </c>
       <c r="F408" s="3"/>
     </row>
-    <row r="409" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B409" s="2">
         <f t="shared" si="6"/>
         <v>405</v>
@@ -9348,7 +9349,7 @@
       </c>
       <c r="F409" s="3"/>
     </row>
-    <row r="410" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B410" s="2">
         <f t="shared" si="6"/>
         <v>406</v>
@@ -9364,7 +9365,7 @@
       </c>
       <c r="F410" s="3"/>
     </row>
-    <row r="411" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B411" s="2">
         <f t="shared" si="6"/>
         <v>407</v>
@@ -9380,7 +9381,7 @@
       </c>
       <c r="F411" s="3"/>
     </row>
-    <row r="412" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B412" s="2">
         <f t="shared" si="6"/>
         <v>408</v>
@@ -9396,7 +9397,7 @@
       </c>
       <c r="F412" s="3"/>
     </row>
-    <row r="413" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B413" s="2">
         <f t="shared" si="6"/>
         <v>409</v>
@@ -9412,7 +9413,7 @@
       </c>
       <c r="F413" s="3"/>
     </row>
-    <row r="414" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B414" s="2">
         <f t="shared" si="6"/>
         <v>410</v>
@@ -9428,7 +9429,7 @@
       </c>
       <c r="F414" s="3"/>
     </row>
-    <row r="415" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B415" s="2">
         <f t="shared" si="6"/>
         <v>411</v>
@@ -9444,7 +9445,7 @@
       </c>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B416" s="2">
         <f t="shared" si="6"/>
         <v>412</v>
@@ -9460,7 +9461,7 @@
       </c>
       <c r="F416" s="3"/>
     </row>
-    <row r="417" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B417" s="2">
         <f t="shared" si="6"/>
         <v>413</v>
@@ -9476,7 +9477,7 @@
       </c>
       <c r="F417" s="3"/>
     </row>
-    <row r="418" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B418" s="2">
         <f t="shared" si="6"/>
         <v>414</v>
@@ -9492,7 +9493,7 @@
       </c>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B419" s="2">
         <f t="shared" si="6"/>
         <v>415</v>
@@ -9508,7 +9509,7 @@
       </c>
       <c r="F419" s="3"/>
     </row>
-    <row r="420" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B420" s="2">
         <f t="shared" si="6"/>
         <v>416</v>
@@ -9524,7 +9525,7 @@
       </c>
       <c r="F420" s="3"/>
     </row>
-    <row r="421" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B421" s="2">
         <f t="shared" si="6"/>
         <v>417</v>
@@ -9540,7 +9541,7 @@
       </c>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B422" s="2">
         <f t="shared" si="6"/>
         <v>418</v>
@@ -9556,7 +9557,7 @@
       </c>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B423" s="2">
         <f t="shared" si="6"/>
         <v>419</v>
@@ -9572,7 +9573,7 @@
       </c>
       <c r="F423" s="3"/>
     </row>
-    <row r="424" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B424" s="2">
         <f t="shared" si="6"/>
         <v>420</v>
@@ -9588,7 +9589,7 @@
       </c>
       <c r="F424" s="3"/>
     </row>
-    <row r="425" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B425" s="2">
         <f t="shared" si="6"/>
         <v>421</v>
@@ -9604,7 +9605,7 @@
       </c>
       <c r="F425" s="3"/>
     </row>
-    <row r="426" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B426" s="2">
         <f t="shared" si="6"/>
         <v>422</v>
@@ -9620,7 +9621,7 @@
       </c>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
@@ -9636,7 +9637,7 @@
       </c>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B428" s="2">
         <f t="shared" si="6"/>
         <v>424</v>
@@ -9652,7 +9653,7 @@
       </c>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B429" s="2">
         <f t="shared" si="6"/>
         <v>425</v>
@@ -9668,13 +9669,13 @@
       </c>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B430" s="2">
         <f t="shared" si="6"/>
         <v>426</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D430" s="2" t="s">
         <v>521</v>
@@ -9684,7 +9685,7 @@
       </c>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B431" s="2">
         <f t="shared" si="6"/>
         <v>427</v>
@@ -9700,7 +9701,7 @@
       </c>
       <c r="F431" s="3"/>
     </row>
-    <row r="432" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B432" s="2">
         <f t="shared" si="6"/>
         <v>428</v>
@@ -9716,7 +9717,7 @@
       </c>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B433" s="2">
         <f t="shared" si="6"/>
         <v>429</v>
@@ -9732,7 +9733,7 @@
       </c>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B434" s="2">
         <f t="shared" si="6"/>
         <v>430</v>
@@ -9748,7 +9749,7 @@
       </c>
       <c r="F434" s="3"/>
     </row>
-    <row r="435" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B435" s="2">
         <f t="shared" si="6"/>
         <v>431</v>
@@ -9764,7 +9765,7 @@
       </c>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B436" s="2">
         <f t="shared" si="6"/>
         <v>432</v>
@@ -9780,7 +9781,7 @@
       </c>
       <c r="F436" s="3"/>
     </row>
-    <row r="437" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B437" s="2">
         <f t="shared" si="6"/>
         <v>433</v>
@@ -9796,7 +9797,7 @@
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B438" s="2">
         <f t="shared" si="6"/>
         <v>434</v>
@@ -9812,7 +9813,7 @@
       </c>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B439" s="2">
         <f t="shared" si="6"/>
         <v>435</v>
@@ -9828,7 +9829,7 @@
       </c>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B440" s="2">
         <f t="shared" si="6"/>
         <v>436</v>
@@ -9844,7 +9845,7 @@
       </c>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B441" s="2">
         <f t="shared" si="6"/>
         <v>437</v>
@@ -9860,7 +9861,7 @@
       </c>
       <c r="F441" s="3"/>
     </row>
-    <row r="442" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B442" s="2">
         <f t="shared" si="6"/>
         <v>438</v>
@@ -9876,7 +9877,7 @@
       </c>
       <c r="F442" s="3"/>
     </row>
-    <row r="443" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="443" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B443" s="2">
         <f t="shared" si="6"/>
         <v>439</v>
@@ -9892,7 +9893,7 @@
       </c>
       <c r="F443" s="3"/>
     </row>
-    <row r="444" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="444" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B444" s="2">
         <f t="shared" si="6"/>
         <v>440</v>
@@ -9908,7 +9909,7 @@
       </c>
       <c r="F444" s="3"/>
     </row>
-    <row r="445" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B445" s="2">
         <f t="shared" si="6"/>
         <v>441</v>
@@ -9924,7 +9925,7 @@
       </c>
       <c r="F445" s="3"/>
     </row>
-    <row r="446" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="446" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B446" s="2">
         <f t="shared" si="6"/>
         <v>442</v>
@@ -9940,7 +9941,7 @@
       </c>
       <c r="F446" s="3"/>
     </row>
-    <row r="447" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="447" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B447" s="2">
         <f t="shared" si="6"/>
         <v>443</v>
@@ -9956,7 +9957,7 @@
       </c>
       <c r="F447" s="3"/>
     </row>
-    <row r="448" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="448" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B448" s="2">
         <f t="shared" si="6"/>
         <v>444</v>
@@ -9972,7 +9973,7 @@
       </c>
       <c r="F448" s="3"/>
     </row>
-    <row r="449" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="449" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B449" s="2">
         <f t="shared" si="6"/>
         <v>445</v>
@@ -9988,7 +9989,7 @@
       </c>
       <c r="F449" s="3"/>
     </row>
-    <row r="450" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="450" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B450" s="2">
         <f t="shared" si="6"/>
         <v>446</v>
@@ -10004,7 +10005,7 @@
       </c>
       <c r="F450" s="3"/>
     </row>
-    <row r="451" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="451" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B451" s="2">
         <f t="shared" si="6"/>
         <v>447</v>
@@ -10020,7 +10021,7 @@
       </c>
       <c r="F451" s="3"/>
     </row>
-    <row r="452" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="452" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B452" s="2">
         <f t="shared" si="6"/>
         <v>448</v>
@@ -10036,7 +10037,7 @@
       </c>
       <c r="F452" s="3"/>
     </row>
-    <row r="453" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="453" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B453" s="2">
         <f t="shared" si="6"/>
         <v>449</v>
@@ -10052,7 +10053,7 @@
       </c>
       <c r="F453" s="3"/>
     </row>
-    <row r="454" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="454" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B454" s="2">
         <f t="shared" si="6"/>
         <v>450</v>
@@ -10068,7 +10069,7 @@
       </c>
       <c r="F454" s="3"/>
     </row>
-    <row r="455" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="455" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B455" s="2">
         <f t="shared" si="6"/>
         <v>451</v>
@@ -10084,7 +10085,7 @@
       </c>
       <c r="F455" s="3"/>
     </row>
-    <row r="456" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="456" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B456" s="2">
         <f t="shared" si="6"/>
         <v>452</v>
@@ -10100,7 +10101,7 @@
       </c>
       <c r="F456" s="3"/>
     </row>
-    <row r="457" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="457" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B457" s="2">
         <f t="shared" si="6"/>
         <v>453</v>
@@ -10116,7 +10117,7 @@
       </c>
       <c r="F457" s="3"/>
     </row>
-    <row r="458" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="458" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B458" s="2">
         <f t="shared" ref="B458:B521" si="7">B457+1</f>
         <v>454</v>
@@ -10132,7 +10133,7 @@
       </c>
       <c r="F458" s="3"/>
     </row>
-    <row r="459" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="459" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B459" s="2">
         <f t="shared" si="7"/>
         <v>455</v>
@@ -10148,7 +10149,7 @@
       </c>
       <c r="F459" s="3"/>
     </row>
-    <row r="460" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="460" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B460" s="2">
         <f t="shared" si="7"/>
         <v>456</v>
@@ -10164,7 +10165,7 @@
       </c>
       <c r="F460" s="3"/>
     </row>
-    <row r="461" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="461" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B461" s="2">
         <f t="shared" si="7"/>
         <v>457</v>
@@ -10180,7 +10181,7 @@
       </c>
       <c r="F461" s="3"/>
     </row>
-    <row r="462" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="462" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B462" s="2">
         <f t="shared" si="7"/>
         <v>458</v>
@@ -10196,7 +10197,7 @@
       </c>
       <c r="F462" s="3"/>
     </row>
-    <row r="463" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="463" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B463" s="2">
         <f t="shared" si="7"/>
         <v>459</v>
@@ -10212,7 +10213,7 @@
       </c>
       <c r="F463" s="3"/>
     </row>
-    <row r="464" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="464" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B464" s="2">
         <f t="shared" si="7"/>
         <v>460</v>
@@ -10228,7 +10229,7 @@
       </c>
       <c r="F464" s="3"/>
     </row>
-    <row r="465" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="465" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B465" s="2">
         <f t="shared" si="7"/>
         <v>461</v>
@@ -10244,7 +10245,7 @@
       </c>
       <c r="F465" s="3"/>
     </row>
-    <row r="466" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="466" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B466" s="2">
         <f t="shared" si="7"/>
         <v>462</v>
@@ -10276,7 +10277,7 @@
       </c>
       <c r="F467" s="3"/>
     </row>
-    <row r="468" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="468" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B468" s="2">
         <f t="shared" si="7"/>
         <v>464</v>
@@ -10292,7 +10293,7 @@
       </c>
       <c r="F468" s="3"/>
     </row>
-    <row r="469" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="469" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B469" s="2">
         <f t="shared" si="7"/>
         <v>465</v>
@@ -10308,7 +10309,7 @@
       </c>
       <c r="F469" s="3"/>
     </row>
-    <row r="470" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="470" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B470" s="2">
         <f t="shared" si="7"/>
         <v>466</v>
@@ -10324,7 +10325,7 @@
       </c>
       <c r="F470" s="3"/>
     </row>
-    <row r="471" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="471" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B471" s="2">
         <f t="shared" si="7"/>
         <v>467</v>
@@ -10340,7 +10341,7 @@
       </c>
       <c r="F471" s="3"/>
     </row>
-    <row r="472" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="472" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B472" s="2">
         <f t="shared" si="7"/>
         <v>468</v>
@@ -10356,7 +10357,7 @@
       </c>
       <c r="F472" s="3"/>
     </row>
-    <row r="473" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="473" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B473" s="2">
         <f t="shared" si="7"/>
         <v>469</v>
@@ -10372,7 +10373,7 @@
       </c>
       <c r="F473" s="3"/>
     </row>
-    <row r="474" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="474" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B474" s="2">
         <f t="shared" si="7"/>
         <v>470</v>
@@ -10388,7 +10389,7 @@
       </c>
       <c r="F474" s="3"/>
     </row>
-    <row r="475" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="475" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B475" s="2">
         <f t="shared" si="7"/>
         <v>471</v>
@@ -10404,7 +10405,7 @@
       </c>
       <c r="F475" s="3"/>
     </row>
-    <row r="476" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="476" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B476" s="2">
         <f t="shared" si="7"/>
         <v>472</v>
@@ -10420,7 +10421,7 @@
       </c>
       <c r="F476" s="3"/>
     </row>
-    <row r="477" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="477" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B477" s="2">
         <f t="shared" si="7"/>
         <v>473</v>
@@ -10436,7 +10437,7 @@
       </c>
       <c r="F477" s="3"/>
     </row>
-    <row r="478" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="478" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B478" s="2">
         <f t="shared" si="7"/>
         <v>474</v>
@@ -10452,7 +10453,7 @@
       </c>
       <c r="F478" s="3"/>
     </row>
-    <row r="479" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="479" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B479" s="2">
         <f t="shared" si="7"/>
         <v>475</v>
@@ -10468,7 +10469,7 @@
       </c>
       <c r="F479" s="3"/>
     </row>
-    <row r="480" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="480" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B480" s="2">
         <f t="shared" si="7"/>
         <v>476</v>
@@ -10484,7 +10485,7 @@
       </c>
       <c r="F480" s="3"/>
     </row>
-    <row r="481" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="481" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B481" s="2">
         <f t="shared" si="7"/>
         <v>477</v>
@@ -10500,7 +10501,7 @@
       </c>
       <c r="F481" s="3"/>
     </row>
-    <row r="482" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="482" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B482" s="2">
         <f t="shared" si="7"/>
         <v>478</v>
@@ -10516,7 +10517,7 @@
       </c>
       <c r="F482" s="3"/>
     </row>
-    <row r="483" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="483" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B483" s="2">
         <f t="shared" si="7"/>
         <v>479</v>
@@ -10532,7 +10533,7 @@
       </c>
       <c r="F483" s="3"/>
     </row>
-    <row r="484" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="484" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B484" s="2">
         <f t="shared" si="7"/>
         <v>480</v>
@@ -10548,7 +10549,7 @@
       </c>
       <c r="F484" s="3"/>
     </row>
-    <row r="485" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="485" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B485" s="2">
         <f t="shared" si="7"/>
         <v>481</v>
@@ -10564,7 +10565,7 @@
       </c>
       <c r="F485" s="3"/>
     </row>
-    <row r="486" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="486" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B486" s="2">
         <f t="shared" si="7"/>
         <v>482</v>
@@ -10580,7 +10581,7 @@
       </c>
       <c r="F486" s="3"/>
     </row>
-    <row r="487" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="487" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B487" s="2">
         <f t="shared" si="7"/>
         <v>483</v>
@@ -10596,7 +10597,7 @@
       </c>
       <c r="F487" s="3"/>
     </row>
-    <row r="488" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="488" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B488" s="2">
         <f t="shared" si="7"/>
         <v>484</v>
@@ -10612,7 +10613,7 @@
       </c>
       <c r="F488" s="3"/>
     </row>
-    <row r="489" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="489" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B489" s="2">
         <f t="shared" si="7"/>
         <v>485</v>
@@ -10628,7 +10629,7 @@
       </c>
       <c r="F489" s="3"/>
     </row>
-    <row r="490" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="490" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B490" s="2">
         <f t="shared" si="7"/>
         <v>486</v>
@@ -10644,7 +10645,7 @@
       </c>
       <c r="F490" s="3"/>
     </row>
-    <row r="491" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="491" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B491" s="2">
         <f t="shared" si="7"/>
         <v>487</v>
@@ -10660,7 +10661,7 @@
       </c>
       <c r="F491" s="3"/>
     </row>
-    <row r="492" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="492" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B492" s="2">
         <f t="shared" si="7"/>
         <v>488</v>
@@ -10676,7 +10677,7 @@
       </c>
       <c r="F492" s="3"/>
     </row>
-    <row r="493" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="493" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B493" s="2">
         <f t="shared" si="7"/>
         <v>489</v>
@@ -10692,7 +10693,7 @@
       </c>
       <c r="F493" s="3"/>
     </row>
-    <row r="494" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="494" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B494" s="2">
         <f t="shared" si="7"/>
         <v>490</v>
@@ -10708,7 +10709,7 @@
       </c>
       <c r="F494" s="3"/>
     </row>
-    <row r="495" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="495" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B495" s="2">
         <f t="shared" si="7"/>
         <v>491</v>
@@ -10724,7 +10725,7 @@
       </c>
       <c r="F495" s="3"/>
     </row>
-    <row r="496" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="496" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B496" s="2">
         <f t="shared" si="7"/>
         <v>492</v>
@@ -10740,7 +10741,7 @@
       </c>
       <c r="F496" s="3"/>
     </row>
-    <row r="497" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="497" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B497" s="2">
         <f t="shared" si="7"/>
         <v>493</v>
@@ -10756,7 +10757,7 @@
       </c>
       <c r="F497" s="3"/>
     </row>
-    <row r="498" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="498" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B498" s="2">
         <f t="shared" si="7"/>
         <v>494</v>
@@ -10772,7 +10773,7 @@
       </c>
       <c r="F498" s="3"/>
     </row>
-    <row r="499" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="499" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B499" s="2">
         <f t="shared" si="7"/>
         <v>495</v>
@@ -10788,7 +10789,7 @@
       </c>
       <c r="F499" s="3"/>
     </row>
-    <row r="500" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="500" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B500" s="2">
         <f t="shared" si="7"/>
         <v>496</v>
@@ -10804,7 +10805,7 @@
       </c>
       <c r="F500" s="3"/>
     </row>
-    <row r="501" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="501" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B501" s="2">
         <f t="shared" si="7"/>
         <v>497</v>
@@ -10820,7 +10821,7 @@
       </c>
       <c r="F501" s="3"/>
     </row>
-    <row r="502" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="502" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B502" s="2">
         <f t="shared" si="7"/>
         <v>498</v>
@@ -10836,7 +10837,7 @@
       </c>
       <c r="F502" s="3"/>
     </row>
-    <row r="503" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="503" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B503" s="2">
         <f t="shared" si="7"/>
         <v>499</v>
@@ -10852,7 +10853,7 @@
       </c>
       <c r="F503" s="3"/>
     </row>
-    <row r="504" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="504" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B504" s="2">
         <f t="shared" si="7"/>
         <v>500</v>
@@ -10868,7 +10869,7 @@
       </c>
       <c r="F504" s="3"/>
     </row>
-    <row r="505" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="505" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B505" s="2">
         <f t="shared" si="7"/>
         <v>501</v>
@@ -10884,13 +10885,13 @@
       </c>
       <c r="F505" s="3"/>
     </row>
-    <row r="506" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="506" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B506" s="2">
         <f t="shared" si="7"/>
         <v>502</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D506" s="2" t="s">
         <v>638</v>
@@ -10900,7 +10901,7 @@
       </c>
       <c r="F506" s="3"/>
     </row>
-    <row r="507" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="507" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B507" s="2">
         <f t="shared" si="7"/>
         <v>503</v>
@@ -10916,7 +10917,7 @@
       </c>
       <c r="F507" s="3"/>
     </row>
-    <row r="508" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="508" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B508" s="2">
         <f t="shared" si="7"/>
         <v>504</v>
@@ -10932,7 +10933,7 @@
       </c>
       <c r="F508" s="3"/>
     </row>
-    <row r="509" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="509" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B509" s="2">
         <f t="shared" si="7"/>
         <v>505</v>
@@ -10948,7 +10949,7 @@
       </c>
       <c r="F509" s="3"/>
     </row>
-    <row r="510" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="510" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B510" s="2">
         <f t="shared" si="7"/>
         <v>506</v>
@@ -10964,7 +10965,7 @@
       </c>
       <c r="F510" s="3"/>
     </row>
-    <row r="511" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="511" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B511" s="2">
         <f t="shared" si="7"/>
         <v>507</v>
@@ -10980,7 +10981,7 @@
       </c>
       <c r="F511" s="3"/>
     </row>
-    <row r="512" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="512" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B512" s="2">
         <f t="shared" si="7"/>
         <v>508</v>
@@ -10996,7 +10997,7 @@
       </c>
       <c r="F512" s="3"/>
     </row>
-    <row r="513" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="513" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B513" s="2">
         <f t="shared" si="7"/>
         <v>509</v>
@@ -11012,7 +11013,7 @@
       </c>
       <c r="F513" s="3"/>
     </row>
-    <row r="514" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="514" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B514" s="2">
         <f t="shared" si="7"/>
         <v>510</v>
@@ -11028,7 +11029,7 @@
       </c>
       <c r="F514" s="3"/>
     </row>
-    <row r="515" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="515" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B515" s="2">
         <f t="shared" si="7"/>
         <v>511</v>
@@ -11044,7 +11045,7 @@
       </c>
       <c r="F515" s="3"/>
     </row>
-    <row r="516" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="516" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B516" s="2">
         <f t="shared" si="7"/>
         <v>512</v>
@@ -11060,7 +11061,7 @@
       </c>
       <c r="F516" s="3"/>
     </row>
-    <row r="517" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="517" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B517" s="2">
         <f t="shared" si="7"/>
         <v>513</v>
@@ -11076,7 +11077,7 @@
       </c>
       <c r="F517" s="3"/>
     </row>
-    <row r="518" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="518" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B518" s="2">
         <f t="shared" si="7"/>
         <v>514</v>
@@ -11092,7 +11093,7 @@
       </c>
       <c r="F518" s="3"/>
     </row>
-    <row r="519" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="519" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B519" s="2">
         <f t="shared" si="7"/>
         <v>515</v>
@@ -11108,7 +11109,7 @@
       </c>
       <c r="F519" s="3"/>
     </row>
-    <row r="520" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="520" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B520" s="2">
         <f t="shared" si="7"/>
         <v>516</v>
@@ -11124,7 +11125,7 @@
       </c>
       <c r="F520" s="3"/>
     </row>
-    <row r="521" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="521" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B521" s="2">
         <f t="shared" si="7"/>
         <v>517</v>
@@ -11140,7 +11141,7 @@
       </c>
       <c r="F521" s="3"/>
     </row>
-    <row r="522" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="522" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B522" s="2">
         <f t="shared" ref="B522:B585" si="8">B521+1</f>
         <v>518</v>
@@ -11156,7 +11157,7 @@
       </c>
       <c r="F522" s="3"/>
     </row>
-    <row r="523" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="523" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B523" s="2">
         <f t="shared" si="8"/>
         <v>519</v>
@@ -11172,7 +11173,7 @@
       </c>
       <c r="F523" s="3"/>
     </row>
-    <row r="524" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="524" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B524" s="2">
         <f t="shared" si="8"/>
         <v>520</v>
@@ -11188,7 +11189,7 @@
       </c>
       <c r="F524" s="3"/>
     </row>
-    <row r="525" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="525" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B525" s="2">
         <f t="shared" si="8"/>
         <v>521</v>
@@ -11204,7 +11205,7 @@
       </c>
       <c r="F525" s="3"/>
     </row>
-    <row r="526" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="526" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B526" s="2">
         <f t="shared" si="8"/>
         <v>522</v>
@@ -11220,7 +11221,7 @@
       </c>
       <c r="F526" s="3"/>
     </row>
-    <row r="527" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="527" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B527" s="2">
         <f t="shared" si="8"/>
         <v>523</v>
@@ -11236,7 +11237,7 @@
       </c>
       <c r="F527" s="3"/>
     </row>
-    <row r="528" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="528" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B528" s="2">
         <f t="shared" si="8"/>
         <v>524</v>
@@ -11252,7 +11253,7 @@
       </c>
       <c r="F528" s="3"/>
     </row>
-    <row r="529" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="529" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B529" s="2">
         <f t="shared" si="8"/>
         <v>525</v>
@@ -11268,7 +11269,7 @@
       </c>
       <c r="F529" s="3"/>
     </row>
-    <row r="530" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="530" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B530" s="2">
         <f t="shared" si="8"/>
         <v>526</v>
@@ -11284,7 +11285,7 @@
       </c>
       <c r="F530" s="3"/>
     </row>
-    <row r="531" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="531" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B531" s="2">
         <f t="shared" si="8"/>
         <v>527</v>
@@ -11300,7 +11301,7 @@
       </c>
       <c r="F531" s="3"/>
     </row>
-    <row r="532" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="532" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B532" s="2">
         <f t="shared" si="8"/>
         <v>528</v>
@@ -11312,11 +11313,11 @@
         <v>686</v>
       </c>
       <c r="E532" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="F532" s="3"/>
     </row>
-    <row r="533" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="533" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B533" s="2">
         <f t="shared" si="8"/>
         <v>529</v>
@@ -11332,7 +11333,7 @@
       </c>
       <c r="F533" s="3"/>
     </row>
-    <row r="534" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="534" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B534" s="2">
         <f t="shared" si="8"/>
         <v>530</v>
@@ -11348,7 +11349,7 @@
       </c>
       <c r="F534" s="3"/>
     </row>
-    <row r="535" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="535" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B535" s="2">
         <f t="shared" si="8"/>
         <v>531</v>
@@ -11364,7 +11365,7 @@
       </c>
       <c r="F535" s="3"/>
     </row>
-    <row r="536" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="536" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B536" s="2">
         <f t="shared" si="8"/>
         <v>532</v>
@@ -11380,7 +11381,7 @@
       </c>
       <c r="F536" s="3"/>
     </row>
-    <row r="537" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="537" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B537" s="2">
         <f t="shared" si="8"/>
         <v>533</v>
@@ -11396,7 +11397,7 @@
       </c>
       <c r="F537" s="3"/>
     </row>
-    <row r="538" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="538" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B538" s="2">
         <f t="shared" si="8"/>
         <v>534</v>
@@ -11412,7 +11413,7 @@
       </c>
       <c r="F538" s="3"/>
     </row>
-    <row r="539" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="539" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B539" s="2">
         <f t="shared" si="8"/>
         <v>535</v>
@@ -11428,7 +11429,7 @@
       </c>
       <c r="F539" s="3"/>
     </row>
-    <row r="540" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="540" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B540" s="2">
         <f t="shared" si="8"/>
         <v>536</v>
@@ -11444,7 +11445,7 @@
       </c>
       <c r="F540" s="3"/>
     </row>
-    <row r="541" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="541" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B541" s="2">
         <f t="shared" si="8"/>
         <v>537</v>
@@ -11460,7 +11461,7 @@
       </c>
       <c r="F541" s="3"/>
     </row>
-    <row r="542" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="542" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B542" s="2">
         <f t="shared" si="8"/>
         <v>538</v>
@@ -11476,7 +11477,7 @@
       </c>
       <c r="F542" s="3"/>
     </row>
-    <row r="543" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="543" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B543" s="2">
         <f t="shared" si="8"/>
         <v>539</v>
@@ -11492,7 +11493,7 @@
       </c>
       <c r="F543" s="3"/>
     </row>
-    <row r="544" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="544" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B544" s="2">
         <f t="shared" si="8"/>
         <v>540</v>
@@ -11508,7 +11509,7 @@
       </c>
       <c r="F544" s="3"/>
     </row>
-    <row r="545" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="545" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B545" s="2">
         <f t="shared" si="8"/>
         <v>541</v>
@@ -11524,7 +11525,7 @@
       </c>
       <c r="F545" s="3"/>
     </row>
-    <row r="546" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="546" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B546" s="2">
         <f t="shared" si="8"/>
         <v>542</v>
@@ -11540,7 +11541,7 @@
       </c>
       <c r="F546" s="3"/>
     </row>
-    <row r="547" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="547" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B547" s="2">
         <f t="shared" si="8"/>
         <v>543</v>
@@ -11556,7 +11557,7 @@
       </c>
       <c r="F547" s="3"/>
     </row>
-    <row r="548" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="548" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B548" s="2">
         <f t="shared" si="8"/>
         <v>544</v>
@@ -11578,10 +11579,10 @@
         <v>545</v>
       </c>
       <c r="C549" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="D549" s="2" t="s">
         <v>711</v>
-      </c>
-      <c r="D549" s="2" t="s">
-        <v>712</v>
       </c>
       <c r="E549" s="1" t="s">
         <v>5</v>
@@ -11594,10 +11595,10 @@
         <v>546</v>
       </c>
       <c r="C550" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="D550" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="D550" s="2" t="s">
-        <v>714</v>
       </c>
       <c r="E550" s="1" t="s">
         <v>5</v>
@@ -11610,7 +11611,7 @@
         <v>547</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>715</v>
+        <v>805</v>
       </c>
       <c r="D551" s="2" t="s">
         <v>584</v>
@@ -11626,10 +11627,10 @@
         <v>548</v>
       </c>
       <c r="C552" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D552" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="E552" s="1" t="s">
         <v>5</v>
@@ -11642,119 +11643,119 @@
         <v>549</v>
       </c>
       <c r="C553" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D553" s="2" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="E553" s="13" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F553" s="3"/>
     </row>
-    <row r="554" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="554" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B554" s="2">
         <f t="shared" si="8"/>
         <v>550</v>
       </c>
       <c r="C554" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D554" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E554" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F554" s="3"/>
     </row>
-    <row r="555" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="555" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B555" s="2">
         <f t="shared" si="8"/>
         <v>551</v>
       </c>
       <c r="C555" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D555" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="E555" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F555" s="3"/>
     </row>
-    <row r="556" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="556" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B556" s="2">
         <f t="shared" si="8"/>
         <v>552</v>
       </c>
       <c r="C556" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D556" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="E556" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F556" s="3"/>
     </row>
-    <row r="557" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="557" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B557" s="2">
         <f t="shared" si="8"/>
         <v>553</v>
       </c>
       <c r="C557" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D557" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E557" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F557" s="3"/>
     </row>
-    <row r="558" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="558" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B558" s="2">
         <f t="shared" si="8"/>
         <v>554</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E558" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F558" s="3"/>
     </row>
-    <row r="559" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="559" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B559" s="2">
         <f t="shared" si="8"/>
         <v>555</v>
       </c>
       <c r="C559" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F559" s="3"/>
     </row>
-    <row r="560" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="560" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B560" s="2">
         <f t="shared" si="8"/>
         <v>556</v>
       </c>
       <c r="C560" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D560" s="2" t="s">
         <v>161</v>
@@ -11764,675 +11765,675 @@
       </c>
       <c r="F560" s="3"/>
     </row>
-    <row r="561" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="561" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B561" s="2">
         <f t="shared" si="8"/>
         <v>557</v>
       </c>
       <c r="C561" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D561" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F561" s="3"/>
     </row>
-    <row r="562" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="562" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B562" s="2">
         <f t="shared" si="8"/>
         <v>558</v>
       </c>
       <c r="C562" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D562" s="2" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E562" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F562" s="3"/>
     </row>
-    <row r="563" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="563" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B563" s="2">
         <f t="shared" si="8"/>
         <v>559</v>
       </c>
       <c r="C563" s="1" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D563" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E563" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F563" s="3"/>
     </row>
-    <row r="564" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="564" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B564" s="2">
         <f t="shared" si="8"/>
         <v>560</v>
       </c>
       <c r="C564" s="1" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E564" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F564" s="3"/>
     </row>
-    <row r="565" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="565" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B565" s="2">
         <f t="shared" si="8"/>
         <v>561</v>
       </c>
       <c r="C565" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E565" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F565" s="3"/>
     </row>
-    <row r="566" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="566" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B566" s="2">
         <f t="shared" si="8"/>
         <v>562</v>
       </c>
       <c r="C566" s="1" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E566" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F566" s="3"/>
     </row>
-    <row r="567" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="567" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B567" s="2">
         <f t="shared" si="8"/>
         <v>563</v>
       </c>
       <c r="C567" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E567" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F567" s="3"/>
     </row>
-    <row r="568" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="568" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B568" s="2">
         <f t="shared" si="8"/>
         <v>564</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D568" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E568" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F568" s="3"/>
     </row>
-    <row r="569" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="569" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B569" s="2">
         <f t="shared" si="8"/>
         <v>565</v>
       </c>
       <c r="C569" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D569" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E569" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F569" s="3"/>
     </row>
-    <row r="570" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="570" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B570" s="2">
         <f t="shared" si="8"/>
         <v>566</v>
       </c>
       <c r="C570" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D570" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E570" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F570" s="3"/>
     </row>
-    <row r="571" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="571" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B571" s="2">
         <f t="shared" si="8"/>
         <v>567</v>
       </c>
       <c r="C571" s="1" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D571" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E571" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F571" s="3"/>
     </row>
-    <row r="572" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="572" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B572" s="2">
         <f t="shared" si="8"/>
         <v>568</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E572" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F572" s="3"/>
     </row>
-    <row r="573" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="573" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B573" s="2">
         <f t="shared" si="8"/>
         <v>569</v>
       </c>
       <c r="C573" s="1" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E573" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F573" s="3"/>
     </row>
-    <row r="574" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="574" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B574" s="2">
         <f t="shared" si="8"/>
         <v>570</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E574" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F574" s="3"/>
     </row>
-    <row r="575" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="575" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B575" s="2">
         <f t="shared" si="8"/>
         <v>571</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E575" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F575" s="3"/>
     </row>
-    <row r="576" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="576" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B576" s="2">
         <f t="shared" si="8"/>
         <v>572</v>
       </c>
       <c r="C576" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E576" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F576" s="3"/>
     </row>
-    <row r="577" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="577" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B577" s="2">
         <f t="shared" si="8"/>
         <v>573</v>
       </c>
       <c r="C577" s="1" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D577" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="E577" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F577" s="3"/>
     </row>
-    <row r="578" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="578" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B578" s="2">
         <f t="shared" si="8"/>
         <v>574</v>
       </c>
       <c r="C578" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D578" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E578" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F578" s="3"/>
     </row>
-    <row r="579" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="579" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B579" s="2">
         <f t="shared" si="8"/>
         <v>575</v>
       </c>
       <c r="C579" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D579" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="E579" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F579" s="3"/>
     </row>
-    <row r="580" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="580" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B580" s="2">
         <f t="shared" si="8"/>
         <v>576</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="E580" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F580" s="3"/>
     </row>
-    <row r="581" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="581" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B581" s="2">
         <f t="shared" si="8"/>
         <v>577</v>
       </c>
       <c r="C581" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D581" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E581" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F581" s="3"/>
     </row>
-    <row r="582" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="582" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B582" s="2">
         <f t="shared" si="8"/>
         <v>578</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D582" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E582" s="7">
         <v>3520268948847</v>
       </c>
       <c r="F582" s="3"/>
     </row>
-    <row r="583" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="583" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B583" s="2">
         <f t="shared" si="8"/>
         <v>579</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D583" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E583" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F583" s="3"/>
     </row>
-    <row r="584" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="584" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B584" s="2">
         <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="C584" s="1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D584" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="E584" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F584" s="3"/>
     </row>
-    <row r="585" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="585" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B585" s="2">
         <f t="shared" si="8"/>
         <v>581</v>
       </c>
       <c r="C585" s="1" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D585" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="E585" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F585" s="3"/>
     </row>
-    <row r="586" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="586" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B586" s="2">
         <f t="shared" ref="B586:B598" si="9">B585+1</f>
         <v>582</v>
       </c>
       <c r="C586" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D586" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="E586" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F586" s="3"/>
     </row>
-    <row r="587" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="587" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B587" s="2">
         <f t="shared" si="9"/>
         <v>583</v>
       </c>
       <c r="C587" s="1" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D587" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="E587" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F587" s="3"/>
     </row>
-    <row r="588" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="588" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B588" s="2">
         <f t="shared" si="9"/>
         <v>584</v>
       </c>
       <c r="C588" s="1" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D588" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E588" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F588" s="3"/>
     </row>
-    <row r="589" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="589" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B589" s="2">
         <f t="shared" si="9"/>
         <v>585</v>
       </c>
       <c r="C589" s="1" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D589" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="E589" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F589" s="3"/>
     </row>
-    <row r="590" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="590" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B590" s="2">
         <f t="shared" si="9"/>
         <v>586</v>
       </c>
       <c r="C590" s="1" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D590" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E590" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F590" s="3"/>
     </row>
-    <row r="591" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="591" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B591" s="2">
         <f t="shared" si="9"/>
         <v>587</v>
       </c>
       <c r="C591" s="1" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D591" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="E591" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F591" s="3"/>
     </row>
-    <row r="592" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="592" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B592" s="2">
         <f t="shared" si="9"/>
         <v>588</v>
       </c>
       <c r="C592" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D592" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="E592" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F592" s="3"/>
     </row>
-    <row r="593" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="593" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B593" s="2">
         <f t="shared" si="9"/>
         <v>589</v>
       </c>
       <c r="C593" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D593" s="2" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="E593" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F593" s="3"/>
     </row>
-    <row r="594" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="594" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B594" s="2">
         <f t="shared" si="9"/>
         <v>590</v>
       </c>
       <c r="C594" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D594" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="E594" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F594" s="3"/>
     </row>
-    <row r="595" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="595" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B595" s="2">
         <f t="shared" si="9"/>
         <v>591</v>
       </c>
       <c r="C595" s="1" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="D595" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="E595" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F595" s="3"/>
     </row>
-    <row r="596" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="596" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B596" s="2">
         <f t="shared" si="9"/>
         <v>592</v>
       </c>
       <c r="C596" s="1" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D596" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="E596" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F596" s="3"/>
     </row>
-    <row r="597" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="597" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B597" s="2">
         <f t="shared" si="9"/>
         <v>593</v>
       </c>
       <c r="C597" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D597" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="E597" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F597" s="3"/>
     </row>
-    <row r="598" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="598" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B598" s="2">
         <f t="shared" si="9"/>
         <v>594</v>
       </c>
       <c r="C598" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D598" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="E598" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F598" s="3"/>
     </row>
-    <row r="599" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="599" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B599" s="6">
         <v>595</v>
       </c>
       <c r="C599" s="1" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D599" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="E599" s="5"/>
     </row>
-    <row r="600" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="600" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B600" s="6">
         <v>596</v>
       </c>
       <c r="C600" s="1" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D600" s="6" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="E600" s="5"/>
     </row>
-    <row r="601" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="601" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C601" s="4"/>
     </row>
-    <row r="602" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="602" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B602" s="2">
         <v>509</v>
       </c>
       <c r="C602" s="4" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D602" s="8" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="603" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="603" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B603">
         <v>334</v>
       </c>
       <c r="C603" s="10" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D603" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="E603" s="11">
         <v>3277876171384</v>
       </c>
     </row>
-    <row r="604" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="604" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B604">
         <v>263</v>
       </c>
       <c r="C604" s="10" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="D604" s="12" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="E604" s="11">
         <v>3520210170957</v>
@@ -12440,6 +12441,16 @@
     </row>
   </sheetData>
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="M.S Traders Harbanspura (Risen)"/>
+        <filter val="Risen / Gajjumata _FR TRADERS"/>
+        <filter val="Risen / Manawa _CB TRADERS"/>
+        <filter val="Risen / Sabzazar _SZ TRADERS"/>
+        <filter val="Risen / Shadbagh _SB Traders"/>
+        <filter val="Risen / TN Traders (Raiwind Road )"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">
       <sortCondition ref="C4"/>
     </sortState>

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40D0489-ED81-447D-968C-A746EE7EC9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82D5E71-017F-48FC-A2FB-D785E1656EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82D5E71-017F-48FC-A2FB-D785E1656EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA74D84-EDA5-4F53-B516-677C579C5190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <f t="shared" si="7"/>
         <v>463</v>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <f t="shared" si="8"/>
         <v>547</v>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <f t="shared" si="8"/>
         <v>548</v>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <f t="shared" si="8"/>
         <v>549</v>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="F555" s="3"/>
     </row>
-    <row r="556" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B556" s="2">
         <f t="shared" si="8"/>
         <v>552</v>
@@ -12443,12 +12443,7 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="M.S Traders Harbanspura (Risen)"/>
-        <filter val="Risen / Gajjumata _FR TRADERS"/>
-        <filter val="Risen / Manawa _CB TRADERS"/>
-        <filter val="Risen / Sabzazar _SZ TRADERS"/>
-        <filter val="Risen / Shadbagh _SB Traders"/>
-        <filter val="Risen / TN Traders (Raiwind Road )"/>
+        <filter val="SANA CASH AND CARRY IQBAL AVENUE CANAL ROAD"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">
